--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="80">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,51 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Palestino</t>
+  </si>
+  <si>
+    <t>O'Higgins</t>
+  </si>
+  <si>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
+    <t>Cobresal</t>
+  </si>
+  <si>
+    <t>Huachipato</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['62', '75']</t>
+  </si>
+  <si>
+    <t>['3', '84', '90+7']</t>
+  </si>
+  <si>
+    <t>['88']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +315,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +824,624 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7818809</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45702.875</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+      <c r="O2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2">
+        <v>2.5</v>
+      </c>
+      <c r="R2">
+        <v>2.2</v>
+      </c>
+      <c r="S2">
+        <v>4.33</v>
+      </c>
+      <c r="T2">
+        <v>1.4</v>
+      </c>
+      <c r="U2">
+        <v>2.75</v>
+      </c>
+      <c r="V2">
+        <v>2.75</v>
+      </c>
+      <c r="W2">
+        <v>1.4</v>
+      </c>
+      <c r="X2">
+        <v>8</v>
+      </c>
+      <c r="Y2">
+        <v>1.08</v>
+      </c>
+      <c r="Z2">
+        <v>1.85</v>
+      </c>
+      <c r="AA2">
+        <v>3.6</v>
+      </c>
+      <c r="AB2">
+        <v>3.7</v>
+      </c>
+      <c r="AC2">
+        <v>1.05</v>
+      </c>
+      <c r="AD2">
+        <v>8.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.28</v>
+      </c>
+      <c r="AF2">
+        <v>3.45</v>
+      </c>
+      <c r="AG2">
+        <v>1.85</v>
+      </c>
+      <c r="AH2">
+        <v>1.95</v>
+      </c>
+      <c r="AI2">
+        <v>1.8</v>
+      </c>
+      <c r="AJ2">
+        <v>1.91</v>
+      </c>
+      <c r="AK2">
+        <v>1.32</v>
+      </c>
+      <c r="AL2">
+        <v>1.32</v>
+      </c>
+      <c r="AM2">
+        <v>1.63</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>3</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>4</v>
+      </c>
+      <c r="AV2">
+        <v>8</v>
+      </c>
+      <c r="AW2">
+        <v>5</v>
+      </c>
+      <c r="AX2">
+        <v>5</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>16</v>
+      </c>
+      <c r="BA2">
+        <v>6</v>
+      </c>
+      <c r="BB2">
+        <v>4</v>
+      </c>
+      <c r="BC2">
+        <v>10</v>
+      </c>
+      <c r="BD2">
+        <v>1.62</v>
+      </c>
+      <c r="BE2">
+        <v>6</v>
+      </c>
+      <c r="BF2">
+        <v>2.92</v>
+      </c>
+      <c r="BG2">
+        <v>1.27</v>
+      </c>
+      <c r="BH2">
+        <v>3.3</v>
+      </c>
+      <c r="BI2">
+        <v>1.51</v>
+      </c>
+      <c r="BJ2">
+        <v>2.3</v>
+      </c>
+      <c r="BK2">
+        <v>1.9</v>
+      </c>
+      <c r="BL2">
+        <v>1.75</v>
+      </c>
+      <c r="BM2">
+        <v>2.55</v>
+      </c>
+      <c r="BN2">
+        <v>1.43</v>
+      </c>
+      <c r="BO2">
+        <v>3.5</v>
+      </c>
+      <c r="BP2">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7818808</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45703.75</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q3">
+        <v>2.3</v>
+      </c>
+      <c r="R3">
+        <v>2.3</v>
+      </c>
+      <c r="S3">
+        <v>4.75</v>
+      </c>
+      <c r="T3">
+        <v>1.36</v>
+      </c>
+      <c r="U3">
+        <v>3</v>
+      </c>
+      <c r="V3">
+        <v>2.63</v>
+      </c>
+      <c r="W3">
+        <v>1.44</v>
+      </c>
+      <c r="X3">
+        <v>7</v>
+      </c>
+      <c r="Y3">
+        <v>1.1</v>
+      </c>
+      <c r="Z3">
+        <v>1.7</v>
+      </c>
+      <c r="AA3">
+        <v>3.75</v>
+      </c>
+      <c r="AB3">
+        <v>4.75</v>
+      </c>
+      <c r="AC3">
+        <v>1.04</v>
+      </c>
+      <c r="AD3">
+        <v>9</v>
+      </c>
+      <c r="AE3">
+        <v>1.25</v>
+      </c>
+      <c r="AF3">
+        <v>3.7</v>
+      </c>
+      <c r="AG3">
+        <v>1.8</v>
+      </c>
+      <c r="AH3">
+        <v>2</v>
+      </c>
+      <c r="AI3">
+        <v>1.73</v>
+      </c>
+      <c r="AJ3">
+        <v>2</v>
+      </c>
+      <c r="AK3">
+        <v>1.18</v>
+      </c>
+      <c r="AL3">
+        <v>1.24</v>
+      </c>
+      <c r="AM3">
+        <v>2.15</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>-1</v>
+      </c>
+      <c r="AV3">
+        <v>-1</v>
+      </c>
+      <c r="AW3">
+        <v>-1</v>
+      </c>
+      <c r="AX3">
+        <v>-1</v>
+      </c>
+      <c r="AY3">
+        <v>-1</v>
+      </c>
+      <c r="AZ3">
+        <v>-1</v>
+      </c>
+      <c r="BA3">
+        <v>-1</v>
+      </c>
+      <c r="BB3">
+        <v>-1</v>
+      </c>
+      <c r="BC3">
+        <v>-1</v>
+      </c>
+      <c r="BD3">
+        <v>1.43</v>
+      </c>
+      <c r="BE3">
+        <v>7.5</v>
+      </c>
+      <c r="BF3">
+        <v>3.4</v>
+      </c>
+      <c r="BG3">
+        <v>1.24</v>
+      </c>
+      <c r="BH3">
+        <v>3.5</v>
+      </c>
+      <c r="BI3">
+        <v>1.46</v>
+      </c>
+      <c r="BJ3">
+        <v>2.45</v>
+      </c>
+      <c r="BK3">
+        <v>1.82</v>
+      </c>
+      <c r="BL3">
+        <v>1.83</v>
+      </c>
+      <c r="BM3">
+        <v>2.37</v>
+      </c>
+      <c r="BN3">
+        <v>1.47</v>
+      </c>
+      <c r="BO3">
+        <v>3.3</v>
+      </c>
+      <c r="BP3">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7818814</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45703.75</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q4">
+        <v>3.1</v>
+      </c>
+      <c r="R4">
+        <v>2.1</v>
+      </c>
+      <c r="S4">
+        <v>3.5</v>
+      </c>
+      <c r="T4">
+        <v>1.4</v>
+      </c>
+      <c r="U4">
+        <v>2.75</v>
+      </c>
+      <c r="V4">
+        <v>3</v>
+      </c>
+      <c r="W4">
+        <v>1.36</v>
+      </c>
+      <c r="X4">
+        <v>9</v>
+      </c>
+      <c r="Y4">
+        <v>1.07</v>
+      </c>
+      <c r="Z4">
+        <v>2.4</v>
+      </c>
+      <c r="AA4">
+        <v>3.3</v>
+      </c>
+      <c r="AB4">
+        <v>2.8</v>
+      </c>
+      <c r="AC4">
+        <v>1.06</v>
+      </c>
+      <c r="AD4">
+        <v>8</v>
+      </c>
+      <c r="AE4">
+        <v>1.32</v>
+      </c>
+      <c r="AF4">
+        <v>3.2</v>
+      </c>
+      <c r="AG4">
+        <v>2</v>
+      </c>
+      <c r="AH4">
+        <v>1.8</v>
+      </c>
+      <c r="AI4">
+        <v>1.8</v>
+      </c>
+      <c r="AJ4">
+        <v>1.91</v>
+      </c>
+      <c r="AK4">
+        <v>1.41</v>
+      </c>
+      <c r="AL4">
+        <v>1.32</v>
+      </c>
+      <c r="AM4">
+        <v>1.52</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>-1</v>
+      </c>
+      <c r="AV4">
+        <v>-1</v>
+      </c>
+      <c r="AW4">
+        <v>-1</v>
+      </c>
+      <c r="AX4">
+        <v>-1</v>
+      </c>
+      <c r="AY4">
+        <v>-1</v>
+      </c>
+      <c r="AZ4">
+        <v>-1</v>
+      </c>
+      <c r="BA4">
+        <v>-1</v>
+      </c>
+      <c r="BB4">
+        <v>-1</v>
+      </c>
+      <c r="BC4">
+        <v>-1</v>
+      </c>
+      <c r="BD4">
+        <v>1.75</v>
+      </c>
+      <c r="BE4">
+        <v>6</v>
+      </c>
+      <c r="BF4">
+        <v>2.55</v>
+      </c>
+      <c r="BG4">
+        <v>1.24</v>
+      </c>
+      <c r="BH4">
+        <v>3.5</v>
+      </c>
+      <c r="BI4">
+        <v>1.46</v>
+      </c>
+      <c r="BJ4">
+        <v>2.45</v>
+      </c>
+      <c r="BK4">
+        <v>1.8</v>
+      </c>
+      <c r="BL4">
+        <v>1.83</v>
+      </c>
+      <c r="BM4">
+        <v>2.37</v>
+      </c>
+      <c r="BN4">
+        <v>1.49</v>
+      </c>
+      <c r="BO4">
+        <v>3.3</v>
+      </c>
+      <c r="BP4">
+        <v>1.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="83">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -235,6 +235,9 @@
     <t>O'Higgins</t>
   </si>
   <si>
+    <t>Universidad Chile</t>
+  </si>
+  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
@@ -244,10 +247,16 @@
     <t>Huachipato</t>
   </si>
   <si>
+    <t>Ñublense</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
     <t>['62', '75']</t>
+  </si>
+  <si>
+    <t>['48', '51', '63', '68', '89']</t>
   </si>
   <si>
     <t>['3', '84', '90+7']</t>
@@ -615,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP4"/>
+  <dimension ref="A1:BP5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -847,7 +856,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -868,10 +877,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1053,7 +1062,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1074,10 +1083,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1170,31 +1179,31 @@
         <v>0</v>
       </c>
       <c r="AU3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY3">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AZ3">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="BA3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD3">
         <v>1.43</v>
@@ -1259,7 +1268,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1280,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1376,31 +1385,31 @@
         <v>0</v>
       </c>
       <c r="AU4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW4">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AX4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY4">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AZ4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BA4">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BB4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC4">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BD4">
         <v>1.75</v>
@@ -1440,6 +1449,212 @@
       </c>
       <c r="BP4">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7818813</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45703.85416666666</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5" t="s">
+        <v>80</v>
+      </c>
+      <c r="P5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q5">
+        <v>1.95</v>
+      </c>
+      <c r="R5">
+        <v>2.4</v>
+      </c>
+      <c r="S5">
+        <v>6.5</v>
+      </c>
+      <c r="T5">
+        <v>1.33</v>
+      </c>
+      <c r="U5">
+        <v>3.25</v>
+      </c>
+      <c r="V5">
+        <v>2.5</v>
+      </c>
+      <c r="W5">
+        <v>1.5</v>
+      </c>
+      <c r="X5">
+        <v>6</v>
+      </c>
+      <c r="Y5">
+        <v>1.13</v>
+      </c>
+      <c r="Z5">
+        <v>1.42</v>
+      </c>
+      <c r="AA5">
+        <v>5</v>
+      </c>
+      <c r="AB5">
+        <v>5.75</v>
+      </c>
+      <c r="AC5">
+        <v>1.03</v>
+      </c>
+      <c r="AD5">
+        <v>10</v>
+      </c>
+      <c r="AE5">
+        <v>1.22</v>
+      </c>
+      <c r="AF5">
+        <v>4.1</v>
+      </c>
+      <c r="AG5">
+        <v>1.67</v>
+      </c>
+      <c r="AH5">
+        <v>2.15</v>
+      </c>
+      <c r="AI5">
+        <v>1.83</v>
+      </c>
+      <c r="AJ5">
+        <v>1.83</v>
+      </c>
+      <c r="AK5">
+        <v>1.11</v>
+      </c>
+      <c r="AL5">
+        <v>1.19</v>
+      </c>
+      <c r="AM5">
+        <v>2.65</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>3</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>15</v>
+      </c>
+      <c r="AV5">
+        <v>2</v>
+      </c>
+      <c r="AW5">
+        <v>14</v>
+      </c>
+      <c r="AX5">
+        <v>5</v>
+      </c>
+      <c r="AY5">
+        <v>36</v>
+      </c>
+      <c r="AZ5">
+        <v>9</v>
+      </c>
+      <c r="BA5">
+        <v>14</v>
+      </c>
+      <c r="BB5">
+        <v>2</v>
+      </c>
+      <c r="BC5">
+        <v>16</v>
+      </c>
+      <c r="BD5">
+        <v>1.1</v>
+      </c>
+      <c r="BE5">
+        <v>11.5</v>
+      </c>
+      <c r="BF5">
+        <v>7.6</v>
+      </c>
+      <c r="BG5">
+        <v>1.19</v>
+      </c>
+      <c r="BH5">
+        <v>4.1</v>
+      </c>
+      <c r="BI5">
+        <v>1.36</v>
+      </c>
+      <c r="BJ5">
+        <v>2.8</v>
+      </c>
+      <c r="BK5">
+        <v>1.65</v>
+      </c>
+      <c r="BL5">
+        <v>2.05</v>
+      </c>
+      <c r="BM5">
+        <v>2.1</v>
+      </c>
+      <c r="BN5">
+        <v>1.6</v>
+      </c>
+      <c r="BO5">
+        <v>2.85</v>
+      </c>
+      <c r="BP5">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="87">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -238,6 +238,9 @@
     <t>Universidad Chile</t>
   </si>
   <si>
+    <t>La Serena</t>
+  </si>
+  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
@@ -250,6 +253,9 @@
     <t>Ñublense</t>
   </si>
   <si>
+    <t>Colo-Colo</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -259,10 +265,16 @@
     <t>['48', '51', '63', '68', '89']</t>
   </si>
   <si>
+    <t>['79']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
     <t>['88']</t>
+  </si>
+  <si>
+    <t>['33', '72', '80']</t>
   </si>
 </sst>
 </file>
@@ -624,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -856,7 +868,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -877,10 +889,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1062,7 +1074,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1083,10 +1095,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1268,7 +1280,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1289,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1474,7 +1486,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1495,10 +1507,10 @@
         <v>5</v>
       </c>
       <c r="O5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P5" t="s">
         <v>80</v>
-      </c>
-      <c r="P5" t="s">
-        <v>78</v>
       </c>
       <c r="Q5">
         <v>1.95</v>
@@ -1655,6 +1667,212 @@
       </c>
       <c r="BP5">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7818807</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45704.5</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6">
+        <v>4</v>
+      </c>
+      <c r="O6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q6">
+        <v>5.5</v>
+      </c>
+      <c r="R6">
+        <v>2.25</v>
+      </c>
+      <c r="S6">
+        <v>2.2</v>
+      </c>
+      <c r="T6">
+        <v>1.4</v>
+      </c>
+      <c r="U6">
+        <v>2.75</v>
+      </c>
+      <c r="V6">
+        <v>2.75</v>
+      </c>
+      <c r="W6">
+        <v>1.4</v>
+      </c>
+      <c r="X6">
+        <v>8</v>
+      </c>
+      <c r="Y6">
+        <v>1.08</v>
+      </c>
+      <c r="Z6">
+        <v>5.25</v>
+      </c>
+      <c r="AA6">
+        <v>3.9</v>
+      </c>
+      <c r="AB6">
+        <v>1.6</v>
+      </c>
+      <c r="AC6">
+        <v>1.05</v>
+      </c>
+      <c r="AD6">
+        <v>8.5</v>
+      </c>
+      <c r="AE6">
+        <v>1.31</v>
+      </c>
+      <c r="AF6">
+        <v>3.3</v>
+      </c>
+      <c r="AG6">
+        <v>1.9</v>
+      </c>
+      <c r="AH6">
+        <v>1.9</v>
+      </c>
+      <c r="AI6">
+        <v>1.91</v>
+      </c>
+      <c r="AJ6">
+        <v>1.8</v>
+      </c>
+      <c r="AK6">
+        <v>2.25</v>
+      </c>
+      <c r="AL6">
+        <v>1.24</v>
+      </c>
+      <c r="AM6">
+        <v>1.15</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>3</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>4</v>
+      </c>
+      <c r="AV6">
+        <v>6</v>
+      </c>
+      <c r="AW6">
+        <v>6</v>
+      </c>
+      <c r="AX6">
+        <v>9</v>
+      </c>
+      <c r="AY6">
+        <v>11</v>
+      </c>
+      <c r="AZ6">
+        <v>20</v>
+      </c>
+      <c r="BA6">
+        <v>5</v>
+      </c>
+      <c r="BB6">
+        <v>5</v>
+      </c>
+      <c r="BC6">
+        <v>10</v>
+      </c>
+      <c r="BD6">
+        <v>3.78</v>
+      </c>
+      <c r="BE6">
+        <v>9</v>
+      </c>
+      <c r="BF6">
+        <v>1.37</v>
+      </c>
+      <c r="BG6">
+        <v>1.33</v>
+      </c>
+      <c r="BH6">
+        <v>2.81</v>
+      </c>
+      <c r="BI6">
+        <v>1.64</v>
+      </c>
+      <c r="BJ6">
+        <v>2.07</v>
+      </c>
+      <c r="BK6">
+        <v>2.05</v>
+      </c>
+      <c r="BL6">
+        <v>1.7</v>
+      </c>
+      <c r="BM6">
+        <v>2.79</v>
+      </c>
+      <c r="BN6">
+        <v>1.36</v>
+      </c>
+      <c r="BO6">
+        <v>3.84</v>
+      </c>
+      <c r="BP6">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -241,6 +241,9 @@
     <t>La Serena</t>
   </si>
   <si>
+    <t>Deportes Limache</t>
+  </si>
+  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
@@ -256,6 +259,9 @@
     <t>Colo-Colo</t>
   </si>
   <si>
+    <t>Everton</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -268,6 +274,9 @@
     <t>['79']</t>
   </si>
   <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -275,6 +284,9 @@
   </si>
   <si>
     <t>['33', '72', '80']</t>
+  </si>
+  <si>
+    <t>['15']</t>
   </si>
 </sst>
 </file>
@@ -636,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -868,7 +880,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -889,10 +901,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1074,7 +1086,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1095,10 +1107,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1280,7 +1292,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1301,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1486,7 +1498,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1507,10 +1519,10 @@
         <v>5</v>
       </c>
       <c r="O5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P5" t="s">
         <v>82</v>
-      </c>
-      <c r="P5" t="s">
-        <v>80</v>
       </c>
       <c r="Q5">
         <v>1.95</v>
@@ -1692,7 +1704,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1713,10 +1725,10 @@
         <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -1873,6 +1885,212 @@
       </c>
       <c r="BP6">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7818810</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45704.85416666666</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7" t="s">
+        <v>86</v>
+      </c>
+      <c r="P7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q7">
+        <v>4</v>
+      </c>
+      <c r="R7">
+        <v>2.25</v>
+      </c>
+      <c r="S7">
+        <v>2.6</v>
+      </c>
+      <c r="T7">
+        <v>1.36</v>
+      </c>
+      <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="V7">
+        <v>2.63</v>
+      </c>
+      <c r="W7">
+        <v>1.44</v>
+      </c>
+      <c r="X7">
+        <v>7</v>
+      </c>
+      <c r="Y7">
+        <v>1.1</v>
+      </c>
+      <c r="Z7">
+        <v>3.75</v>
+      </c>
+      <c r="AA7">
+        <v>3.4</v>
+      </c>
+      <c r="AB7">
+        <v>1.95</v>
+      </c>
+      <c r="AC7">
+        <v>1.05</v>
+      </c>
+      <c r="AD7">
+        <v>8.5</v>
+      </c>
+      <c r="AE7">
+        <v>1.26</v>
+      </c>
+      <c r="AF7">
+        <v>3.65</v>
+      </c>
+      <c r="AG7">
+        <v>1.8</v>
+      </c>
+      <c r="AH7">
+        <v>2</v>
+      </c>
+      <c r="AI7">
+        <v>1.67</v>
+      </c>
+      <c r="AJ7">
+        <v>2.1</v>
+      </c>
+      <c r="AK7">
+        <v>1.78</v>
+      </c>
+      <c r="AL7">
+        <v>1.27</v>
+      </c>
+      <c r="AM7">
+        <v>1.29</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>6</v>
+      </c>
+      <c r="AV7">
+        <v>4</v>
+      </c>
+      <c r="AW7">
+        <v>10</v>
+      </c>
+      <c r="AX7">
+        <v>8</v>
+      </c>
+      <c r="AY7">
+        <v>21</v>
+      </c>
+      <c r="AZ7">
+        <v>15</v>
+      </c>
+      <c r="BA7">
+        <v>5</v>
+      </c>
+      <c r="BB7">
+        <v>3</v>
+      </c>
+      <c r="BC7">
+        <v>8</v>
+      </c>
+      <c r="BD7">
+        <v>2.31</v>
+      </c>
+      <c r="BE7">
+        <v>6.6</v>
+      </c>
+      <c r="BF7">
+        <v>1.92</v>
+      </c>
+      <c r="BG7">
+        <v>1.22</v>
+      </c>
+      <c r="BH7">
+        <v>3.55</v>
+      </c>
+      <c r="BI7">
+        <v>1.31</v>
+      </c>
+      <c r="BJ7">
+        <v>2.92</v>
+      </c>
+      <c r="BK7">
+        <v>1.58</v>
+      </c>
+      <c r="BL7">
+        <v>2.17</v>
+      </c>
+      <c r="BM7">
+        <v>2.05</v>
+      </c>
+      <c r="BN7">
+        <v>1.7</v>
+      </c>
+      <c r="BO7">
+        <v>2.57</v>
+      </c>
+      <c r="BP7">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -1633,13 +1633,13 @@
         <v>9</v>
       </c>
       <c r="BA5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB5">
         <v>2</v>
       </c>
       <c r="BC5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD5">
         <v>1.1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -244,6 +244,12 @@
     <t>Deportes Limache</t>
   </si>
   <si>
+    <t>Universidad Católica</t>
+  </si>
+  <si>
+    <t>Unión La Calera</t>
+  </si>
+  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
@@ -262,6 +268,12 @@
     <t>Everton</t>
   </si>
   <si>
+    <t>Audax Italiano</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -277,6 +289,12 @@
     <t>['90+2']</t>
   </si>
   <si>
+    <t>['7', '24', '80']</t>
+  </si>
+  <si>
+    <t>['28', '43', '55', '67']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -287,6 +305,9 @@
   </si>
   <si>
     <t>['15']</t>
+  </si>
+  <si>
+    <t>['33']</t>
   </si>
 </sst>
 </file>
@@ -648,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -880,7 +901,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -901,10 +922,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1086,7 +1107,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1107,10 +1128,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1292,7 +1313,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1313,10 +1334,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1498,7 +1519,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1519,10 +1540,10 @@
         <v>5</v>
       </c>
       <c r="O5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q5">
         <v>1.95</v>
@@ -1704,7 +1725,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1725,10 +1746,10 @@
         <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -1910,7 +1931,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1931,10 +1952,10 @@
         <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2091,6 +2112,418 @@
       </c>
       <c r="BP7">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7818811</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45705.75</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8" t="s">
+        <v>91</v>
+      </c>
+      <c r="P8" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q8">
+        <v>2.5</v>
+      </c>
+      <c r="R8">
+        <v>2.2</v>
+      </c>
+      <c r="S8">
+        <v>4.5</v>
+      </c>
+      <c r="T8">
+        <v>1.4</v>
+      </c>
+      <c r="U8">
+        <v>2.75</v>
+      </c>
+      <c r="V8">
+        <v>3</v>
+      </c>
+      <c r="W8">
+        <v>1.36</v>
+      </c>
+      <c r="X8">
+        <v>8</v>
+      </c>
+      <c r="Y8">
+        <v>1.08</v>
+      </c>
+      <c r="Z8">
+        <v>1.9</v>
+      </c>
+      <c r="AA8">
+        <v>3.5</v>
+      </c>
+      <c r="AB8">
+        <v>3.9</v>
+      </c>
+      <c r="AC8">
+        <v>1.06</v>
+      </c>
+      <c r="AD8">
+        <v>8</v>
+      </c>
+      <c r="AE8">
+        <v>1.32</v>
+      </c>
+      <c r="AF8">
+        <v>3.2</v>
+      </c>
+      <c r="AG8">
+        <v>1.95</v>
+      </c>
+      <c r="AH8">
+        <v>1.85</v>
+      </c>
+      <c r="AI8">
+        <v>1.83</v>
+      </c>
+      <c r="AJ8">
+        <v>1.83</v>
+      </c>
+      <c r="AK8">
+        <v>1.24</v>
+      </c>
+      <c r="AL8">
+        <v>1.29</v>
+      </c>
+      <c r="AM8">
+        <v>1.85</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>3</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>6</v>
+      </c>
+      <c r="AV8">
+        <v>4</v>
+      </c>
+      <c r="AW8">
+        <v>6</v>
+      </c>
+      <c r="AX8">
+        <v>7</v>
+      </c>
+      <c r="AY8">
+        <v>13</v>
+      </c>
+      <c r="AZ8">
+        <v>13</v>
+      </c>
+      <c r="BA8">
+        <v>3</v>
+      </c>
+      <c r="BB8">
+        <v>8</v>
+      </c>
+      <c r="BC8">
+        <v>11</v>
+      </c>
+      <c r="BD8">
+        <v>1.58</v>
+      </c>
+      <c r="BE8">
+        <v>8.5</v>
+      </c>
+      <c r="BF8">
+        <v>2.82</v>
+      </c>
+      <c r="BG8">
+        <v>1.25</v>
+      </c>
+      <c r="BH8">
+        <v>3.28</v>
+      </c>
+      <c r="BI8">
+        <v>1.49</v>
+      </c>
+      <c r="BJ8">
+        <v>2.38</v>
+      </c>
+      <c r="BK8">
+        <v>1.85</v>
+      </c>
+      <c r="BL8">
+        <v>1.85</v>
+      </c>
+      <c r="BM8">
+        <v>2.4</v>
+      </c>
+      <c r="BN8">
+        <v>1.48</v>
+      </c>
+      <c r="BO8">
+        <v>3.2</v>
+      </c>
+      <c r="BP8">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7818812</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45705.85416666666</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>4</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
+      <c r="O9" t="s">
+        <v>92</v>
+      </c>
+      <c r="P9" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q9">
+        <v>3.4</v>
+      </c>
+      <c r="R9">
+        <v>2.1</v>
+      </c>
+      <c r="S9">
+        <v>3.1</v>
+      </c>
+      <c r="T9">
+        <v>1.4</v>
+      </c>
+      <c r="U9">
+        <v>2.75</v>
+      </c>
+      <c r="V9">
+        <v>3</v>
+      </c>
+      <c r="W9">
+        <v>1.36</v>
+      </c>
+      <c r="X9">
+        <v>8</v>
+      </c>
+      <c r="Y9">
+        <v>1.08</v>
+      </c>
+      <c r="Z9">
+        <v>2.75</v>
+      </c>
+      <c r="AA9">
+        <v>3.4</v>
+      </c>
+      <c r="AB9">
+        <v>2.45</v>
+      </c>
+      <c r="AC9">
+        <v>1.05</v>
+      </c>
+      <c r="AD9">
+        <v>8.5</v>
+      </c>
+      <c r="AE9">
+        <v>1.3</v>
+      </c>
+      <c r="AF9">
+        <v>3.3</v>
+      </c>
+      <c r="AG9">
+        <v>1.95</v>
+      </c>
+      <c r="AH9">
+        <v>1.85</v>
+      </c>
+      <c r="AI9">
+        <v>1.73</v>
+      </c>
+      <c r="AJ9">
+        <v>2</v>
+      </c>
+      <c r="AK9">
+        <v>1.53</v>
+      </c>
+      <c r="AL9">
+        <v>1.31</v>
+      </c>
+      <c r="AM9">
+        <v>1.42</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>3</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>5</v>
+      </c>
+      <c r="AV9">
+        <v>2</v>
+      </c>
+      <c r="AW9">
+        <v>7</v>
+      </c>
+      <c r="AX9">
+        <v>12</v>
+      </c>
+      <c r="AY9">
+        <v>12</v>
+      </c>
+      <c r="AZ9">
+        <v>17</v>
+      </c>
+      <c r="BA9">
+        <v>1</v>
+      </c>
+      <c r="BB9">
+        <v>4</v>
+      </c>
+      <c r="BC9">
+        <v>5</v>
+      </c>
+      <c r="BD9">
+        <v>2.15</v>
+      </c>
+      <c r="BE9">
+        <v>6.45</v>
+      </c>
+      <c r="BF9">
+        <v>2.06</v>
+      </c>
+      <c r="BG9">
+        <v>1.21</v>
+      </c>
+      <c r="BH9">
+        <v>3.58</v>
+      </c>
+      <c r="BI9">
+        <v>1.42</v>
+      </c>
+      <c r="BJ9">
+        <v>2.57</v>
+      </c>
+      <c r="BK9">
+        <v>1.8</v>
+      </c>
+      <c r="BL9">
+        <v>1.91</v>
+      </c>
+      <c r="BM9">
+        <v>2.21</v>
+      </c>
+      <c r="BN9">
+        <v>1.56</v>
+      </c>
+      <c r="BO9">
+        <v>2.92</v>
+      </c>
+      <c r="BP9">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -250,6 +250,12 @@
     <t>Unión La Calera</t>
   </si>
   <si>
+    <t>Audax Italiano</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
@@ -268,12 +274,6 @@
     <t>Everton</t>
   </si>
   <si>
-    <t>Audax Italiano</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
@@ -295,6 +295,9 @@
     <t>['28', '43', '55', '67']</t>
   </si>
   <si>
+    <t>['2', '35', '54', '70']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -308,6 +311,12 @@
   </si>
   <si>
     <t>['33']</t>
+  </si>
+  <si>
+    <t>['72', '79']</t>
+  </si>
+  <si>
+    <t>['42', '83', '88']</t>
   </si>
 </sst>
 </file>
@@ -669,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP9"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -901,7 +910,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -925,7 +934,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1107,7 +1116,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1131,7 +1140,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1313,7 +1322,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1519,7 +1528,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1725,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1749,7 +1758,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -1931,7 +1940,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1955,7 +1964,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2137,7 +2146,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -2161,7 +2170,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2343,7 +2352,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -2524,6 +2533,418 @@
       </c>
       <c r="BP9">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7818816</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45709.75</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>6</v>
+      </c>
+      <c r="O10" t="s">
+        <v>93</v>
+      </c>
+      <c r="P10" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q10">
+        <v>3</v>
+      </c>
+      <c r="R10">
+        <v>2.2</v>
+      </c>
+      <c r="S10">
+        <v>3.4</v>
+      </c>
+      <c r="T10">
+        <v>1.36</v>
+      </c>
+      <c r="U10">
+        <v>3</v>
+      </c>
+      <c r="V10">
+        <v>2.63</v>
+      </c>
+      <c r="W10">
+        <v>1.44</v>
+      </c>
+      <c r="X10">
+        <v>7</v>
+      </c>
+      <c r="Y10">
+        <v>1.1</v>
+      </c>
+      <c r="Z10">
+        <v>2.3</v>
+      </c>
+      <c r="AA10">
+        <v>3.4</v>
+      </c>
+      <c r="AB10">
+        <v>2.7</v>
+      </c>
+      <c r="AC10">
+        <v>1.04</v>
+      </c>
+      <c r="AD10">
+        <v>9</v>
+      </c>
+      <c r="AE10">
+        <v>1.25</v>
+      </c>
+      <c r="AF10">
+        <v>3.65</v>
+      </c>
+      <c r="AG10">
+        <v>1.8</v>
+      </c>
+      <c r="AH10">
+        <v>2</v>
+      </c>
+      <c r="AI10">
+        <v>1.62</v>
+      </c>
+      <c r="AJ10">
+        <v>2.2</v>
+      </c>
+      <c r="AK10">
+        <v>1.4</v>
+      </c>
+      <c r="AL10">
+        <v>1.25</v>
+      </c>
+      <c r="AM10">
+        <v>1.6</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>3</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>6</v>
+      </c>
+      <c r="AV10">
+        <v>6</v>
+      </c>
+      <c r="AW10">
+        <v>11</v>
+      </c>
+      <c r="AX10">
+        <v>10</v>
+      </c>
+      <c r="AY10">
+        <v>18</v>
+      </c>
+      <c r="AZ10">
+        <v>21</v>
+      </c>
+      <c r="BA10">
+        <v>5</v>
+      </c>
+      <c r="BB10">
+        <v>6</v>
+      </c>
+      <c r="BC10">
+        <v>11</v>
+      </c>
+      <c r="BD10">
+        <v>1.84</v>
+      </c>
+      <c r="BE10">
+        <v>6.4</v>
+      </c>
+      <c r="BF10">
+        <v>2.18</v>
+      </c>
+      <c r="BG10">
+        <v>1.37</v>
+      </c>
+      <c r="BH10">
+        <v>2.7</v>
+      </c>
+      <c r="BI10">
+        <v>1.64</v>
+      </c>
+      <c r="BJ10">
+        <v>2.05</v>
+      </c>
+      <c r="BK10">
+        <v>2.04</v>
+      </c>
+      <c r="BL10">
+        <v>1.64</v>
+      </c>
+      <c r="BM10">
+        <v>2.63</v>
+      </c>
+      <c r="BN10">
+        <v>1.38</v>
+      </c>
+      <c r="BO10">
+        <v>3.45</v>
+      </c>
+      <c r="BP10">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7818821</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45709.75</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>3</v>
+      </c>
+      <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11" t="s">
+        <v>86</v>
+      </c>
+      <c r="P11" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q11">
+        <v>3.1</v>
+      </c>
+      <c r="R11">
+        <v>2.2</v>
+      </c>
+      <c r="S11">
+        <v>3.25</v>
+      </c>
+      <c r="T11">
+        <v>1.36</v>
+      </c>
+      <c r="U11">
+        <v>3</v>
+      </c>
+      <c r="V11">
+        <v>2.63</v>
+      </c>
+      <c r="W11">
+        <v>1.44</v>
+      </c>
+      <c r="X11">
+        <v>7</v>
+      </c>
+      <c r="Y11">
+        <v>1.1</v>
+      </c>
+      <c r="Z11">
+        <v>2.45</v>
+      </c>
+      <c r="AA11">
+        <v>3.4</v>
+      </c>
+      <c r="AB11">
+        <v>2.55</v>
+      </c>
+      <c r="AC11">
+        <v>1.04</v>
+      </c>
+      <c r="AD11">
+        <v>9</v>
+      </c>
+      <c r="AE11">
+        <v>1.25</v>
+      </c>
+      <c r="AF11">
+        <v>3.7</v>
+      </c>
+      <c r="AG11">
+        <v>1.8</v>
+      </c>
+      <c r="AH11">
+        <v>2</v>
+      </c>
+      <c r="AI11">
+        <v>1.62</v>
+      </c>
+      <c r="AJ11">
+        <v>2.2</v>
+      </c>
+      <c r="AK11">
+        <v>1.45</v>
+      </c>
+      <c r="AL11">
+        <v>1.25</v>
+      </c>
+      <c r="AM11">
+        <v>1.5</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>3</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>5</v>
+      </c>
+      <c r="AV11">
+        <v>12</v>
+      </c>
+      <c r="AW11">
+        <v>8</v>
+      </c>
+      <c r="AX11">
+        <v>7</v>
+      </c>
+      <c r="AY11">
+        <v>15</v>
+      </c>
+      <c r="AZ11">
+        <v>21</v>
+      </c>
+      <c r="BA11">
+        <v>7</v>
+      </c>
+      <c r="BB11">
+        <v>6</v>
+      </c>
+      <c r="BC11">
+        <v>13</v>
+      </c>
+      <c r="BD11">
+        <v>1.96</v>
+      </c>
+      <c r="BE11">
+        <v>6.4</v>
+      </c>
+      <c r="BF11">
+        <v>2.05</v>
+      </c>
+      <c r="BG11">
+        <v>1.36</v>
+      </c>
+      <c r="BH11">
+        <v>2.75</v>
+      </c>
+      <c r="BI11">
+        <v>1.62</v>
+      </c>
+      <c r="BJ11">
+        <v>2.08</v>
+      </c>
+      <c r="BK11">
+        <v>2</v>
+      </c>
+      <c r="BL11">
+        <v>1.66</v>
+      </c>
+      <c r="BM11">
+        <v>2.55</v>
+      </c>
+      <c r="BN11">
+        <v>1.41</v>
+      </c>
+      <c r="BO11">
+        <v>3.4</v>
+      </c>
+      <c r="BP11">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="104">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -259,15 +259,15 @@
     <t>Coquimbo Unido</t>
   </si>
   <si>
+    <t>Ñublense</t>
+  </si>
+  <si>
     <t>Cobresal</t>
   </si>
   <si>
     <t>Huachipato</t>
   </si>
   <si>
-    <t>Ñublense</t>
-  </si>
-  <si>
     <t>Colo-Colo</t>
   </si>
   <si>
@@ -298,6 +298,12 @@
     <t>['2', '35', '54', '70']</t>
   </si>
   <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -317,6 +323,9 @@
   </si>
   <si>
     <t>['42', '83', '88']</t>
+  </si>
+  <si>
+    <t>['65']</t>
   </si>
 </sst>
 </file>
@@ -678,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -934,7 +943,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1116,7 +1125,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1140,7 +1149,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1322,7 +1331,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1528,7 +1537,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1758,7 +1767,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -1964,7 +1973,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2170,7 +2179,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2582,7 +2591,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2788,7 +2797,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -2945,6 +2954,418 @@
       </c>
       <c r="BP11">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7818815</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45710.75</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
+        <v>94</v>
+      </c>
+      <c r="P12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q12">
+        <v>3.1</v>
+      </c>
+      <c r="R12">
+        <v>2.1</v>
+      </c>
+      <c r="S12">
+        <v>3.6</v>
+      </c>
+      <c r="T12">
+        <v>1.44</v>
+      </c>
+      <c r="U12">
+        <v>2.63</v>
+      </c>
+      <c r="V12">
+        <v>3.25</v>
+      </c>
+      <c r="W12">
+        <v>1.33</v>
+      </c>
+      <c r="X12">
+        <v>9</v>
+      </c>
+      <c r="Y12">
+        <v>1.07</v>
+      </c>
+      <c r="Z12">
+        <v>2.3</v>
+      </c>
+      <c r="AA12">
+        <v>3.25</v>
+      </c>
+      <c r="AB12">
+        <v>2.88</v>
+      </c>
+      <c r="AC12">
+        <v>1.05</v>
+      </c>
+      <c r="AD12">
+        <v>8</v>
+      </c>
+      <c r="AE12">
+        <v>1.34</v>
+      </c>
+      <c r="AF12">
+        <v>3.05</v>
+      </c>
+      <c r="AG12">
+        <v>2.05</v>
+      </c>
+      <c r="AH12">
+        <v>1.75</v>
+      </c>
+      <c r="AI12">
+        <v>1.8</v>
+      </c>
+      <c r="AJ12">
+        <v>1.91</v>
+      </c>
+      <c r="AK12">
+        <v>1.37</v>
+      </c>
+      <c r="AL12">
+        <v>1.3</v>
+      </c>
+      <c r="AM12">
+        <v>1.58</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>3</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>7</v>
+      </c>
+      <c r="AV12">
+        <v>5</v>
+      </c>
+      <c r="AW12">
+        <v>9</v>
+      </c>
+      <c r="AX12">
+        <v>12</v>
+      </c>
+      <c r="AY12">
+        <v>18</v>
+      </c>
+      <c r="AZ12">
+        <v>19</v>
+      </c>
+      <c r="BA12">
+        <v>6</v>
+      </c>
+      <c r="BB12">
+        <v>2</v>
+      </c>
+      <c r="BC12">
+        <v>8</v>
+      </c>
+      <c r="BD12">
+        <v>1.46</v>
+      </c>
+      <c r="BE12">
+        <v>7.5</v>
+      </c>
+      <c r="BF12">
+        <v>3.2</v>
+      </c>
+      <c r="BG12">
+        <v>1.21</v>
+      </c>
+      <c r="BH12">
+        <v>3.8</v>
+      </c>
+      <c r="BI12">
+        <v>1.45</v>
+      </c>
+      <c r="BJ12">
+        <v>2.52</v>
+      </c>
+      <c r="BK12">
+        <v>1.8</v>
+      </c>
+      <c r="BL12">
+        <v>1.88</v>
+      </c>
+      <c r="BM12">
+        <v>2.35</v>
+      </c>
+      <c r="BN12">
+        <v>1.5</v>
+      </c>
+      <c r="BO12">
+        <v>3.2</v>
+      </c>
+      <c r="BP12">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7818820</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45710.85416666666</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13" t="s">
+        <v>95</v>
+      </c>
+      <c r="P13" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q13">
+        <v>2.75</v>
+      </c>
+      <c r="R13">
+        <v>2.2</v>
+      </c>
+      <c r="S13">
+        <v>4</v>
+      </c>
+      <c r="T13">
+        <v>1.4</v>
+      </c>
+      <c r="U13">
+        <v>2.75</v>
+      </c>
+      <c r="V13">
+        <v>2.75</v>
+      </c>
+      <c r="W13">
+        <v>1.4</v>
+      </c>
+      <c r="X13">
+        <v>8</v>
+      </c>
+      <c r="Y13">
+        <v>1.08</v>
+      </c>
+      <c r="Z13">
+        <v>2</v>
+      </c>
+      <c r="AA13">
+        <v>3.3</v>
+      </c>
+      <c r="AB13">
+        <v>3.3</v>
+      </c>
+      <c r="AC13">
+        <v>1.01</v>
+      </c>
+      <c r="AD13">
+        <v>9.65</v>
+      </c>
+      <c r="AE13">
+        <v>1.29</v>
+      </c>
+      <c r="AF13">
+        <v>3.54</v>
+      </c>
+      <c r="AG13">
+        <v>1.95</v>
+      </c>
+      <c r="AH13">
+        <v>1.85</v>
+      </c>
+      <c r="AI13">
+        <v>1.73</v>
+      </c>
+      <c r="AJ13">
+        <v>2</v>
+      </c>
+      <c r="AK13">
+        <v>1.33</v>
+      </c>
+      <c r="AL13">
+        <v>1.3</v>
+      </c>
+      <c r="AM13">
+        <v>1.73</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1</v>
+      </c>
+      <c r="AQ13">
+        <v>1</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>4</v>
+      </c>
+      <c r="AV13">
+        <v>5</v>
+      </c>
+      <c r="AW13">
+        <v>18</v>
+      </c>
+      <c r="AX13">
+        <v>7</v>
+      </c>
+      <c r="AY13">
+        <v>32</v>
+      </c>
+      <c r="AZ13">
+        <v>15</v>
+      </c>
+      <c r="BA13">
+        <v>6</v>
+      </c>
+      <c r="BB13">
+        <v>2</v>
+      </c>
+      <c r="BC13">
+        <v>8</v>
+      </c>
+      <c r="BD13">
+        <v>1.65</v>
+      </c>
+      <c r="BE13">
+        <v>6.4</v>
+      </c>
+      <c r="BF13">
+        <v>2.5</v>
+      </c>
+      <c r="BG13">
+        <v>1.38</v>
+      </c>
+      <c r="BH13">
+        <v>2.65</v>
+      </c>
+      <c r="BI13">
+        <v>1.65</v>
+      </c>
+      <c r="BJ13">
+        <v>2.02</v>
+      </c>
+      <c r="BK13">
+        <v>2.07</v>
+      </c>
+      <c r="BL13">
+        <v>1.62</v>
+      </c>
+      <c r="BM13">
+        <v>2.65</v>
+      </c>
+      <c r="BN13">
+        <v>1.38</v>
+      </c>
+      <c r="BO13">
+        <v>3.55</v>
+      </c>
+      <c r="BP13">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="108">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -262,12 +262,12 @@
     <t>Ñublense</t>
   </si>
   <si>
+    <t>Huachipato</t>
+  </si>
+  <si>
     <t>Cobresal</t>
   </si>
   <si>
-    <t>Huachipato</t>
-  </si>
-  <si>
     <t>Colo-Colo</t>
   </si>
   <si>
@@ -304,6 +304,15 @@
     <t>['83']</t>
   </si>
   <si>
+    <t>['30', '39', '44', '52']</t>
+  </si>
+  <si>
+    <t>['36', '69', '86']</t>
+  </si>
+  <si>
+    <t>['2']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -326,6 +335,9 @@
   </si>
   <si>
     <t>['65']</t>
+  </si>
+  <si>
+    <t>['78']</t>
   </si>
 </sst>
 </file>
@@ -687,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP13"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -943,7 +955,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1125,7 +1137,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1149,7 +1161,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1331,7 +1343,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1767,7 +1779,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -1973,7 +1985,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2054,7 +2066,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2179,7 +2191,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2591,7 +2603,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2797,7 +2809,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3209,7 +3221,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3366,6 +3378,624 @@
       </c>
       <c r="BP13">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7818819</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45711.5</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>3</v>
+      </c>
+      <c r="L14">
+        <v>4</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>4</v>
+      </c>
+      <c r="O14" t="s">
+        <v>96</v>
+      </c>
+      <c r="P14" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q14">
+        <v>3.25</v>
+      </c>
+      <c r="R14">
+        <v>2.1</v>
+      </c>
+      <c r="S14">
+        <v>3.2</v>
+      </c>
+      <c r="T14">
+        <v>1.4</v>
+      </c>
+      <c r="U14">
+        <v>2.75</v>
+      </c>
+      <c r="V14">
+        <v>3</v>
+      </c>
+      <c r="W14">
+        <v>1.36</v>
+      </c>
+      <c r="X14">
+        <v>8</v>
+      </c>
+      <c r="Y14">
+        <v>1.08</v>
+      </c>
+      <c r="Z14">
+        <v>2.6</v>
+      </c>
+      <c r="AA14">
+        <v>3.3</v>
+      </c>
+      <c r="AB14">
+        <v>2.5</v>
+      </c>
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AD14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE14">
+        <v>1.26</v>
+      </c>
+      <c r="AF14">
+        <v>3.22</v>
+      </c>
+      <c r="AG14">
+        <v>1.95</v>
+      </c>
+      <c r="AH14">
+        <v>1.85</v>
+      </c>
+      <c r="AI14">
+        <v>1.73</v>
+      </c>
+      <c r="AJ14">
+        <v>2</v>
+      </c>
+      <c r="AK14">
+        <v>1.49</v>
+      </c>
+      <c r="AL14">
+        <v>1.3</v>
+      </c>
+      <c r="AM14">
+        <v>1.45</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>1</v>
+      </c>
+      <c r="AP14">
+        <v>3</v>
+      </c>
+      <c r="AQ14">
+        <v>0.5</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>1.23</v>
+      </c>
+      <c r="AT14">
+        <v>1.23</v>
+      </c>
+      <c r="AU14">
+        <v>6</v>
+      </c>
+      <c r="AV14">
+        <v>5</v>
+      </c>
+      <c r="AW14">
+        <v>6</v>
+      </c>
+      <c r="AX14">
+        <v>7</v>
+      </c>
+      <c r="AY14">
+        <v>15</v>
+      </c>
+      <c r="AZ14">
+        <v>12</v>
+      </c>
+      <c r="BA14">
+        <v>5</v>
+      </c>
+      <c r="BB14">
+        <v>1</v>
+      </c>
+      <c r="BC14">
+        <v>6</v>
+      </c>
+      <c r="BD14">
+        <v>1.98</v>
+      </c>
+      <c r="BE14">
+        <v>6.25</v>
+      </c>
+      <c r="BF14">
+        <v>1.98</v>
+      </c>
+      <c r="BG14">
+        <v>1.41</v>
+      </c>
+      <c r="BH14">
+        <v>2.55</v>
+      </c>
+      <c r="BI14">
+        <v>1.7</v>
+      </c>
+      <c r="BJ14">
+        <v>1.97</v>
+      </c>
+      <c r="BK14">
+        <v>2.12</v>
+      </c>
+      <c r="BL14">
+        <v>1.6</v>
+      </c>
+      <c r="BM14">
+        <v>2.8</v>
+      </c>
+      <c r="BN14">
+        <v>1.35</v>
+      </c>
+      <c r="BO14">
+        <v>3.7</v>
+      </c>
+      <c r="BP14">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7818817</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45711.75</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>4</v>
+      </c>
+      <c r="O15" t="s">
+        <v>97</v>
+      </c>
+      <c r="P15" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q15">
+        <v>2.5</v>
+      </c>
+      <c r="R15">
+        <v>2.25</v>
+      </c>
+      <c r="S15">
+        <v>4.33</v>
+      </c>
+      <c r="T15">
+        <v>1.36</v>
+      </c>
+      <c r="U15">
+        <v>3</v>
+      </c>
+      <c r="V15">
+        <v>2.63</v>
+      </c>
+      <c r="W15">
+        <v>1.44</v>
+      </c>
+      <c r="X15">
+        <v>7</v>
+      </c>
+      <c r="Y15">
+        <v>1.1</v>
+      </c>
+      <c r="Z15">
+        <v>1.83</v>
+      </c>
+      <c r="AA15">
+        <v>3.5</v>
+      </c>
+      <c r="AB15">
+        <v>3.8</v>
+      </c>
+      <c r="AC15">
+        <v>1.02</v>
+      </c>
+      <c r="AD15">
+        <v>10</v>
+      </c>
+      <c r="AE15">
+        <v>1.19</v>
+      </c>
+      <c r="AF15">
+        <v>3.78</v>
+      </c>
+      <c r="AG15">
+        <v>1.75</v>
+      </c>
+      <c r="AH15">
+        <v>2.05</v>
+      </c>
+      <c r="AI15">
+        <v>1.67</v>
+      </c>
+      <c r="AJ15">
+        <v>2.1</v>
+      </c>
+      <c r="AK15">
+        <v>1.25</v>
+      </c>
+      <c r="AL15">
+        <v>1.25</v>
+      </c>
+      <c r="AM15">
+        <v>1.89</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>3</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>9</v>
+      </c>
+      <c r="AV15">
+        <v>4</v>
+      </c>
+      <c r="AW15">
+        <v>6</v>
+      </c>
+      <c r="AX15">
+        <v>5</v>
+      </c>
+      <c r="AY15">
+        <v>16</v>
+      </c>
+      <c r="AZ15">
+        <v>12</v>
+      </c>
+      <c r="BA15">
+        <v>4</v>
+      </c>
+      <c r="BB15">
+        <v>3</v>
+      </c>
+      <c r="BC15">
+        <v>7</v>
+      </c>
+      <c r="BD15">
+        <v>1.74</v>
+      </c>
+      <c r="BE15">
+        <v>6.4</v>
+      </c>
+      <c r="BF15">
+        <v>2.33</v>
+      </c>
+      <c r="BG15">
+        <v>1.35</v>
+      </c>
+      <c r="BH15">
+        <v>2.8</v>
+      </c>
+      <c r="BI15">
+        <v>1.6</v>
+      </c>
+      <c r="BJ15">
+        <v>2.12</v>
+      </c>
+      <c r="BK15">
+        <v>1.97</v>
+      </c>
+      <c r="BL15">
+        <v>1.68</v>
+      </c>
+      <c r="BM15">
+        <v>2.55</v>
+      </c>
+      <c r="BN15">
+        <v>1.41</v>
+      </c>
+      <c r="BO15">
+        <v>3.35</v>
+      </c>
+      <c r="BP15">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7818818</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45711.85416666666</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="s">
+        <v>98</v>
+      </c>
+      <c r="P16" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q16">
+        <v>1.8</v>
+      </c>
+      <c r="R16">
+        <v>2.5</v>
+      </c>
+      <c r="S16">
+        <v>8.5</v>
+      </c>
+      <c r="T16">
+        <v>1.33</v>
+      </c>
+      <c r="U16">
+        <v>3.25</v>
+      </c>
+      <c r="V16">
+        <v>2.63</v>
+      </c>
+      <c r="W16">
+        <v>1.44</v>
+      </c>
+      <c r="X16">
+        <v>6.5</v>
+      </c>
+      <c r="Y16">
+        <v>1.11</v>
+      </c>
+      <c r="Z16">
+        <v>1.3</v>
+      </c>
+      <c r="AA16">
+        <v>4.75</v>
+      </c>
+      <c r="AB16">
+        <v>9</v>
+      </c>
+      <c r="AC16">
+        <v>1.01</v>
+      </c>
+      <c r="AD16">
+        <v>13</v>
+      </c>
+      <c r="AE16">
+        <v>1.19</v>
+      </c>
+      <c r="AF16">
+        <v>3.8</v>
+      </c>
+      <c r="AG16">
+        <v>1.73</v>
+      </c>
+      <c r="AH16">
+        <v>2.08</v>
+      </c>
+      <c r="AI16">
+        <v>2.2</v>
+      </c>
+      <c r="AJ16">
+        <v>1.62</v>
+      </c>
+      <c r="AK16">
+        <v>1.04</v>
+      </c>
+      <c r="AL16">
+        <v>1.15</v>
+      </c>
+      <c r="AM16">
+        <v>3.34</v>
+      </c>
+      <c r="AN16">
+        <v>3</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>3</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>3.44</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>3.44</v>
+      </c>
+      <c r="AU16">
+        <v>4</v>
+      </c>
+      <c r="AV16">
+        <v>5</v>
+      </c>
+      <c r="AW16">
+        <v>9</v>
+      </c>
+      <c r="AX16">
+        <v>5</v>
+      </c>
+      <c r="AY16">
+        <v>17</v>
+      </c>
+      <c r="AZ16">
+        <v>11</v>
+      </c>
+      <c r="BA16">
+        <v>7</v>
+      </c>
+      <c r="BB16">
+        <v>7</v>
+      </c>
+      <c r="BC16">
+        <v>14</v>
+      </c>
+      <c r="BD16">
+        <v>1.29</v>
+      </c>
+      <c r="BE16">
+        <v>7</v>
+      </c>
+      <c r="BF16">
+        <v>4</v>
+      </c>
+      <c r="BG16">
+        <v>1.36</v>
+      </c>
+      <c r="BH16">
+        <v>2.75</v>
+      </c>
+      <c r="BI16">
+        <v>1.61</v>
+      </c>
+      <c r="BJ16">
+        <v>2.1</v>
+      </c>
+      <c r="BK16">
+        <v>1.98</v>
+      </c>
+      <c r="BL16">
+        <v>1.68</v>
+      </c>
+      <c r="BM16">
+        <v>2.55</v>
+      </c>
+      <c r="BN16">
+        <v>1.41</v>
+      </c>
+      <c r="BO16">
+        <v>3.35</v>
+      </c>
+      <c r="BP16">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="109">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>['78']</t>
+  </si>
+  <si>
+    <t>['67']</t>
   </si>
 </sst>
 </file>
@@ -699,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP16"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3998,6 +4001,212 @@
         <v>1.25</v>
       </c>
     </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7818822</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45712.83333333334</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
+        <v>86</v>
+      </c>
+      <c r="P17" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q17">
+        <v>1.91</v>
+      </c>
+      <c r="R17">
+        <v>2.4</v>
+      </c>
+      <c r="S17">
+        <v>7</v>
+      </c>
+      <c r="T17">
+        <v>1.33</v>
+      </c>
+      <c r="U17">
+        <v>3.25</v>
+      </c>
+      <c r="V17">
+        <v>2.63</v>
+      </c>
+      <c r="W17">
+        <v>1.44</v>
+      </c>
+      <c r="X17">
+        <v>6.5</v>
+      </c>
+      <c r="Y17">
+        <v>1.11</v>
+      </c>
+      <c r="Z17">
+        <v>1.35</v>
+      </c>
+      <c r="AA17">
+        <v>4.45</v>
+      </c>
+      <c r="AB17">
+        <v>7.01</v>
+      </c>
+      <c r="AC17">
+        <v>1.01</v>
+      </c>
+      <c r="AD17">
+        <v>11</v>
+      </c>
+      <c r="AE17">
+        <v>1.24</v>
+      </c>
+      <c r="AF17">
+        <v>3.9</v>
+      </c>
+      <c r="AG17">
+        <v>1.73</v>
+      </c>
+      <c r="AH17">
+        <v>2.08</v>
+      </c>
+      <c r="AI17">
+        <v>2</v>
+      </c>
+      <c r="AJ17">
+        <v>1.73</v>
+      </c>
+      <c r="AK17">
+        <v>1.09</v>
+      </c>
+      <c r="AL17">
+        <v>1.16</v>
+      </c>
+      <c r="AM17">
+        <v>2.85</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>3</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>6</v>
+      </c>
+      <c r="AV17">
+        <v>4</v>
+      </c>
+      <c r="AW17">
+        <v>8</v>
+      </c>
+      <c r="AX17">
+        <v>8</v>
+      </c>
+      <c r="AY17">
+        <v>19</v>
+      </c>
+      <c r="AZ17">
+        <v>15</v>
+      </c>
+      <c r="BA17">
+        <v>6</v>
+      </c>
+      <c r="BB17">
+        <v>2</v>
+      </c>
+      <c r="BC17">
+        <v>8</v>
+      </c>
+      <c r="BD17">
+        <v>1.32</v>
+      </c>
+      <c r="BE17">
+        <v>7</v>
+      </c>
+      <c r="BF17">
+        <v>3.8</v>
+      </c>
+      <c r="BG17">
+        <v>1.35</v>
+      </c>
+      <c r="BH17">
+        <v>2.8</v>
+      </c>
+      <c r="BI17">
+        <v>1.6</v>
+      </c>
+      <c r="BJ17">
+        <v>2.12</v>
+      </c>
+      <c r="BK17">
+        <v>1.97</v>
+      </c>
+      <c r="BL17">
+        <v>1.68</v>
+      </c>
+      <c r="BM17">
+        <v>2.5</v>
+      </c>
+      <c r="BN17">
+        <v>1.43</v>
+      </c>
+      <c r="BO17">
+        <v>3.3</v>
+      </c>
+      <c r="BP17">
+        <v>1.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="111">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -313,6 +313,9 @@
     <t>['2']</t>
   </si>
   <si>
+    <t>['39']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -341,6 +344,9 @@
   </si>
   <si>
     <t>['67']</t>
+  </si>
+  <si>
+    <t>['22', '57']</t>
   </si>
 </sst>
 </file>
@@ -702,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP17"/>
+  <dimension ref="A1:BP18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -958,7 +964,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1164,7 +1170,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1782,7 +1788,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -1988,7 +1994,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2066,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ7">
         <v>0.5</v>
@@ -2194,7 +2200,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2606,7 +2612,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2812,7 +2818,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3224,7 +3230,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3636,7 +3642,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4048,7 +4054,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4205,6 +4211,212 @@
       </c>
       <c r="BP17">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7818826</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45716.83333333334</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18" t="s">
+        <v>99</v>
+      </c>
+      <c r="P18" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q18">
+        <v>3.5</v>
+      </c>
+      <c r="R18">
+        <v>2</v>
+      </c>
+      <c r="S18">
+        <v>2.9</v>
+      </c>
+      <c r="T18">
+        <v>1.44</v>
+      </c>
+      <c r="U18">
+        <v>2.55</v>
+      </c>
+      <c r="V18">
+        <v>3</v>
+      </c>
+      <c r="W18">
+        <v>1.33</v>
+      </c>
+      <c r="X18">
+        <v>8.25</v>
+      </c>
+      <c r="Y18">
+        <v>1.06</v>
+      </c>
+      <c r="Z18">
+        <v>2.9</v>
+      </c>
+      <c r="AA18">
+        <v>3.2</v>
+      </c>
+      <c r="AB18">
+        <v>2.38</v>
+      </c>
+      <c r="AC18">
+        <v>1.07</v>
+      </c>
+      <c r="AD18">
+        <v>7.5</v>
+      </c>
+      <c r="AE18">
+        <v>1.38</v>
+      </c>
+      <c r="AF18">
+        <v>2.85</v>
+      </c>
+      <c r="AG18">
+        <v>2.2</v>
+      </c>
+      <c r="AH18">
+        <v>1.65</v>
+      </c>
+      <c r="AI18">
+        <v>1.9</v>
+      </c>
+      <c r="AJ18">
+        <v>1.78</v>
+      </c>
+      <c r="AK18">
+        <v>1.57</v>
+      </c>
+      <c r="AL18">
+        <v>1.32</v>
+      </c>
+      <c r="AM18">
+        <v>1.36</v>
+      </c>
+      <c r="AN18">
+        <v>1</v>
+      </c>
+      <c r="AO18">
+        <v>3</v>
+      </c>
+      <c r="AP18">
+        <v>0.5</v>
+      </c>
+      <c r="AQ18">
+        <v>3</v>
+      </c>
+      <c r="AR18">
+        <v>1.84</v>
+      </c>
+      <c r="AS18">
+        <v>1.62</v>
+      </c>
+      <c r="AT18">
+        <v>3.46</v>
+      </c>
+      <c r="AU18">
+        <v>3</v>
+      </c>
+      <c r="AV18">
+        <v>5</v>
+      </c>
+      <c r="AW18">
+        <v>6</v>
+      </c>
+      <c r="AX18">
+        <v>13</v>
+      </c>
+      <c r="AY18">
+        <v>14</v>
+      </c>
+      <c r="AZ18">
+        <v>22</v>
+      </c>
+      <c r="BA18">
+        <v>8</v>
+      </c>
+      <c r="BB18">
+        <v>3</v>
+      </c>
+      <c r="BC18">
+        <v>11</v>
+      </c>
+      <c r="BD18">
+        <v>2.18</v>
+      </c>
+      <c r="BE18">
+        <v>6.25</v>
+      </c>
+      <c r="BF18">
+        <v>1.84</v>
+      </c>
+      <c r="BG18">
+        <v>1.44</v>
+      </c>
+      <c r="BH18">
+        <v>2.48</v>
+      </c>
+      <c r="BI18">
+        <v>1.76</v>
+      </c>
+      <c r="BJ18">
+        <v>1.89</v>
+      </c>
+      <c r="BK18">
+        <v>2.23</v>
+      </c>
+      <c r="BL18">
+        <v>1.54</v>
+      </c>
+      <c r="BM18">
+        <v>2.9</v>
+      </c>
+      <c r="BN18">
+        <v>1.32</v>
+      </c>
+      <c r="BO18">
+        <v>3.9</v>
+      </c>
+      <c r="BP18">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="113">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -316,6 +316,9 @@
     <t>['39']</t>
   </si>
   <si>
+    <t>['40']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -347,6 +350,9 @@
   </si>
   <si>
     <t>['22', '57']</t>
+  </si>
+  <si>
+    <t>['31', '90+10']</t>
   </si>
 </sst>
 </file>
@@ -708,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP18"/>
+  <dimension ref="A1:BP21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -964,7 +970,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1170,7 +1176,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1248,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -1788,7 +1794,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -1866,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
         <v>3</v>
@@ -1994,7 +2000,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2200,7 +2206,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2281,7 +2287,7 @@
         <v>3</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2612,7 +2618,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2818,7 +2824,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3230,7 +3236,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3642,7 +3648,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4054,7 +4060,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4260,7 +4266,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4417,6 +4423,624 @@
       </c>
       <c r="BP18">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7818828</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45717.5</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19" t="s">
+        <v>90</v>
+      </c>
+      <c r="P19" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q19">
+        <v>3.45</v>
+      </c>
+      <c r="R19">
+        <v>2.09</v>
+      </c>
+      <c r="S19">
+        <v>3.2</v>
+      </c>
+      <c r="T19">
+        <v>1.46</v>
+      </c>
+      <c r="U19">
+        <v>2.55</v>
+      </c>
+      <c r="V19">
+        <v>3</v>
+      </c>
+      <c r="W19">
+        <v>1.34</v>
+      </c>
+      <c r="X19">
+        <v>8.9</v>
+      </c>
+      <c r="Y19">
+        <v>1.01</v>
+      </c>
+      <c r="Z19">
+        <v>2.65</v>
+      </c>
+      <c r="AA19">
+        <v>2.99</v>
+      </c>
+      <c r="AB19">
+        <v>2.4</v>
+      </c>
+      <c r="AC19">
+        <v>1.01</v>
+      </c>
+      <c r="AD19">
+        <v>8.9</v>
+      </c>
+      <c r="AE19">
+        <v>1.33</v>
+      </c>
+      <c r="AF19">
+        <v>3.24</v>
+      </c>
+      <c r="AG19">
+        <v>2.1</v>
+      </c>
+      <c r="AH19">
+        <v>1.7</v>
+      </c>
+      <c r="AI19">
+        <v>1.83</v>
+      </c>
+      <c r="AJ19">
+        <v>1.91</v>
+      </c>
+      <c r="AK19">
+        <v>1.49</v>
+      </c>
+      <c r="AL19">
+        <v>1.32</v>
+      </c>
+      <c r="AM19">
+        <v>1.42</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>1.5</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>1.05</v>
+      </c>
+      <c r="AS19">
+        <v>1.47</v>
+      </c>
+      <c r="AT19">
+        <v>2.52</v>
+      </c>
+      <c r="AU19">
+        <v>5</v>
+      </c>
+      <c r="AV19">
+        <v>4</v>
+      </c>
+      <c r="AW19">
+        <v>16</v>
+      </c>
+      <c r="AX19">
+        <v>8</v>
+      </c>
+      <c r="AY19">
+        <v>27</v>
+      </c>
+      <c r="AZ19">
+        <v>16</v>
+      </c>
+      <c r="BA19">
+        <v>8</v>
+      </c>
+      <c r="BB19">
+        <v>1</v>
+      </c>
+      <c r="BC19">
+        <v>9</v>
+      </c>
+      <c r="BD19">
+        <v>2.02</v>
+      </c>
+      <c r="BE19">
+        <v>6.4</v>
+      </c>
+      <c r="BF19">
+        <v>1.97</v>
+      </c>
+      <c r="BG19">
+        <v>1.45</v>
+      </c>
+      <c r="BH19">
+        <v>2.43</v>
+      </c>
+      <c r="BI19">
+        <v>1.77</v>
+      </c>
+      <c r="BJ19">
+        <v>1.87</v>
+      </c>
+      <c r="BK19">
+        <v>2.25</v>
+      </c>
+      <c r="BL19">
+        <v>1.53</v>
+      </c>
+      <c r="BM19">
+        <v>2.95</v>
+      </c>
+      <c r="BN19">
+        <v>1.32</v>
+      </c>
+      <c r="BO19">
+        <v>3.95</v>
+      </c>
+      <c r="BP19">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7818825</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45717.75</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20" t="s">
+        <v>100</v>
+      </c>
+      <c r="P20" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q20">
+        <v>2.55</v>
+      </c>
+      <c r="R20">
+        <v>2.35</v>
+      </c>
+      <c r="S20">
+        <v>3.85</v>
+      </c>
+      <c r="T20">
+        <v>1.31</v>
+      </c>
+      <c r="U20">
+        <v>3.15</v>
+      </c>
+      <c r="V20">
+        <v>2.4</v>
+      </c>
+      <c r="W20">
+        <v>1.52</v>
+      </c>
+      <c r="X20">
+        <v>5.1</v>
+      </c>
+      <c r="Y20">
+        <v>1.13</v>
+      </c>
+      <c r="Z20">
+        <v>2.02</v>
+      </c>
+      <c r="AA20">
+        <v>3.45</v>
+      </c>
+      <c r="AB20">
+        <v>3.25</v>
+      </c>
+      <c r="AC20">
+        <v>1.01</v>
+      </c>
+      <c r="AD20">
+        <v>11</v>
+      </c>
+      <c r="AE20">
+        <v>1.21</v>
+      </c>
+      <c r="AF20">
+        <v>4.1</v>
+      </c>
+      <c r="AG20">
+        <v>1.68</v>
+      </c>
+      <c r="AH20">
+        <v>2.15</v>
+      </c>
+      <c r="AI20">
+        <v>1.58</v>
+      </c>
+      <c r="AJ20">
+        <v>2.28</v>
+      </c>
+      <c r="AK20">
+        <v>1.32</v>
+      </c>
+      <c r="AL20">
+        <v>1.26</v>
+      </c>
+      <c r="AM20">
+        <v>1.74</v>
+      </c>
+      <c r="AN20">
+        <v>3</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>3</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>1.33</v>
+      </c>
+      <c r="AS20">
+        <v>1.76</v>
+      </c>
+      <c r="AT20">
+        <v>3.09</v>
+      </c>
+      <c r="AU20">
+        <v>4</v>
+      </c>
+      <c r="AV20">
+        <v>4</v>
+      </c>
+      <c r="AW20">
+        <v>12</v>
+      </c>
+      <c r="AX20">
+        <v>4</v>
+      </c>
+      <c r="AY20">
+        <v>20</v>
+      </c>
+      <c r="AZ20">
+        <v>8</v>
+      </c>
+      <c r="BA20">
+        <v>4</v>
+      </c>
+      <c r="BB20">
+        <v>2</v>
+      </c>
+      <c r="BC20">
+        <v>6</v>
+      </c>
+      <c r="BD20">
+        <v>1.74</v>
+      </c>
+      <c r="BE20">
+        <v>6.5</v>
+      </c>
+      <c r="BF20">
+        <v>2.3</v>
+      </c>
+      <c r="BG20">
+        <v>1.32</v>
+      </c>
+      <c r="BH20">
+        <v>2.95</v>
+      </c>
+      <c r="BI20">
+        <v>1.54</v>
+      </c>
+      <c r="BJ20">
+        <v>2.23</v>
+      </c>
+      <c r="BK20">
+        <v>1.89</v>
+      </c>
+      <c r="BL20">
+        <v>1.76</v>
+      </c>
+      <c r="BM20">
+        <v>2.4</v>
+      </c>
+      <c r="BN20">
+        <v>1.47</v>
+      </c>
+      <c r="BO20">
+        <v>3.15</v>
+      </c>
+      <c r="BP20">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7818827</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45717.75</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21" t="s">
+        <v>86</v>
+      </c>
+      <c r="P21" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q21">
+        <v>2.4</v>
+      </c>
+      <c r="R21">
+        <v>2.25</v>
+      </c>
+      <c r="S21">
+        <v>4.1</v>
+      </c>
+      <c r="T21">
+        <v>1.33</v>
+      </c>
+      <c r="U21">
+        <v>2.95</v>
+      </c>
+      <c r="V21">
+        <v>2.6</v>
+      </c>
+      <c r="W21">
+        <v>1.43</v>
+      </c>
+      <c r="X21">
+        <v>6.1</v>
+      </c>
+      <c r="Y21">
+        <v>1.08</v>
+      </c>
+      <c r="Z21">
+        <v>1.88</v>
+      </c>
+      <c r="AA21">
+        <v>3.45</v>
+      </c>
+      <c r="AB21">
+        <v>3.7</v>
+      </c>
+      <c r="AC21">
+        <v>1.03</v>
+      </c>
+      <c r="AD21">
+        <v>9</v>
+      </c>
+      <c r="AE21">
+        <v>1.25</v>
+      </c>
+      <c r="AF21">
+        <v>3.6</v>
+      </c>
+      <c r="AG21">
+        <v>1.85</v>
+      </c>
+      <c r="AH21">
+        <v>1.85</v>
+      </c>
+      <c r="AI21">
+        <v>1.67</v>
+      </c>
+      <c r="AJ21">
+        <v>2.05</v>
+      </c>
+      <c r="AK21">
+        <v>1.24</v>
+      </c>
+      <c r="AL21">
+        <v>1.28</v>
+      </c>
+      <c r="AM21">
+        <v>1.89</v>
+      </c>
+      <c r="AN21">
+        <v>3</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>1.5</v>
+      </c>
+      <c r="AQ21">
+        <v>1.5</v>
+      </c>
+      <c r="AR21">
+        <v>1.92</v>
+      </c>
+      <c r="AS21">
+        <v>1.31</v>
+      </c>
+      <c r="AT21">
+        <v>3.23</v>
+      </c>
+      <c r="AU21">
+        <v>5</v>
+      </c>
+      <c r="AV21">
+        <v>5</v>
+      </c>
+      <c r="AW21">
+        <v>15</v>
+      </c>
+      <c r="AX21">
+        <v>7</v>
+      </c>
+      <c r="AY21">
+        <v>24</v>
+      </c>
+      <c r="AZ21">
+        <v>13</v>
+      </c>
+      <c r="BA21">
+        <v>3</v>
+      </c>
+      <c r="BB21">
+        <v>2</v>
+      </c>
+      <c r="BC21">
+        <v>5</v>
+      </c>
+      <c r="BD21">
+        <v>1.64</v>
+      </c>
+      <c r="BE21">
+        <v>6.4</v>
+      </c>
+      <c r="BF21">
+        <v>2.55</v>
+      </c>
+      <c r="BG21">
+        <v>1.38</v>
+      </c>
+      <c r="BH21">
+        <v>2.65</v>
+      </c>
+      <c r="BI21">
+        <v>1.65</v>
+      </c>
+      <c r="BJ21">
+        <v>2.02</v>
+      </c>
+      <c r="BK21">
+        <v>2.06</v>
+      </c>
+      <c r="BL21">
+        <v>1.63</v>
+      </c>
+      <c r="BM21">
+        <v>2.65</v>
+      </c>
+      <c r="BN21">
+        <v>1.38</v>
+      </c>
+      <c r="BO21">
+        <v>3.5</v>
+      </c>
+      <c r="BP21">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="114">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>['31', '90+10']</t>
+  </si>
+  <si>
+    <t>['32', '45']</t>
   </si>
 </sst>
 </file>
@@ -714,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP21"/>
+  <dimension ref="A1:BP22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1669,7 +1672,7 @@
         <v>3</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -5041,6 +5044,212 @@
       </c>
       <c r="BP21">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7818830</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45717.85416666666</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>81</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22" t="s">
+        <v>100</v>
+      </c>
+      <c r="P22" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q22">
+        <v>2.34</v>
+      </c>
+      <c r="R22">
+        <v>2.3</v>
+      </c>
+      <c r="S22">
+        <v>4.7</v>
+      </c>
+      <c r="T22">
+        <v>1.35</v>
+      </c>
+      <c r="U22">
+        <v>2.95</v>
+      </c>
+      <c r="V22">
+        <v>2.55</v>
+      </c>
+      <c r="W22">
+        <v>1.45</v>
+      </c>
+      <c r="X22">
+        <v>7.2</v>
+      </c>
+      <c r="Y22">
+        <v>1.04</v>
+      </c>
+      <c r="Z22">
+        <v>1.82</v>
+      </c>
+      <c r="AA22">
+        <v>3.35</v>
+      </c>
+      <c r="AB22">
+        <v>4.1</v>
+      </c>
+      <c r="AC22">
+        <v>1.02</v>
+      </c>
+      <c r="AD22">
+        <v>10</v>
+      </c>
+      <c r="AE22">
+        <v>1.26</v>
+      </c>
+      <c r="AF22">
+        <v>3.65</v>
+      </c>
+      <c r="AG22">
+        <v>1.83</v>
+      </c>
+      <c r="AH22">
+        <v>1.95</v>
+      </c>
+      <c r="AI22">
+        <v>1.72</v>
+      </c>
+      <c r="AJ22">
+        <v>2.04</v>
+      </c>
+      <c r="AK22">
+        <v>1.22</v>
+      </c>
+      <c r="AL22">
+        <v>1.27</v>
+      </c>
+      <c r="AM22">
+        <v>1.91</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>1.5</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0.77</v>
+      </c>
+      <c r="AT22">
+        <v>0.77</v>
+      </c>
+      <c r="AU22">
+        <v>7</v>
+      </c>
+      <c r="AV22">
+        <v>5</v>
+      </c>
+      <c r="AW22">
+        <v>13</v>
+      </c>
+      <c r="AX22">
+        <v>1</v>
+      </c>
+      <c r="AY22">
+        <v>25</v>
+      </c>
+      <c r="AZ22">
+        <v>6</v>
+      </c>
+      <c r="BA22">
+        <v>10</v>
+      </c>
+      <c r="BB22">
+        <v>2</v>
+      </c>
+      <c r="BC22">
+        <v>12</v>
+      </c>
+      <c r="BD22">
+        <v>1.54</v>
+      </c>
+      <c r="BE22">
+        <v>6.75</v>
+      </c>
+      <c r="BF22">
+        <v>2.7</v>
+      </c>
+      <c r="BG22">
+        <v>1.36</v>
+      </c>
+      <c r="BH22">
+        <v>2.75</v>
+      </c>
+      <c r="BI22">
+        <v>1.63</v>
+      </c>
+      <c r="BJ22">
+        <v>2.06</v>
+      </c>
+      <c r="BK22">
+        <v>2.02</v>
+      </c>
+      <c r="BL22">
+        <v>1.66</v>
+      </c>
+      <c r="BM22">
+        <v>2.6</v>
+      </c>
+      <c r="BN22">
+        <v>1.4</v>
+      </c>
+      <c r="BO22">
+        <v>3.4</v>
+      </c>
+      <c r="BP22">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -4780,16 +4780,16 @@
         <v>4</v>
       </c>
       <c r="AW20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY20">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA20">
         <v>4</v>
@@ -4980,22 +4980,22 @@
         <v>3.23</v>
       </c>
       <c r="AU21">
+        <v>4</v>
+      </c>
+      <c r="AV21">
+        <v>4</v>
+      </c>
+      <c r="AW21">
+        <v>11</v>
+      </c>
+      <c r="AX21">
         <v>5</v>
       </c>
-      <c r="AV21">
-        <v>5</v>
-      </c>
-      <c r="AW21">
-        <v>15</v>
-      </c>
-      <c r="AX21">
-        <v>7</v>
-      </c>
       <c r="AY21">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ21">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA21">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="116">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -319,6 +319,9 @@
     <t>['40']</t>
   </si>
   <si>
+    <t>['85', '90+9']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -356,6 +359,9 @@
   </si>
   <si>
     <t>['32', '45']</t>
+  </si>
+  <si>
+    <t>['59']</t>
   </si>
 </sst>
 </file>
@@ -717,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP22"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -973,7 +979,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1179,7 +1185,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1797,7 +1803,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -1878,7 +1884,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2003,7 +2009,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2209,7 +2215,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2621,7 +2627,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2827,7 +2833,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3239,7 +3245,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3651,7 +3657,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4063,7 +4069,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4269,7 +4275,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4887,7 +4893,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5093,7 +5099,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5250,6 +5256,212 @@
       </c>
       <c r="BP22">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7818824</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45718.5</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>3</v>
+      </c>
+      <c r="O23" t="s">
+        <v>101</v>
+      </c>
+      <c r="P23" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q23">
+        <v>5</v>
+      </c>
+      <c r="R23">
+        <v>2.05</v>
+      </c>
+      <c r="S23">
+        <v>2.5</v>
+      </c>
+      <c r="T23">
+        <v>1.44</v>
+      </c>
+      <c r="U23">
+        <v>2.63</v>
+      </c>
+      <c r="V23">
+        <v>3.25</v>
+      </c>
+      <c r="W23">
+        <v>1.33</v>
+      </c>
+      <c r="X23">
+        <v>10</v>
+      </c>
+      <c r="Y23">
+        <v>1.06</v>
+      </c>
+      <c r="Z23">
+        <v>4.4</v>
+      </c>
+      <c r="AA23">
+        <v>3.3</v>
+      </c>
+      <c r="AB23">
+        <v>1.79</v>
+      </c>
+      <c r="AC23">
+        <v>1.03</v>
+      </c>
+      <c r="AD23">
+        <v>7.5</v>
+      </c>
+      <c r="AE23">
+        <v>1.37</v>
+      </c>
+      <c r="AF23">
+        <v>2.9</v>
+      </c>
+      <c r="AG23">
+        <v>2.15</v>
+      </c>
+      <c r="AH23">
+        <v>1.67</v>
+      </c>
+      <c r="AI23">
+        <v>2</v>
+      </c>
+      <c r="AJ23">
+        <v>1.73</v>
+      </c>
+      <c r="AK23">
+        <v>1.95</v>
+      </c>
+      <c r="AL23">
+        <v>1.28</v>
+      </c>
+      <c r="AM23">
+        <v>1.2</v>
+      </c>
+      <c r="AN23">
+        <v>3</v>
+      </c>
+      <c r="AO23">
+        <v>3</v>
+      </c>
+      <c r="AP23">
+        <v>3</v>
+      </c>
+      <c r="AQ23">
+        <v>1.5</v>
+      </c>
+      <c r="AR23">
+        <v>1.43</v>
+      </c>
+      <c r="AS23">
+        <v>1.74</v>
+      </c>
+      <c r="AT23">
+        <v>3.17</v>
+      </c>
+      <c r="AU23">
+        <v>6</v>
+      </c>
+      <c r="AV23">
+        <v>8</v>
+      </c>
+      <c r="AW23">
+        <v>2</v>
+      </c>
+      <c r="AX23">
+        <v>13</v>
+      </c>
+      <c r="AY23">
+        <v>8</v>
+      </c>
+      <c r="AZ23">
+        <v>25</v>
+      </c>
+      <c r="BA23">
+        <v>2</v>
+      </c>
+      <c r="BB23">
+        <v>7</v>
+      </c>
+      <c r="BC23">
+        <v>9</v>
+      </c>
+      <c r="BD23">
+        <v>2.9</v>
+      </c>
+      <c r="BE23">
+        <v>6.5</v>
+      </c>
+      <c r="BF23">
+        <v>1.5</v>
+      </c>
+      <c r="BG23">
+        <v>1.43</v>
+      </c>
+      <c r="BH23">
+        <v>2.5</v>
+      </c>
+      <c r="BI23">
+        <v>1.74</v>
+      </c>
+      <c r="BJ23">
+        <v>1.92</v>
+      </c>
+      <c r="BK23">
+        <v>2.18</v>
+      </c>
+      <c r="BL23">
+        <v>1.56</v>
+      </c>
+      <c r="BM23">
+        <v>2.85</v>
+      </c>
+      <c r="BN23">
+        <v>1.33</v>
+      </c>
+      <c r="BO23">
+        <v>3.8</v>
+      </c>
+      <c r="BP23">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="120">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -322,6 +322,12 @@
     <t>['85', '90+9']</t>
   </si>
   <si>
+    <t>['59', '82']</t>
+  </si>
+  <si>
+    <t>['6', '74']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -362,6 +368,12 @@
   </si>
   <si>
     <t>['59']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['13', '66']</t>
   </si>
 </sst>
 </file>
@@ -723,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP23"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -979,7 +991,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1185,7 +1197,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1803,7 +1815,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2009,7 +2021,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2215,7 +2227,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2499,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
         <v>0</v>
@@ -2627,7 +2639,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2833,7 +2845,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3245,7 +3257,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3657,7 +3669,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4069,7 +4081,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4150,7 +4162,7 @@
         <v>0</v>
       </c>
       <c r="AQ17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4275,7 +4287,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4893,7 +4905,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5099,7 +5111,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5305,7 +5317,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5462,6 +5474,418 @@
       </c>
       <c r="BP23">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7818823</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45718.75</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>3</v>
+      </c>
+      <c r="O24" t="s">
+        <v>102</v>
+      </c>
+      <c r="P24" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q24">
+        <v>5.2</v>
+      </c>
+      <c r="R24">
+        <v>2.5</v>
+      </c>
+      <c r="S24">
+        <v>2.09</v>
+      </c>
+      <c r="T24">
+        <v>1.28</v>
+      </c>
+      <c r="U24">
+        <v>3.35</v>
+      </c>
+      <c r="V24">
+        <v>2.32</v>
+      </c>
+      <c r="W24">
+        <v>1.55</v>
+      </c>
+      <c r="X24">
+        <v>5.55</v>
+      </c>
+      <c r="Y24">
+        <v>1.09</v>
+      </c>
+      <c r="Z24">
+        <v>4.7</v>
+      </c>
+      <c r="AA24">
+        <v>4</v>
+      </c>
+      <c r="AB24">
+        <v>1.6</v>
+      </c>
+      <c r="AC24">
+        <v>1.01</v>
+      </c>
+      <c r="AD24">
+        <v>13</v>
+      </c>
+      <c r="AE24">
+        <v>1.2</v>
+      </c>
+      <c r="AF24">
+        <v>4.4</v>
+      </c>
+      <c r="AG24">
+        <v>1.62</v>
+      </c>
+      <c r="AH24">
+        <v>2.25</v>
+      </c>
+      <c r="AI24">
+        <v>1.66</v>
+      </c>
+      <c r="AJ24">
+        <v>2.13</v>
+      </c>
+      <c r="AK24">
+        <v>2.23</v>
+      </c>
+      <c r="AL24">
+        <v>1.2</v>
+      </c>
+      <c r="AM24">
+        <v>1.17</v>
+      </c>
+      <c r="AN24">
+        <v>3</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>3</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>1.82</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>1.82</v>
+      </c>
+      <c r="AU24">
+        <v>7</v>
+      </c>
+      <c r="AV24">
+        <v>5</v>
+      </c>
+      <c r="AW24">
+        <v>15</v>
+      </c>
+      <c r="AX24">
+        <v>10</v>
+      </c>
+      <c r="AY24">
+        <v>26</v>
+      </c>
+      <c r="AZ24">
+        <v>18</v>
+      </c>
+      <c r="BA24">
+        <v>2</v>
+      </c>
+      <c r="BB24">
+        <v>11</v>
+      </c>
+      <c r="BC24">
+        <v>13</v>
+      </c>
+      <c r="BD24">
+        <v>2.95</v>
+      </c>
+      <c r="BE24">
+        <v>6.75</v>
+      </c>
+      <c r="BF24">
+        <v>1.49</v>
+      </c>
+      <c r="BG24">
+        <v>1.32</v>
+      </c>
+      <c r="BH24">
+        <v>2.9</v>
+      </c>
+      <c r="BI24">
+        <v>1.56</v>
+      </c>
+      <c r="BJ24">
+        <v>2.17</v>
+      </c>
+      <c r="BK24">
+        <v>1.91</v>
+      </c>
+      <c r="BL24">
+        <v>1.74</v>
+      </c>
+      <c r="BM24">
+        <v>2.43</v>
+      </c>
+      <c r="BN24">
+        <v>1.46</v>
+      </c>
+      <c r="BO24">
+        <v>3.15</v>
+      </c>
+      <c r="BP24">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7818829</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45718.85416666666</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>2</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
+      <c r="O25" t="s">
+        <v>103</v>
+      </c>
+      <c r="P25" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q25">
+        <v>2.88</v>
+      </c>
+      <c r="R25">
+        <v>2</v>
+      </c>
+      <c r="S25">
+        <v>4.33</v>
+      </c>
+      <c r="T25">
+        <v>1.5</v>
+      </c>
+      <c r="U25">
+        <v>2.5</v>
+      </c>
+      <c r="V25">
+        <v>3.4</v>
+      </c>
+      <c r="W25">
+        <v>1.3</v>
+      </c>
+      <c r="X25">
+        <v>10</v>
+      </c>
+      <c r="Y25">
+        <v>1.06</v>
+      </c>
+      <c r="Z25">
+        <v>2.04</v>
+      </c>
+      <c r="AA25">
+        <v>3.11</v>
+      </c>
+      <c r="AB25">
+        <v>3.35</v>
+      </c>
+      <c r="AC25">
+        <v>1.03</v>
+      </c>
+      <c r="AD25">
+        <v>7.5</v>
+      </c>
+      <c r="AE25">
+        <v>1.41</v>
+      </c>
+      <c r="AF25">
+        <v>2.7</v>
+      </c>
+      <c r="AG25">
+        <v>2.25</v>
+      </c>
+      <c r="AH25">
+        <v>1.62</v>
+      </c>
+      <c r="AI25">
+        <v>2</v>
+      </c>
+      <c r="AJ25">
+        <v>1.73</v>
+      </c>
+      <c r="AK25">
+        <v>1.29</v>
+      </c>
+      <c r="AL25">
+        <v>1.31</v>
+      </c>
+      <c r="AM25">
+        <v>1.68</v>
+      </c>
+      <c r="AN25">
+        <v>3</v>
+      </c>
+      <c r="AO25">
+        <v>3</v>
+      </c>
+      <c r="AP25">
+        <v>2</v>
+      </c>
+      <c r="AQ25">
+        <v>2</v>
+      </c>
+      <c r="AR25">
+        <v>1.33</v>
+      </c>
+      <c r="AS25">
+        <v>1.26</v>
+      </c>
+      <c r="AT25">
+        <v>2.59</v>
+      </c>
+      <c r="AU25">
+        <v>4</v>
+      </c>
+      <c r="AV25">
+        <v>5</v>
+      </c>
+      <c r="AW25">
+        <v>12</v>
+      </c>
+      <c r="AX25">
+        <v>9</v>
+      </c>
+      <c r="AY25">
+        <v>20</v>
+      </c>
+      <c r="AZ25">
+        <v>19</v>
+      </c>
+      <c r="BA25">
+        <v>2</v>
+      </c>
+      <c r="BB25">
+        <v>1</v>
+      </c>
+      <c r="BC25">
+        <v>3</v>
+      </c>
+      <c r="BD25">
+        <v>1.76</v>
+      </c>
+      <c r="BE25">
+        <v>6.25</v>
+      </c>
+      <c r="BF25">
+        <v>2.32</v>
+      </c>
+      <c r="BG25">
+        <v>1.45</v>
+      </c>
+      <c r="BH25">
+        <v>2.43</v>
+      </c>
+      <c r="BI25">
+        <v>1.77</v>
+      </c>
+      <c r="BJ25">
+        <v>1.87</v>
+      </c>
+      <c r="BK25">
+        <v>2.28</v>
+      </c>
+      <c r="BL25">
+        <v>1.52</v>
+      </c>
+      <c r="BM25">
+        <v>2.95</v>
+      </c>
+      <c r="BN25">
+        <v>1.32</v>
+      </c>
+      <c r="BO25">
+        <v>3.95</v>
+      </c>
+      <c r="BP25">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -5840,13 +5840,13 @@
         <v>19</v>
       </c>
       <c r="BA25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB25">
         <v>1</v>
       </c>
       <c r="BC25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD25">
         <v>1.76</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="122">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -328,12 +328,15 @@
     <t>['6', '74']</t>
   </si>
   <si>
+    <t>['88']</t>
+  </si>
+  <si>
+    <t>['90+7']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
-    <t>['88']</t>
-  </si>
-  <si>
     <t>['33', '72', '80']</t>
   </si>
   <si>
@@ -374,6 +377,9 @@
   </si>
   <si>
     <t>['13', '66']</t>
+  </si>
+  <si>
+    <t>['46']</t>
   </si>
 </sst>
 </file>
@@ -735,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BP27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -991,7 +997,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1197,7 +1203,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q3">
         <v>2.3</v>
@@ -1484,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1815,7 +1821,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2021,7 +2027,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2227,7 +2233,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2511,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ9">
         <v>0</v>
@@ -2639,7 +2645,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2845,7 +2851,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3132,7 +3138,7 @@
         <v>3</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3257,7 +3263,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3669,7 +3675,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4081,7 +4087,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4287,7 +4293,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4905,7 +4911,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5111,7 +5117,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5317,7 +5323,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5523,7 +5529,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5729,7 +5735,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -5807,7 +5813,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ25">
         <v>2</v>
@@ -5886,6 +5892,418 @@
       </c>
       <c r="BP25">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7818838</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45723.83333333334</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" t="s">
+        <v>82</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P26" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q26">
+        <v>3.01</v>
+      </c>
+      <c r="R26">
+        <v>2.13</v>
+      </c>
+      <c r="S26">
+        <v>3.85</v>
+      </c>
+      <c r="T26">
+        <v>1.43</v>
+      </c>
+      <c r="U26">
+        <v>2.76</v>
+      </c>
+      <c r="V26">
+        <v>3.2</v>
+      </c>
+      <c r="W26">
+        <v>1.34</v>
+      </c>
+      <c r="X26">
+        <v>7.9</v>
+      </c>
+      <c r="Y26">
+        <v>1.02</v>
+      </c>
+      <c r="Z26">
+        <v>2.25</v>
+      </c>
+      <c r="AA26">
+        <v>3.1</v>
+      </c>
+      <c r="AB26">
+        <v>3.1</v>
+      </c>
+      <c r="AC26">
+        <v>1.05</v>
+      </c>
+      <c r="AD26">
+        <v>8</v>
+      </c>
+      <c r="AE26">
+        <v>1.3</v>
+      </c>
+      <c r="AF26">
+        <v>3.2</v>
+      </c>
+      <c r="AG26">
+        <v>2.1</v>
+      </c>
+      <c r="AH26">
+        <v>1.65</v>
+      </c>
+      <c r="AI26">
+        <v>1.73</v>
+      </c>
+      <c r="AJ26">
+        <v>2</v>
+      </c>
+      <c r="AK26">
+        <v>1.34</v>
+      </c>
+      <c r="AL26">
+        <v>1.32</v>
+      </c>
+      <c r="AM26">
+        <v>1.6</v>
+      </c>
+      <c r="AN26">
+        <v>2</v>
+      </c>
+      <c r="AO26">
+        <v>1</v>
+      </c>
+      <c r="AP26">
+        <v>2.33</v>
+      </c>
+      <c r="AQ26">
+        <v>0.5</v>
+      </c>
+      <c r="AR26">
+        <v>1.39</v>
+      </c>
+      <c r="AS26">
+        <v>1.14</v>
+      </c>
+      <c r="AT26">
+        <v>2.53</v>
+      </c>
+      <c r="AU26">
+        <v>9</v>
+      </c>
+      <c r="AV26">
+        <v>2</v>
+      </c>
+      <c r="AW26">
+        <v>12</v>
+      </c>
+      <c r="AX26">
+        <v>4</v>
+      </c>
+      <c r="AY26">
+        <v>26</v>
+      </c>
+      <c r="AZ26">
+        <v>7</v>
+      </c>
+      <c r="BA26">
+        <v>10</v>
+      </c>
+      <c r="BB26">
+        <v>3</v>
+      </c>
+      <c r="BC26">
+        <v>13</v>
+      </c>
+      <c r="BD26">
+        <v>1.74</v>
+      </c>
+      <c r="BE26">
+        <v>6.25</v>
+      </c>
+      <c r="BF26">
+        <v>2.33</v>
+      </c>
+      <c r="BG26">
+        <v>1.44</v>
+      </c>
+      <c r="BH26">
+        <v>2.45</v>
+      </c>
+      <c r="BI26">
+        <v>1.76</v>
+      </c>
+      <c r="BJ26">
+        <v>1.89</v>
+      </c>
+      <c r="BK26">
+        <v>2.25</v>
+      </c>
+      <c r="BL26">
+        <v>1.53</v>
+      </c>
+      <c r="BM26">
+        <v>2.9</v>
+      </c>
+      <c r="BN26">
+        <v>1.32</v>
+      </c>
+      <c r="BO26">
+        <v>3.9</v>
+      </c>
+      <c r="BP26">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7818832</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45724.75</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>2</v>
+      </c>
+      <c r="O27" t="s">
+        <v>105</v>
+      </c>
+      <c r="P27" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>2</v>
+      </c>
+      <c r="S27">
+        <v>3.4</v>
+      </c>
+      <c r="T27">
+        <v>1.39</v>
+      </c>
+      <c r="U27">
+        <v>2.94</v>
+      </c>
+      <c r="V27">
+        <v>2.97</v>
+      </c>
+      <c r="W27">
+        <v>1.38</v>
+      </c>
+      <c r="X27">
+        <v>8</v>
+      </c>
+      <c r="Y27">
+        <v>1.02</v>
+      </c>
+      <c r="Z27">
+        <v>2.5</v>
+      </c>
+      <c r="AA27">
+        <v>3.1</v>
+      </c>
+      <c r="AB27">
+        <v>2.62</v>
+      </c>
+      <c r="AC27">
+        <v>1.05</v>
+      </c>
+      <c r="AD27">
+        <v>8</v>
+      </c>
+      <c r="AE27">
+        <v>1.29</v>
+      </c>
+      <c r="AF27">
+        <v>3.3</v>
+      </c>
+      <c r="AG27">
+        <v>1.95</v>
+      </c>
+      <c r="AH27">
+        <v>1.75</v>
+      </c>
+      <c r="AI27">
+        <v>1.67</v>
+      </c>
+      <c r="AJ27">
+        <v>2.1</v>
+      </c>
+      <c r="AK27">
+        <v>1.43</v>
+      </c>
+      <c r="AL27">
+        <v>1.3</v>
+      </c>
+      <c r="AM27">
+        <v>1.51</v>
+      </c>
+      <c r="AN27">
+        <v>1</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>1</v>
+      </c>
+      <c r="AQ27">
+        <v>0.5</v>
+      </c>
+      <c r="AR27">
+        <v>2.18</v>
+      </c>
+      <c r="AS27">
+        <v>1.65</v>
+      </c>
+      <c r="AT27">
+        <v>3.83</v>
+      </c>
+      <c r="AU27">
+        <v>5</v>
+      </c>
+      <c r="AV27">
+        <v>3</v>
+      </c>
+      <c r="AW27">
+        <v>8</v>
+      </c>
+      <c r="AX27">
+        <v>4</v>
+      </c>
+      <c r="AY27">
+        <v>17</v>
+      </c>
+      <c r="AZ27">
+        <v>11</v>
+      </c>
+      <c r="BA27">
+        <v>6</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>6</v>
+      </c>
+      <c r="BD27">
+        <v>1.88</v>
+      </c>
+      <c r="BE27">
+        <v>6.25</v>
+      </c>
+      <c r="BF27">
+        <v>2.15</v>
+      </c>
+      <c r="BG27">
+        <v>1.38</v>
+      </c>
+      <c r="BH27">
+        <v>2.65</v>
+      </c>
+      <c r="BI27">
+        <v>1.66</v>
+      </c>
+      <c r="BJ27">
+        <v>2.02</v>
+      </c>
+      <c r="BK27">
+        <v>2.08</v>
+      </c>
+      <c r="BL27">
+        <v>1.61</v>
+      </c>
+      <c r="BM27">
+        <v>2.7</v>
+      </c>
+      <c r="BN27">
+        <v>1.37</v>
+      </c>
+      <c r="BO27">
+        <v>3.65</v>
+      </c>
+      <c r="BP27">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="126">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -334,6 +334,12 @@
     <t>['90+7']</t>
   </si>
   <si>
+    <t>['16']</t>
+  </si>
+  <si>
+    <t>['48', '62', '90+6']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -380,6 +386,12 @@
   </si>
   <si>
     <t>['46']</t>
+  </si>
+  <si>
+    <t>['9', '31', '79']</t>
+  </si>
+  <si>
+    <t>['5']</t>
   </si>
 </sst>
 </file>
@@ -741,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP27"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -997,7 +1009,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1821,7 +1833,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2027,7 +2039,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2233,7 +2245,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2645,7 +2657,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2851,7 +2863,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3263,7 +3275,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3344,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3675,7 +3687,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4087,7 +4099,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4293,7 +4305,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4911,7 +4923,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5117,7 +5129,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5323,7 +5335,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5529,7 +5541,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5735,7 +5747,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6147,7 +6159,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6304,6 +6316,418 @@
       </c>
       <c r="BP27">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7818837</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45724.85416666666</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" t="s">
+        <v>71</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <v>3</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>3</v>
+      </c>
+      <c r="N28">
+        <v>4</v>
+      </c>
+      <c r="O28" t="s">
+        <v>106</v>
+      </c>
+      <c r="P28" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q28">
+        <v>3.1</v>
+      </c>
+      <c r="R28">
+        <v>2.2</v>
+      </c>
+      <c r="S28">
+        <v>3</v>
+      </c>
+      <c r="T28">
+        <v>1.33</v>
+      </c>
+      <c r="U28">
+        <v>3.23</v>
+      </c>
+      <c r="V28">
+        <v>2.68</v>
+      </c>
+      <c r="W28">
+        <v>1.46</v>
+      </c>
+      <c r="X28">
+        <v>5.8</v>
+      </c>
+      <c r="Y28">
+        <v>1.07</v>
+      </c>
+      <c r="Z28">
+        <v>2.5</v>
+      </c>
+      <c r="AA28">
+        <v>3.3</v>
+      </c>
+      <c r="AB28">
+        <v>2.5</v>
+      </c>
+      <c r="AC28">
+        <v>1.01</v>
+      </c>
+      <c r="AD28">
+        <v>11</v>
+      </c>
+      <c r="AE28">
+        <v>1.17</v>
+      </c>
+      <c r="AF28">
+        <v>4.5</v>
+      </c>
+      <c r="AG28">
+        <v>1.65</v>
+      </c>
+      <c r="AH28">
+        <v>2.1</v>
+      </c>
+      <c r="AI28">
+        <v>1.53</v>
+      </c>
+      <c r="AJ28">
+        <v>2.38</v>
+      </c>
+      <c r="AK28">
+        <v>1.5</v>
+      </c>
+      <c r="AL28">
+        <v>1.28</v>
+      </c>
+      <c r="AM28">
+        <v>1.46</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>3</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>3</v>
+      </c>
+      <c r="AR28">
+        <v>1.27</v>
+      </c>
+      <c r="AS28">
+        <v>2.33</v>
+      </c>
+      <c r="AT28">
+        <v>3.6</v>
+      </c>
+      <c r="AU28">
+        <v>6</v>
+      </c>
+      <c r="AV28">
+        <v>8</v>
+      </c>
+      <c r="AW28">
+        <v>11</v>
+      </c>
+      <c r="AX28">
+        <v>9</v>
+      </c>
+      <c r="AY28">
+        <v>23</v>
+      </c>
+      <c r="AZ28">
+        <v>19</v>
+      </c>
+      <c r="BA28">
+        <v>3</v>
+      </c>
+      <c r="BB28">
+        <v>1</v>
+      </c>
+      <c r="BC28">
+        <v>4</v>
+      </c>
+      <c r="BD28">
+        <v>2.1</v>
+      </c>
+      <c r="BE28">
+        <v>6.4</v>
+      </c>
+      <c r="BF28">
+        <v>1.9</v>
+      </c>
+      <c r="BG28">
+        <v>1.33</v>
+      </c>
+      <c r="BH28">
+        <v>2.88</v>
+      </c>
+      <c r="BI28">
+        <v>1.57</v>
+      </c>
+      <c r="BJ28">
+        <v>2.15</v>
+      </c>
+      <c r="BK28">
+        <v>1.93</v>
+      </c>
+      <c r="BL28">
+        <v>1.72</v>
+      </c>
+      <c r="BM28">
+        <v>2.45</v>
+      </c>
+      <c r="BN28">
+        <v>1.44</v>
+      </c>
+      <c r="BO28">
+        <v>3.2</v>
+      </c>
+      <c r="BP28">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7818836</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45724.85416666666</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>3</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>4</v>
+      </c>
+      <c r="O29" t="s">
+        <v>107</v>
+      </c>
+      <c r="P29" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q29">
+        <v>2.3</v>
+      </c>
+      <c r="R29">
+        <v>2.25</v>
+      </c>
+      <c r="S29">
+        <v>4.35</v>
+      </c>
+      <c r="T29">
+        <v>1.33</v>
+      </c>
+      <c r="U29">
+        <v>2.95</v>
+      </c>
+      <c r="V29">
+        <v>2.55</v>
+      </c>
+      <c r="W29">
+        <v>1.45</v>
+      </c>
+      <c r="X29">
+        <v>5.8</v>
+      </c>
+      <c r="Y29">
+        <v>1.09</v>
+      </c>
+      <c r="Z29">
+        <v>1.7</v>
+      </c>
+      <c r="AA29">
+        <v>3.6</v>
+      </c>
+      <c r="AB29">
+        <v>4.2</v>
+      </c>
+      <c r="AC29">
+        <v>1.03</v>
+      </c>
+      <c r="AD29">
+        <v>9</v>
+      </c>
+      <c r="AE29">
+        <v>1.25</v>
+      </c>
+      <c r="AF29">
+        <v>3.6</v>
+      </c>
+      <c r="AG29">
+        <v>1.85</v>
+      </c>
+      <c r="AH29">
+        <v>1.85</v>
+      </c>
+      <c r="AI29">
+        <v>1.71</v>
+      </c>
+      <c r="AJ29">
+        <v>1.98</v>
+      </c>
+      <c r="AK29">
+        <v>1.21</v>
+      </c>
+      <c r="AL29">
+        <v>1.27</v>
+      </c>
+      <c r="AM29">
+        <v>2</v>
+      </c>
+      <c r="AN29">
+        <v>3</v>
+      </c>
+      <c r="AO29">
+        <v>1</v>
+      </c>
+      <c r="AP29">
+        <v>3</v>
+      </c>
+      <c r="AQ29">
+        <v>0.5</v>
+      </c>
+      <c r="AR29">
+        <v>1.73</v>
+      </c>
+      <c r="AS29">
+        <v>1.43</v>
+      </c>
+      <c r="AT29">
+        <v>3.16</v>
+      </c>
+      <c r="AU29">
+        <v>7</v>
+      </c>
+      <c r="AV29">
+        <v>3</v>
+      </c>
+      <c r="AW29">
+        <v>3</v>
+      </c>
+      <c r="AX29">
+        <v>4</v>
+      </c>
+      <c r="AY29">
+        <v>20</v>
+      </c>
+      <c r="AZ29">
+        <v>11</v>
+      </c>
+      <c r="BA29">
+        <v>6</v>
+      </c>
+      <c r="BB29">
+        <v>6</v>
+      </c>
+      <c r="BC29">
+        <v>12</v>
+      </c>
+      <c r="BD29">
+        <v>1.66</v>
+      </c>
+      <c r="BE29">
+        <v>6.4</v>
+      </c>
+      <c r="BF29">
+        <v>2.5</v>
+      </c>
+      <c r="BG29">
+        <v>1.33</v>
+      </c>
+      <c r="BH29">
+        <v>2.9</v>
+      </c>
+      <c r="BI29">
+        <v>1.56</v>
+      </c>
+      <c r="BJ29">
+        <v>2.18</v>
+      </c>
+      <c r="BK29">
+        <v>1.92</v>
+      </c>
+      <c r="BL29">
+        <v>1.73</v>
+      </c>
+      <c r="BM29">
+        <v>2.45</v>
+      </c>
+      <c r="BN29">
+        <v>1.44</v>
+      </c>
+      <c r="BO29">
+        <v>3.2</v>
+      </c>
+      <c r="BP29">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="131">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -340,6 +340,15 @@
     <t>['48', '62', '90+6']</t>
   </si>
   <si>
+    <t>['60']</t>
+  </si>
+  <si>
+    <t>['84']</t>
+  </si>
+  <si>
+    <t>['44', '73']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -392,6 +401,12 @@
   </si>
   <si>
     <t>['5']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
   </si>
 </sst>
 </file>
@@ -753,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1009,7 +1024,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1296,7 +1311,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1833,7 +1848,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2039,7 +2054,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2120,7 +2135,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2245,7 +2260,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2657,7 +2672,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2863,7 +2878,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3147,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>0.5</v>
@@ -3275,7 +3290,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3562,7 +3577,7 @@
         <v>3</v>
       </c>
       <c r="AQ14">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3687,7 +3702,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3768,7 +3783,7 @@
         <v>3</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4099,7 +4114,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4177,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ17">
         <v>2</v>
@@ -4305,7 +4320,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4923,7 +4938,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5129,7 +5144,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5335,7 +5350,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5541,7 +5556,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5747,7 +5762,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6159,7 +6174,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6365,7 +6380,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6571,7 +6586,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6728,6 +6743,624 @@
       </c>
       <c r="BP29">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7818833</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45725.5</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>80</v>
+      </c>
+      <c r="H30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30" t="s">
+        <v>108</v>
+      </c>
+      <c r="P30" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q30">
+        <v>2.32</v>
+      </c>
+      <c r="R30">
+        <v>2.18</v>
+      </c>
+      <c r="S30">
+        <v>4.6</v>
+      </c>
+      <c r="T30">
+        <v>1.37</v>
+      </c>
+      <c r="U30">
+        <v>2.8</v>
+      </c>
+      <c r="V30">
+        <v>2.7</v>
+      </c>
+      <c r="W30">
+        <v>1.38</v>
+      </c>
+      <c r="X30">
+        <v>6.5</v>
+      </c>
+      <c r="Y30">
+        <v>1.07</v>
+      </c>
+      <c r="Z30">
+        <v>1.72</v>
+      </c>
+      <c r="AA30">
+        <v>3.72</v>
+      </c>
+      <c r="AB30">
+        <v>4.65</v>
+      </c>
+      <c r="AC30">
+        <v>1.03</v>
+      </c>
+      <c r="AD30">
+        <v>9</v>
+      </c>
+      <c r="AE30">
+        <v>1.25</v>
+      </c>
+      <c r="AF30">
+        <v>3.6</v>
+      </c>
+      <c r="AG30">
+        <v>1.78</v>
+      </c>
+      <c r="AH30">
+        <v>1.95</v>
+      </c>
+      <c r="AI30">
+        <v>1.68</v>
+      </c>
+      <c r="AJ30">
+        <v>2.02</v>
+      </c>
+      <c r="AK30">
+        <v>1.2</v>
+      </c>
+      <c r="AL30">
+        <v>1.28</v>
+      </c>
+      <c r="AM30">
+        <v>2</v>
+      </c>
+      <c r="AN30">
+        <v>3</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>2</v>
+      </c>
+      <c r="AQ30">
+        <v>0.5</v>
+      </c>
+      <c r="AR30">
+        <v>1.85</v>
+      </c>
+      <c r="AS30">
+        <v>1.48</v>
+      </c>
+      <c r="AT30">
+        <v>3.33</v>
+      </c>
+      <c r="AU30">
+        <v>8</v>
+      </c>
+      <c r="AV30">
+        <v>4</v>
+      </c>
+      <c r="AW30">
+        <v>17</v>
+      </c>
+      <c r="AX30">
+        <v>10</v>
+      </c>
+      <c r="AY30">
+        <v>28</v>
+      </c>
+      <c r="AZ30">
+        <v>15</v>
+      </c>
+      <c r="BA30">
+        <v>6</v>
+      </c>
+      <c r="BB30">
+        <v>4</v>
+      </c>
+      <c r="BC30">
+        <v>10</v>
+      </c>
+      <c r="BD30">
+        <v>1.55</v>
+      </c>
+      <c r="BE30">
+        <v>6.5</v>
+      </c>
+      <c r="BF30">
+        <v>2.7</v>
+      </c>
+      <c r="BG30">
+        <v>1.37</v>
+      </c>
+      <c r="BH30">
+        <v>2.7</v>
+      </c>
+      <c r="BI30">
+        <v>1.63</v>
+      </c>
+      <c r="BJ30">
+        <v>2.07</v>
+      </c>
+      <c r="BK30">
+        <v>2.02</v>
+      </c>
+      <c r="BL30">
+        <v>1.66</v>
+      </c>
+      <c r="BM30">
+        <v>2.6</v>
+      </c>
+      <c r="BN30">
+        <v>1.4</v>
+      </c>
+      <c r="BO30">
+        <v>3.4</v>
+      </c>
+      <c r="BP30">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7818834</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45725.75</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>2</v>
+      </c>
+      <c r="O31" t="s">
+        <v>109</v>
+      </c>
+      <c r="P31" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q31">
+        <v>2.53</v>
+      </c>
+      <c r="R31">
+        <v>2.08</v>
+      </c>
+      <c r="S31">
+        <v>4.58</v>
+      </c>
+      <c r="T31">
+        <v>1.44</v>
+      </c>
+      <c r="U31">
+        <v>2.63</v>
+      </c>
+      <c r="V31">
+        <v>3.25</v>
+      </c>
+      <c r="W31">
+        <v>1.33</v>
+      </c>
+      <c r="X31">
+        <v>9</v>
+      </c>
+      <c r="Y31">
+        <v>1.07</v>
+      </c>
+      <c r="Z31">
+        <v>1.95</v>
+      </c>
+      <c r="AA31">
+        <v>3.46</v>
+      </c>
+      <c r="AB31">
+        <v>3.79</v>
+      </c>
+      <c r="AC31">
+        <v>1.04</v>
+      </c>
+      <c r="AD31">
+        <v>8.5</v>
+      </c>
+      <c r="AE31">
+        <v>1.33</v>
+      </c>
+      <c r="AF31">
+        <v>3</v>
+      </c>
+      <c r="AG31">
+        <v>2.08</v>
+      </c>
+      <c r="AH31">
+        <v>1.73</v>
+      </c>
+      <c r="AI31">
+        <v>1.83</v>
+      </c>
+      <c r="AJ31">
+        <v>1.83</v>
+      </c>
+      <c r="AK31">
+        <v>1.25</v>
+      </c>
+      <c r="AL31">
+        <v>1.33</v>
+      </c>
+      <c r="AM31">
+        <v>1.83</v>
+      </c>
+      <c r="AN31">
+        <v>1</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>1</v>
+      </c>
+      <c r="AQ31">
+        <v>0.5</v>
+      </c>
+      <c r="AR31">
+        <v>2.38</v>
+      </c>
+      <c r="AS31">
+        <v>1.08</v>
+      </c>
+      <c r="AT31">
+        <v>3.46</v>
+      </c>
+      <c r="AU31">
+        <v>6</v>
+      </c>
+      <c r="AV31">
+        <v>5</v>
+      </c>
+      <c r="AW31">
+        <v>19</v>
+      </c>
+      <c r="AX31">
+        <v>9</v>
+      </c>
+      <c r="AY31">
+        <v>32</v>
+      </c>
+      <c r="AZ31">
+        <v>15</v>
+      </c>
+      <c r="BA31">
+        <v>9</v>
+      </c>
+      <c r="BB31">
+        <v>4</v>
+      </c>
+      <c r="BC31">
+        <v>13</v>
+      </c>
+      <c r="BD31">
+        <v>1.49</v>
+      </c>
+      <c r="BE31">
+        <v>7</v>
+      </c>
+      <c r="BF31">
+        <v>2.9</v>
+      </c>
+      <c r="BG31">
+        <v>1.24</v>
+      </c>
+      <c r="BH31">
+        <v>3.4</v>
+      </c>
+      <c r="BI31">
+        <v>1.42</v>
+      </c>
+      <c r="BJ31">
+        <v>2.55</v>
+      </c>
+      <c r="BK31">
+        <v>1.7</v>
+      </c>
+      <c r="BL31">
+        <v>1.96</v>
+      </c>
+      <c r="BM31">
+        <v>2.1</v>
+      </c>
+      <c r="BN31">
+        <v>1.6</v>
+      </c>
+      <c r="BO31">
+        <v>2.7</v>
+      </c>
+      <c r="BP31">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7818835</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45725.85416666666</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>84</v>
+      </c>
+      <c r="H32" t="s">
+        <v>85</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>2</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="O32" t="s">
+        <v>110</v>
+      </c>
+      <c r="P32" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q32">
+        <v>2.02</v>
+      </c>
+      <c r="R32">
+        <v>2.35</v>
+      </c>
+      <c r="S32">
+        <v>5.6</v>
+      </c>
+      <c r="T32">
+        <v>1.33</v>
+      </c>
+      <c r="U32">
+        <v>2.95</v>
+      </c>
+      <c r="V32">
+        <v>2.65</v>
+      </c>
+      <c r="W32">
+        <v>1.45</v>
+      </c>
+      <c r="X32">
+        <v>6.1</v>
+      </c>
+      <c r="Y32">
+        <v>1.08</v>
+      </c>
+      <c r="Z32">
+        <v>1.53</v>
+      </c>
+      <c r="AA32">
+        <v>3.8</v>
+      </c>
+      <c r="AB32">
+        <v>5.5</v>
+      </c>
+      <c r="AC32">
+        <v>1.02</v>
+      </c>
+      <c r="AD32">
+        <v>10</v>
+      </c>
+      <c r="AE32">
+        <v>1.22</v>
+      </c>
+      <c r="AF32">
+        <v>3.8</v>
+      </c>
+      <c r="AG32">
+        <v>1.85</v>
+      </c>
+      <c r="AH32">
+        <v>1.85</v>
+      </c>
+      <c r="AI32">
+        <v>1.91</v>
+      </c>
+      <c r="AJ32">
+        <v>1.77</v>
+      </c>
+      <c r="AK32">
+        <v>1.11</v>
+      </c>
+      <c r="AL32">
+        <v>1.22</v>
+      </c>
+      <c r="AM32">
+        <v>2.5</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>0.5</v>
+      </c>
+      <c r="AP32">
+        <v>1.5</v>
+      </c>
+      <c r="AQ32">
+        <v>0.33</v>
+      </c>
+      <c r="AR32">
+        <v>1.71</v>
+      </c>
+      <c r="AS32">
+        <v>1.35</v>
+      </c>
+      <c r="AT32">
+        <v>3.06</v>
+      </c>
+      <c r="AU32">
+        <v>9</v>
+      </c>
+      <c r="AV32">
+        <v>3</v>
+      </c>
+      <c r="AW32">
+        <v>15</v>
+      </c>
+      <c r="AX32">
+        <v>9</v>
+      </c>
+      <c r="AY32">
+        <v>30</v>
+      </c>
+      <c r="AZ32">
+        <v>15</v>
+      </c>
+      <c r="BA32">
+        <v>7</v>
+      </c>
+      <c r="BB32">
+        <v>2</v>
+      </c>
+      <c r="BC32">
+        <v>9</v>
+      </c>
+      <c r="BD32">
+        <v>1.38</v>
+      </c>
+      <c r="BE32">
+        <v>7</v>
+      </c>
+      <c r="BF32">
+        <v>3.4</v>
+      </c>
+      <c r="BG32">
+        <v>1.3</v>
+      </c>
+      <c r="BH32">
+        <v>3.05</v>
+      </c>
+      <c r="BI32">
+        <v>1.53</v>
+      </c>
+      <c r="BJ32">
+        <v>2.25</v>
+      </c>
+      <c r="BK32">
+        <v>1.86</v>
+      </c>
+      <c r="BL32">
+        <v>1.78</v>
+      </c>
+      <c r="BM32">
+        <v>2.33</v>
+      </c>
+      <c r="BN32">
+        <v>1.49</v>
+      </c>
+      <c r="BO32">
+        <v>3.05</v>
+      </c>
+      <c r="BP32">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="134">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -349,6 +349,12 @@
     <t>['44', '73']</t>
   </si>
   <si>
+    <t>['56']</t>
+  </si>
+  <si>
+    <t>['4', '45+3']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -407,6 +413,9 @@
   </si>
   <si>
     <t>['45+2']</t>
+  </si>
+  <si>
+    <t>['61', '66', '89']</t>
   </si>
 </sst>
 </file>
@@ -768,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP32"/>
+  <dimension ref="A1:BP34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1024,7 +1033,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1517,7 +1526,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1848,7 +1857,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2054,7 +2063,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2132,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ7">
         <v>0.33</v>
@@ -2260,7 +2269,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2672,7 +2681,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2750,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10">
         <v>0</v>
@@ -2878,7 +2887,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3290,7 +3299,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3702,7 +3711,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4114,7 +4123,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4320,7 +4329,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4398,7 +4407,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ18">
         <v>3</v>
@@ -4938,7 +4947,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5144,7 +5153,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5350,7 +5359,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5556,7 +5565,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5637,7 +5646,7 @@
         <v>3</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR24">
         <v>1.82</v>
@@ -5762,7 +5771,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6049,7 +6058,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ26">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
         <v>1.39</v>
@@ -6174,7 +6183,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6380,7 +6389,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6586,7 +6595,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6664,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ29">
         <v>0.5</v>
@@ -6792,7 +6801,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -6998,7 +7007,7 @@
         <v>109</v>
       </c>
       <c r="P31" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q31">
         <v>2.53</v>
@@ -7361,6 +7370,418 @@
       </c>
       <c r="BP32">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7818962</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45730.75</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" t="s">
+        <v>73</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>2</v>
+      </c>
+      <c r="O33" t="s">
+        <v>111</v>
+      </c>
+      <c r="P33" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q33">
+        <v>4.75</v>
+      </c>
+      <c r="R33">
+        <v>2.1</v>
+      </c>
+      <c r="S33">
+        <v>2.5</v>
+      </c>
+      <c r="T33">
+        <v>1.44</v>
+      </c>
+      <c r="U33">
+        <v>2.63</v>
+      </c>
+      <c r="V33">
+        <v>3.25</v>
+      </c>
+      <c r="W33">
+        <v>1.33</v>
+      </c>
+      <c r="X33">
+        <v>9</v>
+      </c>
+      <c r="Y33">
+        <v>1.07</v>
+      </c>
+      <c r="Z33">
+        <v>4.33</v>
+      </c>
+      <c r="AA33">
+        <v>3.4</v>
+      </c>
+      <c r="AB33">
+        <v>1.83</v>
+      </c>
+      <c r="AC33">
+        <v>1.06</v>
+      </c>
+      <c r="AD33">
+        <v>8</v>
+      </c>
+      <c r="AE33">
+        <v>1.35</v>
+      </c>
+      <c r="AF33">
+        <v>3</v>
+      </c>
+      <c r="AG33">
+        <v>2.05</v>
+      </c>
+      <c r="AH33">
+        <v>1.75</v>
+      </c>
+      <c r="AI33">
+        <v>1.83</v>
+      </c>
+      <c r="AJ33">
+        <v>1.83</v>
+      </c>
+      <c r="AK33">
+        <v>1.9</v>
+      </c>
+      <c r="AL33">
+        <v>1.3</v>
+      </c>
+      <c r="AM33">
+        <v>1.21</v>
+      </c>
+      <c r="AN33">
+        <v>3</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>2.33</v>
+      </c>
+      <c r="AQ33">
+        <v>0.5</v>
+      </c>
+      <c r="AR33">
+        <v>1.64</v>
+      </c>
+      <c r="AS33">
+        <v>1.53</v>
+      </c>
+      <c r="AT33">
+        <v>3.17</v>
+      </c>
+      <c r="AU33">
+        <v>5</v>
+      </c>
+      <c r="AV33">
+        <v>3</v>
+      </c>
+      <c r="AW33">
+        <v>6</v>
+      </c>
+      <c r="AX33">
+        <v>13</v>
+      </c>
+      <c r="AY33">
+        <v>12</v>
+      </c>
+      <c r="AZ33">
+        <v>20</v>
+      </c>
+      <c r="BA33">
+        <v>2</v>
+      </c>
+      <c r="BB33">
+        <v>4</v>
+      </c>
+      <c r="BC33">
+        <v>6</v>
+      </c>
+      <c r="BD33">
+        <v>2.65</v>
+      </c>
+      <c r="BE33">
+        <v>6.5</v>
+      </c>
+      <c r="BF33">
+        <v>1.58</v>
+      </c>
+      <c r="BG33">
+        <v>1.36</v>
+      </c>
+      <c r="BH33">
+        <v>2.75</v>
+      </c>
+      <c r="BI33">
+        <v>1.61</v>
+      </c>
+      <c r="BJ33">
+        <v>2.08</v>
+      </c>
+      <c r="BK33">
+        <v>1.98</v>
+      </c>
+      <c r="BL33">
+        <v>1.68</v>
+      </c>
+      <c r="BM33">
+        <v>2.55</v>
+      </c>
+      <c r="BN33">
+        <v>1.41</v>
+      </c>
+      <c r="BO33">
+        <v>3.35</v>
+      </c>
+      <c r="BP33">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7818846</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45730.85416666666</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34" t="s">
+        <v>82</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>2</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>3</v>
+      </c>
+      <c r="N34">
+        <v>5</v>
+      </c>
+      <c r="O34" t="s">
+        <v>112</v>
+      </c>
+      <c r="P34" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q34">
+        <v>3.4</v>
+      </c>
+      <c r="R34">
+        <v>2.1</v>
+      </c>
+      <c r="S34">
+        <v>3.2</v>
+      </c>
+      <c r="T34">
+        <v>1.4</v>
+      </c>
+      <c r="U34">
+        <v>2.75</v>
+      </c>
+      <c r="V34">
+        <v>3</v>
+      </c>
+      <c r="W34">
+        <v>1.36</v>
+      </c>
+      <c r="X34">
+        <v>8</v>
+      </c>
+      <c r="Y34">
+        <v>1.08</v>
+      </c>
+      <c r="Z34">
+        <v>2.56</v>
+      </c>
+      <c r="AA34">
+        <v>3.25</v>
+      </c>
+      <c r="AB34">
+        <v>2.43</v>
+      </c>
+      <c r="AC34">
+        <v>1.05</v>
+      </c>
+      <c r="AD34">
+        <v>8.5</v>
+      </c>
+      <c r="AE34">
+        <v>1.3</v>
+      </c>
+      <c r="AF34">
+        <v>3.3</v>
+      </c>
+      <c r="AG34">
+        <v>1.89</v>
+      </c>
+      <c r="AH34">
+        <v>1.78</v>
+      </c>
+      <c r="AI34">
+        <v>1.8</v>
+      </c>
+      <c r="AJ34">
+        <v>1.91</v>
+      </c>
+      <c r="AK34">
+        <v>1.49</v>
+      </c>
+      <c r="AL34">
+        <v>1.3</v>
+      </c>
+      <c r="AM34">
+        <v>1.46</v>
+      </c>
+      <c r="AN34">
+        <v>0.5</v>
+      </c>
+      <c r="AO34">
+        <v>0.5</v>
+      </c>
+      <c r="AP34">
+        <v>0.33</v>
+      </c>
+      <c r="AQ34">
+        <v>1.33</v>
+      </c>
+      <c r="AR34">
+        <v>1.52</v>
+      </c>
+      <c r="AS34">
+        <v>0.92</v>
+      </c>
+      <c r="AT34">
+        <v>2.44</v>
+      </c>
+      <c r="AU34">
+        <v>3</v>
+      </c>
+      <c r="AV34">
+        <v>8</v>
+      </c>
+      <c r="AW34">
+        <v>4</v>
+      </c>
+      <c r="AX34">
+        <v>9</v>
+      </c>
+      <c r="AY34">
+        <v>8</v>
+      </c>
+      <c r="AZ34">
+        <v>19</v>
+      </c>
+      <c r="BA34">
+        <v>4</v>
+      </c>
+      <c r="BB34">
+        <v>5</v>
+      </c>
+      <c r="BC34">
+        <v>9</v>
+      </c>
+      <c r="BD34">
+        <v>2.18</v>
+      </c>
+      <c r="BE34">
+        <v>6.25</v>
+      </c>
+      <c r="BF34">
+        <v>1.82</v>
+      </c>
+      <c r="BG34">
+        <v>1.43</v>
+      </c>
+      <c r="BH34">
+        <v>2.5</v>
+      </c>
+      <c r="BI34">
+        <v>1.74</v>
+      </c>
+      <c r="BJ34">
+        <v>1.91</v>
+      </c>
+      <c r="BK34">
+        <v>2.18</v>
+      </c>
+      <c r="BL34">
+        <v>1.56</v>
+      </c>
+      <c r="BM34">
+        <v>2.8</v>
+      </c>
+      <c r="BN34">
+        <v>1.34</v>
+      </c>
+      <c r="BO34">
+        <v>3.8</v>
+      </c>
+      <c r="BP34">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="134">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -777,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP34"/>
+  <dimension ref="A1:BP35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -4410,7 +4410,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ18">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR18">
         <v>1.84</v>
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ22">
         <v>1.5</v>
@@ -7782,6 +7782,212 @@
       </c>
       <c r="BP34">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7818840</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45731.85416666666</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35" t="s">
+        <v>85</v>
+      </c>
+      <c r="H35" t="s">
+        <v>80</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>86</v>
+      </c>
+      <c r="P35" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q35">
+        <v>3.1</v>
+      </c>
+      <c r="R35">
+        <v>2.05</v>
+      </c>
+      <c r="S35">
+        <v>3.75</v>
+      </c>
+      <c r="T35">
+        <v>1.44</v>
+      </c>
+      <c r="U35">
+        <v>2.63</v>
+      </c>
+      <c r="V35">
+        <v>3.4</v>
+      </c>
+      <c r="W35">
+        <v>1.3</v>
+      </c>
+      <c r="X35">
+        <v>10</v>
+      </c>
+      <c r="Y35">
+        <v>1.06</v>
+      </c>
+      <c r="Z35">
+        <v>2.28</v>
+      </c>
+      <c r="AA35">
+        <v>3.04</v>
+      </c>
+      <c r="AB35">
+        <v>2.92</v>
+      </c>
+      <c r="AC35">
+        <v>1.03</v>
+      </c>
+      <c r="AD35">
+        <v>7.4</v>
+      </c>
+      <c r="AE35">
+        <v>1.35</v>
+      </c>
+      <c r="AF35">
+        <v>2.75</v>
+      </c>
+      <c r="AG35">
+        <v>2.15</v>
+      </c>
+      <c r="AH35">
+        <v>1.67</v>
+      </c>
+      <c r="AI35">
+        <v>1.83</v>
+      </c>
+      <c r="AJ35">
+        <v>1.83</v>
+      </c>
+      <c r="AK35">
+        <v>1.36</v>
+      </c>
+      <c r="AL35">
+        <v>1.35</v>
+      </c>
+      <c r="AM35">
+        <v>1.6</v>
+      </c>
+      <c r="AN35">
+        <v>0</v>
+      </c>
+      <c r="AO35">
+        <v>3</v>
+      </c>
+      <c r="AP35">
+        <v>0.5</v>
+      </c>
+      <c r="AQ35">
+        <v>2.33</v>
+      </c>
+      <c r="AR35">
+        <v>2.29</v>
+      </c>
+      <c r="AS35">
+        <v>1.66</v>
+      </c>
+      <c r="AT35">
+        <v>3.95</v>
+      </c>
+      <c r="AU35">
+        <v>5</v>
+      </c>
+      <c r="AV35">
+        <v>7</v>
+      </c>
+      <c r="AW35">
+        <v>9</v>
+      </c>
+      <c r="AX35">
+        <v>6</v>
+      </c>
+      <c r="AY35">
+        <v>17</v>
+      </c>
+      <c r="AZ35">
+        <v>15</v>
+      </c>
+      <c r="BA35">
+        <v>7</v>
+      </c>
+      <c r="BB35">
+        <v>2</v>
+      </c>
+      <c r="BC35">
+        <v>9</v>
+      </c>
+      <c r="BD35">
+        <v>1.84</v>
+      </c>
+      <c r="BE35">
+        <v>6.4</v>
+      </c>
+      <c r="BF35">
+        <v>2.17</v>
+      </c>
+      <c r="BG35">
+        <v>1.24</v>
+      </c>
+      <c r="BH35">
+        <v>3.5</v>
+      </c>
+      <c r="BI35">
+        <v>1.46</v>
+      </c>
+      <c r="BJ35">
+        <v>2.45</v>
+      </c>
+      <c r="BK35">
+        <v>1.8</v>
+      </c>
+      <c r="BL35">
+        <v>2</v>
+      </c>
+      <c r="BM35">
+        <v>2.37</v>
+      </c>
+      <c r="BN35">
+        <v>1.49</v>
+      </c>
+      <c r="BO35">
+        <v>3.3</v>
+      </c>
+      <c r="BP35">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="135">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>['4', '45+3']</t>
+  </si>
+  <si>
+    <t>['50']</t>
   </si>
   <si>
     <t>['3', '84', '90+7']</t>
@@ -777,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP35"/>
+  <dimension ref="A1:BP36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1033,7 +1036,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1857,7 +1860,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -1935,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>1.5</v>
@@ -2063,7 +2066,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2269,7 +2272,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2681,7 +2684,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2887,7 +2890,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3299,7 +3302,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3711,7 +3714,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4123,7 +4126,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4329,7 +4332,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4613,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>0</v>
@@ -4947,7 +4950,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5153,7 +5156,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5359,7 +5362,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5565,7 +5568,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5771,7 +5774,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6183,7 +6186,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6389,7 +6392,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6595,7 +6598,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6801,7 +6804,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7007,7 +7010,7 @@
         <v>109</v>
       </c>
       <c r="P31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q31">
         <v>2.53</v>
@@ -7625,7 +7628,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -7987,6 +7990,212 @@
         <v>3.3</v>
       </c>
       <c r="BP35">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7818841</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45732.5</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36" t="s">
+        <v>113</v>
+      </c>
+      <c r="P36" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q36">
+        <v>3.5</v>
+      </c>
+      <c r="R36">
+        <v>1.91</v>
+      </c>
+      <c r="S36">
+        <v>3.6</v>
+      </c>
+      <c r="T36">
+        <v>1.57</v>
+      </c>
+      <c r="U36">
+        <v>2.25</v>
+      </c>
+      <c r="V36">
+        <v>3.75</v>
+      </c>
+      <c r="W36">
+        <v>1.25</v>
+      </c>
+      <c r="X36">
+        <v>11</v>
+      </c>
+      <c r="Y36">
+        <v>1.05</v>
+      </c>
+      <c r="Z36">
+        <v>2.5</v>
+      </c>
+      <c r="AA36">
+        <v>2.96</v>
+      </c>
+      <c r="AB36">
+        <v>2.55</v>
+      </c>
+      <c r="AC36">
+        <v>1.03</v>
+      </c>
+      <c r="AD36">
+        <v>7.6</v>
+      </c>
+      <c r="AE36">
+        <v>1.41</v>
+      </c>
+      <c r="AF36">
+        <v>2.53</v>
+      </c>
+      <c r="AG36">
+        <v>2.4</v>
+      </c>
+      <c r="AH36">
+        <v>1.53</v>
+      </c>
+      <c r="AI36">
+        <v>2.1</v>
+      </c>
+      <c r="AJ36">
+        <v>1.67</v>
+      </c>
+      <c r="AK36">
+        <v>1.46</v>
+      </c>
+      <c r="AL36">
+        <v>1.34</v>
+      </c>
+      <c r="AM36">
+        <v>1.44</v>
+      </c>
+      <c r="AN36">
+        <v>1.5</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>2</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>1.55</v>
+      </c>
+      <c r="AS36">
+        <v>1.26</v>
+      </c>
+      <c r="AT36">
+        <v>2.81</v>
+      </c>
+      <c r="AU36">
+        <v>5</v>
+      </c>
+      <c r="AV36">
+        <v>3</v>
+      </c>
+      <c r="AW36">
+        <v>9</v>
+      </c>
+      <c r="AX36">
+        <v>7</v>
+      </c>
+      <c r="AY36">
+        <v>18</v>
+      </c>
+      <c r="AZ36">
+        <v>12</v>
+      </c>
+      <c r="BA36">
+        <v>1</v>
+      </c>
+      <c r="BB36">
+        <v>9</v>
+      </c>
+      <c r="BC36">
+        <v>10</v>
+      </c>
+      <c r="BD36">
+        <v>1.98</v>
+      </c>
+      <c r="BE36">
+        <v>6.4</v>
+      </c>
+      <c r="BF36">
+        <v>1.98</v>
+      </c>
+      <c r="BG36">
+        <v>1.24</v>
+      </c>
+      <c r="BH36">
+        <v>3.5</v>
+      </c>
+      <c r="BI36">
+        <v>1.46</v>
+      </c>
+      <c r="BJ36">
+        <v>2.45</v>
+      </c>
+      <c r="BK36">
+        <v>1.88</v>
+      </c>
+      <c r="BL36">
+        <v>1.92</v>
+      </c>
+      <c r="BM36">
+        <v>2.37</v>
+      </c>
+      <c r="BN36">
+        <v>1.47</v>
+      </c>
+      <c r="BO36">
+        <v>3.3</v>
+      </c>
+      <c r="BP36">
         <v>1.27</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="136">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>['50']</t>
+  </si>
+  <si>
+    <t>['43', '86']</t>
   </si>
   <si>
     <t>['3', '84', '90+7']</t>
@@ -780,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP36"/>
+  <dimension ref="A1:BP38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1036,7 +1039,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1320,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0.5</v>
@@ -1735,7 +1738,7 @@
         <v>3</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1860,7 +1863,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2066,7 +2069,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2272,7 +2275,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2684,7 +2687,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2890,7 +2893,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3302,7 +3305,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3714,7 +3717,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3792,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ15">
         <v>0.5</v>
@@ -4126,7 +4129,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4207,7 +4210,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4332,7 +4335,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4950,7 +4953,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5028,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
         <v>1.5</v>
@@ -5156,7 +5159,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5237,7 +5240,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ22">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5362,7 +5365,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5568,7 +5571,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5646,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ24">
         <v>0.5</v>
@@ -5774,7 +5777,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -5855,7 +5858,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ25">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR25">
         <v>1.33</v>
@@ -6186,7 +6189,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6392,7 +6395,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6598,7 +6601,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6804,7 +6807,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7010,7 +7013,7 @@
         <v>109</v>
       </c>
       <c r="P31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q31">
         <v>2.53</v>
@@ -7628,7 +7631,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -7945,13 +7948,13 @@
         <v>15</v>
       </c>
       <c r="BA35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB35">
         <v>2</v>
       </c>
       <c r="BC35">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD35">
         <v>1.84</v>
@@ -8196,6 +8199,418 @@
         <v>3.3</v>
       </c>
       <c r="BP36">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7818845</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45732.75</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37" t="s">
+        <v>71</v>
+      </c>
+      <c r="H37" t="s">
+        <v>81</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>2</v>
+      </c>
+      <c r="O37" t="s">
+        <v>114</v>
+      </c>
+      <c r="P37" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q37">
+        <v>2.38</v>
+      </c>
+      <c r="R37">
+        <v>2.25</v>
+      </c>
+      <c r="S37">
+        <v>4.75</v>
+      </c>
+      <c r="T37">
+        <v>1.36</v>
+      </c>
+      <c r="U37">
+        <v>3</v>
+      </c>
+      <c r="V37">
+        <v>2.75</v>
+      </c>
+      <c r="W37">
+        <v>1.4</v>
+      </c>
+      <c r="X37">
+        <v>7</v>
+      </c>
+      <c r="Y37">
+        <v>1.1</v>
+      </c>
+      <c r="Z37">
+        <v>1.78</v>
+      </c>
+      <c r="AA37">
+        <v>3.48</v>
+      </c>
+      <c r="AB37">
+        <v>3.81</v>
+      </c>
+      <c r="AC37">
+        <v>1.02</v>
+      </c>
+      <c r="AD37">
+        <v>10</v>
+      </c>
+      <c r="AE37">
+        <v>1.21</v>
+      </c>
+      <c r="AF37">
+        <v>3.6</v>
+      </c>
+      <c r="AG37">
+        <v>1.8</v>
+      </c>
+      <c r="AH37">
+        <v>1.87</v>
+      </c>
+      <c r="AI37">
+        <v>1.8</v>
+      </c>
+      <c r="AJ37">
+        <v>1.91</v>
+      </c>
+      <c r="AK37">
+        <v>1.24</v>
+      </c>
+      <c r="AL37">
+        <v>1.26</v>
+      </c>
+      <c r="AM37">
+        <v>1.9</v>
+      </c>
+      <c r="AN37">
+        <v>1.5</v>
+      </c>
+      <c r="AO37">
+        <v>1.5</v>
+      </c>
+      <c r="AP37">
+        <v>2</v>
+      </c>
+      <c r="AQ37">
+        <v>1</v>
+      </c>
+      <c r="AR37">
+        <v>1.78</v>
+      </c>
+      <c r="AS37">
+        <v>0.85</v>
+      </c>
+      <c r="AT37">
+        <v>2.63</v>
+      </c>
+      <c r="AU37">
+        <v>7</v>
+      </c>
+      <c r="AV37">
+        <v>4</v>
+      </c>
+      <c r="AW37">
+        <v>6</v>
+      </c>
+      <c r="AX37">
+        <v>4</v>
+      </c>
+      <c r="AY37">
+        <v>14</v>
+      </c>
+      <c r="AZ37">
+        <v>9</v>
+      </c>
+      <c r="BA37">
+        <v>5</v>
+      </c>
+      <c r="BB37">
+        <v>3</v>
+      </c>
+      <c r="BC37">
+        <v>8</v>
+      </c>
+      <c r="BD37">
+        <v>1.65</v>
+      </c>
+      <c r="BE37">
+        <v>6.75</v>
+      </c>
+      <c r="BF37">
+        <v>2.48</v>
+      </c>
+      <c r="BG37">
+        <v>1.24</v>
+      </c>
+      <c r="BH37">
+        <v>3.5</v>
+      </c>
+      <c r="BI37">
+        <v>1.46</v>
+      </c>
+      <c r="BJ37">
+        <v>2.45</v>
+      </c>
+      <c r="BK37">
+        <v>1.95</v>
+      </c>
+      <c r="BL37">
+        <v>1.85</v>
+      </c>
+      <c r="BM37">
+        <v>2.37</v>
+      </c>
+      <c r="BN37">
+        <v>1.47</v>
+      </c>
+      <c r="BO37">
+        <v>3.3</v>
+      </c>
+      <c r="BP37">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7818844</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45732.75</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" t="s">
+        <v>72</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>86</v>
+      </c>
+      <c r="P38" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q38">
+        <v>2.88</v>
+      </c>
+      <c r="R38">
+        <v>2.2</v>
+      </c>
+      <c r="S38">
+        <v>3.5</v>
+      </c>
+      <c r="T38">
+        <v>1.36</v>
+      </c>
+      <c r="U38">
+        <v>3</v>
+      </c>
+      <c r="V38">
+        <v>2.75</v>
+      </c>
+      <c r="W38">
+        <v>1.4</v>
+      </c>
+      <c r="X38">
+        <v>7</v>
+      </c>
+      <c r="Y38">
+        <v>1.1</v>
+      </c>
+      <c r="Z38">
+        <v>2.22</v>
+      </c>
+      <c r="AA38">
+        <v>3.29</v>
+      </c>
+      <c r="AB38">
+        <v>2.81</v>
+      </c>
+      <c r="AC38">
+        <v>1.02</v>
+      </c>
+      <c r="AD38">
+        <v>10</v>
+      </c>
+      <c r="AE38">
+        <v>1.21</v>
+      </c>
+      <c r="AF38">
+        <v>3.6</v>
+      </c>
+      <c r="AG38">
+        <v>1.76</v>
+      </c>
+      <c r="AH38">
+        <v>1.91</v>
+      </c>
+      <c r="AI38">
+        <v>1.67</v>
+      </c>
+      <c r="AJ38">
+        <v>2.1</v>
+      </c>
+      <c r="AK38">
+        <v>1.42</v>
+      </c>
+      <c r="AL38">
+        <v>1.29</v>
+      </c>
+      <c r="AM38">
+        <v>1.57</v>
+      </c>
+      <c r="AN38">
+        <v>3</v>
+      </c>
+      <c r="AO38">
+        <v>2</v>
+      </c>
+      <c r="AP38">
+        <v>2.33</v>
+      </c>
+      <c r="AQ38">
+        <v>1.67</v>
+      </c>
+      <c r="AR38">
+        <v>2</v>
+      </c>
+      <c r="AS38">
+        <v>1.38</v>
+      </c>
+      <c r="AT38">
+        <v>3.38</v>
+      </c>
+      <c r="AU38">
+        <v>3</v>
+      </c>
+      <c r="AV38">
+        <v>6</v>
+      </c>
+      <c r="AW38">
+        <v>7</v>
+      </c>
+      <c r="AX38">
+        <v>17</v>
+      </c>
+      <c r="AY38">
+        <v>12</v>
+      </c>
+      <c r="AZ38">
+        <v>31</v>
+      </c>
+      <c r="BA38">
+        <v>2</v>
+      </c>
+      <c r="BB38">
+        <v>9</v>
+      </c>
+      <c r="BC38">
+        <v>11</v>
+      </c>
+      <c r="BD38">
+        <v>1.82</v>
+      </c>
+      <c r="BE38">
+        <v>6.4</v>
+      </c>
+      <c r="BF38">
+        <v>2.2</v>
+      </c>
+      <c r="BG38">
+        <v>1.24</v>
+      </c>
+      <c r="BH38">
+        <v>3.5</v>
+      </c>
+      <c r="BI38">
+        <v>1.46</v>
+      </c>
+      <c r="BJ38">
+        <v>2.45</v>
+      </c>
+      <c r="BK38">
+        <v>1.85</v>
+      </c>
+      <c r="BL38">
+        <v>1.95</v>
+      </c>
+      <c r="BM38">
+        <v>2.37</v>
+      </c>
+      <c r="BN38">
+        <v>1.47</v>
+      </c>
+      <c r="BO38">
+        <v>3.3</v>
+      </c>
+      <c r="BP38">
         <v>1.27</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="137">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -422,6 +422,9 @@
   </si>
   <si>
     <t>['61', '66', '89']</t>
+  </si>
+  <si>
+    <t>['45+2', '51', '56', '65']</t>
   </si>
 </sst>
 </file>
@@ -783,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP38"/>
+  <dimension ref="A1:BP39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2562,7 +2565,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -4622,7 +4625,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>1.05</v>
@@ -8612,6 +8615,212 @@
       </c>
       <c r="BP38">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7818843</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45732.85416666666</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39" t="s">
+        <v>70</v>
+      </c>
+      <c r="H39" t="s">
+        <v>79</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>4</v>
+      </c>
+      <c r="N39">
+        <v>4</v>
+      </c>
+      <c r="O39" t="s">
+        <v>86</v>
+      </c>
+      <c r="P39" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q39">
+        <v>2.75</v>
+      </c>
+      <c r="R39">
+        <v>2.3</v>
+      </c>
+      <c r="S39">
+        <v>3.5</v>
+      </c>
+      <c r="T39">
+        <v>1.33</v>
+      </c>
+      <c r="U39">
+        <v>3.25</v>
+      </c>
+      <c r="V39">
+        <v>2.5</v>
+      </c>
+      <c r="W39">
+        <v>1.5</v>
+      </c>
+      <c r="X39">
+        <v>6.5</v>
+      </c>
+      <c r="Y39">
+        <v>1.11</v>
+      </c>
+      <c r="Z39">
+        <v>2.11</v>
+      </c>
+      <c r="AA39">
+        <v>3.37</v>
+      </c>
+      <c r="AB39">
+        <v>2.96</v>
+      </c>
+      <c r="AC39">
+        <v>1.01</v>
+      </c>
+      <c r="AD39">
+        <v>11</v>
+      </c>
+      <c r="AE39">
+        <v>1.16</v>
+      </c>
+      <c r="AF39">
+        <v>4.15</v>
+      </c>
+      <c r="AG39">
+        <v>1.7</v>
+      </c>
+      <c r="AH39">
+        <v>2.1</v>
+      </c>
+      <c r="AI39">
+        <v>1.57</v>
+      </c>
+      <c r="AJ39">
+        <v>2.25</v>
+      </c>
+      <c r="AK39">
+        <v>1.37</v>
+      </c>
+      <c r="AL39">
+        <v>1.26</v>
+      </c>
+      <c r="AM39">
+        <v>1.66</v>
+      </c>
+      <c r="AN39">
+        <v>0</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>0</v>
+      </c>
+      <c r="AQ39">
+        <v>1</v>
+      </c>
+      <c r="AR39">
+        <v>1.64</v>
+      </c>
+      <c r="AS39">
+        <v>1.41</v>
+      </c>
+      <c r="AT39">
+        <v>3.05</v>
+      </c>
+      <c r="AU39">
+        <v>6</v>
+      </c>
+      <c r="AV39">
+        <v>6</v>
+      </c>
+      <c r="AW39">
+        <v>11</v>
+      </c>
+      <c r="AX39">
+        <v>5</v>
+      </c>
+      <c r="AY39">
+        <v>18</v>
+      </c>
+      <c r="AZ39">
+        <v>13</v>
+      </c>
+      <c r="BA39">
+        <v>7</v>
+      </c>
+      <c r="BB39">
+        <v>2</v>
+      </c>
+      <c r="BC39">
+        <v>9</v>
+      </c>
+      <c r="BD39">
+        <v>1.66</v>
+      </c>
+      <c r="BE39">
+        <v>6.65</v>
+      </c>
+      <c r="BF39">
+        <v>2.83</v>
+      </c>
+      <c r="BG39">
+        <v>1.2</v>
+      </c>
+      <c r="BH39">
+        <v>3.68</v>
+      </c>
+      <c r="BI39">
+        <v>1.41</v>
+      </c>
+      <c r="BJ39">
+        <v>2.6</v>
+      </c>
+      <c r="BK39">
+        <v>1.74</v>
+      </c>
+      <c r="BL39">
+        <v>1.98</v>
+      </c>
+      <c r="BM39">
+        <v>2.19</v>
+      </c>
+      <c r="BN39">
+        <v>1.57</v>
+      </c>
+      <c r="BO39">
+        <v>2.88</v>
+      </c>
+      <c r="BP39">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="143">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -367,6 +367,12 @@
     <t>['22', '87']</t>
   </si>
   <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['18']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -434,6 +440,9 @@
   </si>
   <si>
     <t>['21']</t>
+  </si>
+  <si>
+    <t>['15', '55']</t>
   </si>
 </sst>
 </file>
@@ -795,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP41"/>
+  <dimension ref="A1:BP43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1051,7 +1060,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1875,7 +1884,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2081,7 +2090,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2287,7 +2296,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2699,7 +2708,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2780,7 +2789,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -2905,7 +2914,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3192,7 +3201,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3317,7 +3326,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3729,7 +3738,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4141,7 +4150,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4347,7 +4356,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4840,7 +4849,7 @@
         <v>3</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR20">
         <v>1.33</v>
@@ -4965,7 +4974,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5171,7 +5180,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5377,7 +5386,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5583,7 +5592,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5789,7 +5798,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6201,7 +6210,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6282,7 +6291,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR27">
         <v>2.18</v>
@@ -6407,7 +6416,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6613,7 +6622,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6819,7 +6828,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7025,7 +7034,7 @@
         <v>109</v>
       </c>
       <c r="P31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q31">
         <v>2.53</v>
@@ -7643,7 +7652,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8219,7 +8228,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>7818845</v>
+        <v>7818844</v>
       </c>
       <c r="C37" t="s">
         <v>68</v>
@@ -8234,43 +8243,43 @@
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="P37" t="s">
         <v>86</v>
       </c>
       <c r="Q37">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="T37">
         <v>1.36</v>
@@ -8291,13 +8300,13 @@
         <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="AA37">
-        <v>3.48</v>
+        <v>3.29</v>
       </c>
       <c r="AB37">
-        <v>3.81</v>
+        <v>2.81</v>
       </c>
       <c r="AC37">
         <v>1.02</v>
@@ -8312,82 +8321,82 @@
         <v>3.6</v>
       </c>
       <c r="AG37">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AH37">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AI37">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ37">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AK37">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AL37">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AM37">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AN37">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO37">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AR37">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AS37">
-        <v>0.85</v>
+        <v>1.38</v>
       </c>
       <c r="AT37">
-        <v>2.63</v>
+        <v>3.38</v>
       </c>
       <c r="AU37">
+        <v>3</v>
+      </c>
+      <c r="AV37">
+        <v>6</v>
+      </c>
+      <c r="AW37">
         <v>7</v>
       </c>
-      <c r="AV37">
-        <v>4</v>
-      </c>
-      <c r="AW37">
-        <v>6</v>
-      </c>
       <c r="AX37">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AY37">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ37">
+        <v>31</v>
+      </c>
+      <c r="BA37">
+        <v>2</v>
+      </c>
+      <c r="BB37">
         <v>9</v>
       </c>
-      <c r="BA37">
-        <v>5</v>
-      </c>
-      <c r="BB37">
-        <v>3</v>
-      </c>
       <c r="BC37">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD37">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="BE37">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF37">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="BG37">
         <v>1.24</v>
@@ -8402,10 +8411,10 @@
         <v>2.45</v>
       </c>
       <c r="BK37">
+        <v>1.85</v>
+      </c>
+      <c r="BL37">
         <v>1.95</v>
-      </c>
-      <c r="BL37">
-        <v>1.85</v>
       </c>
       <c r="BM37">
         <v>2.37</v>
@@ -8425,7 +8434,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>7818844</v>
+        <v>7818845</v>
       </c>
       <c r="C38" t="s">
         <v>68</v>
@@ -8440,43 +8449,43 @@
         <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38">
         <v>0</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="P38" t="s">
         <v>86</v>
       </c>
       <c r="Q38">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="T38">
         <v>1.36</v>
@@ -8497,13 +8506,13 @@
         <v>1.1</v>
       </c>
       <c r="Z38">
-        <v>2.22</v>
+        <v>1.78</v>
       </c>
       <c r="AA38">
-        <v>3.29</v>
+        <v>3.48</v>
       </c>
       <c r="AB38">
-        <v>2.81</v>
+        <v>3.81</v>
       </c>
       <c r="AC38">
         <v>1.02</v>
@@ -8518,82 +8527,82 @@
         <v>3.6</v>
       </c>
       <c r="AG38">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH38">
+        <v>1.87</v>
+      </c>
+      <c r="AI38">
+        <v>1.8</v>
+      </c>
+      <c r="AJ38">
         <v>1.91</v>
       </c>
-      <c r="AI38">
-        <v>1.67</v>
-      </c>
-      <c r="AJ38">
-        <v>2.1</v>
-      </c>
       <c r="AK38">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AL38">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AM38">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AN38">
+        <v>1.5</v>
+      </c>
+      <c r="AO38">
+        <v>1.5</v>
+      </c>
+      <c r="AP38">
+        <v>2</v>
+      </c>
+      <c r="AQ38">
+        <v>1</v>
+      </c>
+      <c r="AR38">
+        <v>1.78</v>
+      </c>
+      <c r="AS38">
+        <v>0.85</v>
+      </c>
+      <c r="AT38">
+        <v>2.63</v>
+      </c>
+      <c r="AU38">
+        <v>7</v>
+      </c>
+      <c r="AV38">
+        <v>4</v>
+      </c>
+      <c r="AW38">
+        <v>6</v>
+      </c>
+      <c r="AX38">
+        <v>4</v>
+      </c>
+      <c r="AY38">
+        <v>14</v>
+      </c>
+      <c r="AZ38">
+        <v>9</v>
+      </c>
+      <c r="BA38">
+        <v>5</v>
+      </c>
+      <c r="BB38">
         <v>3</v>
       </c>
-      <c r="AO38">
-        <v>2</v>
-      </c>
-      <c r="AP38">
-        <v>2.33</v>
-      </c>
-      <c r="AQ38">
-        <v>1.67</v>
-      </c>
-      <c r="AR38">
-        <v>2</v>
-      </c>
-      <c r="AS38">
-        <v>1.38</v>
-      </c>
-      <c r="AT38">
-        <v>3.38</v>
-      </c>
-      <c r="AU38">
-        <v>3</v>
-      </c>
-      <c r="AV38">
-        <v>6</v>
-      </c>
-      <c r="AW38">
-        <v>7</v>
-      </c>
-      <c r="AX38">
-        <v>17</v>
-      </c>
-      <c r="AY38">
-        <v>12</v>
-      </c>
-      <c r="AZ38">
-        <v>31</v>
-      </c>
-      <c r="BA38">
-        <v>2</v>
-      </c>
-      <c r="BB38">
-        <v>9</v>
-      </c>
       <c r="BC38">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD38">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="BE38">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF38">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="BG38">
         <v>1.24</v>
@@ -8608,10 +8617,10 @@
         <v>2.45</v>
       </c>
       <c r="BK38">
+        <v>1.95</v>
+      </c>
+      <c r="BL38">
         <v>1.85</v>
-      </c>
-      <c r="BL38">
-        <v>1.95</v>
       </c>
       <c r="BM38">
         <v>2.37</v>
@@ -8673,7 +8682,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -8879,7 +8888,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9242,6 +9251,418 @@
       </c>
       <c r="BP41">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:68">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>7818848</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45744.76041666666</v>
+      </c>
+      <c r="F42">
+        <v>6</v>
+      </c>
+      <c r="G42" t="s">
+        <v>79</v>
+      </c>
+      <c r="H42" t="s">
+        <v>76</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>2</v>
+      </c>
+      <c r="N42">
+        <v>3</v>
+      </c>
+      <c r="O42" t="s">
+        <v>117</v>
+      </c>
+      <c r="P42" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q42">
+        <v>3.2</v>
+      </c>
+      <c r="R42">
+        <v>2.2</v>
+      </c>
+      <c r="S42">
+        <v>3.25</v>
+      </c>
+      <c r="T42">
+        <v>1.36</v>
+      </c>
+      <c r="U42">
+        <v>3</v>
+      </c>
+      <c r="V42">
+        <v>2.75</v>
+      </c>
+      <c r="W42">
+        <v>1.4</v>
+      </c>
+      <c r="X42">
+        <v>7</v>
+      </c>
+      <c r="Y42">
+        <v>1.1</v>
+      </c>
+      <c r="Z42">
+        <v>2.5</v>
+      </c>
+      <c r="AA42">
+        <v>3.5</v>
+      </c>
+      <c r="AB42">
+        <v>2.63</v>
+      </c>
+      <c r="AC42">
+        <v>1.04</v>
+      </c>
+      <c r="AD42">
+        <v>9</v>
+      </c>
+      <c r="AE42">
+        <v>1.25</v>
+      </c>
+      <c r="AF42">
+        <v>3.65</v>
+      </c>
+      <c r="AG42">
+        <v>1.85</v>
+      </c>
+      <c r="AH42">
+        <v>1.95</v>
+      </c>
+      <c r="AI42">
+        <v>1.67</v>
+      </c>
+      <c r="AJ42">
+        <v>2.1</v>
+      </c>
+      <c r="AK42">
+        <v>1.44</v>
+      </c>
+      <c r="AL42">
+        <v>1.29</v>
+      </c>
+      <c r="AM42">
+        <v>1.52</v>
+      </c>
+      <c r="AN42">
+        <v>0</v>
+      </c>
+      <c r="AO42">
+        <v>0.5</v>
+      </c>
+      <c r="AP42">
+        <v>0</v>
+      </c>
+      <c r="AQ42">
+        <v>1.33</v>
+      </c>
+      <c r="AR42">
+        <v>1.33</v>
+      </c>
+      <c r="AS42">
+        <v>1.27</v>
+      </c>
+      <c r="AT42">
+        <v>2.6</v>
+      </c>
+      <c r="AU42">
+        <v>8</v>
+      </c>
+      <c r="AV42">
+        <v>6</v>
+      </c>
+      <c r="AW42">
+        <v>3</v>
+      </c>
+      <c r="AX42">
+        <v>2</v>
+      </c>
+      <c r="AY42">
+        <v>11</v>
+      </c>
+      <c r="AZ42">
+        <v>8</v>
+      </c>
+      <c r="BA42">
+        <v>4</v>
+      </c>
+      <c r="BB42">
+        <v>5</v>
+      </c>
+      <c r="BC42">
+        <v>9</v>
+      </c>
+      <c r="BD42">
+        <v>1.89</v>
+      </c>
+      <c r="BE42">
+        <v>6.4</v>
+      </c>
+      <c r="BF42">
+        <v>2.1</v>
+      </c>
+      <c r="BG42">
+        <v>1.4</v>
+      </c>
+      <c r="BH42">
+        <v>2.63</v>
+      </c>
+      <c r="BI42">
+        <v>1.68</v>
+      </c>
+      <c r="BJ42">
+        <v>1.98</v>
+      </c>
+      <c r="BK42">
+        <v>2.1</v>
+      </c>
+      <c r="BL42">
+        <v>1.6</v>
+      </c>
+      <c r="BM42">
+        <v>2.7</v>
+      </c>
+      <c r="BN42">
+        <v>1.37</v>
+      </c>
+      <c r="BO42">
+        <v>3.6</v>
+      </c>
+      <c r="BP42">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:68">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7818849</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45744.85416666666</v>
+      </c>
+      <c r="F43">
+        <v>6</v>
+      </c>
+      <c r="G43" t="s">
+        <v>81</v>
+      </c>
+      <c r="H43" t="s">
+        <v>70</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
+      </c>
+      <c r="O43" t="s">
+        <v>118</v>
+      </c>
+      <c r="P43" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q43">
+        <v>2.75</v>
+      </c>
+      <c r="R43">
+        <v>2.25</v>
+      </c>
+      <c r="S43">
+        <v>3.6</v>
+      </c>
+      <c r="T43">
+        <v>1.33</v>
+      </c>
+      <c r="U43">
+        <v>3.25</v>
+      </c>
+      <c r="V43">
+        <v>2.63</v>
+      </c>
+      <c r="W43">
+        <v>1.44</v>
+      </c>
+      <c r="X43">
+        <v>6.5</v>
+      </c>
+      <c r="Y43">
+        <v>1.11</v>
+      </c>
+      <c r="Z43">
+        <v>2.15</v>
+      </c>
+      <c r="AA43">
+        <v>3.4</v>
+      </c>
+      <c r="AB43">
+        <v>3.2</v>
+      </c>
+      <c r="AC43">
+        <v>1.04</v>
+      </c>
+      <c r="AD43">
+        <v>9</v>
+      </c>
+      <c r="AE43">
+        <v>1.22</v>
+      </c>
+      <c r="AF43">
+        <v>3.95</v>
+      </c>
+      <c r="AG43">
+        <v>1.7</v>
+      </c>
+      <c r="AH43">
+        <v>2.1</v>
+      </c>
+      <c r="AI43">
+        <v>1.57</v>
+      </c>
+      <c r="AJ43">
+        <v>2.25</v>
+      </c>
+      <c r="AK43">
+        <v>1.37</v>
+      </c>
+      <c r="AL43">
+        <v>1.27</v>
+      </c>
+      <c r="AM43">
+        <v>1.65</v>
+      </c>
+      <c r="AN43">
+        <v>1</v>
+      </c>
+      <c r="AO43">
+        <v>0</v>
+      </c>
+      <c r="AP43">
+        <v>1</v>
+      </c>
+      <c r="AQ43">
+        <v>0.33</v>
+      </c>
+      <c r="AR43">
+        <v>1.91</v>
+      </c>
+      <c r="AS43">
+        <v>1.35</v>
+      </c>
+      <c r="AT43">
+        <v>3.26</v>
+      </c>
+      <c r="AU43">
+        <v>4</v>
+      </c>
+      <c r="AV43">
+        <v>6</v>
+      </c>
+      <c r="AW43">
+        <v>15</v>
+      </c>
+      <c r="AX43">
+        <v>9</v>
+      </c>
+      <c r="AY43">
+        <v>26</v>
+      </c>
+      <c r="AZ43">
+        <v>18</v>
+      </c>
+      <c r="BA43">
+        <v>4</v>
+      </c>
+      <c r="BB43">
+        <v>6</v>
+      </c>
+      <c r="BC43">
+        <v>10</v>
+      </c>
+      <c r="BD43">
+        <v>1.84</v>
+      </c>
+      <c r="BE43">
+        <v>6.4</v>
+      </c>
+      <c r="BF43">
+        <v>2.17</v>
+      </c>
+      <c r="BG43">
+        <v>1.32</v>
+      </c>
+      <c r="BH43">
+        <v>2.9</v>
+      </c>
+      <c r="BI43">
+        <v>1.56</v>
+      </c>
+      <c r="BJ43">
+        <v>2.18</v>
+      </c>
+      <c r="BK43">
+        <v>1.91</v>
+      </c>
+      <c r="BL43">
+        <v>1.74</v>
+      </c>
+      <c r="BM43">
+        <v>2.43</v>
+      </c>
+      <c r="BN43">
+        <v>1.46</v>
+      </c>
+      <c r="BO43">
+        <v>3.15</v>
+      </c>
+      <c r="BP43">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="147">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -373,6 +373,12 @@
     <t>['18']</t>
   </si>
   <si>
+    <t>['28', '44', '90+2']</t>
+  </si>
+  <si>
+    <t>['12', '66', '90+2']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -443,6 +449,12 @@
   </si>
   <si>
     <t>['15', '55']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['7']</t>
   </si>
 </sst>
 </file>
@@ -804,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP43"/>
+  <dimension ref="A1:BP45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1060,7 +1072,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1550,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
         <v>1.33</v>
@@ -1884,7 +1896,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2090,7 +2102,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2296,7 +2308,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2708,7 +2720,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2914,7 +2926,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3326,7 +3338,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3407,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3738,7 +3750,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3819,7 +3831,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4150,7 +4162,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4356,7 +4368,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4974,7 +4986,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5180,7 +5192,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5386,7 +5398,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5592,7 +5604,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5798,7 +5810,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6210,7 +6222,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6416,7 +6428,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6622,7 +6634,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6703,7 +6715,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ29">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR29">
         <v>1.73</v>
@@ -6828,7 +6840,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7034,7 +7046,7 @@
         <v>109</v>
       </c>
       <c r="P31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q31">
         <v>2.53</v>
@@ -7112,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -7652,7 +7664,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8682,7 +8694,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -8888,7 +8900,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9300,7 +9312,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9663,6 +9675,418 @@
       </c>
       <c r="BP43">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:68">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>7818852</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="2">
+        <v>45745.75</v>
+      </c>
+      <c r="F44">
+        <v>6</v>
+      </c>
+      <c r="G44" t="s">
+        <v>72</v>
+      </c>
+      <c r="H44" t="s">
+        <v>75</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>2</v>
+      </c>
+      <c r="L44">
+        <v>3</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>4</v>
+      </c>
+      <c r="O44" t="s">
+        <v>119</v>
+      </c>
+      <c r="P44" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q44">
+        <v>2.29</v>
+      </c>
+      <c r="R44">
+        <v>2.14</v>
+      </c>
+      <c r="S44">
+        <v>5.25</v>
+      </c>
+      <c r="T44">
+        <v>1.38</v>
+      </c>
+      <c r="U44">
+        <v>2.81</v>
+      </c>
+      <c r="V44">
+        <v>2.89</v>
+      </c>
+      <c r="W44">
+        <v>1.36</v>
+      </c>
+      <c r="X44">
+        <v>7.4</v>
+      </c>
+      <c r="Y44">
+        <v>1.03</v>
+      </c>
+      <c r="Z44">
+        <v>1.71</v>
+      </c>
+      <c r="AA44">
+        <v>3.42</v>
+      </c>
+      <c r="AB44">
+        <v>4.26</v>
+      </c>
+      <c r="AC44">
+        <v>1.03</v>
+      </c>
+      <c r="AD44">
+        <v>9</v>
+      </c>
+      <c r="AE44">
+        <v>1.3</v>
+      </c>
+      <c r="AF44">
+        <v>3.2</v>
+      </c>
+      <c r="AG44">
+        <v>1.95</v>
+      </c>
+      <c r="AH44">
+        <v>1.85</v>
+      </c>
+      <c r="AI44">
+        <v>1.91</v>
+      </c>
+      <c r="AJ44">
+        <v>1.8</v>
+      </c>
+      <c r="AK44">
+        <v>1.17</v>
+      </c>
+      <c r="AL44">
+        <v>1.26</v>
+      </c>
+      <c r="AM44">
+        <v>2.07</v>
+      </c>
+      <c r="AN44">
+        <v>1</v>
+      </c>
+      <c r="AO44">
+        <v>0.5</v>
+      </c>
+      <c r="AP44">
+        <v>1.67</v>
+      </c>
+      <c r="AQ44">
+        <v>0.33</v>
+      </c>
+      <c r="AR44">
+        <v>2.49</v>
+      </c>
+      <c r="AS44">
+        <v>1.19</v>
+      </c>
+      <c r="AT44">
+        <v>3.68</v>
+      </c>
+      <c r="AU44">
+        <v>7</v>
+      </c>
+      <c r="AV44">
+        <v>12</v>
+      </c>
+      <c r="AW44">
+        <v>8</v>
+      </c>
+      <c r="AX44">
+        <v>12</v>
+      </c>
+      <c r="AY44">
+        <v>18</v>
+      </c>
+      <c r="AZ44">
+        <v>28</v>
+      </c>
+      <c r="BA44">
+        <v>4</v>
+      </c>
+      <c r="BB44">
+        <v>8</v>
+      </c>
+      <c r="BC44">
+        <v>12</v>
+      </c>
+      <c r="BD44">
+        <v>1.5</v>
+      </c>
+      <c r="BE44">
+        <v>6.75</v>
+      </c>
+      <c r="BF44">
+        <v>2.8</v>
+      </c>
+      <c r="BG44">
+        <v>1.37</v>
+      </c>
+      <c r="BH44">
+        <v>2.7</v>
+      </c>
+      <c r="BI44">
+        <v>1.63</v>
+      </c>
+      <c r="BJ44">
+        <v>2.05</v>
+      </c>
+      <c r="BK44">
+        <v>2.02</v>
+      </c>
+      <c r="BL44">
+        <v>1.66</v>
+      </c>
+      <c r="BM44">
+        <v>2.63</v>
+      </c>
+      <c r="BN44">
+        <v>1.4</v>
+      </c>
+      <c r="BO44">
+        <v>3.45</v>
+      </c>
+      <c r="BP44">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:68">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>7818851</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="2">
+        <v>45746.5</v>
+      </c>
+      <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45" t="s">
+        <v>82</v>
+      </c>
+      <c r="H45" t="s">
+        <v>74</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>2</v>
+      </c>
+      <c r="L45">
+        <v>3</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>4</v>
+      </c>
+      <c r="O45" t="s">
+        <v>120</v>
+      </c>
+      <c r="P45" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q45">
+        <v>2.53</v>
+      </c>
+      <c r="R45">
+        <v>2.04</v>
+      </c>
+      <c r="S45">
+        <v>4.55</v>
+      </c>
+      <c r="T45">
+        <v>1.41</v>
+      </c>
+      <c r="U45">
+        <v>2.69</v>
+      </c>
+      <c r="V45">
+        <v>3.1</v>
+      </c>
+      <c r="W45">
+        <v>1.32</v>
+      </c>
+      <c r="X45">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y45">
+        <v>1.01</v>
+      </c>
+      <c r="Z45">
+        <v>1.91</v>
+      </c>
+      <c r="AA45">
+        <v>3.13</v>
+      </c>
+      <c r="AB45">
+        <v>3.48</v>
+      </c>
+      <c r="AC45">
+        <v>1.01</v>
+      </c>
+      <c r="AD45">
+        <v>8.6</v>
+      </c>
+      <c r="AE45">
+        <v>1.3</v>
+      </c>
+      <c r="AF45">
+        <v>2.98</v>
+      </c>
+      <c r="AG45">
+        <v>2.09</v>
+      </c>
+      <c r="AH45">
+        <v>1.71</v>
+      </c>
+      <c r="AI45">
+        <v>1.88</v>
+      </c>
+      <c r="AJ45">
+        <v>1.82</v>
+      </c>
+      <c r="AK45">
+        <v>1.24</v>
+      </c>
+      <c r="AL45">
+        <v>1.28</v>
+      </c>
+      <c r="AM45">
+        <v>1.84</v>
+      </c>
+      <c r="AN45">
+        <v>3</v>
+      </c>
+      <c r="AO45">
+        <v>0.5</v>
+      </c>
+      <c r="AP45">
+        <v>3</v>
+      </c>
+      <c r="AQ45">
+        <v>0.33</v>
+      </c>
+      <c r="AR45">
+        <v>1.28</v>
+      </c>
+      <c r="AS45">
+        <v>1.26</v>
+      </c>
+      <c r="AT45">
+        <v>2.54</v>
+      </c>
+      <c r="AU45">
+        <v>5</v>
+      </c>
+      <c r="AV45">
+        <v>5</v>
+      </c>
+      <c r="AW45">
+        <v>7</v>
+      </c>
+      <c r="AX45">
+        <v>5</v>
+      </c>
+      <c r="AY45">
+        <v>13</v>
+      </c>
+      <c r="AZ45">
+        <v>11</v>
+      </c>
+      <c r="BA45">
+        <v>2</v>
+      </c>
+      <c r="BB45">
+        <v>4</v>
+      </c>
+      <c r="BC45">
+        <v>6</v>
+      </c>
+      <c r="BD45">
+        <v>1.5</v>
+      </c>
+      <c r="BE45">
+        <v>6.75</v>
+      </c>
+      <c r="BF45">
+        <v>2.9</v>
+      </c>
+      <c r="BG45">
+        <v>1.37</v>
+      </c>
+      <c r="BH45">
+        <v>2.7</v>
+      </c>
+      <c r="BI45">
+        <v>1.64</v>
+      </c>
+      <c r="BJ45">
+        <v>2.05</v>
+      </c>
+      <c r="BK45">
+        <v>2.02</v>
+      </c>
+      <c r="BL45">
+        <v>1.65</v>
+      </c>
+      <c r="BM45">
+        <v>2.6</v>
+      </c>
+      <c r="BN45">
+        <v>1.4</v>
+      </c>
+      <c r="BO45">
+        <v>3.4</v>
+      </c>
+      <c r="BP45">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="150">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -379,6 +379,12 @@
     <t>['12', '66', '90+2']</t>
   </si>
   <si>
+    <t>['5', '90+2']</t>
+  </si>
+  <si>
+    <t>['72', '81']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -455,6 +461,9 @@
   </si>
   <si>
     <t>['7']</t>
+  </si>
+  <si>
+    <t>['90+6']</t>
   </si>
 </sst>
 </file>
@@ -816,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP45"/>
+  <dimension ref="A1:BP47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1072,7 +1081,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1359,7 +1368,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1896,7 +1905,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2102,7 +2111,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2308,7 +2317,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2389,7 +2398,7 @@
         <v>3</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2592,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -2720,7 +2729,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2926,7 +2935,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3210,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ12">
         <v>1.33</v>
@@ -3338,7 +3347,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3750,7 +3759,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4162,7 +4171,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4368,7 +4377,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4986,7 +4995,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5067,7 +5076,7 @@
         <v>2</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR21">
         <v>1.92</v>
@@ -5192,7 +5201,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5398,7 +5407,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5604,7 +5613,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5810,7 +5819,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -5888,7 +5897,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ25">
         <v>1.67</v>
@@ -6094,7 +6103,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ26">
         <v>1.33</v>
@@ -6222,7 +6231,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6428,7 +6437,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6634,7 +6643,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6840,7 +6849,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -6918,10 +6927,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR30">
         <v>1.85</v>
@@ -7046,7 +7055,7 @@
         <v>109</v>
       </c>
       <c r="P31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q31">
         <v>2.53</v>
@@ -7664,7 +7673,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8694,7 +8703,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -8900,7 +8909,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9312,7 +9321,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9724,7 +9733,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -9930,7 +9939,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q45">
         <v>2.53</v>
@@ -10087,6 +10096,418 @@
       </c>
       <c r="BP45">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:68">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>7818853</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="2">
+        <v>45746.75</v>
+      </c>
+      <c r="F46">
+        <v>6</v>
+      </c>
+      <c r="G46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H46" t="s">
+        <v>78</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>2</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+      <c r="N46">
+        <v>3</v>
+      </c>
+      <c r="O46" t="s">
+        <v>121</v>
+      </c>
+      <c r="P46" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q46">
+        <v>2.71</v>
+      </c>
+      <c r="R46">
+        <v>2</v>
+      </c>
+      <c r="S46">
+        <v>4.25</v>
+      </c>
+      <c r="T46">
+        <v>1.45</v>
+      </c>
+      <c r="U46">
+        <v>2.56</v>
+      </c>
+      <c r="V46">
+        <v>3.15</v>
+      </c>
+      <c r="W46">
+        <v>1.31</v>
+      </c>
+      <c r="X46">
+        <v>8</v>
+      </c>
+      <c r="Y46">
+        <v>1.02</v>
+      </c>
+      <c r="Z46">
+        <v>2.02</v>
+      </c>
+      <c r="AA46">
+        <v>3.14</v>
+      </c>
+      <c r="AB46">
+        <v>3.38</v>
+      </c>
+      <c r="AC46">
+        <v>1.02</v>
+      </c>
+      <c r="AD46">
+        <v>7.8</v>
+      </c>
+      <c r="AE46">
+        <v>1.34</v>
+      </c>
+      <c r="AF46">
+        <v>2.79</v>
+      </c>
+      <c r="AG46">
+        <v>2.17</v>
+      </c>
+      <c r="AH46">
+        <v>1.66</v>
+      </c>
+      <c r="AI46">
+        <v>1.9</v>
+      </c>
+      <c r="AJ46">
+        <v>1.8</v>
+      </c>
+      <c r="AK46">
+        <v>1.28</v>
+      </c>
+      <c r="AL46">
+        <v>1.31</v>
+      </c>
+      <c r="AM46">
+        <v>1.71</v>
+      </c>
+      <c r="AN46">
+        <v>2</v>
+      </c>
+      <c r="AO46">
+        <v>1.5</v>
+      </c>
+      <c r="AP46">
+        <v>2.33</v>
+      </c>
+      <c r="AQ46">
+        <v>1</v>
+      </c>
+      <c r="AR46">
+        <v>2.2</v>
+      </c>
+      <c r="AS46">
+        <v>1.15</v>
+      </c>
+      <c r="AT46">
+        <v>3.35</v>
+      </c>
+      <c r="AU46">
+        <v>5</v>
+      </c>
+      <c r="AV46">
+        <v>4</v>
+      </c>
+      <c r="AW46">
+        <v>9</v>
+      </c>
+      <c r="AX46">
+        <v>3</v>
+      </c>
+      <c r="AY46">
+        <v>15</v>
+      </c>
+      <c r="AZ46">
+        <v>8</v>
+      </c>
+      <c r="BA46">
+        <v>11</v>
+      </c>
+      <c r="BB46">
+        <v>3</v>
+      </c>
+      <c r="BC46">
+        <v>14</v>
+      </c>
+      <c r="BD46">
+        <v>1.72</v>
+      </c>
+      <c r="BE46">
+        <v>6.25</v>
+      </c>
+      <c r="BF46">
+        <v>2.4</v>
+      </c>
+      <c r="BG46">
+        <v>1.41</v>
+      </c>
+      <c r="BH46">
+        <v>2.55</v>
+      </c>
+      <c r="BI46">
+        <v>1.7</v>
+      </c>
+      <c r="BJ46">
+        <v>1.96</v>
+      </c>
+      <c r="BK46">
+        <v>2.14</v>
+      </c>
+      <c r="BL46">
+        <v>1.58</v>
+      </c>
+      <c r="BM46">
+        <v>2.8</v>
+      </c>
+      <c r="BN46">
+        <v>1.35</v>
+      </c>
+      <c r="BO46">
+        <v>3.65</v>
+      </c>
+      <c r="BP46">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:68">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>7818850</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="2">
+        <v>45746.85416666666</v>
+      </c>
+      <c r="F47">
+        <v>6</v>
+      </c>
+      <c r="G47" t="s">
+        <v>77</v>
+      </c>
+      <c r="H47" t="s">
+        <v>83</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>2</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>3</v>
+      </c>
+      <c r="O47" t="s">
+        <v>122</v>
+      </c>
+      <c r="P47" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q47">
+        <v>2.6</v>
+      </c>
+      <c r="R47">
+        <v>2.05</v>
+      </c>
+      <c r="S47">
+        <v>4.3</v>
+      </c>
+      <c r="T47">
+        <v>1.42</v>
+      </c>
+      <c r="U47">
+        <v>2.65</v>
+      </c>
+      <c r="V47">
+        <v>2.89</v>
+      </c>
+      <c r="W47">
+        <v>1.36</v>
+      </c>
+      <c r="X47">
+        <v>6.85</v>
+      </c>
+      <c r="Y47">
+        <v>1.04</v>
+      </c>
+      <c r="Z47">
+        <v>1.99</v>
+      </c>
+      <c r="AA47">
+        <v>3.25</v>
+      </c>
+      <c r="AB47">
+        <v>3.34</v>
+      </c>
+      <c r="AC47">
+        <v>1.02</v>
+      </c>
+      <c r="AD47">
+        <v>8</v>
+      </c>
+      <c r="AE47">
+        <v>1.28</v>
+      </c>
+      <c r="AF47">
+        <v>3.08</v>
+      </c>
+      <c r="AG47">
+        <v>2.04</v>
+      </c>
+      <c r="AH47">
+        <v>1.79</v>
+      </c>
+      <c r="AI47">
+        <v>1.81</v>
+      </c>
+      <c r="AJ47">
+        <v>1.89</v>
+      </c>
+      <c r="AK47">
+        <v>1.26</v>
+      </c>
+      <c r="AL47">
+        <v>1.3</v>
+      </c>
+      <c r="AM47">
+        <v>1.75</v>
+      </c>
+      <c r="AN47">
+        <v>2.33</v>
+      </c>
+      <c r="AO47">
+        <v>0.5</v>
+      </c>
+      <c r="AP47">
+        <v>2.5</v>
+      </c>
+      <c r="AQ47">
+        <v>0.33</v>
+      </c>
+      <c r="AR47">
+        <v>1.72</v>
+      </c>
+      <c r="AS47">
+        <v>1.45</v>
+      </c>
+      <c r="AT47">
+        <v>3.17</v>
+      </c>
+      <c r="AU47">
+        <v>6</v>
+      </c>
+      <c r="AV47">
+        <v>3</v>
+      </c>
+      <c r="AW47">
+        <v>4</v>
+      </c>
+      <c r="AX47">
+        <v>11</v>
+      </c>
+      <c r="AY47">
+        <v>11</v>
+      </c>
+      <c r="AZ47">
+        <v>19</v>
+      </c>
+      <c r="BA47">
+        <v>1</v>
+      </c>
+      <c r="BB47">
+        <v>4</v>
+      </c>
+      <c r="BC47">
+        <v>5</v>
+      </c>
+      <c r="BD47">
+        <v>1.72</v>
+      </c>
+      <c r="BE47">
+        <v>6.4</v>
+      </c>
+      <c r="BF47">
+        <v>2.4</v>
+      </c>
+      <c r="BG47">
+        <v>1.38</v>
+      </c>
+      <c r="BH47">
+        <v>2.65</v>
+      </c>
+      <c r="BI47">
+        <v>1.66</v>
+      </c>
+      <c r="BJ47">
+        <v>2.02</v>
+      </c>
+      <c r="BK47">
+        <v>2.07</v>
+      </c>
+      <c r="BL47">
+        <v>1.63</v>
+      </c>
+      <c r="BM47">
+        <v>2.65</v>
+      </c>
+      <c r="BN47">
+        <v>1.38</v>
+      </c>
+      <c r="BO47">
+        <v>3.55</v>
+      </c>
+      <c r="BP47">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="207">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -499,6 +499,9 @@
     <t>['62', '9001']</t>
   </si>
   <si>
+    <t>['36']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -626,6 +629,12 @@
   </si>
   <si>
     <t>['4503']</t>
+  </si>
+  <si>
+    <t>['53', '59']</t>
+  </si>
+  <si>
+    <t>['63']</t>
   </si>
 </sst>
 </file>
@@ -987,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP101"/>
+  <dimension ref="A1:BP103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1243,7 +1252,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1321,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ2">
         <v>2</v>
@@ -2067,7 +2076,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2148,7 +2157,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2273,7 +2282,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2351,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
         <v>0.67</v>
@@ -2479,7 +2488,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2891,7 +2900,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3097,7 +3106,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3921,7 +3930,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4208,7 +4217,7 @@
         <v>3</v>
       </c>
       <c r="AQ16">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR16">
         <v>3.44</v>
@@ -4333,7 +4342,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4539,7 +4548,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4617,7 +4626,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18">
         <v>2</v>
@@ -5157,7 +5166,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5363,7 +5372,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5569,7 +5578,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5650,7 +5659,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -5775,7 +5784,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5981,7 +5990,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6393,7 +6402,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6599,7 +6608,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6677,7 +6686,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ28">
         <v>2</v>
@@ -6805,7 +6814,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7011,7 +7020,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7835,7 +7844,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -7913,7 +7922,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ34">
         <v>0.71</v>
@@ -8328,7 +8337,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR36">
         <v>1.55</v>
@@ -8865,7 +8874,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -8943,7 +8952,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ39">
         <v>0.5</v>
@@ -9071,7 +9080,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9483,7 +9492,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9895,7 +9904,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10307,7 +10316,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10925,7 +10934,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11337,7 +11346,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -11624,7 +11633,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ52">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR52">
         <v>1.77</v>
@@ -12033,7 +12042,7 @@
         <v>0.33</v>
       </c>
       <c r="AP54">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ54">
         <v>0.29</v>
@@ -12573,7 +12582,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12779,7 +12788,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -12985,7 +12994,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13066,7 +13075,7 @@
         <v>1</v>
       </c>
       <c r="AQ59">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR59">
         <v>1.93</v>
@@ -14221,7 +14230,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14633,7 +14642,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14839,7 +14848,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15045,7 +15054,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15329,10 +15338,10 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15663,7 +15672,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16359,7 +16368,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ75">
         <v>0.71</v>
@@ -16487,7 +16496,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16693,7 +16702,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -16774,7 +16783,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ77">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR77">
         <v>1.74</v>
@@ -17105,7 +17114,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17517,7 +17526,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17595,7 +17604,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ81">
         <v>2</v>
@@ -17929,7 +17938,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18135,7 +18144,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18341,7 +18350,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18625,7 +18634,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ86">
         <v>0.8</v>
@@ -18753,7 +18762,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19371,7 +19380,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q90">
         <v>2.88</v>
@@ -19577,7 +19586,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19861,10 +19870,10 @@
         <v>0.4</v>
       </c>
       <c r="AP92">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ92">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR92">
         <v>1.67</v>
@@ -19989,7 +19998,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20195,7 +20204,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20401,7 +20410,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -20813,7 +20822,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21019,7 +21028,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21225,7 +21234,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21306,7 +21315,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ99">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR99">
         <v>1.47</v>
@@ -21431,7 +21440,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21794,6 +21803,418 @@
       </c>
       <c r="BP101">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7818863</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45820.875</v>
+      </c>
+      <c r="F102">
+        <v>8</v>
+      </c>
+      <c r="G102" t="s">
+        <v>70</v>
+      </c>
+      <c r="H102" t="s">
+        <v>84</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102">
+        <v>2</v>
+      </c>
+      <c r="N102">
+        <v>3</v>
+      </c>
+      <c r="O102" t="s">
+        <v>161</v>
+      </c>
+      <c r="P102" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q102">
+        <v>5.5</v>
+      </c>
+      <c r="R102">
+        <v>2.3</v>
+      </c>
+      <c r="S102">
+        <v>2.1</v>
+      </c>
+      <c r="T102">
+        <v>1.36</v>
+      </c>
+      <c r="U102">
+        <v>3</v>
+      </c>
+      <c r="V102">
+        <v>2.63</v>
+      </c>
+      <c r="W102">
+        <v>1.44</v>
+      </c>
+      <c r="X102">
+        <v>7</v>
+      </c>
+      <c r="Y102">
+        <v>1.1</v>
+      </c>
+      <c r="Z102">
+        <v>5.31</v>
+      </c>
+      <c r="AA102">
+        <v>4.05</v>
+      </c>
+      <c r="AB102">
+        <v>1.59</v>
+      </c>
+      <c r="AC102">
+        <v>1.01</v>
+      </c>
+      <c r="AD102">
+        <v>11</v>
+      </c>
+      <c r="AE102">
+        <v>1.2</v>
+      </c>
+      <c r="AF102">
+        <v>3.72</v>
+      </c>
+      <c r="AG102">
+        <v>1.85</v>
+      </c>
+      <c r="AH102">
+        <v>1.95</v>
+      </c>
+      <c r="AI102">
+        <v>1.83</v>
+      </c>
+      <c r="AJ102">
+        <v>1.83</v>
+      </c>
+      <c r="AK102">
+        <v>2.25</v>
+      </c>
+      <c r="AL102">
+        <v>1.25</v>
+      </c>
+      <c r="AM102">
+        <v>1.17</v>
+      </c>
+      <c r="AN102">
+        <v>0.6</v>
+      </c>
+      <c r="AO102">
+        <v>1.5</v>
+      </c>
+      <c r="AP102">
+        <v>0.5</v>
+      </c>
+      <c r="AQ102">
+        <v>1.8</v>
+      </c>
+      <c r="AR102">
+        <v>1.69</v>
+      </c>
+      <c r="AS102">
+        <v>1.89</v>
+      </c>
+      <c r="AT102">
+        <v>3.58</v>
+      </c>
+      <c r="AU102">
+        <v>3</v>
+      </c>
+      <c r="AV102">
+        <v>5</v>
+      </c>
+      <c r="AW102">
+        <v>8</v>
+      </c>
+      <c r="AX102">
+        <v>11</v>
+      </c>
+      <c r="AY102">
+        <v>11</v>
+      </c>
+      <c r="AZ102">
+        <v>16</v>
+      </c>
+      <c r="BA102">
+        <v>6</v>
+      </c>
+      <c r="BB102">
+        <v>6</v>
+      </c>
+      <c r="BC102">
+        <v>12</v>
+      </c>
+      <c r="BD102">
+        <v>3.15</v>
+      </c>
+      <c r="BE102">
+        <v>6.75</v>
+      </c>
+      <c r="BF102">
+        <v>1.44</v>
+      </c>
+      <c r="BG102">
+        <v>1.36</v>
+      </c>
+      <c r="BH102">
+        <v>2.75</v>
+      </c>
+      <c r="BI102">
+        <v>1.63</v>
+      </c>
+      <c r="BJ102">
+        <v>2.06</v>
+      </c>
+      <c r="BK102">
+        <v>2.06</v>
+      </c>
+      <c r="BL102">
+        <v>1.63</v>
+      </c>
+      <c r="BM102">
+        <v>2.65</v>
+      </c>
+      <c r="BN102">
+        <v>1.38</v>
+      </c>
+      <c r="BO102">
+        <v>3.45</v>
+      </c>
+      <c r="BP102">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7818914</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45821.875</v>
+      </c>
+      <c r="F103">
+        <v>14</v>
+      </c>
+      <c r="G103" t="s">
+        <v>75</v>
+      </c>
+      <c r="H103" t="s">
+        <v>77</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" t="s">
+        <v>86</v>
+      </c>
+      <c r="P103" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q103">
+        <v>2.88</v>
+      </c>
+      <c r="R103">
+        <v>2.05</v>
+      </c>
+      <c r="S103">
+        <v>4</v>
+      </c>
+      <c r="T103">
+        <v>1.44</v>
+      </c>
+      <c r="U103">
+        <v>2.63</v>
+      </c>
+      <c r="V103">
+        <v>3.25</v>
+      </c>
+      <c r="W103">
+        <v>1.33</v>
+      </c>
+      <c r="X103">
+        <v>10</v>
+      </c>
+      <c r="Y103">
+        <v>1.06</v>
+      </c>
+      <c r="Z103">
+        <v>2.12</v>
+      </c>
+      <c r="AA103">
+        <v>3.43</v>
+      </c>
+      <c r="AB103">
+        <v>3.36</v>
+      </c>
+      <c r="AC103">
+        <v>1.02</v>
+      </c>
+      <c r="AD103">
+        <v>7.8</v>
+      </c>
+      <c r="AE103">
+        <v>1.41</v>
+      </c>
+      <c r="AF103">
+        <v>2.83</v>
+      </c>
+      <c r="AG103">
+        <v>2.25</v>
+      </c>
+      <c r="AH103">
+        <v>1.62</v>
+      </c>
+      <c r="AI103">
+        <v>1.91</v>
+      </c>
+      <c r="AJ103">
+        <v>1.8</v>
+      </c>
+      <c r="AK103">
+        <v>1.3</v>
+      </c>
+      <c r="AL103">
+        <v>1.35</v>
+      </c>
+      <c r="AM103">
+        <v>1.7</v>
+      </c>
+      <c r="AN103">
+        <v>1.43</v>
+      </c>
+      <c r="AO103">
+        <v>0.83</v>
+      </c>
+      <c r="AP103">
+        <v>1.25</v>
+      </c>
+      <c r="AQ103">
+        <v>1.14</v>
+      </c>
+      <c r="AR103">
+        <v>1.48</v>
+      </c>
+      <c r="AS103">
+        <v>1.23</v>
+      </c>
+      <c r="AT103">
+        <v>2.71</v>
+      </c>
+      <c r="AU103">
+        <v>6</v>
+      </c>
+      <c r="AV103">
+        <v>3</v>
+      </c>
+      <c r="AW103">
+        <v>11</v>
+      </c>
+      <c r="AX103">
+        <v>9</v>
+      </c>
+      <c r="AY103">
+        <v>17</v>
+      </c>
+      <c r="AZ103">
+        <v>12</v>
+      </c>
+      <c r="BA103">
+        <v>6</v>
+      </c>
+      <c r="BB103">
+        <v>2</v>
+      </c>
+      <c r="BC103">
+        <v>8</v>
+      </c>
+      <c r="BD103">
+        <v>1.85</v>
+      </c>
+      <c r="BE103">
+        <v>6.75</v>
+      </c>
+      <c r="BF103">
+        <v>2.12</v>
+      </c>
+      <c r="BG103">
+        <v>1.3</v>
+      </c>
+      <c r="BH103">
+        <v>3</v>
+      </c>
+      <c r="BI103">
+        <v>1.54</v>
+      </c>
+      <c r="BJ103">
+        <v>2.23</v>
+      </c>
+      <c r="BK103">
+        <v>1.9</v>
+      </c>
+      <c r="BL103">
+        <v>1.75</v>
+      </c>
+      <c r="BM103">
+        <v>2.4</v>
+      </c>
+      <c r="BN103">
+        <v>1.47</v>
+      </c>
+      <c r="BO103">
+        <v>3.1</v>
+      </c>
+      <c r="BP103">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="208">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,6 +502,12 @@
     <t>['36']</t>
   </si>
   <si>
+    <t>['58', '65']</t>
+  </si>
+  <si>
+    <t>['53']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -611,9 +617,6 @@
   </si>
   <si>
     <t>['13', '45+6']</t>
-  </si>
-  <si>
-    <t>['53']</t>
   </si>
   <si>
     <t>['11', '57', '74']</t>
@@ -996,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP103"/>
+  <dimension ref="A1:BP105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1252,7 +1255,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1536,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ3">
         <v>1.33</v>
@@ -1745,7 +1748,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2076,7 +2079,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2282,7 +2285,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2488,7 +2491,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2566,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ8">
         <v>1.17</v>
@@ -2900,7 +2903,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3106,7 +3109,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3930,7 +3933,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4011,7 +4014,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4342,7 +4345,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4548,7 +4551,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -5038,7 +5041,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20">
         <v>0.29</v>
@@ -5166,7 +5169,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5244,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ21">
         <v>1.17</v>
@@ -5372,7 +5375,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5578,7 +5581,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5784,7 +5787,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5990,7 +5993,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6277,7 +6280,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ26">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR26">
         <v>1.39</v>
@@ -6402,7 +6405,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6608,7 +6611,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6814,7 +6817,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7020,7 +7023,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7307,7 +7310,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -7844,7 +7847,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -7925,7 +7928,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ34">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR34">
         <v>1.52</v>
@@ -8540,7 +8543,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ37">
         <v>1.17</v>
@@ -8874,7 +8877,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9080,7 +9083,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9492,7 +9495,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9904,7 +9907,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10191,7 +10194,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR45">
         <v>1.28</v>
@@ -10316,7 +10319,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10809,7 +10812,7 @@
         <v>2</v>
       </c>
       <c r="AQ48">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR48">
         <v>2</v>
@@ -10934,7 +10937,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11346,7 +11349,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -11630,7 +11633,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52">
         <v>1.14</v>
@@ -12251,7 +12254,7 @@
         <v>3</v>
       </c>
       <c r="AQ55">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
         <v>2.44</v>
@@ -12582,7 +12585,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12788,7 +12791,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -12866,7 +12869,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ58">
         <v>0.17</v>
@@ -12994,7 +12997,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13899,7 +13902,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ63">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR63">
         <v>1.77</v>
@@ -14102,7 +14105,7 @@
         <v>0.25</v>
       </c>
       <c r="AP64">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ64">
         <v>0.67</v>
@@ -14230,7 +14233,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14642,7 +14645,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14848,7 +14851,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -14926,7 +14929,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ68">
         <v>0.8</v>
@@ -15054,7 +15057,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15672,7 +15675,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16371,7 +16374,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ75">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR75">
         <v>1.77</v>
@@ -16496,7 +16499,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16577,7 +16580,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ76">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR76">
         <v>1.65</v>
@@ -16702,7 +16705,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17114,7 +17117,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17526,7 +17529,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17813,7 +17816,7 @@
         <v>3</v>
       </c>
       <c r="AQ82">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR82">
         <v>2.19</v>
@@ -17938,7 +17941,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18144,7 +18147,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18350,7 +18353,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18762,7 +18765,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19380,7 +19383,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="Q90">
         <v>2.88</v>
@@ -19586,7 +19589,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19664,10 +19667,10 @@
         <v>0.17</v>
       </c>
       <c r="AP91">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ91">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR91">
         <v>1.68</v>
@@ -19998,7 +20001,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20079,7 +20082,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ93">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR93">
         <v>1.73</v>
@@ -20204,7 +20207,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20410,7 +20413,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -20822,7 +20825,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21028,7 +21031,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21106,7 +21109,7 @@
         <v>0.83</v>
       </c>
       <c r="AP98">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ98">
         <v>0.86</v>
@@ -21234,7 +21237,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21440,7 +21443,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21852,7 +21855,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -22058,7 +22061,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22215,6 +22218,418 @@
       </c>
       <c r="BP103">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7818913</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45822.5625</v>
+      </c>
+      <c r="F104">
+        <v>14</v>
+      </c>
+      <c r="G104" t="s">
+        <v>71</v>
+      </c>
+      <c r="H104" t="s">
+        <v>74</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>3</v>
+      </c>
+      <c r="O104" t="s">
+        <v>162</v>
+      </c>
+      <c r="P104" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q104">
+        <v>2.38</v>
+      </c>
+      <c r="R104">
+        <v>2.2</v>
+      </c>
+      <c r="S104">
+        <v>5</v>
+      </c>
+      <c r="T104">
+        <v>1.4</v>
+      </c>
+      <c r="U104">
+        <v>2.75</v>
+      </c>
+      <c r="V104">
+        <v>2.75</v>
+      </c>
+      <c r="W104">
+        <v>1.4</v>
+      </c>
+      <c r="X104">
+        <v>8</v>
+      </c>
+      <c r="Y104">
+        <v>1.08</v>
+      </c>
+      <c r="Z104">
+        <v>1.75</v>
+      </c>
+      <c r="AA104">
+        <v>3.75</v>
+      </c>
+      <c r="AB104">
+        <v>4.33</v>
+      </c>
+      <c r="AC104">
+        <v>1.01</v>
+      </c>
+      <c r="AD104">
+        <v>8.4</v>
+      </c>
+      <c r="AE104">
+        <v>1.28</v>
+      </c>
+      <c r="AF104">
+        <v>3.1</v>
+      </c>
+      <c r="AG104">
+        <v>2</v>
+      </c>
+      <c r="AH104">
+        <v>1.8</v>
+      </c>
+      <c r="AI104">
+        <v>1.91</v>
+      </c>
+      <c r="AJ104">
+        <v>1.8</v>
+      </c>
+      <c r="AK104">
+        <v>1.2</v>
+      </c>
+      <c r="AL104">
+        <v>1.3</v>
+      </c>
+      <c r="AM104">
+        <v>2</v>
+      </c>
+      <c r="AN104">
+        <v>1.67</v>
+      </c>
+      <c r="AO104">
+        <v>0.57</v>
+      </c>
+      <c r="AP104">
+        <v>1.86</v>
+      </c>
+      <c r="AQ104">
+        <v>0.5</v>
+      </c>
+      <c r="AR104">
+        <v>1.8</v>
+      </c>
+      <c r="AS104">
+        <v>1.29</v>
+      </c>
+      <c r="AT104">
+        <v>3.09</v>
+      </c>
+      <c r="AU104">
+        <v>7</v>
+      </c>
+      <c r="AV104">
+        <v>4</v>
+      </c>
+      <c r="AW104">
+        <v>8</v>
+      </c>
+      <c r="AX104">
+        <v>8</v>
+      </c>
+      <c r="AY104">
+        <v>15</v>
+      </c>
+      <c r="AZ104">
+        <v>12</v>
+      </c>
+      <c r="BA104">
+        <v>7</v>
+      </c>
+      <c r="BB104">
+        <v>4</v>
+      </c>
+      <c r="BC104">
+        <v>11</v>
+      </c>
+      <c r="BD104">
+        <v>1.49</v>
+      </c>
+      <c r="BE104">
+        <v>6.5</v>
+      </c>
+      <c r="BF104">
+        <v>2.95</v>
+      </c>
+      <c r="BG104">
+        <v>1.42</v>
+      </c>
+      <c r="BH104">
+        <v>2.55</v>
+      </c>
+      <c r="BI104">
+        <v>1.71</v>
+      </c>
+      <c r="BJ104">
+        <v>1.94</v>
+      </c>
+      <c r="BK104">
+        <v>2.14</v>
+      </c>
+      <c r="BL104">
+        <v>1.58</v>
+      </c>
+      <c r="BM104">
+        <v>2.8</v>
+      </c>
+      <c r="BN104">
+        <v>1.35</v>
+      </c>
+      <c r="BO104">
+        <v>3.7</v>
+      </c>
+      <c r="BP104">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7818918</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45822.66666666666</v>
+      </c>
+      <c r="F105">
+        <v>14</v>
+      </c>
+      <c r="G105" t="s">
+        <v>76</v>
+      </c>
+      <c r="H105" t="s">
+        <v>82</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>163</v>
+      </c>
+      <c r="P105" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q105">
+        <v>2.3</v>
+      </c>
+      <c r="R105">
+        <v>2.25</v>
+      </c>
+      <c r="S105">
+        <v>5</v>
+      </c>
+      <c r="T105">
+        <v>1.36</v>
+      </c>
+      <c r="U105">
+        <v>3</v>
+      </c>
+      <c r="V105">
+        <v>2.75</v>
+      </c>
+      <c r="W105">
+        <v>1.4</v>
+      </c>
+      <c r="X105">
+        <v>7</v>
+      </c>
+      <c r="Y105">
+        <v>1.1</v>
+      </c>
+      <c r="Z105">
+        <v>1.72</v>
+      </c>
+      <c r="AA105">
+        <v>3.77</v>
+      </c>
+      <c r="AB105">
+        <v>4.63</v>
+      </c>
+      <c r="AC105">
+        <v>1</v>
+      </c>
+      <c r="AD105">
+        <v>9.1</v>
+      </c>
+      <c r="AE105">
+        <v>1.24</v>
+      </c>
+      <c r="AF105">
+        <v>3.36</v>
+      </c>
+      <c r="AG105">
+        <v>1.9</v>
+      </c>
+      <c r="AH105">
+        <v>1.9</v>
+      </c>
+      <c r="AI105">
+        <v>1.83</v>
+      </c>
+      <c r="AJ105">
+        <v>1.83</v>
+      </c>
+      <c r="AK105">
+        <v>1.18</v>
+      </c>
+      <c r="AL105">
+        <v>1.29</v>
+      </c>
+      <c r="AM105">
+        <v>2.1</v>
+      </c>
+      <c r="AN105">
+        <v>2.4</v>
+      </c>
+      <c r="AO105">
+        <v>0.71</v>
+      </c>
+      <c r="AP105">
+        <v>2.5</v>
+      </c>
+      <c r="AQ105">
+        <v>0.63</v>
+      </c>
+      <c r="AR105">
+        <v>1.74</v>
+      </c>
+      <c r="AS105">
+        <v>1.29</v>
+      </c>
+      <c r="AT105">
+        <v>3.03</v>
+      </c>
+      <c r="AU105">
+        <v>7</v>
+      </c>
+      <c r="AV105">
+        <v>4</v>
+      </c>
+      <c r="AW105">
+        <v>13</v>
+      </c>
+      <c r="AX105">
+        <v>4</v>
+      </c>
+      <c r="AY105">
+        <v>20</v>
+      </c>
+      <c r="AZ105">
+        <v>8</v>
+      </c>
+      <c r="BA105">
+        <v>4</v>
+      </c>
+      <c r="BB105">
+        <v>0</v>
+      </c>
+      <c r="BC105">
+        <v>4</v>
+      </c>
+      <c r="BD105">
+        <v>1.65</v>
+      </c>
+      <c r="BE105">
+        <v>6.4</v>
+      </c>
+      <c r="BF105">
+        <v>2.5</v>
+      </c>
+      <c r="BG105">
+        <v>1.32</v>
+      </c>
+      <c r="BH105">
+        <v>2.9</v>
+      </c>
+      <c r="BI105">
+        <v>1.55</v>
+      </c>
+      <c r="BJ105">
+        <v>2.2</v>
+      </c>
+      <c r="BK105">
+        <v>1.9</v>
+      </c>
+      <c r="BL105">
+        <v>1.74</v>
+      </c>
+      <c r="BM105">
+        <v>2.43</v>
+      </c>
+      <c r="BN105">
+        <v>1.45</v>
+      </c>
+      <c r="BO105">
+        <v>3.2</v>
+      </c>
+      <c r="BP105">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="212">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,15 @@
     <t>['53']</t>
   </si>
   <si>
+    <t>['9008']</t>
+  </si>
+  <si>
+    <t>['48']</t>
+  </si>
+  <si>
+    <t>['4503', '84']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -638,6 +647,9 @@
   </si>
   <si>
     <t>['63']</t>
+  </si>
+  <si>
+    <t>['5', '10', '54']</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP105"/>
+  <dimension ref="A1:BP108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1255,7 +1267,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1745,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ4">
         <v>0.63</v>
@@ -2079,7 +2091,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2285,7 +2297,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2491,7 +2503,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2572,7 +2584,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ8">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2778,7 +2790,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2903,7 +2915,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3109,7 +3121,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3393,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ12">
         <v>0.86</v>
@@ -3599,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
         <v>0.17</v>
@@ -3933,7 +3945,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4345,7 +4357,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4551,7 +4563,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4838,7 +4850,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR19">
         <v>1.05</v>
@@ -5169,7 +5181,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5250,7 +5262,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ21">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR21">
         <v>1.92</v>
@@ -5375,7 +5387,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5581,7 +5593,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5787,7 +5799,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5868,7 +5880,7 @@
         <v>2</v>
       </c>
       <c r="AQ24">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR24">
         <v>1.82</v>
@@ -5993,7 +6005,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6405,7 +6417,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6483,7 +6495,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>0.86</v>
@@ -6611,7 +6623,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6817,7 +6829,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7023,7 +7035,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7101,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ30">
         <v>1.33</v>
@@ -7307,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ31">
         <v>0.5</v>
@@ -7722,7 +7734,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ33">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR33">
         <v>1.64</v>
@@ -7847,7 +7859,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8877,7 +8889,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -8958,7 +8970,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ39">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR39">
         <v>1.64</v>
@@ -9083,7 +9095,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9370,7 +9382,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR41">
         <v>2.17</v>
@@ -9495,7 +9507,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9779,7 +9791,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ43">
         <v>0.29</v>
@@ -9907,7 +9919,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -9985,7 +9997,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ44">
         <v>0.17</v>
@@ -10319,7 +10331,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10397,10 +10409,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ46">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR46">
         <v>2.2</v>
@@ -10809,7 +10821,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ48">
         <v>0.63</v>
@@ -10937,7 +10949,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11349,7 +11361,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -12460,7 +12472,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ56">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -12585,7 +12597,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12791,7 +12803,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -12997,7 +13009,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13281,7 +13293,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ60">
         <v>2</v>
@@ -13487,7 +13499,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
         <v>2</v>
@@ -13696,7 +13708,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ62">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR62">
         <v>1.63</v>
@@ -13899,7 +13911,7 @@
         <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ63">
         <v>0.5</v>
@@ -14233,7 +14245,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14645,7 +14657,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14723,7 +14735,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ67">
         <v>0.29</v>
@@ -14851,7 +14863,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -14932,7 +14944,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ68">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR68">
         <v>1.78</v>
@@ -15057,7 +15069,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15138,7 +15150,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR69">
         <v>1.45</v>
@@ -15675,7 +15687,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16165,7 +16177,7 @@
         <v>1.25</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ74">
         <v>1.14</v>
@@ -16499,7 +16511,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16705,7 +16717,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -16783,7 +16795,7 @@
         <v>0.25</v>
       </c>
       <c r="AP77">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
         <v>1.14</v>
@@ -17117,7 +17129,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17198,7 +17210,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR79">
         <v>1.73</v>
@@ -17401,7 +17413,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ80">
         <v>0.86</v>
@@ -17529,7 +17541,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17941,7 +17953,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18147,7 +18159,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18353,7 +18365,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18640,7 +18652,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ86">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR86">
         <v>1.51</v>
@@ -18765,7 +18777,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19052,7 +19064,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ88">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR88">
         <v>2.08</v>
@@ -19255,7 +19267,7 @@
         <v>2.17</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ89">
         <v>2</v>
@@ -19461,7 +19473,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
         <v>1.14</v>
@@ -19589,7 +19601,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -20001,7 +20013,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20207,7 +20219,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20413,7 +20425,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -20906,7 +20918,7 @@
         <v>1</v>
       </c>
       <c r="AQ97">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR97">
         <v>1.81</v>
@@ -21031,7 +21043,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21237,7 +21249,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21443,7 +21455,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21855,7 +21867,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -22061,7 +22073,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22629,6 +22641,624 @@
         <v>3.2</v>
       </c>
       <c r="BP105">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7818917</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45823.5625</v>
+      </c>
+      <c r="F106">
+        <v>14</v>
+      </c>
+      <c r="G106" t="s">
+        <v>72</v>
+      </c>
+      <c r="H106" t="s">
+        <v>79</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>1</v>
+      </c>
+      <c r="O106" t="s">
+        <v>164</v>
+      </c>
+      <c r="P106" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q106">
+        <v>2.4</v>
+      </c>
+      <c r="R106">
+        <v>2.25</v>
+      </c>
+      <c r="S106">
+        <v>4.33</v>
+      </c>
+      <c r="T106">
+        <v>1.36</v>
+      </c>
+      <c r="U106">
+        <v>3</v>
+      </c>
+      <c r="V106">
+        <v>2.63</v>
+      </c>
+      <c r="W106">
+        <v>1.44</v>
+      </c>
+      <c r="X106">
+        <v>7</v>
+      </c>
+      <c r="Y106">
+        <v>1.1</v>
+      </c>
+      <c r="Z106">
+        <v>1.9</v>
+      </c>
+      <c r="AA106">
+        <v>3.65</v>
+      </c>
+      <c r="AB106">
+        <v>3.85</v>
+      </c>
+      <c r="AC106">
+        <v>1.05</v>
+      </c>
+      <c r="AD106">
+        <v>8.5</v>
+      </c>
+      <c r="AE106">
+        <v>1.25</v>
+      </c>
+      <c r="AF106">
+        <v>3.6</v>
+      </c>
+      <c r="AG106">
+        <v>1.85</v>
+      </c>
+      <c r="AH106">
+        <v>1.95</v>
+      </c>
+      <c r="AI106">
+        <v>1.73</v>
+      </c>
+      <c r="AJ106">
+        <v>2</v>
+      </c>
+      <c r="AK106">
+        <v>1.24</v>
+      </c>
+      <c r="AL106">
+        <v>1.27</v>
+      </c>
+      <c r="AM106">
+        <v>1.88</v>
+      </c>
+      <c r="AN106">
+        <v>2</v>
+      </c>
+      <c r="AO106">
+        <v>0.5</v>
+      </c>
+      <c r="AP106">
+        <v>2.14</v>
+      </c>
+      <c r="AQ106">
+        <v>0.43</v>
+      </c>
+      <c r="AR106">
+        <v>1.87</v>
+      </c>
+      <c r="AS106">
+        <v>1.69</v>
+      </c>
+      <c r="AT106">
+        <v>3.56</v>
+      </c>
+      <c r="AU106">
+        <v>6</v>
+      </c>
+      <c r="AV106">
+        <v>2</v>
+      </c>
+      <c r="AW106">
+        <v>15</v>
+      </c>
+      <c r="AX106">
+        <v>7</v>
+      </c>
+      <c r="AY106">
+        <v>21</v>
+      </c>
+      <c r="AZ106">
+        <v>9</v>
+      </c>
+      <c r="BA106">
+        <v>6</v>
+      </c>
+      <c r="BB106">
+        <v>9</v>
+      </c>
+      <c r="BC106">
+        <v>15</v>
+      </c>
+      <c r="BD106">
+        <v>1.6</v>
+      </c>
+      <c r="BE106">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF106">
+        <v>2.73</v>
+      </c>
+      <c r="BG106">
+        <v>1.27</v>
+      </c>
+      <c r="BH106">
+        <v>3.2</v>
+      </c>
+      <c r="BI106">
+        <v>1.34</v>
+      </c>
+      <c r="BJ106">
+        <v>2.78</v>
+      </c>
+      <c r="BK106">
+        <v>1.62</v>
+      </c>
+      <c r="BL106">
+        <v>2.1</v>
+      </c>
+      <c r="BM106">
+        <v>2.06</v>
+      </c>
+      <c r="BN106">
+        <v>1.68</v>
+      </c>
+      <c r="BO106">
+        <v>2.67</v>
+      </c>
+      <c r="BP106">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7818911</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45823.66666666666</v>
+      </c>
+      <c r="F107">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s">
+        <v>80</v>
+      </c>
+      <c r="H107" t="s">
+        <v>73</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
+      <c r="O107" t="s">
+        <v>165</v>
+      </c>
+      <c r="P107" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q107">
+        <v>3.4</v>
+      </c>
+      <c r="R107">
+        <v>2.1</v>
+      </c>
+      <c r="S107">
+        <v>3.2</v>
+      </c>
+      <c r="T107">
+        <v>1.4</v>
+      </c>
+      <c r="U107">
+        <v>2.75</v>
+      </c>
+      <c r="V107">
+        <v>3</v>
+      </c>
+      <c r="W107">
+        <v>1.36</v>
+      </c>
+      <c r="X107">
+        <v>8</v>
+      </c>
+      <c r="Y107">
+        <v>1.08</v>
+      </c>
+      <c r="Z107">
+        <v>2.72</v>
+      </c>
+      <c r="AA107">
+        <v>3.28</v>
+      </c>
+      <c r="AB107">
+        <v>2.59</v>
+      </c>
+      <c r="AC107">
+        <v>1.06</v>
+      </c>
+      <c r="AD107">
+        <v>8</v>
+      </c>
+      <c r="AE107">
+        <v>1.35</v>
+      </c>
+      <c r="AF107">
+        <v>3</v>
+      </c>
+      <c r="AG107">
+        <v>2.08</v>
+      </c>
+      <c r="AH107">
+        <v>1.73</v>
+      </c>
+      <c r="AI107">
+        <v>1.8</v>
+      </c>
+      <c r="AJ107">
+        <v>1.91</v>
+      </c>
+      <c r="AK107">
+        <v>1.49</v>
+      </c>
+      <c r="AL107">
+        <v>1.31</v>
+      </c>
+      <c r="AM107">
+        <v>1.44</v>
+      </c>
+      <c r="AN107">
+        <v>2</v>
+      </c>
+      <c r="AO107">
+        <v>0.8</v>
+      </c>
+      <c r="AP107">
+        <v>2.14</v>
+      </c>
+      <c r="AQ107">
+        <v>0.67</v>
+      </c>
+      <c r="AR107">
+        <v>1.82</v>
+      </c>
+      <c r="AS107">
+        <v>1.91</v>
+      </c>
+      <c r="AT107">
+        <v>3.73</v>
+      </c>
+      <c r="AU107">
+        <v>3</v>
+      </c>
+      <c r="AV107">
+        <v>2</v>
+      </c>
+      <c r="AW107">
+        <v>1</v>
+      </c>
+      <c r="AX107">
+        <v>13</v>
+      </c>
+      <c r="AY107">
+        <v>4</v>
+      </c>
+      <c r="AZ107">
+        <v>15</v>
+      </c>
+      <c r="BA107">
+        <v>1</v>
+      </c>
+      <c r="BB107">
+        <v>5</v>
+      </c>
+      <c r="BC107">
+        <v>6</v>
+      </c>
+      <c r="BD107">
+        <v>1.97</v>
+      </c>
+      <c r="BE107">
+        <v>6.35</v>
+      </c>
+      <c r="BF107">
+        <v>2.27</v>
+      </c>
+      <c r="BG107">
+        <v>1.24</v>
+      </c>
+      <c r="BH107">
+        <v>3.34</v>
+      </c>
+      <c r="BI107">
+        <v>1.47</v>
+      </c>
+      <c r="BJ107">
+        <v>2.42</v>
+      </c>
+      <c r="BK107">
+        <v>1.83</v>
+      </c>
+      <c r="BL107">
+        <v>1.87</v>
+      </c>
+      <c r="BM107">
+        <v>2.34</v>
+      </c>
+      <c r="BN107">
+        <v>1.5</v>
+      </c>
+      <c r="BO107">
+        <v>3.14</v>
+      </c>
+      <c r="BP107">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7818916</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45823.875</v>
+      </c>
+      <c r="F108">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s">
+        <v>81</v>
+      </c>
+      <c r="H108" t="s">
+        <v>78</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>2</v>
+      </c>
+      <c r="K108">
+        <v>3</v>
+      </c>
+      <c r="L108">
+        <v>2</v>
+      </c>
+      <c r="M108">
+        <v>3</v>
+      </c>
+      <c r="N108">
+        <v>5</v>
+      </c>
+      <c r="O108" t="s">
+        <v>166</v>
+      </c>
+      <c r="P108" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q108">
+        <v>3.1</v>
+      </c>
+      <c r="R108">
+        <v>2.05</v>
+      </c>
+      <c r="S108">
+        <v>3.75</v>
+      </c>
+      <c r="T108">
+        <v>1.44</v>
+      </c>
+      <c r="U108">
+        <v>2.63</v>
+      </c>
+      <c r="V108">
+        <v>3.25</v>
+      </c>
+      <c r="W108">
+        <v>1.33</v>
+      </c>
+      <c r="X108">
+        <v>10</v>
+      </c>
+      <c r="Y108">
+        <v>1.06</v>
+      </c>
+      <c r="Z108">
+        <v>2.33</v>
+      </c>
+      <c r="AA108">
+        <v>3.26</v>
+      </c>
+      <c r="AB108">
+        <v>3.09</v>
+      </c>
+      <c r="AC108">
+        <v>1.07</v>
+      </c>
+      <c r="AD108">
+        <v>7.5</v>
+      </c>
+      <c r="AE108">
+        <v>1.38</v>
+      </c>
+      <c r="AF108">
+        <v>2.88</v>
+      </c>
+      <c r="AG108">
+        <v>2.15</v>
+      </c>
+      <c r="AH108">
+        <v>1.67</v>
+      </c>
+      <c r="AI108">
+        <v>1.91</v>
+      </c>
+      <c r="AJ108">
+        <v>1.8</v>
+      </c>
+      <c r="AK108">
+        <v>1.39</v>
+      </c>
+      <c r="AL108">
+        <v>1.32</v>
+      </c>
+      <c r="AM108">
+        <v>1.55</v>
+      </c>
+      <c r="AN108">
+        <v>1.14</v>
+      </c>
+      <c r="AO108">
+        <v>1.17</v>
+      </c>
+      <c r="AP108">
+        <v>1</v>
+      </c>
+      <c r="AQ108">
+        <v>1.43</v>
+      </c>
+      <c r="AR108">
+        <v>1.78</v>
+      </c>
+      <c r="AS108">
+        <v>1.21</v>
+      </c>
+      <c r="AT108">
+        <v>2.99</v>
+      </c>
+      <c r="AU108">
+        <v>4</v>
+      </c>
+      <c r="AV108">
+        <v>5</v>
+      </c>
+      <c r="AW108">
+        <v>15</v>
+      </c>
+      <c r="AX108">
+        <v>5</v>
+      </c>
+      <c r="AY108">
+        <v>19</v>
+      </c>
+      <c r="AZ108">
+        <v>10</v>
+      </c>
+      <c r="BA108">
+        <v>7</v>
+      </c>
+      <c r="BB108">
+        <v>1</v>
+      </c>
+      <c r="BC108">
+        <v>8</v>
+      </c>
+      <c r="BD108">
+        <v>1.64</v>
+      </c>
+      <c r="BE108">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF108">
+        <v>2.66</v>
+      </c>
+      <c r="BG108">
+        <v>1.24</v>
+      </c>
+      <c r="BH108">
+        <v>3.34</v>
+      </c>
+      <c r="BI108">
+        <v>1.48</v>
+      </c>
+      <c r="BJ108">
+        <v>2.4</v>
+      </c>
+      <c r="BK108">
+        <v>1.91</v>
+      </c>
+      <c r="BL108">
+        <v>1.8</v>
+      </c>
+      <c r="BM108">
+        <v>2.38</v>
+      </c>
+      <c r="BN108">
+        <v>1.49</v>
+      </c>
+      <c r="BO108">
+        <v>3.14</v>
+      </c>
+      <c r="BP108">
         <v>1.27</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="213">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -651,6 +651,9 @@
   <si>
     <t>['5', '10', '54']</t>
   </si>
+  <si>
+    <t>['4502', '48']</t>
+  </si>
 </sst>
 </file>
 
@@ -1011,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP108"/>
+  <dimension ref="A1:BP109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1345,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ2">
         <v>2</v>
@@ -2378,7 +2381,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ7">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3820,7 +3823,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -6701,7 +6704,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ28">
         <v>2</v>
@@ -7528,7 +7531,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ32">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.71</v>
@@ -8967,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ39">
         <v>0.43</v>
@@ -11442,7 +11445,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.51</v>
@@ -14120,7 +14123,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ64">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>1.63</v>
@@ -16383,7 +16386,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ75">
         <v>0.63</v>
@@ -18034,7 +18037,7 @@
         <v>1</v>
       </c>
       <c r="AQ83">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR83">
         <v>1.65</v>
@@ -19885,7 +19888,7 @@
         <v>0.4</v>
       </c>
       <c r="AP92">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ92">
         <v>1.14</v>
@@ -21945,7 +21948,7 @@
         <v>1.5</v>
       </c>
       <c r="AP102">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ102">
         <v>1.8</v>
@@ -23260,6 +23263,212 @@
       </c>
       <c r="BP108">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7818915</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45824.875</v>
+      </c>
+      <c r="F109">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>70</v>
+      </c>
+      <c r="H109" t="s">
+        <v>85</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="M109">
+        <v>2</v>
+      </c>
+      <c r="N109">
+        <v>3</v>
+      </c>
+      <c r="O109" t="s">
+        <v>157</v>
+      </c>
+      <c r="P109" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q109">
+        <v>3.2</v>
+      </c>
+      <c r="R109">
+        <v>2</v>
+      </c>
+      <c r="S109">
+        <v>3.75</v>
+      </c>
+      <c r="T109">
+        <v>1.5</v>
+      </c>
+      <c r="U109">
+        <v>2.5</v>
+      </c>
+      <c r="V109">
+        <v>3.4</v>
+      </c>
+      <c r="W109">
+        <v>1.3</v>
+      </c>
+      <c r="X109">
+        <v>10</v>
+      </c>
+      <c r="Y109">
+        <v>1.06</v>
+      </c>
+      <c r="Z109">
+        <v>2.68</v>
+      </c>
+      <c r="AA109">
+        <v>3.32</v>
+      </c>
+      <c r="AB109">
+        <v>2.53</v>
+      </c>
+      <c r="AC109">
+        <v>1.04</v>
+      </c>
+      <c r="AD109">
+        <v>7.1</v>
+      </c>
+      <c r="AE109">
+        <v>1.5</v>
+      </c>
+      <c r="AF109">
+        <v>2.52</v>
+      </c>
+      <c r="AG109">
+        <v>2.35</v>
+      </c>
+      <c r="AH109">
+        <v>1.57</v>
+      </c>
+      <c r="AI109">
+        <v>2</v>
+      </c>
+      <c r="AJ109">
+        <v>1.73</v>
+      </c>
+      <c r="AK109">
+        <v>1.37</v>
+      </c>
+      <c r="AL109">
+        <v>1.36</v>
+      </c>
+      <c r="AM109">
+        <v>1.52</v>
+      </c>
+      <c r="AN109">
+        <v>0.5</v>
+      </c>
+      <c r="AO109">
+        <v>0.67</v>
+      </c>
+      <c r="AP109">
+        <v>0.43</v>
+      </c>
+      <c r="AQ109">
+        <v>1</v>
+      </c>
+      <c r="AR109">
+        <v>1.6</v>
+      </c>
+      <c r="AS109">
+        <v>1.47</v>
+      </c>
+      <c r="AT109">
+        <v>3.07</v>
+      </c>
+      <c r="AU109">
+        <v>6</v>
+      </c>
+      <c r="AV109">
+        <v>6</v>
+      </c>
+      <c r="AW109">
+        <v>7</v>
+      </c>
+      <c r="AX109">
+        <v>6</v>
+      </c>
+      <c r="AY109">
+        <v>13</v>
+      </c>
+      <c r="AZ109">
+        <v>12</v>
+      </c>
+      <c r="BA109">
+        <v>4</v>
+      </c>
+      <c r="BB109">
+        <v>4</v>
+      </c>
+      <c r="BC109">
+        <v>8</v>
+      </c>
+      <c r="BD109">
+        <v>1.8</v>
+      </c>
+      <c r="BE109">
+        <v>6.5</v>
+      </c>
+      <c r="BF109">
+        <v>2.18</v>
+      </c>
+      <c r="BG109">
+        <v>1.33</v>
+      </c>
+      <c r="BH109">
+        <v>2.88</v>
+      </c>
+      <c r="BI109">
+        <v>1.58</v>
+      </c>
+      <c r="BJ109">
+        <v>2.14</v>
+      </c>
+      <c r="BK109">
+        <v>1.96</v>
+      </c>
+      <c r="BL109">
+        <v>1.7</v>
+      </c>
+      <c r="BM109">
+        <v>2.5</v>
+      </c>
+      <c r="BN109">
+        <v>1.43</v>
+      </c>
+      <c r="BO109">
+        <v>3.3</v>
+      </c>
+      <c r="BP109">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,9 @@
     <t>['4503', '84']</t>
   </si>
   <si>
+    <t>['27', '55', '75', '85']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -1014,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1270,7 +1273,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1557,7 +1560,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ3">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2094,7 +2097,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2300,7 +2303,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2506,7 +2509,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2918,7 +2921,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3124,7 +3127,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3948,7 +3951,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4360,7 +4363,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4438,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
         <v>1.14</v>
@@ -4566,7 +4569,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -5184,7 +5187,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5390,7 +5393,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5596,7 +5599,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5802,7 +5805,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -6008,7 +6011,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6420,7 +6423,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6626,7 +6629,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6832,7 +6835,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7038,7 +7041,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7119,7 +7122,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR30">
         <v>1.85</v>
@@ -7528,7 +7531,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7862,7 +7865,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8892,7 +8895,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9098,7 +9101,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9176,7 +9179,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
         <v>2</v>
@@ -9510,7 +9513,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9922,7 +9925,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10334,7 +10337,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10621,7 +10624,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ47">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR47">
         <v>1.72</v>
@@ -10952,7 +10955,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11364,7 +11367,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -12600,7 +12603,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12681,7 +12684,7 @@
         <v>2</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR57">
         <v>1.34</v>
@@ -12806,7 +12809,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13012,7 +13015,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -14248,7 +14251,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14532,7 +14535,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>2</v>
@@ -14660,7 +14663,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14866,7 +14869,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15072,7 +15075,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15565,7 +15568,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR71">
         <v>1.48</v>
@@ -15690,7 +15693,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16514,7 +16517,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16720,7 +16723,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17132,7 +17135,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17544,7 +17547,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17956,7 +17959,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18162,7 +18165,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18240,7 +18243,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>1.17</v>
@@ -18368,7 +18371,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18780,7 +18783,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -18861,7 +18864,7 @@
         <v>1</v>
       </c>
       <c r="AQ87">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR87">
         <v>1.7</v>
@@ -19064,7 +19067,7 @@
         <v>0.6</v>
       </c>
       <c r="AP88">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
         <v>0.43</v>
@@ -19604,7 +19607,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -20016,7 +20019,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20222,7 +20225,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20428,7 +20431,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -21046,7 +21049,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21252,7 +21255,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21458,7 +21461,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21870,7 +21873,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -22076,7 +22079,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23106,7 +23109,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23312,7 +23315,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23469,6 +23472,212 @@
       </c>
       <c r="BP109">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7818912</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45825.79166666666</v>
+      </c>
+      <c r="F110">
+        <v>14</v>
+      </c>
+      <c r="G110" t="s">
+        <v>84</v>
+      </c>
+      <c r="H110" t="s">
+        <v>83</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>4</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>4</v>
+      </c>
+      <c r="O110" t="s">
+        <v>167</v>
+      </c>
+      <c r="P110" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q110">
+        <v>1.95</v>
+      </c>
+      <c r="R110">
+        <v>2.4</v>
+      </c>
+      <c r="S110">
+        <v>6.5</v>
+      </c>
+      <c r="T110">
+        <v>1.33</v>
+      </c>
+      <c r="U110">
+        <v>3.25</v>
+      </c>
+      <c r="V110">
+        <v>2.63</v>
+      </c>
+      <c r="W110">
+        <v>1.44</v>
+      </c>
+      <c r="X110">
+        <v>6.5</v>
+      </c>
+      <c r="Y110">
+        <v>1.11</v>
+      </c>
+      <c r="Z110">
+        <v>1.45</v>
+      </c>
+      <c r="AA110">
+        <v>4</v>
+      </c>
+      <c r="AB110">
+        <v>7.5</v>
+      </c>
+      <c r="AC110">
+        <v>1.01</v>
+      </c>
+      <c r="AD110">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE110">
+        <v>1.19</v>
+      </c>
+      <c r="AF110">
+        <v>3.78</v>
+      </c>
+      <c r="AG110">
+        <v>1.75</v>
+      </c>
+      <c r="AH110">
+        <v>2.05</v>
+      </c>
+      <c r="AI110">
+        <v>1.91</v>
+      </c>
+      <c r="AJ110">
+        <v>1.8</v>
+      </c>
+      <c r="AK110">
+        <v>1.08</v>
+      </c>
+      <c r="AL110">
+        <v>1.18</v>
+      </c>
+      <c r="AM110">
+        <v>2.78</v>
+      </c>
+      <c r="AN110">
+        <v>1.83</v>
+      </c>
+      <c r="AO110">
+        <v>1.33</v>
+      </c>
+      <c r="AP110">
+        <v>2</v>
+      </c>
+      <c r="AQ110">
+        <v>1.14</v>
+      </c>
+      <c r="AR110">
+        <v>2.16</v>
+      </c>
+      <c r="AS110">
+        <v>1.49</v>
+      </c>
+      <c r="AT110">
+        <v>3.65</v>
+      </c>
+      <c r="AU110">
+        <v>7</v>
+      </c>
+      <c r="AV110">
+        <v>6</v>
+      </c>
+      <c r="AW110">
+        <v>10</v>
+      </c>
+      <c r="AX110">
+        <v>7</v>
+      </c>
+      <c r="AY110">
+        <v>17</v>
+      </c>
+      <c r="AZ110">
+        <v>13</v>
+      </c>
+      <c r="BA110">
+        <v>8</v>
+      </c>
+      <c r="BB110">
+        <v>2</v>
+      </c>
+      <c r="BC110">
+        <v>10</v>
+      </c>
+      <c r="BD110">
+        <v>1.32</v>
+      </c>
+      <c r="BE110">
+        <v>7.5</v>
+      </c>
+      <c r="BF110">
+        <v>3.65</v>
+      </c>
+      <c r="BG110">
+        <v>1.28</v>
+      </c>
+      <c r="BH110">
+        <v>3.15</v>
+      </c>
+      <c r="BI110">
+        <v>1.49</v>
+      </c>
+      <c r="BJ110">
+        <v>2.35</v>
+      </c>
+      <c r="BK110">
+        <v>1.79</v>
+      </c>
+      <c r="BL110">
+        <v>1.85</v>
+      </c>
+      <c r="BM110">
+        <v>2.23</v>
+      </c>
+      <c r="BN110">
+        <v>1.54</v>
+      </c>
+      <c r="BO110">
+        <v>2.88</v>
+      </c>
+      <c r="BP110">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -517,7 +517,7 @@
     <t>['4503', '84']</t>
   </si>
   <si>
-    <t>['27', '55', '75', '85']</t>
+    <t>['55', '75', '85']</t>
   </si>
   <si>
     <t>['3', '84', '90+7']</t>
@@ -23500,22 +23500,22 @@
         <v>83</v>
       </c>
       <c r="I110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110">
         <v>0</v>
       </c>
       <c r="K110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M110">
         <v>0</v>
       </c>
       <c r="N110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O110" t="s">
         <v>167</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1017,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP110"/>
+  <dimension ref="A1:BP111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ9">
         <v>0.43</v>
@@ -3414,7 +3414,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ12">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -6089,7 +6089,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ25">
         <v>1.14</v>
@@ -6295,7 +6295,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ26">
         <v>0.63</v>
@@ -6504,7 +6504,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR27">
         <v>2.18</v>
@@ -9594,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR42">
         <v>1.33</v>
@@ -10621,7 +10621,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ47">
         <v>1.14</v>
@@ -11036,7 +11036,7 @@
         <v>2</v>
       </c>
       <c r="AQ49">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -13711,7 +13711,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ62">
         <v>1.43</v>
@@ -15980,7 +15980,7 @@
         <v>3</v>
       </c>
       <c r="AQ73">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR73">
         <v>2.35</v>
@@ -17007,7 +17007,7 @@
         <v>1.6</v>
       </c>
       <c r="AP78">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ78">
         <v>2</v>
@@ -17422,7 +17422,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ80">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR80">
         <v>2.04</v>
@@ -21130,7 +21130,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ98">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR98">
         <v>1.8</v>
@@ -21333,7 +21333,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ99">
         <v>1.8</v>
@@ -22190,13 +22190,13 @@
         <v>12</v>
       </c>
       <c r="BA103">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB103">
         <v>2</v>
       </c>
       <c r="BC103">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD103">
         <v>1.85</v>
@@ -23220,13 +23220,13 @@
         <v>10</v>
       </c>
       <c r="BA108">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB108">
         <v>1</v>
       </c>
       <c r="BC108">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD108">
         <v>1.64</v>
@@ -23678,6 +23678,212 @@
       </c>
       <c r="BP110">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7818920</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45828.77083333334</v>
+      </c>
+      <c r="F111">
+        <v>15</v>
+      </c>
+      <c r="G111" t="s">
+        <v>77</v>
+      </c>
+      <c r="H111" t="s">
+        <v>76</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111" t="s">
+        <v>86</v>
+      </c>
+      <c r="P111" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q111">
+        <v>3.3</v>
+      </c>
+      <c r="R111">
+        <v>2</v>
+      </c>
+      <c r="S111">
+        <v>3.3</v>
+      </c>
+      <c r="T111">
+        <v>1.48</v>
+      </c>
+      <c r="U111">
+        <v>2.48</v>
+      </c>
+      <c r="V111">
+        <v>3.3</v>
+      </c>
+      <c r="W111">
+        <v>1.29</v>
+      </c>
+      <c r="X111">
+        <v>8</v>
+      </c>
+      <c r="Y111">
+        <v>1.04</v>
+      </c>
+      <c r="Z111">
+        <v>2.55</v>
+      </c>
+      <c r="AA111">
+        <v>3.2</v>
+      </c>
+      <c r="AB111">
+        <v>2.65</v>
+      </c>
+      <c r="AC111">
+        <v>1.05</v>
+      </c>
+      <c r="AD111">
+        <v>8</v>
+      </c>
+      <c r="AE111">
+        <v>1.36</v>
+      </c>
+      <c r="AF111">
+        <v>2.88</v>
+      </c>
+      <c r="AG111">
+        <v>2.28</v>
+      </c>
+      <c r="AH111">
+        <v>1.58</v>
+      </c>
+      <c r="AI111">
+        <v>1.91</v>
+      </c>
+      <c r="AJ111">
+        <v>1.77</v>
+      </c>
+      <c r="AK111">
+        <v>1.46</v>
+      </c>
+      <c r="AL111">
+        <v>1.33</v>
+      </c>
+      <c r="AM111">
+        <v>1.49</v>
+      </c>
+      <c r="AN111">
+        <v>1.86</v>
+      </c>
+      <c r="AO111">
+        <v>0.86</v>
+      </c>
+      <c r="AP111">
+        <v>1.63</v>
+      </c>
+      <c r="AQ111">
+        <v>1.13</v>
+      </c>
+      <c r="AR111">
+        <v>1.47</v>
+      </c>
+      <c r="AS111">
+        <v>1.22</v>
+      </c>
+      <c r="AT111">
+        <v>2.69</v>
+      </c>
+      <c r="AU111">
+        <v>3</v>
+      </c>
+      <c r="AV111">
+        <v>6</v>
+      </c>
+      <c r="AW111">
+        <v>5</v>
+      </c>
+      <c r="AX111">
+        <v>7</v>
+      </c>
+      <c r="AY111">
+        <v>8</v>
+      </c>
+      <c r="AZ111">
+        <v>13</v>
+      </c>
+      <c r="BA111">
+        <v>7</v>
+      </c>
+      <c r="BB111">
+        <v>5</v>
+      </c>
+      <c r="BC111">
+        <v>12</v>
+      </c>
+      <c r="BD111">
+        <v>1.82</v>
+      </c>
+      <c r="BE111">
+        <v>6.4</v>
+      </c>
+      <c r="BF111">
+        <v>2.18</v>
+      </c>
+      <c r="BG111">
+        <v>1.38</v>
+      </c>
+      <c r="BH111">
+        <v>2.65</v>
+      </c>
+      <c r="BI111">
+        <v>1.65</v>
+      </c>
+      <c r="BJ111">
+        <v>2.02</v>
+      </c>
+      <c r="BK111">
+        <v>2.06</v>
+      </c>
+      <c r="BL111">
+        <v>1.63</v>
+      </c>
+      <c r="BM111">
+        <v>2.65</v>
+      </c>
+      <c r="BN111">
+        <v>1.38</v>
+      </c>
+      <c r="BO111">
+        <v>3.5</v>
+      </c>
+      <c r="BP111">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="219">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -520,6 +520,12 @@
     <t>['55', '75', '85']</t>
   </si>
   <si>
+    <t>['58', '70', '9004']</t>
+  </si>
+  <si>
+    <t>['50', '64']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -656,6 +662,15 @@
   </si>
   <si>
     <t>['4502', '48']</t>
+  </si>
+  <si>
+    <t>['42', '87']</t>
+  </si>
+  <si>
+    <t>['24']</t>
+  </si>
+  <si>
+    <t>['29', '45']</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP111"/>
+  <dimension ref="A1:BP114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1273,7 +1288,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1354,7 +1369,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2097,7 +2112,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2303,7 +2318,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2509,7 +2524,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2921,7 +2936,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3002,7 +3017,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ10">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3127,7 +3142,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3205,10 +3220,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3823,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -3951,7 +3966,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4363,7 +4378,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4569,7 +4584,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4650,7 +4665,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR18">
         <v>1.84</v>
@@ -5062,7 +5077,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ20">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR20">
         <v>1.33</v>
@@ -5187,7 +5202,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5393,7 +5408,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5599,7 +5614,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5677,7 +5692,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ23">
         <v>1.8</v>
@@ -5805,7 +5820,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -6011,7 +6026,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6423,7 +6438,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6629,7 +6644,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6710,7 +6725,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR28">
         <v>1.27</v>
@@ -6835,7 +6850,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7041,7 +7056,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7865,7 +7880,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8152,7 +8167,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR35">
         <v>2.29</v>
@@ -8895,7 +8910,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9101,7 +9116,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9182,7 +9197,7 @@
         <v>2</v>
       </c>
       <c r="AQ40">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR40">
         <v>2.12</v>
@@ -9513,7 +9528,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9591,7 +9606,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ42">
         <v>1.13</v>
@@ -9800,7 +9815,7 @@
         <v>1</v>
       </c>
       <c r="AQ43">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR43">
         <v>1.91</v>
@@ -9925,7 +9940,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10209,7 +10224,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ45">
         <v>0.5</v>
@@ -10337,7 +10352,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10955,7 +10970,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11367,7 +11382,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -11857,7 +11872,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ53">
         <v>1.17</v>
@@ -12066,7 +12081,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ54">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR54">
         <v>1.28</v>
@@ -12603,7 +12618,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12681,7 +12696,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ57">
         <v>1.14</v>
@@ -12809,7 +12824,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13015,7 +13030,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13302,7 +13317,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ60">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR60">
         <v>2.23</v>
@@ -13508,7 +13523,7 @@
         <v>1</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR61">
         <v>1.9</v>
@@ -14251,7 +14266,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14538,7 +14553,7 @@
         <v>2</v>
       </c>
       <c r="AQ66">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR66">
         <v>2.18</v>
@@ -14663,7 +14678,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14744,7 +14759,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ67">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR67">
         <v>2.15</v>
@@ -14869,7 +14884,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15075,7 +15090,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15153,7 +15168,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ69">
         <v>0.43</v>
@@ -15565,7 +15580,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ71">
         <v>1.14</v>
@@ -15693,7 +15708,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15774,7 +15789,7 @@
         <v>1</v>
       </c>
       <c r="AQ72">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR72">
         <v>1.83</v>
@@ -16517,7 +16532,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16723,7 +16738,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17010,7 +17025,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ78">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR78">
         <v>1.51</v>
@@ -17135,7 +17150,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17547,7 +17562,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17628,7 +17643,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ81">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17959,7 +17974,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18037,7 +18052,7 @@
         <v>0.2</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18165,7 +18180,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18371,7 +18386,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18452,7 +18467,7 @@
         <v>2</v>
       </c>
       <c r="AQ85">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR85">
         <v>1.47</v>
@@ -18783,7 +18798,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19276,7 +19291,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ89">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR89">
         <v>1.86</v>
@@ -19607,7 +19622,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -20019,7 +20034,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20225,7 +20240,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20303,7 +20318,7 @@
         <v>0.8</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ94">
         <v>1.17</v>
@@ -20431,7 +20446,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -20512,7 +20527,7 @@
         <v>2</v>
       </c>
       <c r="AQ95">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR95">
         <v>1.68</v>
@@ -21049,7 +21064,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21255,7 +21270,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21461,7 +21476,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21542,7 +21557,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR100">
         <v>1.73</v>
@@ -21745,7 +21760,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ101">
         <v>0.17</v>
@@ -21873,7 +21888,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -22079,7 +22094,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23109,7 +23124,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23315,7 +23330,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23884,6 +23899,624 @@
       </c>
       <c r="BP111">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7818922</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45829.5625</v>
+      </c>
+      <c r="F112">
+        <v>15</v>
+      </c>
+      <c r="G112" t="s">
+        <v>79</v>
+      </c>
+      <c r="H112" t="s">
+        <v>80</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>1</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>2</v>
+      </c>
+      <c r="N112">
+        <v>2</v>
+      </c>
+      <c r="O112" t="s">
+        <v>86</v>
+      </c>
+      <c r="P112" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q112">
+        <v>3.45</v>
+      </c>
+      <c r="R112">
+        <v>2.18</v>
+      </c>
+      <c r="S112">
+        <v>2.75</v>
+      </c>
+      <c r="T112">
+        <v>1.36</v>
+      </c>
+      <c r="U112">
+        <v>2.95</v>
+      </c>
+      <c r="V112">
+        <v>2.7</v>
+      </c>
+      <c r="W112">
+        <v>1.43</v>
+      </c>
+      <c r="X112">
+        <v>6.4</v>
+      </c>
+      <c r="Y112">
+        <v>1.08</v>
+      </c>
+      <c r="Z112">
+        <v>2.95</v>
+      </c>
+      <c r="AA112">
+        <v>3.45</v>
+      </c>
+      <c r="AB112">
+        <v>2.2</v>
+      </c>
+      <c r="AC112">
+        <v>1.01</v>
+      </c>
+      <c r="AD112">
+        <v>8.4</v>
+      </c>
+      <c r="AE112">
+        <v>1.28</v>
+      </c>
+      <c r="AF112">
+        <v>3.1</v>
+      </c>
+      <c r="AG112">
+        <v>1.86</v>
+      </c>
+      <c r="AH112">
+        <v>1.86</v>
+      </c>
+      <c r="AI112">
+        <v>1.68</v>
+      </c>
+      <c r="AJ112">
+        <v>2.04</v>
+      </c>
+      <c r="AK112">
+        <v>1.63</v>
+      </c>
+      <c r="AL112">
+        <v>1.29</v>
+      </c>
+      <c r="AM112">
+        <v>1.38</v>
+      </c>
+      <c r="AN112">
+        <v>1</v>
+      </c>
+      <c r="AO112">
+        <v>2</v>
+      </c>
+      <c r="AP112">
+        <v>0.86</v>
+      </c>
+      <c r="AQ112">
+        <v>2.13</v>
+      </c>
+      <c r="AR112">
+        <v>1.64</v>
+      </c>
+      <c r="AS112">
+        <v>1.39</v>
+      </c>
+      <c r="AT112">
+        <v>3.03</v>
+      </c>
+      <c r="AU112">
+        <v>2</v>
+      </c>
+      <c r="AV112">
+        <v>10</v>
+      </c>
+      <c r="AW112">
+        <v>4</v>
+      </c>
+      <c r="AX112">
+        <v>11</v>
+      </c>
+      <c r="AY112">
+        <v>6</v>
+      </c>
+      <c r="AZ112">
+        <v>21</v>
+      </c>
+      <c r="BA112">
+        <v>2</v>
+      </c>
+      <c r="BB112">
+        <v>9</v>
+      </c>
+      <c r="BC112">
+        <v>11</v>
+      </c>
+      <c r="BD112">
+        <v>1.95</v>
+      </c>
+      <c r="BE112">
+        <v>6.75</v>
+      </c>
+      <c r="BF112">
+        <v>2.02</v>
+      </c>
+      <c r="BG112">
+        <v>1.18</v>
+      </c>
+      <c r="BH112">
+        <v>3.9</v>
+      </c>
+      <c r="BI112">
+        <v>1.34</v>
+      </c>
+      <c r="BJ112">
+        <v>2.8</v>
+      </c>
+      <c r="BK112">
+        <v>1.57</v>
+      </c>
+      <c r="BL112">
+        <v>2.17</v>
+      </c>
+      <c r="BM112">
+        <v>1.91</v>
+      </c>
+      <c r="BN112">
+        <v>1.74</v>
+      </c>
+      <c r="BO112">
+        <v>2.38</v>
+      </c>
+      <c r="BP112">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7818921</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45829.66666666666</v>
+      </c>
+      <c r="F113">
+        <v>15</v>
+      </c>
+      <c r="G113" t="s">
+        <v>73</v>
+      </c>
+      <c r="H113" t="s">
+        <v>70</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>3</v>
+      </c>
+      <c r="M113">
+        <v>1</v>
+      </c>
+      <c r="N113">
+        <v>4</v>
+      </c>
+      <c r="O113" t="s">
+        <v>168</v>
+      </c>
+      <c r="P113" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q113">
+        <v>1.76</v>
+      </c>
+      <c r="R113">
+        <v>2.55</v>
+      </c>
+      <c r="S113">
+        <v>6.75</v>
+      </c>
+      <c r="T113">
+        <v>1.27</v>
+      </c>
+      <c r="U113">
+        <v>3.4</v>
+      </c>
+      <c r="V113">
+        <v>2.3</v>
+      </c>
+      <c r="W113">
+        <v>1.55</v>
+      </c>
+      <c r="X113">
+        <v>5.1</v>
+      </c>
+      <c r="Y113">
+        <v>1.13</v>
+      </c>
+      <c r="Z113">
+        <v>1.29</v>
+      </c>
+      <c r="AA113">
+        <v>4.8</v>
+      </c>
+      <c r="AB113">
+        <v>10</v>
+      </c>
+      <c r="AC113">
+        <v>1.01</v>
+      </c>
+      <c r="AD113">
+        <v>17</v>
+      </c>
+      <c r="AE113">
+        <v>1.1</v>
+      </c>
+      <c r="AF113">
+        <v>5.1</v>
+      </c>
+      <c r="AG113">
+        <v>1.57</v>
+      </c>
+      <c r="AH113">
+        <v>2.28</v>
+      </c>
+      <c r="AI113">
+        <v>1.89</v>
+      </c>
+      <c r="AJ113">
+        <v>1.8</v>
+      </c>
+      <c r="AK113">
+        <v>1.05</v>
+      </c>
+      <c r="AL113">
+        <v>1.18</v>
+      </c>
+      <c r="AM113">
+        <v>3.2</v>
+      </c>
+      <c r="AN113">
+        <v>3</v>
+      </c>
+      <c r="AO113">
+        <v>0.29</v>
+      </c>
+      <c r="AP113">
+        <v>3</v>
+      </c>
+      <c r="AQ113">
+        <v>0.25</v>
+      </c>
+      <c r="AR113">
+        <v>2.13</v>
+      </c>
+      <c r="AS113">
+        <v>1.31</v>
+      </c>
+      <c r="AT113">
+        <v>3.44</v>
+      </c>
+      <c r="AU113">
+        <v>10</v>
+      </c>
+      <c r="AV113">
+        <v>5</v>
+      </c>
+      <c r="AW113">
+        <v>9</v>
+      </c>
+      <c r="AX113">
+        <v>3</v>
+      </c>
+      <c r="AY113">
+        <v>19</v>
+      </c>
+      <c r="AZ113">
+        <v>8</v>
+      </c>
+      <c r="BA113">
+        <v>7</v>
+      </c>
+      <c r="BB113">
+        <v>1</v>
+      </c>
+      <c r="BC113">
+        <v>8</v>
+      </c>
+      <c r="BD113">
+        <v>1.26</v>
+      </c>
+      <c r="BE113">
+        <v>8</v>
+      </c>
+      <c r="BF113">
+        <v>4.1</v>
+      </c>
+      <c r="BG113">
+        <v>1.27</v>
+      </c>
+      <c r="BH113">
+        <v>3.2</v>
+      </c>
+      <c r="BI113">
+        <v>1.47</v>
+      </c>
+      <c r="BJ113">
+        <v>2.38</v>
+      </c>
+      <c r="BK113">
+        <v>1.78</v>
+      </c>
+      <c r="BL113">
+        <v>1.87</v>
+      </c>
+      <c r="BM113">
+        <v>2.2</v>
+      </c>
+      <c r="BN113">
+        <v>1.55</v>
+      </c>
+      <c r="BO113">
+        <v>2.8</v>
+      </c>
+      <c r="BP113">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7818924</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45829.77083333334</v>
+      </c>
+      <c r="F114">
+        <v>15</v>
+      </c>
+      <c r="G114" t="s">
+        <v>82</v>
+      </c>
+      <c r="H114" t="s">
+        <v>71</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>2</v>
+      </c>
+      <c r="K114">
+        <v>2</v>
+      </c>
+      <c r="L114">
+        <v>2</v>
+      </c>
+      <c r="M114">
+        <v>2</v>
+      </c>
+      <c r="N114">
+        <v>4</v>
+      </c>
+      <c r="O114" t="s">
+        <v>169</v>
+      </c>
+      <c r="P114" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q114">
+        <v>3.3</v>
+      </c>
+      <c r="R114">
+        <v>2.17</v>
+      </c>
+      <c r="S114">
+        <v>2.9</v>
+      </c>
+      <c r="T114">
+        <v>1.38</v>
+      </c>
+      <c r="U114">
+        <v>2.88</v>
+      </c>
+      <c r="V114">
+        <v>2.8</v>
+      </c>
+      <c r="W114">
+        <v>1.38</v>
+      </c>
+      <c r="X114">
+        <v>6.75</v>
+      </c>
+      <c r="Y114">
+        <v>1.07</v>
+      </c>
+      <c r="Z114">
+        <v>2.75</v>
+      </c>
+      <c r="AA114">
+        <v>3.25</v>
+      </c>
+      <c r="AB114">
+        <v>2.3</v>
+      </c>
+      <c r="AC114">
+        <v>1.03</v>
+      </c>
+      <c r="AD114">
+        <v>9</v>
+      </c>
+      <c r="AE114">
+        <v>1.29</v>
+      </c>
+      <c r="AF114">
+        <v>3.3</v>
+      </c>
+      <c r="AG114">
+        <v>1.94</v>
+      </c>
+      <c r="AH114">
+        <v>1.79</v>
+      </c>
+      <c r="AI114">
+        <v>1.73</v>
+      </c>
+      <c r="AJ114">
+        <v>1.97</v>
+      </c>
+      <c r="AK114">
+        <v>1.55</v>
+      </c>
+      <c r="AL114">
+        <v>1.29</v>
+      </c>
+      <c r="AM114">
+        <v>1.44</v>
+      </c>
+      <c r="AN114">
+        <v>2</v>
+      </c>
+      <c r="AO114">
+        <v>2</v>
+      </c>
+      <c r="AP114">
+        <v>1.86</v>
+      </c>
+      <c r="AQ114">
+        <v>1.88</v>
+      </c>
+      <c r="AR114">
+        <v>1.4</v>
+      </c>
+      <c r="AS114">
+        <v>1.53</v>
+      </c>
+      <c r="AT114">
+        <v>2.93</v>
+      </c>
+      <c r="AU114">
+        <v>10</v>
+      </c>
+      <c r="AV114">
+        <v>5</v>
+      </c>
+      <c r="AW114">
+        <v>11</v>
+      </c>
+      <c r="AX114">
+        <v>6</v>
+      </c>
+      <c r="AY114">
+        <v>21</v>
+      </c>
+      <c r="AZ114">
+        <v>11</v>
+      </c>
+      <c r="BA114">
+        <v>4</v>
+      </c>
+      <c r="BB114">
+        <v>2</v>
+      </c>
+      <c r="BC114">
+        <v>6</v>
+      </c>
+      <c r="BD114">
+        <v>1.95</v>
+      </c>
+      <c r="BE114">
+        <v>6.4</v>
+      </c>
+      <c r="BF114">
+        <v>2.05</v>
+      </c>
+      <c r="BG114">
+        <v>1.35</v>
+      </c>
+      <c r="BH114">
+        <v>2.8</v>
+      </c>
+      <c r="BI114">
+        <v>1.58</v>
+      </c>
+      <c r="BJ114">
+        <v>2.12</v>
+      </c>
+      <c r="BK114">
+        <v>1.96</v>
+      </c>
+      <c r="BL114">
+        <v>1.7</v>
+      </c>
+      <c r="BM114">
+        <v>2.55</v>
+      </c>
+      <c r="BN114">
+        <v>1.42</v>
+      </c>
+      <c r="BO114">
+        <v>3.3</v>
+      </c>
+      <c r="BP114">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="223">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,15 @@
     <t>['50', '64']</t>
   </si>
   <si>
+    <t>['67']</t>
+  </si>
+  <si>
+    <t>['66', '88']</t>
+  </si>
+  <si>
+    <t>['4501']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -545,9 +554,6 @@
   </si>
   <si>
     <t>['78']</t>
-  </si>
-  <si>
-    <t>['67']</t>
   </si>
   <si>
     <t>['22', '57']</t>
@@ -671,6 +677,12 @@
   </si>
   <si>
     <t>['29', '45']</t>
+  </si>
+  <si>
+    <t>['14']</t>
+  </si>
+  <si>
+    <t>['75']</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP114"/>
+  <dimension ref="A1:BP118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1288,7 +1300,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1987,7 +1999,7 @@
         <v>3</v>
       </c>
       <c r="AQ5">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2112,7 +2124,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2190,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2318,7 +2330,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2524,7 +2536,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2936,7 +2948,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3014,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ10">
         <v>0.25</v>
@@ -3142,7 +3154,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3635,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3966,7 +3978,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4044,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ15">
         <v>0.5</v>
@@ -4378,7 +4390,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4459,7 +4471,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4584,7 +4596,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4868,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ19">
         <v>0.43</v>
@@ -5202,7 +5214,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5408,7 +5420,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5486,10 +5498,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ22">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5614,7 +5626,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5695,7 +5707,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ23">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -5820,7 +5832,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5898,7 +5910,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ24">
         <v>0.67</v>
@@ -6026,7 +6038,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6107,7 +6119,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ25">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR25">
         <v>1.33</v>
@@ -6438,7 +6450,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6644,7 +6656,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6850,7 +6862,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6928,10 +6940,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ29">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR29">
         <v>1.73</v>
@@ -7056,7 +7068,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7752,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ33">
         <v>0.67</v>
@@ -7880,7 +7892,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8164,7 +8176,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ35">
         <v>2.13</v>
@@ -8370,7 +8382,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ36">
         <v>1.14</v>
@@ -8579,7 +8591,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ37">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR37">
         <v>1.78</v>
@@ -8782,10 +8794,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ38">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR38">
         <v>2</v>
@@ -8910,7 +8922,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9116,7 +9128,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9400,7 +9412,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ41">
         <v>0.67</v>
@@ -9528,7 +9540,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9940,7 +9952,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10021,7 +10033,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ44">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR44">
         <v>2.49</v>
@@ -10352,7 +10364,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10970,7 +10982,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11048,7 +11060,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ49">
         <v>1.13</v>
@@ -11254,10 +11266,10 @@
         <v>1.67</v>
       </c>
       <c r="AP50">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ50">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR50">
         <v>1.54</v>
@@ -11382,7 +11394,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -11460,7 +11472,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -11875,7 +11887,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ53">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR53">
         <v>1.48</v>
@@ -12490,7 +12502,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ56">
         <v>0.43</v>
@@ -12618,7 +12630,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12824,7 +12836,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -12905,7 +12917,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ58">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13030,7 +13042,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13108,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ59">
         <v>1.14</v>
@@ -14266,7 +14278,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14344,10 +14356,10 @@
         <v>0.25</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ65">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR65">
         <v>1.71</v>
@@ -14678,7 +14690,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14884,7 +14896,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15090,7 +15102,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15377,7 +15389,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15708,7 +15720,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15786,7 +15798,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ72">
         <v>1.88</v>
@@ -16201,7 +16213,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ74">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR74">
         <v>1.93</v>
@@ -16532,7 +16544,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16610,7 +16622,7 @@
         <v>0.2</v>
       </c>
       <c r="AP76">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ76">
         <v>0.5</v>
@@ -16738,7 +16750,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17150,7 +17162,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17228,7 +17240,7 @@
         <v>0.75</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ79">
         <v>1.43</v>
@@ -17562,7 +17574,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17974,7 +17986,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18180,7 +18192,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18261,7 +18273,7 @@
         <v>2</v>
       </c>
       <c r="AQ84">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR84">
         <v>1.95</v>
@@ -18386,7 +18398,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18464,7 +18476,7 @@
         <v>0.4</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ85">
         <v>0.25</v>
@@ -18798,7 +18810,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -18876,7 +18888,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ87">
         <v>1.14</v>
@@ -19497,7 +19509,7 @@
         <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR90">
         <v>1.8</v>
@@ -19622,7 +19634,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -20034,7 +20046,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20112,7 +20124,7 @@
         <v>0.83</v>
       </c>
       <c r="AP93">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ93">
         <v>0.63</v>
@@ -20240,7 +20252,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20321,7 +20333,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ94">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR94">
         <v>1.4</v>
@@ -20446,7 +20458,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -20524,7 +20536,7 @@
         <v>1.83</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ95">
         <v>2.13</v>
@@ -20733,7 +20745,7 @@
         <v>3</v>
       </c>
       <c r="AQ96">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR96">
         <v>2.13</v>
@@ -20936,7 +20948,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ97">
         <v>1.43</v>
@@ -21064,7 +21076,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21270,7 +21282,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21351,7 +21363,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ99">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR99">
         <v>1.47</v>
@@ -21476,7 +21488,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21554,7 +21566,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ100">
         <v>0.25</v>
@@ -21763,7 +21775,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ101">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR101">
         <v>1.56</v>
@@ -21888,7 +21900,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -21969,7 +21981,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ102">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR102">
         <v>1.69</v>
@@ -22094,7 +22106,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23124,7 +23136,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23330,7 +23342,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23948,7 +23960,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q112">
         <v>3.45</v>
@@ -24154,7 +24166,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q113">
         <v>1.76</v>
@@ -24360,7 +24372,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q114">
         <v>3.3</v>
@@ -24517,6 +24529,830 @@
       </c>
       <c r="BP114">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7818923</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45830.5625</v>
+      </c>
+      <c r="F115">
+        <v>15</v>
+      </c>
+      <c r="G115" t="s">
+        <v>74</v>
+      </c>
+      <c r="H115" t="s">
+        <v>75</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>2</v>
+      </c>
+      <c r="O115" t="s">
+        <v>170</v>
+      </c>
+      <c r="P115" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q115">
+        <v>3</v>
+      </c>
+      <c r="R115">
+        <v>2.25</v>
+      </c>
+      <c r="S115">
+        <v>3.4</v>
+      </c>
+      <c r="T115">
+        <v>1.36</v>
+      </c>
+      <c r="U115">
+        <v>3</v>
+      </c>
+      <c r="V115">
+        <v>2.63</v>
+      </c>
+      <c r="W115">
+        <v>1.44</v>
+      </c>
+      <c r="X115">
+        <v>7</v>
+      </c>
+      <c r="Y115">
+        <v>1.1</v>
+      </c>
+      <c r="Z115">
+        <v>2.44</v>
+      </c>
+      <c r="AA115">
+        <v>3.54</v>
+      </c>
+      <c r="AB115">
+        <v>2.75</v>
+      </c>
+      <c r="AC115">
+        <v>1</v>
+      </c>
+      <c r="AD115">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE115">
+        <v>1.27</v>
+      </c>
+      <c r="AF115">
+        <v>3.66</v>
+      </c>
+      <c r="AG115">
+        <v>1.86</v>
+      </c>
+      <c r="AH115">
+        <v>1.96</v>
+      </c>
+      <c r="AI115">
+        <v>1.67</v>
+      </c>
+      <c r="AJ115">
+        <v>2.1</v>
+      </c>
+      <c r="AK115">
+        <v>1.44</v>
+      </c>
+      <c r="AL115">
+        <v>1.29</v>
+      </c>
+      <c r="AM115">
+        <v>1.53</v>
+      </c>
+      <c r="AN115">
+        <v>2</v>
+      </c>
+      <c r="AO115">
+        <v>0.17</v>
+      </c>
+      <c r="AP115">
+        <v>1.86</v>
+      </c>
+      <c r="AQ115">
+        <v>0.29</v>
+      </c>
+      <c r="AR115">
+        <v>1.68</v>
+      </c>
+      <c r="AS115">
+        <v>1.62</v>
+      </c>
+      <c r="AT115">
+        <v>3.3</v>
+      </c>
+      <c r="AU115">
+        <v>6</v>
+      </c>
+      <c r="AV115">
+        <v>5</v>
+      </c>
+      <c r="AW115">
+        <v>12</v>
+      </c>
+      <c r="AX115">
+        <v>11</v>
+      </c>
+      <c r="AY115">
+        <v>18</v>
+      </c>
+      <c r="AZ115">
+        <v>16</v>
+      </c>
+      <c r="BA115">
+        <v>2</v>
+      </c>
+      <c r="BB115">
+        <v>5</v>
+      </c>
+      <c r="BC115">
+        <v>7</v>
+      </c>
+      <c r="BD115">
+        <v>1.97</v>
+      </c>
+      <c r="BE115">
+        <v>6.4</v>
+      </c>
+      <c r="BF115">
+        <v>2.02</v>
+      </c>
+      <c r="BG115">
+        <v>1.26</v>
+      </c>
+      <c r="BH115">
+        <v>3.3</v>
+      </c>
+      <c r="BI115">
+        <v>1.46</v>
+      </c>
+      <c r="BJ115">
+        <v>2.4</v>
+      </c>
+      <c r="BK115">
+        <v>1.77</v>
+      </c>
+      <c r="BL115">
+        <v>1.88</v>
+      </c>
+      <c r="BM115">
+        <v>2.2</v>
+      </c>
+      <c r="BN115">
+        <v>1.55</v>
+      </c>
+      <c r="BO115">
+        <v>2.8</v>
+      </c>
+      <c r="BP115">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7818919</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45830.66666666666</v>
+      </c>
+      <c r="F116">
+        <v>15</v>
+      </c>
+      <c r="G116" t="s">
+        <v>78</v>
+      </c>
+      <c r="H116" t="s">
+        <v>84</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>2</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116">
+        <v>3</v>
+      </c>
+      <c r="O116" t="s">
+        <v>171</v>
+      </c>
+      <c r="P116" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q116">
+        <v>4.33</v>
+      </c>
+      <c r="R116">
+        <v>2.2</v>
+      </c>
+      <c r="S116">
+        <v>2.5</v>
+      </c>
+      <c r="T116">
+        <v>1.36</v>
+      </c>
+      <c r="U116">
+        <v>3</v>
+      </c>
+      <c r="V116">
+        <v>2.75</v>
+      </c>
+      <c r="W116">
+        <v>1.4</v>
+      </c>
+      <c r="X116">
+        <v>7</v>
+      </c>
+      <c r="Y116">
+        <v>1.1</v>
+      </c>
+      <c r="Z116">
+        <v>3.7</v>
+      </c>
+      <c r="AA116">
+        <v>3.5</v>
+      </c>
+      <c r="AB116">
+        <v>1.91</v>
+      </c>
+      <c r="AC116">
+        <v>1.01</v>
+      </c>
+      <c r="AD116">
+        <v>9.9</v>
+      </c>
+      <c r="AE116">
+        <v>1.24</v>
+      </c>
+      <c r="AF116">
+        <v>3.36</v>
+      </c>
+      <c r="AG116">
+        <v>1.9</v>
+      </c>
+      <c r="AH116">
+        <v>1.9</v>
+      </c>
+      <c r="AI116">
+        <v>1.73</v>
+      </c>
+      <c r="AJ116">
+        <v>2</v>
+      </c>
+      <c r="AK116">
+        <v>1.79</v>
+      </c>
+      <c r="AL116">
+        <v>1.28</v>
+      </c>
+      <c r="AM116">
+        <v>1.28</v>
+      </c>
+      <c r="AN116">
+        <v>2.71</v>
+      </c>
+      <c r="AO116">
+        <v>1.8</v>
+      </c>
+      <c r="AP116">
+        <v>2.75</v>
+      </c>
+      <c r="AQ116">
+        <v>1.5</v>
+      </c>
+      <c r="AR116">
+        <v>1.79</v>
+      </c>
+      <c r="AS116">
+        <v>1.84</v>
+      </c>
+      <c r="AT116">
+        <v>3.63</v>
+      </c>
+      <c r="AU116">
+        <v>5</v>
+      </c>
+      <c r="AV116">
+        <v>13</v>
+      </c>
+      <c r="AW116">
+        <v>8</v>
+      </c>
+      <c r="AX116">
+        <v>13</v>
+      </c>
+      <c r="AY116">
+        <v>13</v>
+      </c>
+      <c r="AZ116">
+        <v>26</v>
+      </c>
+      <c r="BA116">
+        <v>2</v>
+      </c>
+      <c r="BB116">
+        <v>7</v>
+      </c>
+      <c r="BC116">
+        <v>9</v>
+      </c>
+      <c r="BD116">
+        <v>2.65</v>
+      </c>
+      <c r="BE116">
+        <v>6.5</v>
+      </c>
+      <c r="BF116">
+        <v>1.56</v>
+      </c>
+      <c r="BG116">
+        <v>1.37</v>
+      </c>
+      <c r="BH116">
+        <v>2.7</v>
+      </c>
+      <c r="BI116">
+        <v>1.62</v>
+      </c>
+      <c r="BJ116">
+        <v>2.08</v>
+      </c>
+      <c r="BK116">
+        <v>2</v>
+      </c>
+      <c r="BL116">
+        <v>1.67</v>
+      </c>
+      <c r="BM116">
+        <v>2.55</v>
+      </c>
+      <c r="BN116">
+        <v>1.42</v>
+      </c>
+      <c r="BO116">
+        <v>3.35</v>
+      </c>
+      <c r="BP116">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7818926</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45830.77083333334</v>
+      </c>
+      <c r="F117">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>83</v>
+      </c>
+      <c r="H117" t="s">
+        <v>81</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117">
+        <v>2</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>2</v>
+      </c>
+      <c r="O117" t="s">
+        <v>172</v>
+      </c>
+      <c r="P117" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q117">
+        <v>2.75</v>
+      </c>
+      <c r="R117">
+        <v>2.2</v>
+      </c>
+      <c r="S117">
+        <v>3.75</v>
+      </c>
+      <c r="T117">
+        <v>1.36</v>
+      </c>
+      <c r="U117">
+        <v>3</v>
+      </c>
+      <c r="V117">
+        <v>2.75</v>
+      </c>
+      <c r="W117">
+        <v>1.4</v>
+      </c>
+      <c r="X117">
+        <v>7</v>
+      </c>
+      <c r="Y117">
+        <v>1.1</v>
+      </c>
+      <c r="Z117">
+        <v>2.15</v>
+      </c>
+      <c r="AA117">
+        <v>3.25</v>
+      </c>
+      <c r="AB117">
+        <v>3.3</v>
+      </c>
+      <c r="AC117">
+        <v>1.01</v>
+      </c>
+      <c r="AD117">
+        <v>9.85</v>
+      </c>
+      <c r="AE117">
+        <v>1.22</v>
+      </c>
+      <c r="AF117">
+        <v>3.5</v>
+      </c>
+      <c r="AG117">
+        <v>1.85</v>
+      </c>
+      <c r="AH117">
+        <v>1.95</v>
+      </c>
+      <c r="AI117">
+        <v>1.67</v>
+      </c>
+      <c r="AJ117">
+        <v>2.1</v>
+      </c>
+      <c r="AK117">
+        <v>1.33</v>
+      </c>
+      <c r="AL117">
+        <v>1.29</v>
+      </c>
+      <c r="AM117">
+        <v>1.67</v>
+      </c>
+      <c r="AN117">
+        <v>2</v>
+      </c>
+      <c r="AO117">
+        <v>1.17</v>
+      </c>
+      <c r="AP117">
+        <v>1.88</v>
+      </c>
+      <c r="AQ117">
+        <v>1.14</v>
+      </c>
+      <c r="AR117">
+        <v>1.73</v>
+      </c>
+      <c r="AS117">
+        <v>1.22</v>
+      </c>
+      <c r="AT117">
+        <v>2.95</v>
+      </c>
+      <c r="AU117">
+        <v>6</v>
+      </c>
+      <c r="AV117">
+        <v>5</v>
+      </c>
+      <c r="AW117">
+        <v>9</v>
+      </c>
+      <c r="AX117">
+        <v>12</v>
+      </c>
+      <c r="AY117">
+        <v>15</v>
+      </c>
+      <c r="AZ117">
+        <v>17</v>
+      </c>
+      <c r="BA117">
+        <v>3</v>
+      </c>
+      <c r="BB117">
+        <v>11</v>
+      </c>
+      <c r="BC117">
+        <v>14</v>
+      </c>
+      <c r="BD117">
+        <v>1.75</v>
+      </c>
+      <c r="BE117">
+        <v>6.5</v>
+      </c>
+      <c r="BF117">
+        <v>2.3</v>
+      </c>
+      <c r="BG117">
+        <v>1.3</v>
+      </c>
+      <c r="BH117">
+        <v>3.05</v>
+      </c>
+      <c r="BI117">
+        <v>1.53</v>
+      </c>
+      <c r="BJ117">
+        <v>2.25</v>
+      </c>
+      <c r="BK117">
+        <v>1.87</v>
+      </c>
+      <c r="BL117">
+        <v>1.78</v>
+      </c>
+      <c r="BM117">
+        <v>2.35</v>
+      </c>
+      <c r="BN117">
+        <v>1.49</v>
+      </c>
+      <c r="BO117">
+        <v>3.05</v>
+      </c>
+      <c r="BP117">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7818925</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45830.875</v>
+      </c>
+      <c r="F118">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s">
+        <v>85</v>
+      </c>
+      <c r="H118" t="s">
+        <v>72</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>1</v>
+      </c>
+      <c r="N118">
+        <v>1</v>
+      </c>
+      <c r="O118" t="s">
+        <v>86</v>
+      </c>
+      <c r="P118" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q118">
+        <v>3</v>
+      </c>
+      <c r="R118">
+        <v>2.1</v>
+      </c>
+      <c r="S118">
+        <v>3.6</v>
+      </c>
+      <c r="T118">
+        <v>1.4</v>
+      </c>
+      <c r="U118">
+        <v>2.75</v>
+      </c>
+      <c r="V118">
+        <v>3</v>
+      </c>
+      <c r="W118">
+        <v>1.36</v>
+      </c>
+      <c r="X118">
+        <v>8</v>
+      </c>
+      <c r="Y118">
+        <v>1.08</v>
+      </c>
+      <c r="Z118">
+        <v>2.3</v>
+      </c>
+      <c r="AA118">
+        <v>3.2</v>
+      </c>
+      <c r="AB118">
+        <v>3.1</v>
+      </c>
+      <c r="AC118">
+        <v>1.02</v>
+      </c>
+      <c r="AD118">
+        <v>7.9</v>
+      </c>
+      <c r="AE118">
+        <v>1.27</v>
+      </c>
+      <c r="AF118">
+        <v>3.15</v>
+      </c>
+      <c r="AG118">
+        <v>2.05</v>
+      </c>
+      <c r="AH118">
+        <v>1.75</v>
+      </c>
+      <c r="AI118">
+        <v>1.8</v>
+      </c>
+      <c r="AJ118">
+        <v>1.91</v>
+      </c>
+      <c r="AK118">
+        <v>1.36</v>
+      </c>
+      <c r="AL118">
+        <v>1.31</v>
+      </c>
+      <c r="AM118">
+        <v>1.61</v>
+      </c>
+      <c r="AN118">
+        <v>1</v>
+      </c>
+      <c r="AO118">
+        <v>1.14</v>
+      </c>
+      <c r="AP118">
+        <v>0.88</v>
+      </c>
+      <c r="AQ118">
+        <v>1.38</v>
+      </c>
+      <c r="AR118">
+        <v>1.81</v>
+      </c>
+      <c r="AS118">
+        <v>1.65</v>
+      </c>
+      <c r="AT118">
+        <v>3.46</v>
+      </c>
+      <c r="AU118">
+        <v>3</v>
+      </c>
+      <c r="AV118">
+        <v>4</v>
+      </c>
+      <c r="AW118">
+        <v>9</v>
+      </c>
+      <c r="AX118">
+        <v>11</v>
+      </c>
+      <c r="AY118">
+        <v>12</v>
+      </c>
+      <c r="AZ118">
+        <v>15</v>
+      </c>
+      <c r="BA118">
+        <v>3</v>
+      </c>
+      <c r="BB118">
+        <v>7</v>
+      </c>
+      <c r="BC118">
+        <v>10</v>
+      </c>
+      <c r="BD118">
+        <v>1.71</v>
+      </c>
+      <c r="BE118">
+        <v>6.75</v>
+      </c>
+      <c r="BF118">
+        <v>2.33</v>
+      </c>
+      <c r="BG118">
+        <v>1.19</v>
+      </c>
+      <c r="BH118">
+        <v>3.8</v>
+      </c>
+      <c r="BI118">
+        <v>1.35</v>
+      </c>
+      <c r="BJ118">
+        <v>2.8</v>
+      </c>
+      <c r="BK118">
+        <v>1.6</v>
+      </c>
+      <c r="BL118">
+        <v>2.12</v>
+      </c>
+      <c r="BM118">
+        <v>1.93</v>
+      </c>
+      <c r="BN118">
+        <v>1.72</v>
+      </c>
+      <c r="BO118">
+        <v>2.43</v>
+      </c>
+      <c r="BP118">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -21993,31 +21993,31 @@
         <v>3.58</v>
       </c>
       <c r="AU102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV102">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW102">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX102">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AY102">
         <v>11</v>
       </c>
       <c r="AZ102">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BA102">
         <v>6</v>
       </c>
       <c r="BB102">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC102">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD102">
         <v>3.15</v>
@@ -23426,13 +23426,13 @@
         <v>1</v>
       </c>
       <c r="AR109">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AS109">
         <v>1.47</v>
       </c>
       <c r="AT109">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="AU109">
         <v>6</v>
@@ -24871,10 +24871,10 @@
         <v>1.79</v>
       </c>
       <c r="AS116">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AT116">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="AU116">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -21993,31 +21993,31 @@
         <v>3.58</v>
       </c>
       <c r="AU102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV102">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW102">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX102">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY102">
         <v>11</v>
       </c>
       <c r="AZ102">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BA102">
         <v>6</v>
       </c>
       <c r="BB102">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC102">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD102">
         <v>3.15</v>
@@ -23426,13 +23426,13 @@
         <v>1</v>
       </c>
       <c r="AR109">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AS109">
         <v>1.47</v>
       </c>
       <c r="AT109">
-        <v>3.16</v>
+        <v>3.07</v>
       </c>
       <c r="AU109">
         <v>6</v>
@@ -24871,10 +24871,10 @@
         <v>1.79</v>
       </c>
       <c r="AS116">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AT116">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
       <c r="AU116">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -493,13 +493,13 @@
     <t>['32']</t>
   </si>
   <si>
-    <t>['4505', '77']</t>
+    <t>['45+5', '77']</t>
   </si>
   <si>
-    <t>['62', '9001']</t>
+    <t>['62', '90+1']</t>
   </si>
   <si>
-    <t>['36']</t>
+    <t>['36', '56']</t>
   </si>
   <si>
     <t>['58', '65']</t>
@@ -508,19 +508,19 @@
     <t>['53']</t>
   </si>
   <si>
-    <t>['9008']</t>
-  </si>
-  <si>
     <t>['48']</t>
   </si>
   <si>
-    <t>['4503', '84']</t>
+    <t>['45+3', '84']</t>
   </si>
   <si>
-    <t>['55', '75', '85']</t>
+    <t>['27', '55', '75', '85']</t>
   </si>
   <si>
-    <t>['58', '70', '9004']</t>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['58', '70', '90+4']</t>
   </si>
   <si>
     <t>['50', '64']</t>
@@ -532,7 +532,7 @@
     <t>['66', '88']</t>
   </si>
   <si>
-    <t>['4501']</t>
+    <t>['45+1']</t>
   </si>
   <si>
     <t>['3', '84', '90+7']</t>
@@ -655,7 +655,7 @@
     <t>['13', '37', '77', '90']</t>
   </si>
   <si>
-    <t>['4503']</t>
+    <t>['34', '64']</t>
   </si>
   <si>
     <t>['53', '59']</t>
@@ -667,7 +667,7 @@
     <t>['5', '10', '54']</t>
   </si>
   <si>
-    <t>['4502', '48']</t>
+    <t>['45+2', '48']</t>
   </si>
   <si>
     <t>['42', '87']</t>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AQ2">
         <v>2.13</v>
@@ -2205,7 +2205,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9">
         <v>0.43</v>
@@ -3232,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="AQ11">
         <v>1.88</v>
@@ -3441,7 +3441,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ12">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3647,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ23">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -6116,7 +6116,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25">
         <v>1.38</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ26">
         <v>0.63</v>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AR27">
         <v>2.18</v>
@@ -6734,7 +6734,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AQ28">
         <v>1.88</v>
@@ -6943,7 +6943,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ29">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="AR29">
         <v>1.73</v>
@@ -9000,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AQ39">
         <v>0.43</v>
@@ -9618,10 +9618,10 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="AQ42">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AR42">
         <v>1.33</v>
@@ -10033,7 +10033,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ44">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="AR44">
         <v>2.49</v>
@@ -10648,7 +10648,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ47">
         <v>1.14</v>
@@ -11063,7 +11063,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ49">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -11884,7 +11884,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="AQ53">
         <v>1.14</v>
@@ -12917,7 +12917,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ58">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13738,7 +13738,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ62">
         <v>1.43</v>
@@ -14359,7 +14359,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ65">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="AR65">
         <v>1.71</v>
@@ -15389,7 +15389,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15592,7 +15592,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="AQ71">
         <v>1.14</v>
@@ -16007,7 +16007,7 @@
         <v>3</v>
       </c>
       <c r="AQ73">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AR73">
         <v>2.35</v>
@@ -16416,7 +16416,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AQ75">
         <v>0.63</v>
@@ -17034,7 +17034,7 @@
         <v>1.6</v>
       </c>
       <c r="AP78">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ78">
         <v>2.13</v>
@@ -17449,7 +17449,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ80">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AR80">
         <v>2.04</v>
@@ -18064,7 +18064,7 @@
         <v>0.2</v>
       </c>
       <c r="AP83">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -19918,7 +19918,7 @@
         <v>0.4</v>
       </c>
       <c r="AP92">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AQ92">
         <v>1.14</v>
@@ -21157,7 +21157,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ98">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AR98">
         <v>1.8</v>
@@ -21282,7 +21282,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21360,10 +21360,10 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ99">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AR99">
         <v>1.47</v>
@@ -21685,16 +21685,16 @@
         <v>2</v>
       </c>
       <c r="M101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N101">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O101" t="s">
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>140</v>
+        <v>213</v>
       </c>
       <c r="Q101">
         <v>2.75</v>
@@ -21772,10 +21772,10 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="AQ101">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="AR101">
         <v>1.56</v>
@@ -21888,13 +21888,13 @@
         <v>1</v>
       </c>
       <c r="L102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M102">
         <v>2</v>
       </c>
       <c r="N102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O102" t="s">
         <v>161</v>
@@ -21978,10 +21978,10 @@
         <v>1.5</v>
       </c>
       <c r="AP102">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AQ102">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AR102">
         <v>1.69</v>
@@ -22721,7 +22721,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="P106" t="s">
         <v>86</v>
@@ -22927,7 +22927,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P107" t="s">
         <v>86</v>
@@ -23133,7 +23133,7 @@
         <v>5</v>
       </c>
       <c r="O108" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P108" t="s">
         <v>216</v>
@@ -23414,13 +23414,13 @@
         <v>1.52</v>
       </c>
       <c r="AN109">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO109">
         <v>0.67</v>
       </c>
       <c r="AP109">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23527,25 +23527,25 @@
         <v>83</v>
       </c>
       <c r="I110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110">
         <v>0</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M110">
         <v>0</v>
       </c>
       <c r="N110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O110" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P110" t="s">
         <v>86</v>
@@ -23733,25 +23733,25 @@
         <v>76</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111">
         <v>1</v>
       </c>
       <c r="K111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111">
         <v>1</v>
       </c>
       <c r="N111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O111" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="P111" t="s">
         <v>99</v>
@@ -23832,10 +23832,10 @@
         <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ111">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AR111">
         <v>1.47</v>
@@ -24032,13 +24032,13 @@
         <v>1.38</v>
       </c>
       <c r="AN112">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO112">
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="AQ112">
         <v>2.13</v>
@@ -24653,13 +24653,13 @@
         <v>2</v>
       </c>
       <c r="AO115">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="AP115">
         <v>1.86</v>
       </c>
       <c r="AQ115">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="AR115">
         <v>1.68</v>
@@ -24859,13 +24859,13 @@
         <v>2.71</v>
       </c>
       <c r="AO116">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP116">
         <v>2.75</v>
       </c>
       <c r="AQ116">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AR116">
         <v>1.79</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="224">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -684,6 +684,9 @@
   <si>
     <t>['75']</t>
   </si>
+  <si>
+    <t>['25', '90+7']</t>
+  </si>
 </sst>
 </file>
 
@@ -1044,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP118"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3232,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ11">
         <v>1.88</v>
@@ -5913,7 +5916,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ24">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>1.82</v>
@@ -7767,7 +7770,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ33">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.64</v>
@@ -9415,7 +9418,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ41">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>2.17</v>
@@ -9618,7 +9621,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ42">
         <v>0.88</v>
@@ -11884,7 +11887,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ53">
         <v>1.14</v>
@@ -14977,7 +14980,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ68">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.78</v>
@@ -15592,7 +15595,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ71">
         <v>1.14</v>
@@ -18064,7 +18067,7 @@
         <v>0.2</v>
       </c>
       <c r="AP83">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18685,7 +18688,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ86">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.51</v>
@@ -21772,7 +21775,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ101">
         <v>0.43</v>
@@ -23011,7 +23014,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ107">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR107">
         <v>1.82</v>
@@ -24038,7 +24041,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ112">
         <v>2.13</v>
@@ -25353,6 +25356,212 @@
       </c>
       <c r="BP118">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7818831</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45843.66666666666</v>
+      </c>
+      <c r="F119">
+        <v>4</v>
+      </c>
+      <c r="G119" t="s">
+        <v>79</v>
+      </c>
+      <c r="H119" t="s">
+        <v>73</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>1</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>2</v>
+      </c>
+      <c r="N119">
+        <v>2</v>
+      </c>
+      <c r="O119" t="s">
+        <v>86</v>
+      </c>
+      <c r="P119" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q119">
+        <v>4.5</v>
+      </c>
+      <c r="R119">
+        <v>2.3</v>
+      </c>
+      <c r="S119">
+        <v>2.38</v>
+      </c>
+      <c r="T119">
+        <v>1.33</v>
+      </c>
+      <c r="U119">
+        <v>3.25</v>
+      </c>
+      <c r="V119">
+        <v>2.5</v>
+      </c>
+      <c r="W119">
+        <v>1.5</v>
+      </c>
+      <c r="X119">
+        <v>6.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.11</v>
+      </c>
+      <c r="Z119">
+        <v>4.2</v>
+      </c>
+      <c r="AA119">
+        <v>3.8</v>
+      </c>
+      <c r="AB119">
+        <v>1.8</v>
+      </c>
+      <c r="AC119">
+        <v>1.04</v>
+      </c>
+      <c r="AD119">
+        <v>13</v>
+      </c>
+      <c r="AE119">
+        <v>1.21</v>
+      </c>
+      <c r="AF119">
+        <v>4.32</v>
+      </c>
+      <c r="AG119">
+        <v>1.67</v>
+      </c>
+      <c r="AH119">
+        <v>2.15</v>
+      </c>
+      <c r="AI119">
+        <v>1.62</v>
+      </c>
+      <c r="AJ119">
+        <v>2.2</v>
+      </c>
+      <c r="AK119">
+        <v>1.91</v>
+      </c>
+      <c r="AL119">
+        <v>1.29</v>
+      </c>
+      <c r="AM119">
+        <v>1.25</v>
+      </c>
+      <c r="AN119">
+        <v>0.57</v>
+      </c>
+      <c r="AO119">
+        <v>0.67</v>
+      </c>
+      <c r="AP119">
+        <v>0.5</v>
+      </c>
+      <c r="AQ119">
+        <v>1</v>
+      </c>
+      <c r="AR119">
+        <v>1.53</v>
+      </c>
+      <c r="AS119">
+        <v>1.84</v>
+      </c>
+      <c r="AT119">
+        <v>3.37</v>
+      </c>
+      <c r="AU119">
+        <v>4</v>
+      </c>
+      <c r="AV119">
+        <v>4</v>
+      </c>
+      <c r="AW119">
+        <v>3</v>
+      </c>
+      <c r="AX119">
+        <v>7</v>
+      </c>
+      <c r="AY119">
+        <v>7</v>
+      </c>
+      <c r="AZ119">
+        <v>11</v>
+      </c>
+      <c r="BA119">
+        <v>4</v>
+      </c>
+      <c r="BB119">
+        <v>3</v>
+      </c>
+      <c r="BC119">
+        <v>7</v>
+      </c>
+      <c r="BD119">
+        <v>2.6</v>
+      </c>
+      <c r="BE119">
+        <v>6.75</v>
+      </c>
+      <c r="BF119">
+        <v>1.58</v>
+      </c>
+      <c r="BG119">
+        <v>1.25</v>
+      </c>
+      <c r="BH119">
+        <v>3.35</v>
+      </c>
+      <c r="BI119">
+        <v>1.44</v>
+      </c>
+      <c r="BJ119">
+        <v>2.45</v>
+      </c>
+      <c r="BK119">
+        <v>1.73</v>
+      </c>
+      <c r="BL119">
+        <v>1.93</v>
+      </c>
+      <c r="BM119">
+        <v>2.14</v>
+      </c>
+      <c r="BN119">
+        <v>1.58</v>
+      </c>
+      <c r="BO119">
+        <v>2.7</v>
+      </c>
+      <c r="BP119">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="201">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -490,51 +490,6 @@
     <t>['74']</t>
   </si>
   <si>
-    <t>['32']</t>
-  </si>
-  <si>
-    <t>['45+5', '77']</t>
-  </si>
-  <si>
-    <t>['62', '90+1']</t>
-  </si>
-  <si>
-    <t>['36', '56']</t>
-  </si>
-  <si>
-    <t>['58', '65']</t>
-  </si>
-  <si>
-    <t>['53']</t>
-  </si>
-  <si>
-    <t>['48']</t>
-  </si>
-  <si>
-    <t>['45+3', '84']</t>
-  </si>
-  <si>
-    <t>['27', '55', '75', '85']</t>
-  </si>
-  <si>
-    <t>['6']</t>
-  </si>
-  <si>
-    <t>['58', '70', '90+4']</t>
-  </si>
-  <si>
-    <t>['50', '64']</t>
-  </si>
-  <si>
-    <t>['67']</t>
-  </si>
-  <si>
-    <t>['66', '88']</t>
-  </si>
-  <si>
-    <t>['45+1']</t>
-  </si>
-  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -554,6 +509,9 @@
   </si>
   <si>
     <t>['78']</t>
+  </si>
+  <si>
+    <t>['67']</t>
   </si>
   <si>
     <t>['22', '57']</t>
@@ -643,6 +601,9 @@
     <t>['13', '45+6']</t>
   </si>
   <si>
+    <t>['53']</t>
+  </si>
+  <si>
     <t>['11', '57', '74']</t>
   </si>
   <si>
@@ -653,36 +614,6 @@
   </si>
   <si>
     <t>['13', '37', '77', '90']</t>
-  </si>
-  <si>
-    <t>['34', '64']</t>
-  </si>
-  <si>
-    <t>['53', '59']</t>
-  </si>
-  <si>
-    <t>['63']</t>
-  </si>
-  <si>
-    <t>['5', '10', '54']</t>
-  </si>
-  <si>
-    <t>['45+2', '48']</t>
-  </si>
-  <si>
-    <t>['42', '87']</t>
-  </si>
-  <si>
-    <t>['24']</t>
-  </si>
-  <si>
-    <t>['29', '45']</t>
-  </si>
-  <si>
-    <t>['14']</t>
-  </si>
-  <si>
-    <t>['75']</t>
   </si>
   <si>
     <t>['25', '90+7']</t>
@@ -1047,7 +978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1303,7 +1234,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1381,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ2">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1587,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ3">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1793,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2002,7 +1933,7 @@
         <v>3</v>
       </c>
       <c r="AQ5">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2127,7 +2058,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2205,10 +2136,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2333,7 +2264,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2411,10 +2342,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2539,7 +2470,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2617,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ8">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2823,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AQ9">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2951,7 +2882,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3029,10 +2960,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AQ10">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3157,7 +3088,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3238,7 +3169,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ11">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3441,10 +3372,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3647,10 +3578,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ13">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3853,10 +3784,10 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3981,7 +3912,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4059,10 +3990,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4268,7 +4199,7 @@
         <v>3</v>
       </c>
       <c r="AQ16">
-        <v>1.14</v>
+        <v>0.83</v>
       </c>
       <c r="AR16">
         <v>3.44</v>
@@ -4393,7 +4324,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4471,10 +4402,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ17">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4599,7 +4530,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4677,10 +4608,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AQ18">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR18">
         <v>1.84</v>
@@ -4883,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR19">
         <v>1.05</v>
@@ -5089,10 +5020,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ20">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR20">
         <v>1.33</v>
@@ -5217,7 +5148,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5295,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ21">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR21">
         <v>1.92</v>
@@ -5423,7 +5354,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5501,10 +5432,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5629,7 +5560,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5707,10 +5638,10 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -5835,7 +5766,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5913,10 +5844,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR24">
         <v>1.82</v>
@@ -6041,7 +5972,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6119,10 +6050,10 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AQ25">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AR25">
         <v>1.33</v>
@@ -6325,10 +6256,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AQ26">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AR26">
         <v>1.39</v>
@@ -6453,7 +6384,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6531,10 +6462,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ27">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR27">
         <v>2.18</v>
@@ -6659,7 +6590,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6737,10 +6668,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ28">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR28">
         <v>1.27</v>
@@ -6865,7 +6796,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6943,10 +6874,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AQ29">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="AR29">
         <v>1.73</v>
@@ -7071,7 +7002,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7149,10 +7080,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.85</v>
@@ -7355,10 +7286,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -7561,10 +7492,10 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR32">
         <v>1.71</v>
@@ -7767,10 +7698,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR33">
         <v>1.64</v>
@@ -7895,7 +7826,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -7973,10 +7904,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AQ34">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AR34">
         <v>1.52</v>
@@ -8179,10 +8110,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ35">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR35">
         <v>2.29</v>
@@ -8385,10 +8316,10 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
-        <v>1.14</v>
+        <v>0.83</v>
       </c>
       <c r="AR36">
         <v>1.55</v>
@@ -8591,10 +8522,10 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ37">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AR37">
         <v>1.78</v>
@@ -8797,10 +8728,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AQ38">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AR38">
         <v>2</v>
@@ -8925,7 +8856,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9003,10 +8934,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ39">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR39">
         <v>1.64</v>
@@ -9131,7 +9062,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9209,10 +9140,10 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ40">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR40">
         <v>2.12</v>
@@ -9415,10 +9346,10 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR41">
         <v>2.17</v>
@@ -9543,7 +9474,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9624,7 +9555,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ42">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR42">
         <v>1.33</v>
@@ -9827,10 +9758,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ43">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR43">
         <v>1.91</v>
@@ -9955,7 +9886,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10033,10 +9964,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="AR44">
         <v>2.49</v>
@@ -10239,10 +10170,10 @@
         <v>0.5</v>
       </c>
       <c r="AP45">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR45">
         <v>1.28</v>
@@ -10367,7 +10298,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10445,10 +10376,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR46">
         <v>2.2</v>
@@ -10651,10 +10582,10 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AQ47">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AR47">
         <v>1.72</v>
@@ -10857,10 +10788,10 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AR48">
         <v>2</v>
@@ -10985,7 +10916,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11063,10 +10994,10 @@
         <v>1.33</v>
       </c>
       <c r="AP49">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AQ49">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -11269,10 +11200,10 @@
         <v>1.67</v>
       </c>
       <c r="AP50">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AQ50">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AR50">
         <v>1.54</v>
@@ -11397,7 +11328,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -11475,10 +11406,10 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR51">
         <v>1.51</v>
@@ -11681,10 +11612,10 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ52">
-        <v>1.14</v>
+        <v>0.83</v>
       </c>
       <c r="AR52">
         <v>1.77</v>
@@ -11890,7 +11821,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ53">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AR53">
         <v>1.48</v>
@@ -12093,10 +12024,10 @@
         <v>0.33</v>
       </c>
       <c r="AP54">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AQ54">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR54">
         <v>1.28</v>
@@ -12302,7 +12233,7 @@
         <v>3</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR55">
         <v>2.44</v>
@@ -12505,10 +12436,10 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AQ56">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -12633,7 +12564,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12711,10 +12642,10 @@
         <v>0.33</v>
       </c>
       <c r="AP57">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AR57">
         <v>1.34</v>
@@ -12839,7 +12770,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -12917,10 +12848,10 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ58">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13045,7 +12976,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13123,10 +13054,10 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
-        <v>1.14</v>
+        <v>0.83</v>
       </c>
       <c r="AR59">
         <v>1.93</v>
@@ -13329,10 +13260,10 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR60">
         <v>2.23</v>
@@ -13535,10 +13466,10 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ61">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR61">
         <v>1.9</v>
@@ -13741,10 +13672,10 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AQ62">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR62">
         <v>1.63</v>
@@ -13947,10 +13878,10 @@
         <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ63">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR63">
         <v>1.77</v>
@@ -14153,10 +14084,10 @@
         <v>0.25</v>
       </c>
       <c r="AP64">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR64">
         <v>1.63</v>
@@ -14281,7 +14212,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14359,10 +14290,10 @@
         <v>0.25</v>
       </c>
       <c r="AP65">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AQ65">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="AR65">
         <v>1.71</v>
@@ -14565,10 +14496,10 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ66">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR66">
         <v>2.18</v>
@@ -14693,7 +14624,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14771,10 +14702,10 @@
         <v>0.25</v>
       </c>
       <c r="AP67">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR67">
         <v>2.15</v>
@@ -14899,7 +14830,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -14977,10 +14908,10 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR68">
         <v>1.78</v>
@@ -15105,7 +15036,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15183,10 +15114,10 @@
         <v>0.75</v>
       </c>
       <c r="AP69">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR69">
         <v>1.45</v>
@@ -15389,10 +15320,10 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AQ70">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15598,7 +15529,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ71">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AR71">
         <v>1.48</v>
@@ -15723,7 +15654,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15801,10 +15732,10 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR72">
         <v>1.83</v>
@@ -16010,7 +15941,7 @@
         <v>3</v>
       </c>
       <c r="AQ73">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR73">
         <v>2.35</v>
@@ -16213,10 +16144,10 @@
         <v>1.25</v>
       </c>
       <c r="AP74">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ74">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AR74">
         <v>1.93</v>
@@ -16419,10 +16350,10 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ75">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AR75">
         <v>1.77</v>
@@ -16547,7 +16478,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16625,10 +16556,10 @@
         <v>0.2</v>
       </c>
       <c r="AP76">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AQ76">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR76">
         <v>1.65</v>
@@ -16753,7 +16684,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -16831,10 +16762,10 @@
         <v>0.25</v>
       </c>
       <c r="AP77">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ77">
-        <v>1.14</v>
+        <v>0.83</v>
       </c>
       <c r="AR77">
         <v>1.74</v>
@@ -17037,10 +16968,10 @@
         <v>1.6</v>
       </c>
       <c r="AP78">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AQ78">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR78">
         <v>1.51</v>
@@ -17165,7 +17096,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17243,10 +17174,10 @@
         <v>0.75</v>
       </c>
       <c r="AP79">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AQ79">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR79">
         <v>1.73</v>
@@ -17449,10 +17380,10 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR80">
         <v>2.04</v>
@@ -17577,7 +17508,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17655,10 +17586,10 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AQ81">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17864,7 +17795,7 @@
         <v>3</v>
       </c>
       <c r="AQ82">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AR82">
         <v>2.19</v>
@@ -17989,7 +17920,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18070,7 +18001,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR83">
         <v>1.65</v>
@@ -18195,7 +18126,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18273,10 +18204,10 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ84">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AR84">
         <v>1.95</v>
@@ -18401,7 +18332,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18479,10 +18410,10 @@
         <v>0.4</v>
       </c>
       <c r="AP85">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ85">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR85">
         <v>1.47</v>
@@ -18685,10 +18616,10 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR86">
         <v>1.51</v>
@@ -18813,7 +18744,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -18891,10 +18822,10 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AR87">
         <v>1.7</v>
@@ -19097,10 +19028,10 @@
         <v>0.6</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ88">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR88">
         <v>2.08</v>
@@ -19303,10 +19234,10 @@
         <v>2.17</v>
       </c>
       <c r="AP89">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ89">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR89">
         <v>1.86</v>
@@ -19431,7 +19362,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="Q90">
         <v>2.88</v>
@@ -19509,10 +19440,10 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ90">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AR90">
         <v>1.8</v>
@@ -19637,7 +19568,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19715,10 +19646,10 @@
         <v>0.17</v>
       </c>
       <c r="AP91">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ91">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR91">
         <v>1.68</v>
@@ -19921,10 +19852,10 @@
         <v>0.4</v>
       </c>
       <c r="AP92">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ92">
-        <v>1.14</v>
+        <v>0.83</v>
       </c>
       <c r="AR92">
         <v>1.67</v>
@@ -20049,7 +19980,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20127,10 +20058,10 @@
         <v>0.83</v>
       </c>
       <c r="AP93">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AQ93">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="AR93">
         <v>1.73</v>
@@ -20255,7 +20186,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20333,10 +20264,10 @@
         <v>0.8</v>
       </c>
       <c r="AP94">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AR94">
         <v>1.4</v>
@@ -20461,7 +20392,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -20539,10 +20470,10 @@
         <v>1.83</v>
       </c>
       <c r="AP95">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR95">
         <v>1.68</v>
@@ -20748,7 +20679,7 @@
         <v>3</v>
       </c>
       <c r="AQ96">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AR96">
         <v>2.13</v>
@@ -20873,7 +20804,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -20951,10 +20882,10 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ97">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR97">
         <v>1.81</v>
@@ -21037,7 +20968,7 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>7818904</v>
+        <v>7818831</v>
       </c>
       <c r="C98" t="s">
         <v>68</v>
@@ -21046,4521 +20977,195 @@
         <v>69</v>
       </c>
       <c r="E98" s="2">
-        <v>45809.66666666666</v>
+        <v>45843.66666666666</v>
       </c>
       <c r="F98">
+        <v>4</v>
+      </c>
+      <c r="G98" t="s">
+        <v>79</v>
+      </c>
+      <c r="H98" t="s">
+        <v>73</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>2</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98" t="s">
+        <v>86</v>
+      </c>
+      <c r="P98" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q98">
+        <v>4.5</v>
+      </c>
+      <c r="R98">
+        <v>2.3</v>
+      </c>
+      <c r="S98">
+        <v>2.38</v>
+      </c>
+      <c r="T98">
+        <v>1.33</v>
+      </c>
+      <c r="U98">
+        <v>3.25</v>
+      </c>
+      <c r="V98">
+        <v>2.5</v>
+      </c>
+      <c r="W98">
+        <v>1.5</v>
+      </c>
+      <c r="X98">
+        <v>6.5</v>
+      </c>
+      <c r="Y98">
+        <v>1.11</v>
+      </c>
+      <c r="Z98">
+        <v>4.2</v>
+      </c>
+      <c r="AA98">
+        <v>3.8</v>
+      </c>
+      <c r="AB98">
+        <v>1.8</v>
+      </c>
+      <c r="AC98">
+        <v>1.04</v>
+      </c>
+      <c r="AD98">
         <v>13</v>
       </c>
-      <c r="G98" t="s">
-        <v>71</v>
-      </c>
-      <c r="H98" t="s">
-        <v>76</v>
-      </c>
-      <c r="I98">
-        <v>1</v>
-      </c>
-      <c r="J98">
-        <v>0</v>
-      </c>
-      <c r="K98">
-        <v>1</v>
-      </c>
-      <c r="L98">
-        <v>1</v>
-      </c>
-      <c r="M98">
-        <v>1</v>
-      </c>
-      <c r="N98">
-        <v>2</v>
-      </c>
-      <c r="O98" t="s">
-        <v>158</v>
-      </c>
-      <c r="P98" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q98">
+      <c r="AE98">
+        <v>1.21</v>
+      </c>
+      <c r="AF98">
+        <v>4.32</v>
+      </c>
+      <c r="AG98">
+        <v>1.67</v>
+      </c>
+      <c r="AH98">
+        <v>2.15</v>
+      </c>
+      <c r="AI98">
+        <v>1.62</v>
+      </c>
+      <c r="AJ98">
+        <v>2.2</v>
+      </c>
+      <c r="AK98">
+        <v>1.91</v>
+      </c>
+      <c r="AL98">
+        <v>1.29</v>
+      </c>
+      <c r="AM98">
+        <v>1.25</v>
+      </c>
+      <c r="AN98">
+        <v>0.6</v>
+      </c>
+      <c r="AO98">
+        <v>0.8</v>
+      </c>
+      <c r="AP98">
+        <v>0.5</v>
+      </c>
+      <c r="AQ98">
+        <v>1.17</v>
+      </c>
+      <c r="AR98">
+        <v>1.56</v>
+      </c>
+      <c r="AS98">
+        <v>1.91</v>
+      </c>
+      <c r="AT98">
+        <v>3.47</v>
+      </c>
+      <c r="AU98">
+        <v>4</v>
+      </c>
+      <c r="AV98">
         <v>3</v>
       </c>
-      <c r="R98">
-        <v>2.2</v>
-      </c>
-      <c r="S98">
-        <v>3.5</v>
-      </c>
-      <c r="T98">
-        <v>1.36</v>
-      </c>
-      <c r="U98">
+      <c r="AW98">
+        <v>6</v>
+      </c>
+      <c r="AX98">
+        <v>7</v>
+      </c>
+      <c r="AY98">
+        <v>10</v>
+      </c>
+      <c r="AZ98">
+        <v>10</v>
+      </c>
+      <c r="BA98">
+        <v>4</v>
+      </c>
+      <c r="BB98">
         <v>3</v>
       </c>
-      <c r="V98">
-        <v>2.75</v>
-      </c>
-      <c r="W98">
-        <v>1.4</v>
-      </c>
-      <c r="X98">
+      <c r="BC98">
         <v>7</v>
       </c>
-      <c r="Y98">
-        <v>1.1</v>
-      </c>
-      <c r="Z98">
-        <v>2.39</v>
-      </c>
-      <c r="AA98">
-        <v>3.32</v>
-      </c>
-      <c r="AB98">
-        <v>2.95</v>
-      </c>
-      <c r="AC98">
-        <v>1.03</v>
-      </c>
-      <c r="AD98">
-        <v>9</v>
-      </c>
-      <c r="AE98">
-        <v>1.29</v>
-      </c>
-      <c r="AF98">
-        <v>3.3</v>
-      </c>
-      <c r="AG98">
-        <v>1.96</v>
-      </c>
-      <c r="AH98">
-        <v>1.85</v>
-      </c>
-      <c r="AI98">
-        <v>1.67</v>
-      </c>
-      <c r="AJ98">
-        <v>2.1</v>
-      </c>
-      <c r="AK98">
-        <v>1.39</v>
-      </c>
-      <c r="AL98">
-        <v>1.3</v>
-      </c>
-      <c r="AM98">
-        <v>1.57</v>
-      </c>
-      <c r="AN98">
-        <v>1.8</v>
-      </c>
-      <c r="AO98">
-        <v>0.83</v>
-      </c>
-      <c r="AP98">
-        <v>1.86</v>
-      </c>
-      <c r="AQ98">
-        <v>0.88</v>
-      </c>
-      <c r="AR98">
-        <v>1.8</v>
-      </c>
-      <c r="AS98">
-        <v>1.22</v>
-      </c>
-      <c r="AT98">
-        <v>3.02</v>
-      </c>
-      <c r="AU98">
-        <v>5</v>
-      </c>
-      <c r="AV98">
-        <v>8</v>
-      </c>
-      <c r="AW98">
-        <v>2</v>
-      </c>
-      <c r="AX98">
-        <v>4</v>
-      </c>
-      <c r="AY98">
-        <v>7</v>
-      </c>
-      <c r="AZ98">
-        <v>12</v>
-      </c>
-      <c r="BA98">
-        <v>1</v>
-      </c>
-      <c r="BB98">
-        <v>8</v>
-      </c>
-      <c r="BC98">
-        <v>9</v>
-      </c>
       <c r="BD98">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="BE98">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF98">
-        <v>2.07</v>
+        <v>1.58</v>
       </c>
       <c r="BG98">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="BH98">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="BI98">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="BJ98">
+        <v>2.45</v>
+      </c>
+      <c r="BK98">
+        <v>1.73</v>
+      </c>
+      <c r="BL98">
         <v>1.93</v>
       </c>
-      <c r="BK98">
-        <v>2.18</v>
-      </c>
-      <c r="BL98">
-        <v>1.56</v>
-      </c>
       <c r="BM98">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="BN98">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="BO98">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="BP98">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="99" spans="1:68">
-      <c r="A99" s="1">
-        <v>98</v>
-      </c>
-      <c r="B99">
-        <v>7818903</v>
-      </c>
-      <c r="C99" t="s">
-        <v>68</v>
-      </c>
-      <c r="D99" t="s">
-        <v>69</v>
-      </c>
-      <c r="E99" s="2">
-        <v>45809.77083333334</v>
-      </c>
-      <c r="F99">
-        <v>13</v>
-      </c>
-      <c r="G99" t="s">
-        <v>77</v>
-      </c>
-      <c r="H99" t="s">
-        <v>84</v>
-      </c>
-      <c r="I99">
-        <v>0</v>
-      </c>
-      <c r="J99">
-        <v>1</v>
-      </c>
-      <c r="K99">
-        <v>1</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99">
-        <v>1</v>
-      </c>
-      <c r="N99">
-        <v>1</v>
-      </c>
-      <c r="O99" t="s">
-        <v>86</v>
-      </c>
-      <c r="P99" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q99">
-        <v>4.75</v>
-      </c>
-      <c r="R99">
-        <v>2.05</v>
-      </c>
-      <c r="S99">
-        <v>2.63</v>
-      </c>
-      <c r="T99">
-        <v>1.5</v>
-      </c>
-      <c r="U99">
-        <v>2.5</v>
-      </c>
-      <c r="V99">
-        <v>3.4</v>
-      </c>
-      <c r="W99">
-        <v>1.3</v>
-      </c>
-      <c r="X99">
-        <v>10</v>
-      </c>
-      <c r="Y99">
-        <v>1.06</v>
-      </c>
-      <c r="Z99">
-        <v>4.13</v>
-      </c>
-      <c r="AA99">
-        <v>3.31</v>
-      </c>
-      <c r="AB99">
-        <v>1.94</v>
-      </c>
-      <c r="AC99">
-        <v>1.06</v>
-      </c>
-      <c r="AD99">
-        <v>7.5</v>
-      </c>
-      <c r="AE99">
-        <v>1.4</v>
-      </c>
-      <c r="AF99">
-        <v>2.75</v>
-      </c>
-      <c r="AG99">
-        <v>2.35</v>
-      </c>
-      <c r="AH99">
-        <v>1.57</v>
-      </c>
-      <c r="AI99">
-        <v>2.1</v>
-      </c>
-      <c r="AJ99">
-        <v>1.67</v>
-      </c>
-      <c r="AK99">
-        <v>1.83</v>
-      </c>
-      <c r="AL99">
-        <v>1.31</v>
-      </c>
-      <c r="AM99">
-        <v>1.23</v>
-      </c>
-      <c r="AN99">
-        <v>2.17</v>
-      </c>
-      <c r="AO99">
-        <v>1</v>
-      </c>
-      <c r="AP99">
-        <v>1.75</v>
-      </c>
-      <c r="AQ99">
-        <v>1.17</v>
-      </c>
-      <c r="AR99">
-        <v>1.47</v>
-      </c>
-      <c r="AS99">
-        <v>1.89</v>
-      </c>
-      <c r="AT99">
-        <v>3.36</v>
-      </c>
-      <c r="AU99">
-        <v>3</v>
-      </c>
-      <c r="AV99">
-        <v>2</v>
-      </c>
-      <c r="AW99">
-        <v>12</v>
-      </c>
-      <c r="AX99">
-        <v>1</v>
-      </c>
-      <c r="AY99">
-        <v>15</v>
-      </c>
-      <c r="AZ99">
-        <v>3</v>
-      </c>
-      <c r="BA99">
-        <v>3</v>
-      </c>
-      <c r="BB99">
-        <v>1</v>
-      </c>
-      <c r="BC99">
-        <v>4</v>
-      </c>
-      <c r="BD99">
-        <v>2.65</v>
-      </c>
-      <c r="BE99">
-        <v>6.5</v>
-      </c>
-      <c r="BF99">
-        <v>1.58</v>
-      </c>
-      <c r="BG99">
-        <v>1.47</v>
-      </c>
-      <c r="BH99">
-        <v>2.38</v>
-      </c>
-      <c r="BI99">
-        <v>1.81</v>
-      </c>
-      <c r="BJ99">
-        <v>1.83</v>
-      </c>
-      <c r="BK99">
-        <v>2.3</v>
-      </c>
-      <c r="BL99">
-        <v>1.5</v>
-      </c>
-      <c r="BM99">
-        <v>3</v>
-      </c>
-      <c r="BN99">
-        <v>1.3</v>
-      </c>
-      <c r="BO99">
-        <v>4</v>
-      </c>
-      <c r="BP99">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="100" spans="1:68">
-      <c r="A100" s="1">
-        <v>99</v>
-      </c>
-      <c r="B100">
-        <v>7818905</v>
-      </c>
-      <c r="C100" t="s">
-        <v>68</v>
-      </c>
-      <c r="D100" t="s">
-        <v>69</v>
-      </c>
-      <c r="E100" s="2">
-        <v>45810.79166666666</v>
-      </c>
-      <c r="F100">
-        <v>13</v>
-      </c>
-      <c r="G100" t="s">
-        <v>83</v>
-      </c>
-      <c r="H100" t="s">
-        <v>70</v>
-      </c>
-      <c r="I100">
-        <v>1</v>
-      </c>
-      <c r="J100">
-        <v>0</v>
-      </c>
-      <c r="K100">
-        <v>1</v>
-      </c>
-      <c r="L100">
-        <v>2</v>
-      </c>
-      <c r="M100">
-        <v>1</v>
-      </c>
-      <c r="N100">
-        <v>3</v>
-      </c>
-      <c r="O100" t="s">
-        <v>159</v>
-      </c>
-      <c r="P100" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q100">
-        <v>2.32</v>
-      </c>
-      <c r="R100">
-        <v>2.23</v>
-      </c>
-      <c r="S100">
-        <v>4.45</v>
-      </c>
-      <c r="T100">
-        <v>1.32</v>
-      </c>
-      <c r="U100">
-        <v>3.1</v>
-      </c>
-      <c r="V100">
-        <v>2.53</v>
-      </c>
-      <c r="W100">
-        <v>1.46</v>
-      </c>
-      <c r="X100">
-        <v>5.95</v>
-      </c>
-      <c r="Y100">
-        <v>1.07</v>
-      </c>
-      <c r="Z100">
-        <v>1.82</v>
-      </c>
-      <c r="AA100">
-        <v>3.72</v>
-      </c>
-      <c r="AB100">
-        <v>4.05</v>
-      </c>
-      <c r="AC100">
-        <v>1.02</v>
-      </c>
-      <c r="AD100">
-        <v>10</v>
-      </c>
-      <c r="AE100">
-        <v>1.19</v>
-      </c>
-      <c r="AF100">
-        <v>3.8</v>
-      </c>
-      <c r="AG100">
-        <v>1.75</v>
-      </c>
-      <c r="AH100">
-        <v>2.04</v>
-      </c>
-      <c r="AI100">
-        <v>1.65</v>
-      </c>
-      <c r="AJ100">
-        <v>2.11</v>
-      </c>
-      <c r="AK100">
-        <v>1.23</v>
-      </c>
-      <c r="AL100">
-        <v>1.26</v>
-      </c>
-      <c r="AM100">
-        <v>1.95</v>
-      </c>
-      <c r="AN100">
-        <v>1.83</v>
-      </c>
-      <c r="AO100">
-        <v>0.33</v>
-      </c>
-      <c r="AP100">
-        <v>1.88</v>
-      </c>
-      <c r="AQ100">
-        <v>0.25</v>
-      </c>
-      <c r="AR100">
-        <v>1.73</v>
-      </c>
-      <c r="AS100">
-        <v>1.31</v>
-      </c>
-      <c r="AT100">
-        <v>3.04</v>
-      </c>
-      <c r="AU100">
-        <v>9</v>
-      </c>
-      <c r="AV100">
-        <v>8</v>
-      </c>
-      <c r="AW100">
-        <v>9</v>
-      </c>
-      <c r="AX100">
-        <v>2</v>
-      </c>
-      <c r="AY100">
-        <v>18</v>
-      </c>
-      <c r="AZ100">
-        <v>10</v>
-      </c>
-      <c r="BA100">
-        <v>7</v>
-      </c>
-      <c r="BB100">
-        <v>5</v>
-      </c>
-      <c r="BC100">
-        <v>12</v>
-      </c>
-      <c r="BD100">
-        <v>1.71</v>
-      </c>
-      <c r="BE100">
-        <v>6.4</v>
-      </c>
-      <c r="BF100">
-        <v>2.4</v>
-      </c>
-      <c r="BG100">
-        <v>1.32</v>
-      </c>
-      <c r="BH100">
-        <v>2.95</v>
-      </c>
-      <c r="BI100">
-        <v>1.54</v>
-      </c>
-      <c r="BJ100">
-        <v>2.23</v>
-      </c>
-      <c r="BK100">
-        <v>1.88</v>
-      </c>
-      <c r="BL100">
-        <v>1.77</v>
-      </c>
-      <c r="BM100">
-        <v>2.38</v>
-      </c>
-      <c r="BN100">
-        <v>1.47</v>
-      </c>
-      <c r="BO100">
-        <v>3.05</v>
-      </c>
-      <c r="BP100">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="101" spans="1:68">
-      <c r="A101" s="1">
-        <v>100</v>
-      </c>
-      <c r="B101">
-        <v>7818907</v>
-      </c>
-      <c r="C101" t="s">
-        <v>68</v>
-      </c>
-      <c r="D101" t="s">
-        <v>69</v>
-      </c>
-      <c r="E101" s="2">
-        <v>45811.66666666666</v>
-      </c>
-      <c r="F101">
-        <v>13</v>
-      </c>
-      <c r="G101" t="s">
-        <v>79</v>
-      </c>
-      <c r="H101" t="s">
-        <v>75</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1</v>
-      </c>
-      <c r="K101">
-        <v>1</v>
-      </c>
-      <c r="L101">
-        <v>2</v>
-      </c>
-      <c r="M101">
-        <v>2</v>
-      </c>
-      <c r="N101">
-        <v>4</v>
-      </c>
-      <c r="O101" t="s">
-        <v>160</v>
-      </c>
-      <c r="P101" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q101">
-        <v>2.75</v>
-      </c>
-      <c r="R101">
-        <v>2.38</v>
-      </c>
-      <c r="S101">
-        <v>3.4</v>
-      </c>
-      <c r="T101">
-        <v>1.3</v>
-      </c>
-      <c r="U101">
-        <v>3.4</v>
-      </c>
-      <c r="V101">
-        <v>2.38</v>
-      </c>
-      <c r="W101">
-        <v>1.53</v>
-      </c>
-      <c r="X101">
-        <v>6</v>
-      </c>
-      <c r="Y101">
-        <v>1.13</v>
-      </c>
-      <c r="Z101">
-        <v>2.16</v>
-      </c>
-      <c r="AA101">
-        <v>3.75</v>
-      </c>
-      <c r="AB101">
-        <v>3.03</v>
-      </c>
-      <c r="AC101">
-        <v>1.01</v>
-      </c>
-      <c r="AD101">
-        <v>11</v>
-      </c>
-      <c r="AE101">
-        <v>1.14</v>
-      </c>
-      <c r="AF101">
-        <v>4.45</v>
-      </c>
-      <c r="AG101">
-        <v>1.65</v>
-      </c>
-      <c r="AH101">
-        <v>2.2</v>
-      </c>
-      <c r="AI101">
-        <v>1.53</v>
-      </c>
-      <c r="AJ101">
-        <v>2.38</v>
-      </c>
-      <c r="AK101">
-        <v>1.36</v>
-      </c>
-      <c r="AL101">
-        <v>1.3</v>
-      </c>
-      <c r="AM101">
-        <v>1.62</v>
-      </c>
-      <c r="AN101">
-        <v>0.6</v>
-      </c>
-      <c r="AO101">
-        <v>0.2</v>
-      </c>
-      <c r="AP101">
-        <v>0.5</v>
-      </c>
-      <c r="AQ101">
-        <v>0.43</v>
-      </c>
-      <c r="AR101">
-        <v>1.56</v>
-      </c>
-      <c r="AS101">
-        <v>1.66</v>
-      </c>
-      <c r="AT101">
-        <v>3.22</v>
-      </c>
-      <c r="AU101">
-        <v>5</v>
-      </c>
-      <c r="AV101">
-        <v>4</v>
-      </c>
-      <c r="AW101">
-        <v>14</v>
-      </c>
-      <c r="AX101">
-        <v>9</v>
-      </c>
-      <c r="AY101">
-        <v>19</v>
-      </c>
-      <c r="AZ101">
-        <v>13</v>
-      </c>
-      <c r="BA101">
-        <v>10</v>
-      </c>
-      <c r="BB101">
-        <v>3</v>
-      </c>
-      <c r="BC101">
-        <v>13</v>
-      </c>
-      <c r="BD101">
-        <v>1.78</v>
-      </c>
-      <c r="BE101">
-        <v>6.75</v>
-      </c>
-      <c r="BF101">
-        <v>2.23</v>
-      </c>
-      <c r="BG101">
-        <v>1.16</v>
-      </c>
-      <c r="BH101">
-        <v>4.1</v>
-      </c>
-      <c r="BI101">
-        <v>1.32</v>
-      </c>
-      <c r="BJ101">
-        <v>2.95</v>
-      </c>
-      <c r="BK101">
-        <v>1.52</v>
-      </c>
-      <c r="BL101">
-        <v>2.28</v>
-      </c>
-      <c r="BM101">
-        <v>1.82</v>
-      </c>
-      <c r="BN101">
-        <v>1.82</v>
-      </c>
-      <c r="BO101">
-        <v>2.25</v>
-      </c>
-      <c r="BP101">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="102" spans="1:68">
-      <c r="A102" s="1">
-        <v>101</v>
-      </c>
-      <c r="B102">
-        <v>7818863</v>
-      </c>
-      <c r="C102" t="s">
-        <v>68</v>
-      </c>
-      <c r="D102" t="s">
-        <v>69</v>
-      </c>
-      <c r="E102" s="2">
-        <v>45820.875</v>
-      </c>
-      <c r="F102">
-        <v>8</v>
-      </c>
-      <c r="G102" t="s">
-        <v>70</v>
-      </c>
-      <c r="H102" t="s">
-        <v>84</v>
-      </c>
-      <c r="I102">
-        <v>1</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102">
-        <v>1</v>
-      </c>
-      <c r="L102">
-        <v>2</v>
-      </c>
-      <c r="M102">
-        <v>2</v>
-      </c>
-      <c r="N102">
-        <v>4</v>
-      </c>
-      <c r="O102" t="s">
-        <v>161</v>
-      </c>
-      <c r="P102" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q102">
-        <v>5.5</v>
-      </c>
-      <c r="R102">
-        <v>2.3</v>
-      </c>
-      <c r="S102">
-        <v>2.1</v>
-      </c>
-      <c r="T102">
-        <v>1.36</v>
-      </c>
-      <c r="U102">
-        <v>3</v>
-      </c>
-      <c r="V102">
-        <v>2.63</v>
-      </c>
-      <c r="W102">
-        <v>1.44</v>
-      </c>
-      <c r="X102">
-        <v>7</v>
-      </c>
-      <c r="Y102">
-        <v>1.1</v>
-      </c>
-      <c r="Z102">
-        <v>5.31</v>
-      </c>
-      <c r="AA102">
-        <v>4.05</v>
-      </c>
-      <c r="AB102">
-        <v>1.59</v>
-      </c>
-      <c r="AC102">
-        <v>1.01</v>
-      </c>
-      <c r="AD102">
-        <v>11</v>
-      </c>
-      <c r="AE102">
-        <v>1.2</v>
-      </c>
-      <c r="AF102">
-        <v>3.72</v>
-      </c>
-      <c r="AG102">
-        <v>1.85</v>
-      </c>
-      <c r="AH102">
-        <v>1.95</v>
-      </c>
-      <c r="AI102">
-        <v>1.83</v>
-      </c>
-      <c r="AJ102">
-        <v>1.83</v>
-      </c>
-      <c r="AK102">
-        <v>2.25</v>
-      </c>
-      <c r="AL102">
-        <v>1.25</v>
-      </c>
-      <c r="AM102">
-        <v>1.17</v>
-      </c>
-      <c r="AN102">
-        <v>0.6</v>
-      </c>
-      <c r="AO102">
-        <v>1.5</v>
-      </c>
-      <c r="AP102">
-        <v>0.57</v>
-      </c>
-      <c r="AQ102">
-        <v>1.17</v>
-      </c>
-      <c r="AR102">
-        <v>1.69</v>
-      </c>
-      <c r="AS102">
-        <v>1.89</v>
-      </c>
-      <c r="AT102">
-        <v>3.58</v>
-      </c>
-      <c r="AU102">
-        <v>3</v>
-      </c>
-      <c r="AV102">
-        <v>5</v>
-      </c>
-      <c r="AW102">
-        <v>8</v>
-      </c>
-      <c r="AX102">
-        <v>11</v>
-      </c>
-      <c r="AY102">
-        <v>11</v>
-      </c>
-      <c r="AZ102">
-        <v>16</v>
-      </c>
-      <c r="BA102">
-        <v>6</v>
-      </c>
-      <c r="BB102">
-        <v>6</v>
-      </c>
-      <c r="BC102">
-        <v>12</v>
-      </c>
-      <c r="BD102">
-        <v>3.15</v>
-      </c>
-      <c r="BE102">
-        <v>6.75</v>
-      </c>
-      <c r="BF102">
-        <v>1.44</v>
-      </c>
-      <c r="BG102">
-        <v>1.36</v>
-      </c>
-      <c r="BH102">
-        <v>2.75</v>
-      </c>
-      <c r="BI102">
-        <v>1.63</v>
-      </c>
-      <c r="BJ102">
-        <v>2.06</v>
-      </c>
-      <c r="BK102">
-        <v>2.06</v>
-      </c>
-      <c r="BL102">
-        <v>1.63</v>
-      </c>
-      <c r="BM102">
-        <v>2.65</v>
-      </c>
-      <c r="BN102">
-        <v>1.38</v>
-      </c>
-      <c r="BO102">
-        <v>3.45</v>
-      </c>
-      <c r="BP102">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="103" spans="1:68">
-      <c r="A103" s="1">
-        <v>102</v>
-      </c>
-      <c r="B103">
-        <v>7818914</v>
-      </c>
-      <c r="C103" t="s">
-        <v>68</v>
-      </c>
-      <c r="D103" t="s">
-        <v>69</v>
-      </c>
-      <c r="E103" s="2">
-        <v>45821.875</v>
-      </c>
-      <c r="F103">
-        <v>14</v>
-      </c>
-      <c r="G103" t="s">
-        <v>75</v>
-      </c>
-      <c r="H103" t="s">
-        <v>77</v>
-      </c>
-      <c r="I103">
-        <v>0</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
-      </c>
-      <c r="K103">
-        <v>0</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
-        <v>1</v>
-      </c>
-      <c r="N103">
-        <v>1</v>
-      </c>
-      <c r="O103" t="s">
-        <v>86</v>
-      </c>
-      <c r="P103" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q103">
-        <v>2.88</v>
-      </c>
-      <c r="R103">
-        <v>2.05</v>
-      </c>
-      <c r="S103">
-        <v>4</v>
-      </c>
-      <c r="T103">
-        <v>1.44</v>
-      </c>
-      <c r="U103">
-        <v>2.63</v>
-      </c>
-      <c r="V103">
-        <v>3.25</v>
-      </c>
-      <c r="W103">
-        <v>1.33</v>
-      </c>
-      <c r="X103">
-        <v>10</v>
-      </c>
-      <c r="Y103">
-        <v>1.06</v>
-      </c>
-      <c r="Z103">
-        <v>2.12</v>
-      </c>
-      <c r="AA103">
-        <v>3.43</v>
-      </c>
-      <c r="AB103">
-        <v>3.36</v>
-      </c>
-      <c r="AC103">
-        <v>1.02</v>
-      </c>
-      <c r="AD103">
-        <v>7.8</v>
-      </c>
-      <c r="AE103">
-        <v>1.41</v>
-      </c>
-      <c r="AF103">
-        <v>2.83</v>
-      </c>
-      <c r="AG103">
-        <v>2.25</v>
-      </c>
-      <c r="AH103">
-        <v>1.62</v>
-      </c>
-      <c r="AI103">
-        <v>1.91</v>
-      </c>
-      <c r="AJ103">
-        <v>1.8</v>
-      </c>
-      <c r="AK103">
-        <v>1.3</v>
-      </c>
-      <c r="AL103">
-        <v>1.35</v>
-      </c>
-      <c r="AM103">
-        <v>1.7</v>
-      </c>
-      <c r="AN103">
-        <v>1.43</v>
-      </c>
-      <c r="AO103">
-        <v>0.83</v>
-      </c>
-      <c r="AP103">
-        <v>1.25</v>
-      </c>
-      <c r="AQ103">
-        <v>1.14</v>
-      </c>
-      <c r="AR103">
-        <v>1.48</v>
-      </c>
-      <c r="AS103">
-        <v>1.23</v>
-      </c>
-      <c r="AT103">
-        <v>2.71</v>
-      </c>
-      <c r="AU103">
-        <v>6</v>
-      </c>
-      <c r="AV103">
-        <v>3</v>
-      </c>
-      <c r="AW103">
-        <v>11</v>
-      </c>
-      <c r="AX103">
-        <v>9</v>
-      </c>
-      <c r="AY103">
-        <v>17</v>
-      </c>
-      <c r="AZ103">
-        <v>12</v>
-      </c>
-      <c r="BA103">
-        <v>5</v>
-      </c>
-      <c r="BB103">
-        <v>2</v>
-      </c>
-      <c r="BC103">
-        <v>7</v>
-      </c>
-      <c r="BD103">
-        <v>1.85</v>
-      </c>
-      <c r="BE103">
-        <v>6.75</v>
-      </c>
-      <c r="BF103">
-        <v>2.12</v>
-      </c>
-      <c r="BG103">
-        <v>1.3</v>
-      </c>
-      <c r="BH103">
-        <v>3</v>
-      </c>
-      <c r="BI103">
-        <v>1.54</v>
-      </c>
-      <c r="BJ103">
-        <v>2.23</v>
-      </c>
-      <c r="BK103">
-        <v>1.9</v>
-      </c>
-      <c r="BL103">
-        <v>1.75</v>
-      </c>
-      <c r="BM103">
-        <v>2.4</v>
-      </c>
-      <c r="BN103">
-        <v>1.47</v>
-      </c>
-      <c r="BO103">
-        <v>3.1</v>
-      </c>
-      <c r="BP103">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="104" spans="1:68">
-      <c r="A104" s="1">
-        <v>103</v>
-      </c>
-      <c r="B104">
-        <v>7818913</v>
-      </c>
-      <c r="C104" t="s">
-        <v>68</v>
-      </c>
-      <c r="D104" t="s">
-        <v>69</v>
-      </c>
-      <c r="E104" s="2">
-        <v>45822.5625</v>
-      </c>
-      <c r="F104">
-        <v>14</v>
-      </c>
-      <c r="G104" t="s">
-        <v>71</v>
-      </c>
-      <c r="H104" t="s">
-        <v>74</v>
-      </c>
-      <c r="I104">
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <v>0</v>
-      </c>
-      <c r="L104">
-        <v>2</v>
-      </c>
-      <c r="M104">
-        <v>1</v>
-      </c>
-      <c r="N104">
-        <v>3</v>
-      </c>
-      <c r="O104" t="s">
-        <v>162</v>
-      </c>
-      <c r="P104" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q104">
-        <v>2.38</v>
-      </c>
-      <c r="R104">
-        <v>2.2</v>
-      </c>
-      <c r="S104">
-        <v>5</v>
-      </c>
-      <c r="T104">
-        <v>1.4</v>
-      </c>
-      <c r="U104">
-        <v>2.75</v>
-      </c>
-      <c r="V104">
-        <v>2.75</v>
-      </c>
-      <c r="W104">
-        <v>1.4</v>
-      </c>
-      <c r="X104">
-        <v>8</v>
-      </c>
-      <c r="Y104">
-        <v>1.08</v>
-      </c>
-      <c r="Z104">
-        <v>1.75</v>
-      </c>
-      <c r="AA104">
-        <v>3.75</v>
-      </c>
-      <c r="AB104">
-        <v>4.33</v>
-      </c>
-      <c r="AC104">
-        <v>1.01</v>
-      </c>
-      <c r="AD104">
-        <v>8.4</v>
-      </c>
-      <c r="AE104">
-        <v>1.28</v>
-      </c>
-      <c r="AF104">
-        <v>3.1</v>
-      </c>
-      <c r="AG104">
-        <v>2</v>
-      </c>
-      <c r="AH104">
-        <v>1.8</v>
-      </c>
-      <c r="AI104">
-        <v>1.91</v>
-      </c>
-      <c r="AJ104">
-        <v>1.8</v>
-      </c>
-      <c r="AK104">
-        <v>1.2</v>
-      </c>
-      <c r="AL104">
-        <v>1.3</v>
-      </c>
-      <c r="AM104">
-        <v>2</v>
-      </c>
-      <c r="AN104">
-        <v>1.67</v>
-      </c>
-      <c r="AO104">
-        <v>0.57</v>
-      </c>
-      <c r="AP104">
-        <v>1.86</v>
-      </c>
-      <c r="AQ104">
-        <v>0.5</v>
-      </c>
-      <c r="AR104">
-        <v>1.8</v>
-      </c>
-      <c r="AS104">
-        <v>1.29</v>
-      </c>
-      <c r="AT104">
-        <v>3.09</v>
-      </c>
-      <c r="AU104">
-        <v>7</v>
-      </c>
-      <c r="AV104">
-        <v>4</v>
-      </c>
-      <c r="AW104">
-        <v>8</v>
-      </c>
-      <c r="AX104">
-        <v>8</v>
-      </c>
-      <c r="AY104">
-        <v>15</v>
-      </c>
-      <c r="AZ104">
-        <v>12</v>
-      </c>
-      <c r="BA104">
-        <v>7</v>
-      </c>
-      <c r="BB104">
-        <v>4</v>
-      </c>
-      <c r="BC104">
-        <v>11</v>
-      </c>
-      <c r="BD104">
-        <v>1.49</v>
-      </c>
-      <c r="BE104">
-        <v>6.5</v>
-      </c>
-      <c r="BF104">
-        <v>2.95</v>
-      </c>
-      <c r="BG104">
-        <v>1.42</v>
-      </c>
-      <c r="BH104">
-        <v>2.55</v>
-      </c>
-      <c r="BI104">
-        <v>1.71</v>
-      </c>
-      <c r="BJ104">
-        <v>1.94</v>
-      </c>
-      <c r="BK104">
-        <v>2.14</v>
-      </c>
-      <c r="BL104">
-        <v>1.58</v>
-      </c>
-      <c r="BM104">
-        <v>2.8</v>
-      </c>
-      <c r="BN104">
-        <v>1.35</v>
-      </c>
-      <c r="BO104">
-        <v>3.7</v>
-      </c>
-      <c r="BP104">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:68">
-      <c r="A105" s="1">
-        <v>104</v>
-      </c>
-      <c r="B105">
-        <v>7818918</v>
-      </c>
-      <c r="C105" t="s">
-        <v>68</v>
-      </c>
-      <c r="D105" t="s">
-        <v>69</v>
-      </c>
-      <c r="E105" s="2">
-        <v>45822.66666666666</v>
-      </c>
-      <c r="F105">
-        <v>14</v>
-      </c>
-      <c r="G105" t="s">
-        <v>76</v>
-      </c>
-      <c r="H105" t="s">
-        <v>82</v>
-      </c>
-      <c r="I105">
-        <v>0</v>
-      </c>
-      <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105">
-        <v>0</v>
-      </c>
-      <c r="L105">
-        <v>1</v>
-      </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-      <c r="N105">
-        <v>1</v>
-      </c>
-      <c r="O105" t="s">
-        <v>163</v>
-      </c>
-      <c r="P105" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q105">
-        <v>2.3</v>
-      </c>
-      <c r="R105">
-        <v>2.25</v>
-      </c>
-      <c r="S105">
-        <v>5</v>
-      </c>
-      <c r="T105">
-        <v>1.36</v>
-      </c>
-      <c r="U105">
-        <v>3</v>
-      </c>
-      <c r="V105">
-        <v>2.75</v>
-      </c>
-      <c r="W105">
-        <v>1.4</v>
-      </c>
-      <c r="X105">
-        <v>7</v>
-      </c>
-      <c r="Y105">
-        <v>1.1</v>
-      </c>
-      <c r="Z105">
-        <v>1.72</v>
-      </c>
-      <c r="AA105">
-        <v>3.77</v>
-      </c>
-      <c r="AB105">
-        <v>4.63</v>
-      </c>
-      <c r="AC105">
-        <v>1</v>
-      </c>
-      <c r="AD105">
-        <v>9.1</v>
-      </c>
-      <c r="AE105">
-        <v>1.24</v>
-      </c>
-      <c r="AF105">
-        <v>3.36</v>
-      </c>
-      <c r="AG105">
-        <v>1.9</v>
-      </c>
-      <c r="AH105">
-        <v>1.9</v>
-      </c>
-      <c r="AI105">
-        <v>1.83</v>
-      </c>
-      <c r="AJ105">
-        <v>1.83</v>
-      </c>
-      <c r="AK105">
-        <v>1.18</v>
-      </c>
-      <c r="AL105">
-        <v>1.29</v>
-      </c>
-      <c r="AM105">
-        <v>2.1</v>
-      </c>
-      <c r="AN105">
-        <v>2.4</v>
-      </c>
-      <c r="AO105">
-        <v>0.71</v>
-      </c>
-      <c r="AP105">
-        <v>2.5</v>
-      </c>
-      <c r="AQ105">
-        <v>0.63</v>
-      </c>
-      <c r="AR105">
-        <v>1.74</v>
-      </c>
-      <c r="AS105">
-        <v>1.29</v>
-      </c>
-      <c r="AT105">
-        <v>3.03</v>
-      </c>
-      <c r="AU105">
-        <v>7</v>
-      </c>
-      <c r="AV105">
-        <v>4</v>
-      </c>
-      <c r="AW105">
-        <v>13</v>
-      </c>
-      <c r="AX105">
-        <v>4</v>
-      </c>
-      <c r="AY105">
-        <v>20</v>
-      </c>
-      <c r="AZ105">
-        <v>8</v>
-      </c>
-      <c r="BA105">
-        <v>4</v>
-      </c>
-      <c r="BB105">
-        <v>0</v>
-      </c>
-      <c r="BC105">
-        <v>4</v>
-      </c>
-      <c r="BD105">
-        <v>1.65</v>
-      </c>
-      <c r="BE105">
-        <v>6.4</v>
-      </c>
-      <c r="BF105">
-        <v>2.5</v>
-      </c>
-      <c r="BG105">
-        <v>1.32</v>
-      </c>
-      <c r="BH105">
-        <v>2.9</v>
-      </c>
-      <c r="BI105">
-        <v>1.55</v>
-      </c>
-      <c r="BJ105">
-        <v>2.2</v>
-      </c>
-      <c r="BK105">
-        <v>1.9</v>
-      </c>
-      <c r="BL105">
-        <v>1.74</v>
-      </c>
-      <c r="BM105">
-        <v>2.43</v>
-      </c>
-      <c r="BN105">
-        <v>1.45</v>
-      </c>
-      <c r="BO105">
-        <v>3.2</v>
-      </c>
-      <c r="BP105">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="106" spans="1:68">
-      <c r="A106" s="1">
-        <v>105</v>
-      </c>
-      <c r="B106">
-        <v>7818917</v>
-      </c>
-      <c r="C106" t="s">
-        <v>68</v>
-      </c>
-      <c r="D106" t="s">
-        <v>69</v>
-      </c>
-      <c r="E106" s="2">
-        <v>45823.5625</v>
-      </c>
-      <c r="F106">
-        <v>14</v>
-      </c>
-      <c r="G106" t="s">
-        <v>72</v>
-      </c>
-      <c r="H106" t="s">
-        <v>79</v>
-      </c>
-      <c r="I106">
-        <v>0</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="K106">
-        <v>0</v>
-      </c>
-      <c r="L106">
-        <v>1</v>
-      </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-      <c r="N106">
-        <v>1</v>
-      </c>
-      <c r="O106" t="s">
-        <v>153</v>
-      </c>
-      <c r="P106" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q106">
-        <v>2.4</v>
-      </c>
-      <c r="R106">
-        <v>2.25</v>
-      </c>
-      <c r="S106">
-        <v>4.33</v>
-      </c>
-      <c r="T106">
-        <v>1.36</v>
-      </c>
-      <c r="U106">
-        <v>3</v>
-      </c>
-      <c r="V106">
-        <v>2.63</v>
-      </c>
-      <c r="W106">
-        <v>1.44</v>
-      </c>
-      <c r="X106">
-        <v>7</v>
-      </c>
-      <c r="Y106">
-        <v>1.1</v>
-      </c>
-      <c r="Z106">
-        <v>1.9</v>
-      </c>
-      <c r="AA106">
-        <v>3.65</v>
-      </c>
-      <c r="AB106">
-        <v>3.85</v>
-      </c>
-      <c r="AC106">
-        <v>1.05</v>
-      </c>
-      <c r="AD106">
-        <v>8.5</v>
-      </c>
-      <c r="AE106">
-        <v>1.25</v>
-      </c>
-      <c r="AF106">
-        <v>3.6</v>
-      </c>
-      <c r="AG106">
-        <v>1.85</v>
-      </c>
-      <c r="AH106">
-        <v>1.95</v>
-      </c>
-      <c r="AI106">
-        <v>1.73</v>
-      </c>
-      <c r="AJ106">
-        <v>2</v>
-      </c>
-      <c r="AK106">
-        <v>1.24</v>
-      </c>
-      <c r="AL106">
-        <v>1.27</v>
-      </c>
-      <c r="AM106">
-        <v>1.88</v>
-      </c>
-      <c r="AN106">
-        <v>2</v>
-      </c>
-      <c r="AO106">
-        <v>0.5</v>
-      </c>
-      <c r="AP106">
-        <v>2.14</v>
-      </c>
-      <c r="AQ106">
-        <v>0.43</v>
-      </c>
-      <c r="AR106">
-        <v>1.87</v>
-      </c>
-      <c r="AS106">
-        <v>1.69</v>
-      </c>
-      <c r="AT106">
-        <v>3.56</v>
-      </c>
-      <c r="AU106">
-        <v>6</v>
-      </c>
-      <c r="AV106">
-        <v>2</v>
-      </c>
-      <c r="AW106">
-        <v>15</v>
-      </c>
-      <c r="AX106">
-        <v>7</v>
-      </c>
-      <c r="AY106">
-        <v>21</v>
-      </c>
-      <c r="AZ106">
-        <v>9</v>
-      </c>
-      <c r="BA106">
-        <v>6</v>
-      </c>
-      <c r="BB106">
-        <v>9</v>
-      </c>
-      <c r="BC106">
-        <v>15</v>
-      </c>
-      <c r="BD106">
-        <v>1.6</v>
-      </c>
-      <c r="BE106">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF106">
-        <v>2.73</v>
-      </c>
-      <c r="BG106">
-        <v>1.27</v>
-      </c>
-      <c r="BH106">
-        <v>3.2</v>
-      </c>
-      <c r="BI106">
-        <v>1.34</v>
-      </c>
-      <c r="BJ106">
-        <v>2.78</v>
-      </c>
-      <c r="BK106">
-        <v>1.62</v>
-      </c>
-      <c r="BL106">
-        <v>2.1</v>
-      </c>
-      <c r="BM106">
-        <v>2.06</v>
-      </c>
-      <c r="BN106">
-        <v>1.68</v>
-      </c>
-      <c r="BO106">
-        <v>2.67</v>
-      </c>
-      <c r="BP106">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="107" spans="1:68">
-      <c r="A107" s="1">
-        <v>106</v>
-      </c>
-      <c r="B107">
-        <v>7818911</v>
-      </c>
-      <c r="C107" t="s">
-        <v>68</v>
-      </c>
-      <c r="D107" t="s">
-        <v>69</v>
-      </c>
-      <c r="E107" s="2">
-        <v>45823.66666666666</v>
-      </c>
-      <c r="F107">
-        <v>14</v>
-      </c>
-      <c r="G107" t="s">
-        <v>80</v>
-      </c>
-      <c r="H107" t="s">
-        <v>73</v>
-      </c>
-      <c r="I107">
-        <v>0</v>
-      </c>
-      <c r="J107">
-        <v>0</v>
-      </c>
-      <c r="K107">
-        <v>0</v>
-      </c>
-      <c r="L107">
-        <v>1</v>
-      </c>
-      <c r="M107">
-        <v>0</v>
-      </c>
-      <c r="N107">
-        <v>1</v>
-      </c>
-      <c r="O107" t="s">
-        <v>164</v>
-      </c>
-      <c r="P107" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q107">
-        <v>3.4</v>
-      </c>
-      <c r="R107">
-        <v>2.1</v>
-      </c>
-      <c r="S107">
-        <v>3.2</v>
-      </c>
-      <c r="T107">
-        <v>1.4</v>
-      </c>
-      <c r="U107">
-        <v>2.75</v>
-      </c>
-      <c r="V107">
-        <v>3</v>
-      </c>
-      <c r="W107">
-        <v>1.36</v>
-      </c>
-      <c r="X107">
-        <v>8</v>
-      </c>
-      <c r="Y107">
-        <v>1.08</v>
-      </c>
-      <c r="Z107">
-        <v>2.72</v>
-      </c>
-      <c r="AA107">
-        <v>3.28</v>
-      </c>
-      <c r="AB107">
-        <v>2.59</v>
-      </c>
-      <c r="AC107">
-        <v>1.06</v>
-      </c>
-      <c r="AD107">
-        <v>8</v>
-      </c>
-      <c r="AE107">
-        <v>1.35</v>
-      </c>
-      <c r="AF107">
-        <v>3</v>
-      </c>
-      <c r="AG107">
-        <v>2.08</v>
-      </c>
-      <c r="AH107">
-        <v>1.73</v>
-      </c>
-      <c r="AI107">
-        <v>1.8</v>
-      </c>
-      <c r="AJ107">
-        <v>1.91</v>
-      </c>
-      <c r="AK107">
-        <v>1.49</v>
-      </c>
-      <c r="AL107">
-        <v>1.31</v>
-      </c>
-      <c r="AM107">
-        <v>1.44</v>
-      </c>
-      <c r="AN107">
-        <v>2</v>
-      </c>
-      <c r="AO107">
-        <v>0.8</v>
-      </c>
-      <c r="AP107">
-        <v>2.14</v>
-      </c>
-      <c r="AQ107">
-        <v>1</v>
-      </c>
-      <c r="AR107">
-        <v>1.82</v>
-      </c>
-      <c r="AS107">
-        <v>1.91</v>
-      </c>
-      <c r="AT107">
-        <v>3.73</v>
-      </c>
-      <c r="AU107">
-        <v>3</v>
-      </c>
-      <c r="AV107">
-        <v>2</v>
-      </c>
-      <c r="AW107">
-        <v>1</v>
-      </c>
-      <c r="AX107">
-        <v>13</v>
-      </c>
-      <c r="AY107">
-        <v>4</v>
-      </c>
-      <c r="AZ107">
-        <v>15</v>
-      </c>
-      <c r="BA107">
-        <v>1</v>
-      </c>
-      <c r="BB107">
-        <v>5</v>
-      </c>
-      <c r="BC107">
-        <v>6</v>
-      </c>
-      <c r="BD107">
-        <v>1.97</v>
-      </c>
-      <c r="BE107">
-        <v>6.35</v>
-      </c>
-      <c r="BF107">
-        <v>2.27</v>
-      </c>
-      <c r="BG107">
-        <v>1.24</v>
-      </c>
-      <c r="BH107">
-        <v>3.34</v>
-      </c>
-      <c r="BI107">
-        <v>1.47</v>
-      </c>
-      <c r="BJ107">
-        <v>2.42</v>
-      </c>
-      <c r="BK107">
-        <v>1.83</v>
-      </c>
-      <c r="BL107">
-        <v>1.87</v>
-      </c>
-      <c r="BM107">
-        <v>2.34</v>
-      </c>
-      <c r="BN107">
-        <v>1.5</v>
-      </c>
-      <c r="BO107">
-        <v>3.14</v>
-      </c>
-      <c r="BP107">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="108" spans="1:68">
-      <c r="A108" s="1">
-        <v>107</v>
-      </c>
-      <c r="B108">
-        <v>7818916</v>
-      </c>
-      <c r="C108" t="s">
-        <v>68</v>
-      </c>
-      <c r="D108" t="s">
-        <v>69</v>
-      </c>
-      <c r="E108" s="2">
-        <v>45823.875</v>
-      </c>
-      <c r="F108">
-        <v>14</v>
-      </c>
-      <c r="G108" t="s">
-        <v>81</v>
-      </c>
-      <c r="H108" t="s">
-        <v>78</v>
-      </c>
-      <c r="I108">
-        <v>1</v>
-      </c>
-      <c r="J108">
-        <v>2</v>
-      </c>
-      <c r="K108">
-        <v>3</v>
-      </c>
-      <c r="L108">
-        <v>2</v>
-      </c>
-      <c r="M108">
-        <v>3</v>
-      </c>
-      <c r="N108">
-        <v>5</v>
-      </c>
-      <c r="O108" t="s">
-        <v>165</v>
-      </c>
-      <c r="P108" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q108">
-        <v>3.1</v>
-      </c>
-      <c r="R108">
-        <v>2.05</v>
-      </c>
-      <c r="S108">
-        <v>3.75</v>
-      </c>
-      <c r="T108">
-        <v>1.44</v>
-      </c>
-      <c r="U108">
-        <v>2.63</v>
-      </c>
-      <c r="V108">
-        <v>3.25</v>
-      </c>
-      <c r="W108">
-        <v>1.33</v>
-      </c>
-      <c r="X108">
-        <v>10</v>
-      </c>
-      <c r="Y108">
-        <v>1.06</v>
-      </c>
-      <c r="Z108">
-        <v>2.33</v>
-      </c>
-      <c r="AA108">
-        <v>3.26</v>
-      </c>
-      <c r="AB108">
-        <v>3.09</v>
-      </c>
-      <c r="AC108">
-        <v>1.07</v>
-      </c>
-      <c r="AD108">
-        <v>7.5</v>
-      </c>
-      <c r="AE108">
-        <v>1.38</v>
-      </c>
-      <c r="AF108">
-        <v>2.88</v>
-      </c>
-      <c r="AG108">
-        <v>2.15</v>
-      </c>
-      <c r="AH108">
-        <v>1.67</v>
-      </c>
-      <c r="AI108">
-        <v>1.91</v>
-      </c>
-      <c r="AJ108">
-        <v>1.8</v>
-      </c>
-      <c r="AK108">
-        <v>1.39</v>
-      </c>
-      <c r="AL108">
-        <v>1.32</v>
-      </c>
-      <c r="AM108">
-        <v>1.55</v>
-      </c>
-      <c r="AN108">
-        <v>1.14</v>
-      </c>
-      <c r="AO108">
-        <v>1.17</v>
-      </c>
-      <c r="AP108">
-        <v>1</v>
-      </c>
-      <c r="AQ108">
-        <v>1.43</v>
-      </c>
-      <c r="AR108">
-        <v>1.78</v>
-      </c>
-      <c r="AS108">
-        <v>1.21</v>
-      </c>
-      <c r="AT108">
-        <v>2.99</v>
-      </c>
-      <c r="AU108">
-        <v>4</v>
-      </c>
-      <c r="AV108">
-        <v>5</v>
-      </c>
-      <c r="AW108">
-        <v>15</v>
-      </c>
-      <c r="AX108">
-        <v>5</v>
-      </c>
-      <c r="AY108">
-        <v>19</v>
-      </c>
-      <c r="AZ108">
-        <v>10</v>
-      </c>
-      <c r="BA108">
-        <v>8</v>
-      </c>
-      <c r="BB108">
-        <v>1</v>
-      </c>
-      <c r="BC108">
-        <v>9</v>
-      </c>
-      <c r="BD108">
-        <v>1.64</v>
-      </c>
-      <c r="BE108">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="BF108">
-        <v>2.66</v>
-      </c>
-      <c r="BG108">
-        <v>1.24</v>
-      </c>
-      <c r="BH108">
-        <v>3.34</v>
-      </c>
-      <c r="BI108">
-        <v>1.48</v>
-      </c>
-      <c r="BJ108">
-        <v>2.4</v>
-      </c>
-      <c r="BK108">
-        <v>1.91</v>
-      </c>
-      <c r="BL108">
-        <v>1.8</v>
-      </c>
-      <c r="BM108">
-        <v>2.38</v>
-      </c>
-      <c r="BN108">
-        <v>1.49</v>
-      </c>
-      <c r="BO108">
-        <v>3.14</v>
-      </c>
-      <c r="BP108">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="109" spans="1:68">
-      <c r="A109" s="1">
-        <v>108</v>
-      </c>
-      <c r="B109">
-        <v>7818915</v>
-      </c>
-      <c r="C109" t="s">
-        <v>68</v>
-      </c>
-      <c r="D109" t="s">
-        <v>69</v>
-      </c>
-      <c r="E109" s="2">
-        <v>45824.875</v>
-      </c>
-      <c r="F109">
-        <v>14</v>
-      </c>
-      <c r="G109" t="s">
-        <v>70</v>
-      </c>
-      <c r="H109" t="s">
-        <v>85</v>
-      </c>
-      <c r="I109">
-        <v>0</v>
-      </c>
-      <c r="J109">
-        <v>1</v>
-      </c>
-      <c r="K109">
-        <v>1</v>
-      </c>
-      <c r="L109">
-        <v>1</v>
-      </c>
-      <c r="M109">
-        <v>2</v>
-      </c>
-      <c r="N109">
-        <v>3</v>
-      </c>
-      <c r="O109" t="s">
-        <v>157</v>
-      </c>
-      <c r="P109" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q109">
-        <v>3.2</v>
-      </c>
-      <c r="R109">
-        <v>2</v>
-      </c>
-      <c r="S109">
-        <v>3.75</v>
-      </c>
-      <c r="T109">
-        <v>1.5</v>
-      </c>
-      <c r="U109">
-        <v>2.5</v>
-      </c>
-      <c r="V109">
-        <v>3.4</v>
-      </c>
-      <c r="W109">
-        <v>1.3</v>
-      </c>
-      <c r="X109">
-        <v>10</v>
-      </c>
-      <c r="Y109">
-        <v>1.06</v>
-      </c>
-      <c r="Z109">
-        <v>2.68</v>
-      </c>
-      <c r="AA109">
-        <v>3.32</v>
-      </c>
-      <c r="AB109">
-        <v>2.53</v>
-      </c>
-      <c r="AC109">
-        <v>1.04</v>
-      </c>
-      <c r="AD109">
-        <v>7.1</v>
-      </c>
-      <c r="AE109">
-        <v>1.5</v>
-      </c>
-      <c r="AF109">
-        <v>2.52</v>
-      </c>
-      <c r="AG109">
-        <v>2.35</v>
-      </c>
-      <c r="AH109">
-        <v>1.57</v>
-      </c>
-      <c r="AI109">
-        <v>2</v>
-      </c>
-      <c r="AJ109">
-        <v>1.73</v>
-      </c>
-      <c r="AK109">
-        <v>1.37</v>
-      </c>
-      <c r="AL109">
-        <v>1.36</v>
-      </c>
-      <c r="AM109">
-        <v>1.52</v>
-      </c>
-      <c r="AN109">
-        <v>0.67</v>
-      </c>
-      <c r="AO109">
-        <v>0.67</v>
-      </c>
-      <c r="AP109">
-        <v>0.57</v>
-      </c>
-      <c r="AQ109">
-        <v>1</v>
-      </c>
-      <c r="AR109">
-        <v>1.6</v>
-      </c>
-      <c r="AS109">
-        <v>1.47</v>
-      </c>
-      <c r="AT109">
-        <v>3.07</v>
-      </c>
-      <c r="AU109">
-        <v>6</v>
-      </c>
-      <c r="AV109">
-        <v>6</v>
-      </c>
-      <c r="AW109">
-        <v>7</v>
-      </c>
-      <c r="AX109">
-        <v>6</v>
-      </c>
-      <c r="AY109">
-        <v>13</v>
-      </c>
-      <c r="AZ109">
-        <v>12</v>
-      </c>
-      <c r="BA109">
-        <v>4</v>
-      </c>
-      <c r="BB109">
-        <v>4</v>
-      </c>
-      <c r="BC109">
-        <v>8</v>
-      </c>
-      <c r="BD109">
-        <v>1.8</v>
-      </c>
-      <c r="BE109">
-        <v>6.5</v>
-      </c>
-      <c r="BF109">
-        <v>2.18</v>
-      </c>
-      <c r="BG109">
-        <v>1.33</v>
-      </c>
-      <c r="BH109">
-        <v>2.88</v>
-      </c>
-      <c r="BI109">
-        <v>1.58</v>
-      </c>
-      <c r="BJ109">
-        <v>2.14</v>
-      </c>
-      <c r="BK109">
-        <v>1.96</v>
-      </c>
-      <c r="BL109">
-        <v>1.7</v>
-      </c>
-      <c r="BM109">
-        <v>2.5</v>
-      </c>
-      <c r="BN109">
-        <v>1.43</v>
-      </c>
-      <c r="BO109">
-        <v>3.3</v>
-      </c>
-      <c r="BP109">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="110" spans="1:68">
-      <c r="A110" s="1">
-        <v>109</v>
-      </c>
-      <c r="B110">
-        <v>7818912</v>
-      </c>
-      <c r="C110" t="s">
-        <v>68</v>
-      </c>
-      <c r="D110" t="s">
-        <v>69</v>
-      </c>
-      <c r="E110" s="2">
-        <v>45825.79166666666</v>
-      </c>
-      <c r="F110">
-        <v>14</v>
-      </c>
-      <c r="G110" t="s">
-        <v>84</v>
-      </c>
-      <c r="H110" t="s">
-        <v>83</v>
-      </c>
-      <c r="I110">
-        <v>1</v>
-      </c>
-      <c r="J110">
-        <v>0</v>
-      </c>
-      <c r="K110">
-        <v>1</v>
-      </c>
-      <c r="L110">
-        <v>4</v>
-      </c>
-      <c r="M110">
-        <v>0</v>
-      </c>
-      <c r="N110">
-        <v>4</v>
-      </c>
-      <c r="O110" t="s">
-        <v>166</v>
-      </c>
-      <c r="P110" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q110">
-        <v>1.95</v>
-      </c>
-      <c r="R110">
-        <v>2.4</v>
-      </c>
-      <c r="S110">
-        <v>6.5</v>
-      </c>
-      <c r="T110">
-        <v>1.33</v>
-      </c>
-      <c r="U110">
-        <v>3.25</v>
-      </c>
-      <c r="V110">
-        <v>2.63</v>
-      </c>
-      <c r="W110">
-        <v>1.44</v>
-      </c>
-      <c r="X110">
-        <v>6.5</v>
-      </c>
-      <c r="Y110">
-        <v>1.11</v>
-      </c>
-      <c r="Z110">
-        <v>1.45</v>
-      </c>
-      <c r="AA110">
-        <v>4</v>
-      </c>
-      <c r="AB110">
-        <v>7.5</v>
-      </c>
-      <c r="AC110">
-        <v>1.01</v>
-      </c>
-      <c r="AD110">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AE110">
-        <v>1.19</v>
-      </c>
-      <c r="AF110">
-        <v>3.78</v>
-      </c>
-      <c r="AG110">
-        <v>1.75</v>
-      </c>
-      <c r="AH110">
-        <v>2.05</v>
-      </c>
-      <c r="AI110">
-        <v>1.91</v>
-      </c>
-      <c r="AJ110">
-        <v>1.8</v>
-      </c>
-      <c r="AK110">
-        <v>1.08</v>
-      </c>
-      <c r="AL110">
-        <v>1.18</v>
-      </c>
-      <c r="AM110">
-        <v>2.78</v>
-      </c>
-      <c r="AN110">
-        <v>1.83</v>
-      </c>
-      <c r="AO110">
-        <v>1.33</v>
-      </c>
-      <c r="AP110">
-        <v>2</v>
-      </c>
-      <c r="AQ110">
-        <v>1.14</v>
-      </c>
-      <c r="AR110">
-        <v>2.16</v>
-      </c>
-      <c r="AS110">
-        <v>1.49</v>
-      </c>
-      <c r="AT110">
-        <v>3.65</v>
-      </c>
-      <c r="AU110">
-        <v>7</v>
-      </c>
-      <c r="AV110">
-        <v>6</v>
-      </c>
-      <c r="AW110">
-        <v>10</v>
-      </c>
-      <c r="AX110">
-        <v>7</v>
-      </c>
-      <c r="AY110">
-        <v>17</v>
-      </c>
-      <c r="AZ110">
-        <v>13</v>
-      </c>
-      <c r="BA110">
-        <v>8</v>
-      </c>
-      <c r="BB110">
-        <v>2</v>
-      </c>
-      <c r="BC110">
-        <v>10</v>
-      </c>
-      <c r="BD110">
-        <v>1.32</v>
-      </c>
-      <c r="BE110">
-        <v>7.5</v>
-      </c>
-      <c r="BF110">
-        <v>3.65</v>
-      </c>
-      <c r="BG110">
-        <v>1.28</v>
-      </c>
-      <c r="BH110">
-        <v>3.15</v>
-      </c>
-      <c r="BI110">
-        <v>1.49</v>
-      </c>
-      <c r="BJ110">
-        <v>2.35</v>
-      </c>
-      <c r="BK110">
-        <v>1.79</v>
-      </c>
-      <c r="BL110">
-        <v>1.85</v>
-      </c>
-      <c r="BM110">
-        <v>2.23</v>
-      </c>
-      <c r="BN110">
-        <v>1.54</v>
-      </c>
-      <c r="BO110">
-        <v>2.88</v>
-      </c>
-      <c r="BP110">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="111" spans="1:68">
-      <c r="A111" s="1">
-        <v>110</v>
-      </c>
-      <c r="B111">
-        <v>7818920</v>
-      </c>
-      <c r="C111" t="s">
-        <v>68</v>
-      </c>
-      <c r="D111" t="s">
-        <v>69</v>
-      </c>
-      <c r="E111" s="2">
-        <v>45828.77083333334</v>
-      </c>
-      <c r="F111">
-        <v>15</v>
-      </c>
-      <c r="G111" t="s">
-        <v>77</v>
-      </c>
-      <c r="H111" t="s">
-        <v>76</v>
-      </c>
-      <c r="I111">
-        <v>1</v>
-      </c>
-      <c r="J111">
-        <v>1</v>
-      </c>
-      <c r="K111">
-        <v>2</v>
-      </c>
-      <c r="L111">
-        <v>1</v>
-      </c>
-      <c r="M111">
-        <v>1</v>
-      </c>
-      <c r="N111">
-        <v>2</v>
-      </c>
-      <c r="O111" t="s">
-        <v>167</v>
-      </c>
-      <c r="P111" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q111">
-        <v>3.3</v>
-      </c>
-      <c r="R111">
-        <v>2</v>
-      </c>
-      <c r="S111">
-        <v>3.3</v>
-      </c>
-      <c r="T111">
-        <v>1.48</v>
-      </c>
-      <c r="U111">
-        <v>2.48</v>
-      </c>
-      <c r="V111">
-        <v>3.3</v>
-      </c>
-      <c r="W111">
-        <v>1.29</v>
-      </c>
-      <c r="X111">
-        <v>8</v>
-      </c>
-      <c r="Y111">
-        <v>1.04</v>
-      </c>
-      <c r="Z111">
-        <v>2.55</v>
-      </c>
-      <c r="AA111">
-        <v>3.2</v>
-      </c>
-      <c r="AB111">
-        <v>2.65</v>
-      </c>
-      <c r="AC111">
-        <v>1.05</v>
-      </c>
-      <c r="AD111">
-        <v>8</v>
-      </c>
-      <c r="AE111">
-        <v>1.36</v>
-      </c>
-      <c r="AF111">
-        <v>2.88</v>
-      </c>
-      <c r="AG111">
-        <v>2.28</v>
-      </c>
-      <c r="AH111">
-        <v>1.58</v>
-      </c>
-      <c r="AI111">
-        <v>1.91</v>
-      </c>
-      <c r="AJ111">
-        <v>1.77</v>
-      </c>
-      <c r="AK111">
-        <v>1.46</v>
-      </c>
-      <c r="AL111">
-        <v>1.33</v>
-      </c>
-      <c r="AM111">
-        <v>1.49</v>
-      </c>
-      <c r="AN111">
-        <v>1.86</v>
-      </c>
-      <c r="AO111">
-        <v>0.86</v>
-      </c>
-      <c r="AP111">
-        <v>1.75</v>
-      </c>
-      <c r="AQ111">
-        <v>0.88</v>
-      </c>
-      <c r="AR111">
-        <v>1.47</v>
-      </c>
-      <c r="AS111">
-        <v>1.22</v>
-      </c>
-      <c r="AT111">
-        <v>2.69</v>
-      </c>
-      <c r="AU111">
-        <v>3</v>
-      </c>
-      <c r="AV111">
-        <v>6</v>
-      </c>
-      <c r="AW111">
-        <v>5</v>
-      </c>
-      <c r="AX111">
-        <v>7</v>
-      </c>
-      <c r="AY111">
-        <v>8</v>
-      </c>
-      <c r="AZ111">
-        <v>13</v>
-      </c>
-      <c r="BA111">
-        <v>7</v>
-      </c>
-      <c r="BB111">
-        <v>5</v>
-      </c>
-      <c r="BC111">
-        <v>12</v>
-      </c>
-      <c r="BD111">
-        <v>1.82</v>
-      </c>
-      <c r="BE111">
-        <v>6.4</v>
-      </c>
-      <c r="BF111">
-        <v>2.18</v>
-      </c>
-      <c r="BG111">
-        <v>1.38</v>
-      </c>
-      <c r="BH111">
-        <v>2.65</v>
-      </c>
-      <c r="BI111">
-        <v>1.65</v>
-      </c>
-      <c r="BJ111">
-        <v>2.02</v>
-      </c>
-      <c r="BK111">
-        <v>2.06</v>
-      </c>
-      <c r="BL111">
-        <v>1.63</v>
-      </c>
-      <c r="BM111">
-        <v>2.65</v>
-      </c>
-      <c r="BN111">
-        <v>1.38</v>
-      </c>
-      <c r="BO111">
-        <v>3.5</v>
-      </c>
-      <c r="BP111">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="112" spans="1:68">
-      <c r="A112" s="1">
-        <v>111</v>
-      </c>
-      <c r="B112">
-        <v>7818922</v>
-      </c>
-      <c r="C112" t="s">
-        <v>68</v>
-      </c>
-      <c r="D112" t="s">
-        <v>69</v>
-      </c>
-      <c r="E112" s="2">
-        <v>45829.5625</v>
-      </c>
-      <c r="F112">
-        <v>15</v>
-      </c>
-      <c r="G112" t="s">
-        <v>79</v>
-      </c>
-      <c r="H112" t="s">
-        <v>80</v>
-      </c>
-      <c r="I112">
-        <v>0</v>
-      </c>
-      <c r="J112">
-        <v>1</v>
-      </c>
-      <c r="K112">
-        <v>1</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112">
-        <v>2</v>
-      </c>
-      <c r="N112">
-        <v>2</v>
-      </c>
-      <c r="O112" t="s">
-        <v>86</v>
-      </c>
-      <c r="P112" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q112">
-        <v>3.45</v>
-      </c>
-      <c r="R112">
-        <v>2.18</v>
-      </c>
-      <c r="S112">
-        <v>2.75</v>
-      </c>
-      <c r="T112">
-        <v>1.36</v>
-      </c>
-      <c r="U112">
-        <v>2.95</v>
-      </c>
-      <c r="V112">
-        <v>2.7</v>
-      </c>
-      <c r="W112">
-        <v>1.43</v>
-      </c>
-      <c r="X112">
-        <v>6.4</v>
-      </c>
-      <c r="Y112">
-        <v>1.08</v>
-      </c>
-      <c r="Z112">
-        <v>2.95</v>
-      </c>
-      <c r="AA112">
-        <v>3.45</v>
-      </c>
-      <c r="AB112">
-        <v>2.2</v>
-      </c>
-      <c r="AC112">
-        <v>1.01</v>
-      </c>
-      <c r="AD112">
-        <v>8.4</v>
-      </c>
-      <c r="AE112">
-        <v>1.28</v>
-      </c>
-      <c r="AF112">
-        <v>3.1</v>
-      </c>
-      <c r="AG112">
-        <v>1.86</v>
-      </c>
-      <c r="AH112">
-        <v>1.86</v>
-      </c>
-      <c r="AI112">
-        <v>1.68</v>
-      </c>
-      <c r="AJ112">
-        <v>2.04</v>
-      </c>
-      <c r="AK112">
-        <v>1.63</v>
-      </c>
-      <c r="AL112">
-        <v>1.29</v>
-      </c>
-      <c r="AM112">
-        <v>1.38</v>
-      </c>
-      <c r="AN112">
-        <v>0.67</v>
-      </c>
-      <c r="AO112">
-        <v>2</v>
-      </c>
-      <c r="AP112">
-        <v>0.5</v>
-      </c>
-      <c r="AQ112">
-        <v>2.13</v>
-      </c>
-      <c r="AR112">
-        <v>1.64</v>
-      </c>
-      <c r="AS112">
-        <v>1.39</v>
-      </c>
-      <c r="AT112">
-        <v>3.03</v>
-      </c>
-      <c r="AU112">
-        <v>2</v>
-      </c>
-      <c r="AV112">
-        <v>10</v>
-      </c>
-      <c r="AW112">
-        <v>4</v>
-      </c>
-      <c r="AX112">
-        <v>11</v>
-      </c>
-      <c r="AY112">
-        <v>6</v>
-      </c>
-      <c r="AZ112">
-        <v>21</v>
-      </c>
-      <c r="BA112">
-        <v>2</v>
-      </c>
-      <c r="BB112">
-        <v>9</v>
-      </c>
-      <c r="BC112">
-        <v>11</v>
-      </c>
-      <c r="BD112">
-        <v>1.95</v>
-      </c>
-      <c r="BE112">
-        <v>6.75</v>
-      </c>
-      <c r="BF112">
-        <v>2.02</v>
-      </c>
-      <c r="BG112">
-        <v>1.18</v>
-      </c>
-      <c r="BH112">
-        <v>3.9</v>
-      </c>
-      <c r="BI112">
-        <v>1.34</v>
-      </c>
-      <c r="BJ112">
-        <v>2.8</v>
-      </c>
-      <c r="BK112">
-        <v>1.57</v>
-      </c>
-      <c r="BL112">
-        <v>2.17</v>
-      </c>
-      <c r="BM112">
-        <v>1.91</v>
-      </c>
-      <c r="BN112">
-        <v>1.74</v>
-      </c>
-      <c r="BO112">
-        <v>2.38</v>
-      </c>
-      <c r="BP112">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="113" spans="1:68">
-      <c r="A113" s="1">
-        <v>112</v>
-      </c>
-      <c r="B113">
-        <v>7818921</v>
-      </c>
-      <c r="C113" t="s">
-        <v>68</v>
-      </c>
-      <c r="D113" t="s">
-        <v>69</v>
-      </c>
-      <c r="E113" s="2">
-        <v>45829.66666666666</v>
-      </c>
-      <c r="F113">
-        <v>15</v>
-      </c>
-      <c r="G113" t="s">
-        <v>73</v>
-      </c>
-      <c r="H113" t="s">
-        <v>70</v>
-      </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-      <c r="J113">
-        <v>1</v>
-      </c>
-      <c r="K113">
-        <v>1</v>
-      </c>
-      <c r="L113">
-        <v>3</v>
-      </c>
-      <c r="M113">
-        <v>1</v>
-      </c>
-      <c r="N113">
-        <v>4</v>
-      </c>
-      <c r="O113" t="s">
-        <v>168</v>
-      </c>
-      <c r="P113" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q113">
-        <v>1.76</v>
-      </c>
-      <c r="R113">
-        <v>2.55</v>
-      </c>
-      <c r="S113">
-        <v>6.75</v>
-      </c>
-      <c r="T113">
-        <v>1.27</v>
-      </c>
-      <c r="U113">
-        <v>3.4</v>
-      </c>
-      <c r="V113">
-        <v>2.3</v>
-      </c>
-      <c r="W113">
-        <v>1.55</v>
-      </c>
-      <c r="X113">
-        <v>5.1</v>
-      </c>
-      <c r="Y113">
-        <v>1.13</v>
-      </c>
-      <c r="Z113">
-        <v>1.29</v>
-      </c>
-      <c r="AA113">
-        <v>4.8</v>
-      </c>
-      <c r="AB113">
-        <v>10</v>
-      </c>
-      <c r="AC113">
-        <v>1.01</v>
-      </c>
-      <c r="AD113">
-        <v>17</v>
-      </c>
-      <c r="AE113">
-        <v>1.1</v>
-      </c>
-      <c r="AF113">
-        <v>5.1</v>
-      </c>
-      <c r="AG113">
-        <v>1.57</v>
-      </c>
-      <c r="AH113">
-        <v>2.28</v>
-      </c>
-      <c r="AI113">
-        <v>1.89</v>
-      </c>
-      <c r="AJ113">
-        <v>1.8</v>
-      </c>
-      <c r="AK113">
-        <v>1.05</v>
-      </c>
-      <c r="AL113">
-        <v>1.18</v>
-      </c>
-      <c r="AM113">
-        <v>3.2</v>
-      </c>
-      <c r="AN113">
-        <v>3</v>
-      </c>
-      <c r="AO113">
-        <v>0.29</v>
-      </c>
-      <c r="AP113">
-        <v>3</v>
-      </c>
-      <c r="AQ113">
-        <v>0.25</v>
-      </c>
-      <c r="AR113">
-        <v>2.13</v>
-      </c>
-      <c r="AS113">
-        <v>1.31</v>
-      </c>
-      <c r="AT113">
-        <v>3.44</v>
-      </c>
-      <c r="AU113">
-        <v>10</v>
-      </c>
-      <c r="AV113">
-        <v>5</v>
-      </c>
-      <c r="AW113">
-        <v>9</v>
-      </c>
-      <c r="AX113">
-        <v>3</v>
-      </c>
-      <c r="AY113">
-        <v>19</v>
-      </c>
-      <c r="AZ113">
-        <v>8</v>
-      </c>
-      <c r="BA113">
-        <v>7</v>
-      </c>
-      <c r="BB113">
-        <v>1</v>
-      </c>
-      <c r="BC113">
-        <v>8</v>
-      </c>
-      <c r="BD113">
-        <v>1.26</v>
-      </c>
-      <c r="BE113">
-        <v>8</v>
-      </c>
-      <c r="BF113">
-        <v>4.1</v>
-      </c>
-      <c r="BG113">
-        <v>1.27</v>
-      </c>
-      <c r="BH113">
-        <v>3.2</v>
-      </c>
-      <c r="BI113">
-        <v>1.47</v>
-      </c>
-      <c r="BJ113">
-        <v>2.38</v>
-      </c>
-      <c r="BK113">
-        <v>1.78</v>
-      </c>
-      <c r="BL113">
-        <v>1.87</v>
-      </c>
-      <c r="BM113">
-        <v>2.2</v>
-      </c>
-      <c r="BN113">
-        <v>1.55</v>
-      </c>
-      <c r="BO113">
-        <v>2.8</v>
-      </c>
-      <c r="BP113">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="114" spans="1:68">
-      <c r="A114" s="1">
-        <v>113</v>
-      </c>
-      <c r="B114">
-        <v>7818924</v>
-      </c>
-      <c r="C114" t="s">
-        <v>68</v>
-      </c>
-      <c r="D114" t="s">
-        <v>69</v>
-      </c>
-      <c r="E114" s="2">
-        <v>45829.77083333334</v>
-      </c>
-      <c r="F114">
-        <v>15</v>
-      </c>
-      <c r="G114" t="s">
-        <v>82</v>
-      </c>
-      <c r="H114" t="s">
-        <v>71</v>
-      </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-      <c r="J114">
-        <v>2</v>
-      </c>
-      <c r="K114">
-        <v>2</v>
-      </c>
-      <c r="L114">
-        <v>2</v>
-      </c>
-      <c r="M114">
-        <v>2</v>
-      </c>
-      <c r="N114">
-        <v>4</v>
-      </c>
-      <c r="O114" t="s">
-        <v>169</v>
-      </c>
-      <c r="P114" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q114">
-        <v>3.3</v>
-      </c>
-      <c r="R114">
-        <v>2.17</v>
-      </c>
-      <c r="S114">
-        <v>2.9</v>
-      </c>
-      <c r="T114">
-        <v>1.38</v>
-      </c>
-      <c r="U114">
-        <v>2.88</v>
-      </c>
-      <c r="V114">
-        <v>2.8</v>
-      </c>
-      <c r="W114">
-        <v>1.38</v>
-      </c>
-      <c r="X114">
-        <v>6.75</v>
-      </c>
-      <c r="Y114">
-        <v>1.07</v>
-      </c>
-      <c r="Z114">
-        <v>2.75</v>
-      </c>
-      <c r="AA114">
-        <v>3.25</v>
-      </c>
-      <c r="AB114">
-        <v>2.3</v>
-      </c>
-      <c r="AC114">
-        <v>1.03</v>
-      </c>
-      <c r="AD114">
-        <v>9</v>
-      </c>
-      <c r="AE114">
-        <v>1.29</v>
-      </c>
-      <c r="AF114">
-        <v>3.3</v>
-      </c>
-      <c r="AG114">
-        <v>1.94</v>
-      </c>
-      <c r="AH114">
-        <v>1.79</v>
-      </c>
-      <c r="AI114">
-        <v>1.73</v>
-      </c>
-      <c r="AJ114">
-        <v>1.97</v>
-      </c>
-      <c r="AK114">
-        <v>1.55</v>
-      </c>
-      <c r="AL114">
-        <v>1.29</v>
-      </c>
-      <c r="AM114">
-        <v>1.44</v>
-      </c>
-      <c r="AN114">
-        <v>2</v>
-      </c>
-      <c r="AO114">
-        <v>2</v>
-      </c>
-      <c r="AP114">
-        <v>1.86</v>
-      </c>
-      <c r="AQ114">
-        <v>1.88</v>
-      </c>
-      <c r="AR114">
-        <v>1.4</v>
-      </c>
-      <c r="AS114">
-        <v>1.53</v>
-      </c>
-      <c r="AT114">
-        <v>2.93</v>
-      </c>
-      <c r="AU114">
-        <v>10</v>
-      </c>
-      <c r="AV114">
-        <v>5</v>
-      </c>
-      <c r="AW114">
-        <v>11</v>
-      </c>
-      <c r="AX114">
-        <v>6</v>
-      </c>
-      <c r="AY114">
-        <v>21</v>
-      </c>
-      <c r="AZ114">
-        <v>11</v>
-      </c>
-      <c r="BA114">
-        <v>4</v>
-      </c>
-      <c r="BB114">
-        <v>2</v>
-      </c>
-      <c r="BC114">
-        <v>6</v>
-      </c>
-      <c r="BD114">
-        <v>1.95</v>
-      </c>
-      <c r="BE114">
-        <v>6.4</v>
-      </c>
-      <c r="BF114">
-        <v>2.05</v>
-      </c>
-      <c r="BG114">
-        <v>1.35</v>
-      </c>
-      <c r="BH114">
-        <v>2.8</v>
-      </c>
-      <c r="BI114">
-        <v>1.58</v>
-      </c>
-      <c r="BJ114">
-        <v>2.12</v>
-      </c>
-      <c r="BK114">
-        <v>1.96</v>
-      </c>
-      <c r="BL114">
-        <v>1.7</v>
-      </c>
-      <c r="BM114">
-        <v>2.55</v>
-      </c>
-      <c r="BN114">
-        <v>1.42</v>
-      </c>
-      <c r="BO114">
-        <v>3.3</v>
-      </c>
-      <c r="BP114">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="115" spans="1:68">
-      <c r="A115" s="1">
-        <v>114</v>
-      </c>
-      <c r="B115">
-        <v>7818923</v>
-      </c>
-      <c r="C115" t="s">
-        <v>68</v>
-      </c>
-      <c r="D115" t="s">
-        <v>69</v>
-      </c>
-      <c r="E115" s="2">
-        <v>45830.5625</v>
-      </c>
-      <c r="F115">
-        <v>15</v>
-      </c>
-      <c r="G115" t="s">
-        <v>74</v>
-      </c>
-      <c r="H115" t="s">
-        <v>75</v>
-      </c>
-      <c r="I115">
-        <v>0</v>
-      </c>
-      <c r="J115">
-        <v>1</v>
-      </c>
-      <c r="K115">
-        <v>1</v>
-      </c>
-      <c r="L115">
-        <v>1</v>
-      </c>
-      <c r="M115">
-        <v>1</v>
-      </c>
-      <c r="N115">
-        <v>2</v>
-      </c>
-      <c r="O115" t="s">
-        <v>170</v>
-      </c>
-      <c r="P115" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q115">
-        <v>3</v>
-      </c>
-      <c r="R115">
-        <v>2.25</v>
-      </c>
-      <c r="S115">
-        <v>3.4</v>
-      </c>
-      <c r="T115">
-        <v>1.36</v>
-      </c>
-      <c r="U115">
-        <v>3</v>
-      </c>
-      <c r="V115">
-        <v>2.63</v>
-      </c>
-      <c r="W115">
-        <v>1.44</v>
-      </c>
-      <c r="X115">
-        <v>7</v>
-      </c>
-      <c r="Y115">
-        <v>1.1</v>
-      </c>
-      <c r="Z115">
-        <v>2.44</v>
-      </c>
-      <c r="AA115">
-        <v>3.54</v>
-      </c>
-      <c r="AB115">
-        <v>2.75</v>
-      </c>
-      <c r="AC115">
-        <v>1</v>
-      </c>
-      <c r="AD115">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AE115">
-        <v>1.27</v>
-      </c>
-      <c r="AF115">
-        <v>3.66</v>
-      </c>
-      <c r="AG115">
-        <v>1.86</v>
-      </c>
-      <c r="AH115">
-        <v>1.96</v>
-      </c>
-      <c r="AI115">
-        <v>1.67</v>
-      </c>
-      <c r="AJ115">
-        <v>2.1</v>
-      </c>
-      <c r="AK115">
-        <v>1.44</v>
-      </c>
-      <c r="AL115">
-        <v>1.29</v>
-      </c>
-      <c r="AM115">
-        <v>1.53</v>
-      </c>
-      <c r="AN115">
-        <v>2</v>
-      </c>
-      <c r="AO115">
-        <v>0.33</v>
-      </c>
-      <c r="AP115">
-        <v>1.86</v>
-      </c>
-      <c r="AQ115">
-        <v>0.43</v>
-      </c>
-      <c r="AR115">
-        <v>1.68</v>
-      </c>
-      <c r="AS115">
-        <v>1.62</v>
-      </c>
-      <c r="AT115">
-        <v>3.3</v>
-      </c>
-      <c r="AU115">
-        <v>6</v>
-      </c>
-      <c r="AV115">
-        <v>5</v>
-      </c>
-      <c r="AW115">
-        <v>12</v>
-      </c>
-      <c r="AX115">
-        <v>11</v>
-      </c>
-      <c r="AY115">
-        <v>18</v>
-      </c>
-      <c r="AZ115">
-        <v>16</v>
-      </c>
-      <c r="BA115">
-        <v>2</v>
-      </c>
-      <c r="BB115">
-        <v>5</v>
-      </c>
-      <c r="BC115">
-        <v>7</v>
-      </c>
-      <c r="BD115">
-        <v>1.97</v>
-      </c>
-      <c r="BE115">
-        <v>6.4</v>
-      </c>
-      <c r="BF115">
-        <v>2.02</v>
-      </c>
-      <c r="BG115">
-        <v>1.26</v>
-      </c>
-      <c r="BH115">
-        <v>3.3</v>
-      </c>
-      <c r="BI115">
-        <v>1.46</v>
-      </c>
-      <c r="BJ115">
-        <v>2.4</v>
-      </c>
-      <c r="BK115">
-        <v>1.77</v>
-      </c>
-      <c r="BL115">
-        <v>1.88</v>
-      </c>
-      <c r="BM115">
-        <v>2.2</v>
-      </c>
-      <c r="BN115">
-        <v>1.55</v>
-      </c>
-      <c r="BO115">
-        <v>2.8</v>
-      </c>
-      <c r="BP115">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="116" spans="1:68">
-      <c r="A116" s="1">
-        <v>115</v>
-      </c>
-      <c r="B116">
-        <v>7818919</v>
-      </c>
-      <c r="C116" t="s">
-        <v>68</v>
-      </c>
-      <c r="D116" t="s">
-        <v>69</v>
-      </c>
-      <c r="E116" s="2">
-        <v>45830.66666666666</v>
-      </c>
-      <c r="F116">
-        <v>15</v>
-      </c>
-      <c r="G116" t="s">
-        <v>78</v>
-      </c>
-      <c r="H116" t="s">
-        <v>84</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116">
-        <v>0</v>
-      </c>
-      <c r="L116">
-        <v>2</v>
-      </c>
-      <c r="M116">
-        <v>1</v>
-      </c>
-      <c r="N116">
-        <v>3</v>
-      </c>
-      <c r="O116" t="s">
-        <v>171</v>
-      </c>
-      <c r="P116" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q116">
-        <v>4.33</v>
-      </c>
-      <c r="R116">
-        <v>2.2</v>
-      </c>
-      <c r="S116">
-        <v>2.5</v>
-      </c>
-      <c r="T116">
-        <v>1.36</v>
-      </c>
-      <c r="U116">
-        <v>3</v>
-      </c>
-      <c r="V116">
-        <v>2.75</v>
-      </c>
-      <c r="W116">
-        <v>1.4</v>
-      </c>
-      <c r="X116">
-        <v>7</v>
-      </c>
-      <c r="Y116">
-        <v>1.1</v>
-      </c>
-      <c r="Z116">
-        <v>3.7</v>
-      </c>
-      <c r="AA116">
-        <v>3.5</v>
-      </c>
-      <c r="AB116">
-        <v>1.91</v>
-      </c>
-      <c r="AC116">
-        <v>1.01</v>
-      </c>
-      <c r="AD116">
-        <v>9.9</v>
-      </c>
-      <c r="AE116">
-        <v>1.24</v>
-      </c>
-      <c r="AF116">
-        <v>3.36</v>
-      </c>
-      <c r="AG116">
-        <v>1.9</v>
-      </c>
-      <c r="AH116">
-        <v>1.9</v>
-      </c>
-      <c r="AI116">
-        <v>1.73</v>
-      </c>
-      <c r="AJ116">
-        <v>2</v>
-      </c>
-      <c r="AK116">
-        <v>1.79</v>
-      </c>
-      <c r="AL116">
-        <v>1.28</v>
-      </c>
-      <c r="AM116">
-        <v>1.28</v>
-      </c>
-      <c r="AN116">
-        <v>2.71</v>
-      </c>
-      <c r="AO116">
-        <v>1.4</v>
-      </c>
-      <c r="AP116">
-        <v>2.75</v>
-      </c>
-      <c r="AQ116">
-        <v>1.17</v>
-      </c>
-      <c r="AR116">
-        <v>1.79</v>
-      </c>
-      <c r="AS116">
-        <v>1.84</v>
-      </c>
-      <c r="AT116">
-        <v>3.63</v>
-      </c>
-      <c r="AU116">
-        <v>5</v>
-      </c>
-      <c r="AV116">
-        <v>13</v>
-      </c>
-      <c r="AW116">
-        <v>8</v>
-      </c>
-      <c r="AX116">
-        <v>13</v>
-      </c>
-      <c r="AY116">
-        <v>13</v>
-      </c>
-      <c r="AZ116">
-        <v>26</v>
-      </c>
-      <c r="BA116">
-        <v>2</v>
-      </c>
-      <c r="BB116">
-        <v>7</v>
-      </c>
-      <c r="BC116">
-        <v>9</v>
-      </c>
-      <c r="BD116">
-        <v>2.65</v>
-      </c>
-      <c r="BE116">
-        <v>6.5</v>
-      </c>
-      <c r="BF116">
-        <v>1.56</v>
-      </c>
-      <c r="BG116">
-        <v>1.37</v>
-      </c>
-      <c r="BH116">
-        <v>2.7</v>
-      </c>
-      <c r="BI116">
-        <v>1.62</v>
-      </c>
-      <c r="BJ116">
-        <v>2.08</v>
-      </c>
-      <c r="BK116">
-        <v>2</v>
-      </c>
-      <c r="BL116">
-        <v>1.67</v>
-      </c>
-      <c r="BM116">
-        <v>2.55</v>
-      </c>
-      <c r="BN116">
-        <v>1.42</v>
-      </c>
-      <c r="BO116">
-        <v>3.35</v>
-      </c>
-      <c r="BP116">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="117" spans="1:68">
-      <c r="A117" s="1">
-        <v>116</v>
-      </c>
-      <c r="B117">
-        <v>7818926</v>
-      </c>
-      <c r="C117" t="s">
-        <v>68</v>
-      </c>
-      <c r="D117" t="s">
-        <v>69</v>
-      </c>
-      <c r="E117" s="2">
-        <v>45830.77083333334</v>
-      </c>
-      <c r="F117">
-        <v>15</v>
-      </c>
-      <c r="G117" t="s">
-        <v>83</v>
-      </c>
-      <c r="H117" t="s">
-        <v>81</v>
-      </c>
-      <c r="I117">
-        <v>1</v>
-      </c>
-      <c r="J117">
-        <v>1</v>
-      </c>
-      <c r="K117">
-        <v>2</v>
-      </c>
-      <c r="L117">
-        <v>1</v>
-      </c>
-      <c r="M117">
-        <v>1</v>
-      </c>
-      <c r="N117">
-        <v>2</v>
-      </c>
-      <c r="O117" t="s">
-        <v>172</v>
-      </c>
-      <c r="P117" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q117">
-        <v>2.75</v>
-      </c>
-      <c r="R117">
-        <v>2.2</v>
-      </c>
-      <c r="S117">
-        <v>3.75</v>
-      </c>
-      <c r="T117">
-        <v>1.36</v>
-      </c>
-      <c r="U117">
-        <v>3</v>
-      </c>
-      <c r="V117">
-        <v>2.75</v>
-      </c>
-      <c r="W117">
-        <v>1.4</v>
-      </c>
-      <c r="X117">
-        <v>7</v>
-      </c>
-      <c r="Y117">
-        <v>1.1</v>
-      </c>
-      <c r="Z117">
-        <v>2.15</v>
-      </c>
-      <c r="AA117">
-        <v>3.25</v>
-      </c>
-      <c r="AB117">
-        <v>3.3</v>
-      </c>
-      <c r="AC117">
-        <v>1.01</v>
-      </c>
-      <c r="AD117">
-        <v>9.85</v>
-      </c>
-      <c r="AE117">
-        <v>1.22</v>
-      </c>
-      <c r="AF117">
-        <v>3.5</v>
-      </c>
-      <c r="AG117">
-        <v>1.85</v>
-      </c>
-      <c r="AH117">
-        <v>1.95</v>
-      </c>
-      <c r="AI117">
-        <v>1.67</v>
-      </c>
-      <c r="AJ117">
-        <v>2.1</v>
-      </c>
-      <c r="AK117">
-        <v>1.33</v>
-      </c>
-      <c r="AL117">
-        <v>1.29</v>
-      </c>
-      <c r="AM117">
-        <v>1.67</v>
-      </c>
-      <c r="AN117">
-        <v>2</v>
-      </c>
-      <c r="AO117">
-        <v>1.17</v>
-      </c>
-      <c r="AP117">
-        <v>1.88</v>
-      </c>
-      <c r="AQ117">
-        <v>1.14</v>
-      </c>
-      <c r="AR117">
-        <v>1.73</v>
-      </c>
-      <c r="AS117">
-        <v>1.22</v>
-      </c>
-      <c r="AT117">
-        <v>2.95</v>
-      </c>
-      <c r="AU117">
-        <v>6</v>
-      </c>
-      <c r="AV117">
-        <v>5</v>
-      </c>
-      <c r="AW117">
-        <v>9</v>
-      </c>
-      <c r="AX117">
-        <v>12</v>
-      </c>
-      <c r="AY117">
-        <v>15</v>
-      </c>
-      <c r="AZ117">
-        <v>17</v>
-      </c>
-      <c r="BA117">
-        <v>3</v>
-      </c>
-      <c r="BB117">
-        <v>11</v>
-      </c>
-      <c r="BC117">
-        <v>14</v>
-      </c>
-      <c r="BD117">
-        <v>1.75</v>
-      </c>
-      <c r="BE117">
-        <v>6.5</v>
-      </c>
-      <c r="BF117">
-        <v>2.3</v>
-      </c>
-      <c r="BG117">
-        <v>1.3</v>
-      </c>
-      <c r="BH117">
-        <v>3.05</v>
-      </c>
-      <c r="BI117">
-        <v>1.53</v>
-      </c>
-      <c r="BJ117">
-        <v>2.25</v>
-      </c>
-      <c r="BK117">
-        <v>1.87</v>
-      </c>
-      <c r="BL117">
-        <v>1.78</v>
-      </c>
-      <c r="BM117">
-        <v>2.35</v>
-      </c>
-      <c r="BN117">
-        <v>1.49</v>
-      </c>
-      <c r="BO117">
-        <v>3.05</v>
-      </c>
-      <c r="BP117">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="118" spans="1:68">
-      <c r="A118" s="1">
-        <v>117</v>
-      </c>
-      <c r="B118">
-        <v>7818925</v>
-      </c>
-      <c r="C118" t="s">
-        <v>68</v>
-      </c>
-      <c r="D118" t="s">
-        <v>69</v>
-      </c>
-      <c r="E118" s="2">
-        <v>45830.875</v>
-      </c>
-      <c r="F118">
-        <v>15</v>
-      </c>
-      <c r="G118" t="s">
-        <v>85</v>
-      </c>
-      <c r="H118" t="s">
-        <v>72</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>0</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118">
-        <v>1</v>
-      </c>
-      <c r="N118">
-        <v>1</v>
-      </c>
-      <c r="O118" t="s">
-        <v>86</v>
-      </c>
-      <c r="P118" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q118">
-        <v>3</v>
-      </c>
-      <c r="R118">
-        <v>2.1</v>
-      </c>
-      <c r="S118">
-        <v>3.6</v>
-      </c>
-      <c r="T118">
-        <v>1.4</v>
-      </c>
-      <c r="U118">
-        <v>2.75</v>
-      </c>
-      <c r="V118">
-        <v>3</v>
-      </c>
-      <c r="W118">
-        <v>1.36</v>
-      </c>
-      <c r="X118">
-        <v>8</v>
-      </c>
-      <c r="Y118">
-        <v>1.08</v>
-      </c>
-      <c r="Z118">
-        <v>2.3</v>
-      </c>
-      <c r="AA118">
-        <v>3.2</v>
-      </c>
-      <c r="AB118">
-        <v>3.1</v>
-      </c>
-      <c r="AC118">
-        <v>1.02</v>
-      </c>
-      <c r="AD118">
-        <v>7.9</v>
-      </c>
-      <c r="AE118">
-        <v>1.27</v>
-      </c>
-      <c r="AF118">
-        <v>3.15</v>
-      </c>
-      <c r="AG118">
-        <v>2.05</v>
-      </c>
-      <c r="AH118">
-        <v>1.75</v>
-      </c>
-      <c r="AI118">
-        <v>1.8</v>
-      </c>
-      <c r="AJ118">
-        <v>1.91</v>
-      </c>
-      <c r="AK118">
-        <v>1.36</v>
-      </c>
-      <c r="AL118">
-        <v>1.31</v>
-      </c>
-      <c r="AM118">
-        <v>1.61</v>
-      </c>
-      <c r="AN118">
-        <v>1</v>
-      </c>
-      <c r="AO118">
-        <v>1.14</v>
-      </c>
-      <c r="AP118">
-        <v>0.88</v>
-      </c>
-      <c r="AQ118">
-        <v>1.38</v>
-      </c>
-      <c r="AR118">
-        <v>1.81</v>
-      </c>
-      <c r="AS118">
-        <v>1.65</v>
-      </c>
-      <c r="AT118">
-        <v>3.46</v>
-      </c>
-      <c r="AU118">
-        <v>3</v>
-      </c>
-      <c r="AV118">
-        <v>4</v>
-      </c>
-      <c r="AW118">
-        <v>9</v>
-      </c>
-      <c r="AX118">
-        <v>11</v>
-      </c>
-      <c r="AY118">
-        <v>12</v>
-      </c>
-      <c r="AZ118">
-        <v>15</v>
-      </c>
-      <c r="BA118">
-        <v>3</v>
-      </c>
-      <c r="BB118">
-        <v>7</v>
-      </c>
-      <c r="BC118">
-        <v>10</v>
-      </c>
-      <c r="BD118">
-        <v>1.71</v>
-      </c>
-      <c r="BE118">
-        <v>6.75</v>
-      </c>
-      <c r="BF118">
-        <v>2.33</v>
-      </c>
-      <c r="BG118">
-        <v>1.19</v>
-      </c>
-      <c r="BH118">
-        <v>3.8</v>
-      </c>
-      <c r="BI118">
-        <v>1.35</v>
-      </c>
-      <c r="BJ118">
-        <v>2.8</v>
-      </c>
-      <c r="BK118">
-        <v>1.6</v>
-      </c>
-      <c r="BL118">
-        <v>2.12</v>
-      </c>
-      <c r="BM118">
-        <v>1.93</v>
-      </c>
-      <c r="BN118">
-        <v>1.72</v>
-      </c>
-      <c r="BO118">
-        <v>2.43</v>
-      </c>
-      <c r="BP118">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="119" spans="1:68">
-      <c r="A119" s="1">
-        <v>118</v>
-      </c>
-      <c r="B119">
-        <v>7818831</v>
-      </c>
-      <c r="C119" t="s">
-        <v>68</v>
-      </c>
-      <c r="D119" t="s">
-        <v>69</v>
-      </c>
-      <c r="E119" s="2">
-        <v>45843.66666666666</v>
-      </c>
-      <c r="F119">
-        <v>4</v>
-      </c>
-      <c r="G119" t="s">
-        <v>79</v>
-      </c>
-      <c r="H119" t="s">
-        <v>73</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>1</v>
-      </c>
-      <c r="K119">
-        <v>1</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119">
-        <v>2</v>
-      </c>
-      <c r="N119">
-        <v>2</v>
-      </c>
-      <c r="O119" t="s">
-        <v>86</v>
-      </c>
-      <c r="P119" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q119">
-        <v>4.5</v>
-      </c>
-      <c r="R119">
-        <v>2.3</v>
-      </c>
-      <c r="S119">
-        <v>2.38</v>
-      </c>
-      <c r="T119">
-        <v>1.33</v>
-      </c>
-      <c r="U119">
-        <v>3.25</v>
-      </c>
-      <c r="V119">
-        <v>2.5</v>
-      </c>
-      <c r="W119">
-        <v>1.5</v>
-      </c>
-      <c r="X119">
-        <v>6.5</v>
-      </c>
-      <c r="Y119">
-        <v>1.11</v>
-      </c>
-      <c r="Z119">
-        <v>4.2</v>
-      </c>
-      <c r="AA119">
-        <v>3.8</v>
-      </c>
-      <c r="AB119">
-        <v>1.8</v>
-      </c>
-      <c r="AC119">
-        <v>1.04</v>
-      </c>
-      <c r="AD119">
-        <v>13</v>
-      </c>
-      <c r="AE119">
-        <v>1.21</v>
-      </c>
-      <c r="AF119">
-        <v>4.32</v>
-      </c>
-      <c r="AG119">
-        <v>1.67</v>
-      </c>
-      <c r="AH119">
-        <v>2.15</v>
-      </c>
-      <c r="AI119">
-        <v>1.62</v>
-      </c>
-      <c r="AJ119">
-        <v>2.2</v>
-      </c>
-      <c r="AK119">
-        <v>1.91</v>
-      </c>
-      <c r="AL119">
-        <v>1.29</v>
-      </c>
-      <c r="AM119">
-        <v>1.25</v>
-      </c>
-      <c r="AN119">
-        <v>0.57</v>
-      </c>
-      <c r="AO119">
-        <v>0.67</v>
-      </c>
-      <c r="AP119">
-        <v>0.5</v>
-      </c>
-      <c r="AQ119">
-        <v>1</v>
-      </c>
-      <c r="AR119">
-        <v>1.53</v>
-      </c>
-      <c r="AS119">
-        <v>1.84</v>
-      </c>
-      <c r="AT119">
-        <v>3.37</v>
-      </c>
-      <c r="AU119">
-        <v>4</v>
-      </c>
-      <c r="AV119">
-        <v>4</v>
-      </c>
-      <c r="AW119">
-        <v>3</v>
-      </c>
-      <c r="AX119">
-        <v>7</v>
-      </c>
-      <c r="AY119">
-        <v>7</v>
-      </c>
-      <c r="AZ119">
-        <v>11</v>
-      </c>
-      <c r="BA119">
-        <v>4</v>
-      </c>
-      <c r="BB119">
-        <v>3</v>
-      </c>
-      <c r="BC119">
-        <v>7</v>
-      </c>
-      <c r="BD119">
-        <v>2.6</v>
-      </c>
-      <c r="BE119">
-        <v>6.75</v>
-      </c>
-      <c r="BF119">
-        <v>1.58</v>
-      </c>
-      <c r="BG119">
-        <v>1.25</v>
-      </c>
-      <c r="BH119">
-        <v>3.35</v>
-      </c>
-      <c r="BI119">
-        <v>1.44</v>
-      </c>
-      <c r="BJ119">
-        <v>2.45</v>
-      </c>
-      <c r="BK119">
-        <v>1.73</v>
-      </c>
-      <c r="BL119">
-        <v>1.93</v>
-      </c>
-      <c r="BM119">
-        <v>2.14</v>
-      </c>
-      <c r="BN119">
-        <v>1.58</v>
-      </c>
-      <c r="BO119">
-        <v>2.7</v>
-      </c>
-      <c r="BP119">
         <v>1.37</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="224">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -490,6 +490,51 @@
     <t>['74']</t>
   </si>
   <si>
+    <t>['32']</t>
+  </si>
+  <si>
+    <t>['45+5', '77']</t>
+  </si>
+  <si>
+    <t>['62', '90+1']</t>
+  </si>
+  <si>
+    <t>['36', '56']</t>
+  </si>
+  <si>
+    <t>['58', '65']</t>
+  </si>
+  <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['48']</t>
+  </si>
+  <si>
+    <t>['45+3', '84']</t>
+  </si>
+  <si>
+    <t>['27', '55', '75', '85']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['58', '70', '90+4']</t>
+  </si>
+  <si>
+    <t>['50', '64']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
+    <t>['66', '88']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -509,9 +554,6 @@
   </si>
   <si>
     <t>['78']</t>
-  </si>
-  <si>
-    <t>['67']</t>
   </si>
   <si>
     <t>['22', '57']</t>
@@ -601,9 +643,6 @@
     <t>['13', '45+6']</t>
   </si>
   <si>
-    <t>['53']</t>
-  </si>
-  <si>
     <t>['11', '57', '74']</t>
   </si>
   <si>
@@ -614,6 +653,36 @@
   </si>
   <si>
     <t>['13', '37', '77', '90']</t>
+  </si>
+  <si>
+    <t>['34', '64']</t>
+  </si>
+  <si>
+    <t>['53', '59']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['5', '10', '54']</t>
+  </si>
+  <si>
+    <t>['45+2', '48']</t>
+  </si>
+  <si>
+    <t>['42', '87']</t>
+  </si>
+  <si>
+    <t>['24']</t>
+  </si>
+  <si>
+    <t>['29', '45']</t>
+  </si>
+  <si>
+    <t>['14']</t>
+  </si>
+  <si>
+    <t>['75']</t>
   </si>
   <si>
     <t>['25', '90+7']</t>
@@ -978,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP98"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1234,7 +1303,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1312,10 +1381,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1518,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AQ3">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1724,10 +1793,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ4">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1933,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="AQ5">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2058,7 +2127,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2136,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2264,7 +2333,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2342,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2470,7 +2539,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2548,10 +2617,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ8">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2754,10 +2823,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2882,7 +2951,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2960,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ10">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3088,7 +3157,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3169,7 +3238,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3372,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ12">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3578,10 +3647,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3784,10 +3853,10 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ14">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3912,7 +3981,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3990,10 +4059,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AQ15">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4199,7 +4268,7 @@
         <v>3</v>
       </c>
       <c r="AQ16">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR16">
         <v>3.44</v>
@@ -4324,7 +4393,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="Q17">
         <v>1.91</v>
@@ -4402,10 +4471,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4530,7 +4599,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4608,10 +4677,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR18">
         <v>1.84</v>
@@ -4814,10 +4883,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ19">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR19">
         <v>1.05</v>
@@ -5020,10 +5089,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR20">
         <v>1.33</v>
@@ -5148,7 +5217,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5226,10 +5295,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AQ21">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR21">
         <v>1.92</v>
@@ -5354,7 +5423,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5432,10 +5501,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ22">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5560,7 +5629,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5638,10 +5707,10 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -5766,7 +5835,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5844,10 +5913,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AQ24">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>1.82</v>
@@ -5972,7 +6041,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6050,10 +6119,10 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR25">
         <v>1.33</v>
@@ -6256,10 +6325,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AQ26">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR26">
         <v>1.39</v>
@@ -6384,7 +6453,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6462,10 +6531,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="AR27">
         <v>2.18</v>
@@ -6590,7 +6659,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6668,10 +6737,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR28">
         <v>1.27</v>
@@ -6796,7 +6865,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6874,10 +6943,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ29">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
       <c r="AR29">
         <v>1.73</v>
@@ -7002,7 +7071,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7080,10 +7149,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR30">
         <v>1.85</v>
@@ -7286,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ31">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -7492,10 +7561,10 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.71</v>
@@ -7698,10 +7767,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ33">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.64</v>
@@ -7826,7 +7895,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -7904,10 +7973,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ34">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR34">
         <v>1.52</v>
@@ -8110,10 +8179,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ35">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR35">
         <v>2.29</v>
@@ -8316,10 +8385,10 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ36">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR36">
         <v>1.55</v>
@@ -8522,10 +8591,10 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AQ37">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR37">
         <v>1.78</v>
@@ -8728,10 +8797,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AQ38">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR38">
         <v>2</v>
@@ -8856,7 +8925,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -8934,10 +9003,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="AQ39">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR39">
         <v>1.64</v>
@@ -9062,7 +9131,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9140,10 +9209,10 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR40">
         <v>2.12</v>
@@ -9346,10 +9415,10 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ41">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>2.17</v>
@@ -9474,7 +9543,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9555,7 +9624,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ42">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="AR42">
         <v>1.33</v>
@@ -9758,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ43">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR43">
         <v>1.91</v>
@@ -9886,7 +9955,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -9964,10 +10033,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ44">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
       <c r="AR44">
         <v>2.49</v>
@@ -10170,10 +10239,10 @@
         <v>0.5</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ45">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR45">
         <v>1.28</v>
@@ -10298,7 +10367,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10376,10 +10445,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ46">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR46">
         <v>2.2</v>
@@ -10582,10 +10651,10 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AQ47">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR47">
         <v>1.72</v>
@@ -10788,10 +10857,10 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ48">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR48">
         <v>2</v>
@@ -10916,7 +10985,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -10994,10 +11063,10 @@
         <v>1.33</v>
       </c>
       <c r="AP49">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AQ49">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -11200,10 +11269,10 @@
         <v>1.67</v>
       </c>
       <c r="AP50">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ50">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR50">
         <v>1.54</v>
@@ -11328,7 +11397,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -11406,10 +11475,10 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ51">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.51</v>
@@ -11612,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR52">
         <v>1.77</v>
@@ -11821,7 +11890,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ53">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR53">
         <v>1.48</v>
@@ -12024,10 +12093,10 @@
         <v>0.33</v>
       </c>
       <c r="AP54">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ54">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR54">
         <v>1.28</v>
@@ -12233,7 +12302,7 @@
         <v>3</v>
       </c>
       <c r="AQ55">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
         <v>2.44</v>
@@ -12436,10 +12505,10 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ56">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -12564,7 +12633,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12642,10 +12711,10 @@
         <v>0.33</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR57">
         <v>1.34</v>
@@ -12770,7 +12839,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -12848,10 +12917,10 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ58">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -12976,7 +13045,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13054,10 +13123,10 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ59">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR59">
         <v>1.93</v>
@@ -13260,10 +13329,10 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ60">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR60">
         <v>2.23</v>
@@ -13466,10 +13535,10 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR61">
         <v>1.9</v>
@@ -13672,10 +13741,10 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AQ62">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR62">
         <v>1.63</v>
@@ -13878,10 +13947,10 @@
         <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ63">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR63">
         <v>1.77</v>
@@ -14084,10 +14153,10 @@
         <v>0.25</v>
       </c>
       <c r="AP64">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ64">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>1.63</v>
@@ -14212,7 +14281,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14290,10 +14359,10 @@
         <v>0.25</v>
       </c>
       <c r="AP65">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AQ65">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
       <c r="AR65">
         <v>1.71</v>
@@ -14496,10 +14565,10 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR66">
         <v>2.18</v>
@@ -14624,7 +14693,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14702,10 +14771,10 @@
         <v>0.25</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ67">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR67">
         <v>2.15</v>
@@ -14830,7 +14899,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -14908,10 +14977,10 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AQ68">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.78</v>
@@ -15036,7 +15105,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15114,10 +15183,10 @@
         <v>0.75</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ69">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR69">
         <v>1.45</v>
@@ -15320,10 +15389,10 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15529,7 +15598,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ71">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR71">
         <v>1.48</v>
@@ -15654,7 +15723,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15732,10 +15801,10 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ72">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR72">
         <v>1.83</v>
@@ -15941,7 +16010,7 @@
         <v>3</v>
       </c>
       <c r="AQ73">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="AR73">
         <v>2.35</v>
@@ -16144,10 +16213,10 @@
         <v>1.25</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ74">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR74">
         <v>1.93</v>
@@ -16350,10 +16419,10 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="AQ75">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR75">
         <v>1.77</v>
@@ -16478,7 +16547,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16556,10 +16625,10 @@
         <v>0.2</v>
       </c>
       <c r="AP76">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ76">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR76">
         <v>1.65</v>
@@ -16684,7 +16753,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -16762,10 +16831,10 @@
         <v>0.25</v>
       </c>
       <c r="AP77">
+        <v>1</v>
+      </c>
+      <c r="AQ77">
         <v>1.14</v>
-      </c>
-      <c r="AQ77">
-        <v>0.83</v>
       </c>
       <c r="AR77">
         <v>1.74</v>
@@ -16968,10 +17037,10 @@
         <v>1.6</v>
       </c>
       <c r="AP78">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AQ78">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR78">
         <v>1.51</v>
@@ -17096,7 +17165,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17174,10 +17243,10 @@
         <v>0.75</v>
       </c>
       <c r="AP79">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AQ79">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR79">
         <v>1.73</v>
@@ -17380,10 +17449,10 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ80">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="AR80">
         <v>2.04</v>
@@ -17508,7 +17577,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17586,10 +17655,10 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ81">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR81">
         <v>1.51</v>
@@ -17795,7 +17864,7 @@
         <v>3</v>
       </c>
       <c r="AQ82">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR82">
         <v>2.19</v>
@@ -17920,7 +17989,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18001,7 +18070,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ83">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR83">
         <v>1.65</v>
@@ -18126,7 +18195,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18204,10 +18273,10 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR84">
         <v>1.95</v>
@@ -18332,7 +18401,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18410,10 +18479,10 @@
         <v>0.4</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ85">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR85">
         <v>1.47</v>
@@ -18616,10 +18685,10 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ86">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.51</v>
@@ -18744,7 +18813,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -18822,10 +18891,10 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ87">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR87">
         <v>1.7</v>
@@ -19028,10 +19097,10 @@
         <v>0.6</v>
       </c>
       <c r="AP88">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR88">
         <v>2.08</v>
@@ -19234,10 +19303,10 @@
         <v>2.17</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ89">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR89">
         <v>1.86</v>
@@ -19362,7 +19431,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="Q90">
         <v>2.88</v>
@@ -19440,10 +19509,10 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR90">
         <v>1.8</v>
@@ -19568,7 +19637,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19646,10 +19715,10 @@
         <v>0.17</v>
       </c>
       <c r="AP91">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ91">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR91">
         <v>1.68</v>
@@ -19852,10 +19921,10 @@
         <v>0.4</v>
       </c>
       <c r="AP92">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="AQ92">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR92">
         <v>1.67</v>
@@ -19980,7 +20049,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20058,10 +20127,10 @@
         <v>0.83</v>
       </c>
       <c r="AP93">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ93">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR93">
         <v>1.73</v>
@@ -20186,7 +20255,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20264,10 +20333,10 @@
         <v>0.8</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ94">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR94">
         <v>1.4</v>
@@ -20392,7 +20461,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -20470,10 +20539,10 @@
         <v>1.83</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ95">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR95">
         <v>1.68</v>
@@ -20679,7 +20748,7 @@
         <v>3</v>
       </c>
       <c r="AQ96">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR96">
         <v>2.13</v>
@@ -20804,7 +20873,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -20882,10 +20951,10 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ97">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR97">
         <v>1.81</v>
@@ -20968,7 +21037,7 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>7818831</v>
+        <v>7818904</v>
       </c>
       <c r="C98" t="s">
         <v>68</v>
@@ -20977,195 +21046,4521 @@
         <v>69</v>
       </c>
       <c r="E98" s="2">
+        <v>45809.66666666666</v>
+      </c>
+      <c r="F98">
+        <v>13</v>
+      </c>
+      <c r="G98" t="s">
+        <v>71</v>
+      </c>
+      <c r="H98" t="s">
+        <v>76</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98" t="s">
+        <v>158</v>
+      </c>
+      <c r="P98" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q98">
+        <v>3</v>
+      </c>
+      <c r="R98">
+        <v>2.2</v>
+      </c>
+      <c r="S98">
+        <v>3.5</v>
+      </c>
+      <c r="T98">
+        <v>1.36</v>
+      </c>
+      <c r="U98">
+        <v>3</v>
+      </c>
+      <c r="V98">
+        <v>2.75</v>
+      </c>
+      <c r="W98">
+        <v>1.4</v>
+      </c>
+      <c r="X98">
+        <v>7</v>
+      </c>
+      <c r="Y98">
+        <v>1.1</v>
+      </c>
+      <c r="Z98">
+        <v>2.39</v>
+      </c>
+      <c r="AA98">
+        <v>3.32</v>
+      </c>
+      <c r="AB98">
+        <v>2.95</v>
+      </c>
+      <c r="AC98">
+        <v>1.03</v>
+      </c>
+      <c r="AD98">
+        <v>9</v>
+      </c>
+      <c r="AE98">
+        <v>1.29</v>
+      </c>
+      <c r="AF98">
+        <v>3.3</v>
+      </c>
+      <c r="AG98">
+        <v>1.96</v>
+      </c>
+      <c r="AH98">
+        <v>1.85</v>
+      </c>
+      <c r="AI98">
+        <v>1.67</v>
+      </c>
+      <c r="AJ98">
+        <v>2.1</v>
+      </c>
+      <c r="AK98">
+        <v>1.39</v>
+      </c>
+      <c r="AL98">
+        <v>1.3</v>
+      </c>
+      <c r="AM98">
+        <v>1.57</v>
+      </c>
+      <c r="AN98">
+        <v>1.8</v>
+      </c>
+      <c r="AO98">
+        <v>0.83</v>
+      </c>
+      <c r="AP98">
+        <v>1.86</v>
+      </c>
+      <c r="AQ98">
+        <v>0.88</v>
+      </c>
+      <c r="AR98">
+        <v>1.8</v>
+      </c>
+      <c r="AS98">
+        <v>1.22</v>
+      </c>
+      <c r="AT98">
+        <v>3.02</v>
+      </c>
+      <c r="AU98">
+        <v>5</v>
+      </c>
+      <c r="AV98">
+        <v>8</v>
+      </c>
+      <c r="AW98">
+        <v>2</v>
+      </c>
+      <c r="AX98">
+        <v>4</v>
+      </c>
+      <c r="AY98">
+        <v>7</v>
+      </c>
+      <c r="AZ98">
+        <v>12</v>
+      </c>
+      <c r="BA98">
+        <v>1</v>
+      </c>
+      <c r="BB98">
+        <v>8</v>
+      </c>
+      <c r="BC98">
+        <v>9</v>
+      </c>
+      <c r="BD98">
+        <v>1.94</v>
+      </c>
+      <c r="BE98">
+        <v>6.4</v>
+      </c>
+      <c r="BF98">
+        <v>2.07</v>
+      </c>
+      <c r="BG98">
+        <v>1.43</v>
+      </c>
+      <c r="BH98">
+        <v>2.5</v>
+      </c>
+      <c r="BI98">
+        <v>1.72</v>
+      </c>
+      <c r="BJ98">
+        <v>1.93</v>
+      </c>
+      <c r="BK98">
+        <v>2.18</v>
+      </c>
+      <c r="BL98">
+        <v>1.56</v>
+      </c>
+      <c r="BM98">
+        <v>2.88</v>
+      </c>
+      <c r="BN98">
+        <v>1.33</v>
+      </c>
+      <c r="BO98">
+        <v>3.85</v>
+      </c>
+      <c r="BP98">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7818903</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45809.77083333334</v>
+      </c>
+      <c r="F99">
+        <v>13</v>
+      </c>
+      <c r="G99" t="s">
+        <v>77</v>
+      </c>
+      <c r="H99" t="s">
+        <v>84</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+      <c r="O99" t="s">
+        <v>86</v>
+      </c>
+      <c r="P99" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q99">
+        <v>4.75</v>
+      </c>
+      <c r="R99">
+        <v>2.05</v>
+      </c>
+      <c r="S99">
+        <v>2.63</v>
+      </c>
+      <c r="T99">
+        <v>1.5</v>
+      </c>
+      <c r="U99">
+        <v>2.5</v>
+      </c>
+      <c r="V99">
+        <v>3.4</v>
+      </c>
+      <c r="W99">
+        <v>1.3</v>
+      </c>
+      <c r="X99">
+        <v>10</v>
+      </c>
+      <c r="Y99">
+        <v>1.06</v>
+      </c>
+      <c r="Z99">
+        <v>4.13</v>
+      </c>
+      <c r="AA99">
+        <v>3.31</v>
+      </c>
+      <c r="AB99">
+        <v>1.94</v>
+      </c>
+      <c r="AC99">
+        <v>1.06</v>
+      </c>
+      <c r="AD99">
+        <v>7.5</v>
+      </c>
+      <c r="AE99">
+        <v>1.4</v>
+      </c>
+      <c r="AF99">
+        <v>2.75</v>
+      </c>
+      <c r="AG99">
+        <v>2.35</v>
+      </c>
+      <c r="AH99">
+        <v>1.57</v>
+      </c>
+      <c r="AI99">
+        <v>2.1</v>
+      </c>
+      <c r="AJ99">
+        <v>1.67</v>
+      </c>
+      <c r="AK99">
+        <v>1.83</v>
+      </c>
+      <c r="AL99">
+        <v>1.31</v>
+      </c>
+      <c r="AM99">
+        <v>1.23</v>
+      </c>
+      <c r="AN99">
+        <v>2.17</v>
+      </c>
+      <c r="AO99">
+        <v>1</v>
+      </c>
+      <c r="AP99">
+        <v>1.75</v>
+      </c>
+      <c r="AQ99">
+        <v>1.17</v>
+      </c>
+      <c r="AR99">
+        <v>1.47</v>
+      </c>
+      <c r="AS99">
+        <v>1.89</v>
+      </c>
+      <c r="AT99">
+        <v>3.36</v>
+      </c>
+      <c r="AU99">
+        <v>3</v>
+      </c>
+      <c r="AV99">
+        <v>2</v>
+      </c>
+      <c r="AW99">
+        <v>12</v>
+      </c>
+      <c r="AX99">
+        <v>1</v>
+      </c>
+      <c r="AY99">
+        <v>15</v>
+      </c>
+      <c r="AZ99">
+        <v>3</v>
+      </c>
+      <c r="BA99">
+        <v>3</v>
+      </c>
+      <c r="BB99">
+        <v>1</v>
+      </c>
+      <c r="BC99">
+        <v>4</v>
+      </c>
+      <c r="BD99">
+        <v>2.65</v>
+      </c>
+      <c r="BE99">
+        <v>6.5</v>
+      </c>
+      <c r="BF99">
+        <v>1.58</v>
+      </c>
+      <c r="BG99">
+        <v>1.47</v>
+      </c>
+      <c r="BH99">
+        <v>2.38</v>
+      </c>
+      <c r="BI99">
+        <v>1.81</v>
+      </c>
+      <c r="BJ99">
+        <v>1.83</v>
+      </c>
+      <c r="BK99">
+        <v>2.3</v>
+      </c>
+      <c r="BL99">
+        <v>1.5</v>
+      </c>
+      <c r="BM99">
+        <v>3</v>
+      </c>
+      <c r="BN99">
+        <v>1.3</v>
+      </c>
+      <c r="BO99">
+        <v>4</v>
+      </c>
+      <c r="BP99">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7818905</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45810.79166666666</v>
+      </c>
+      <c r="F100">
+        <v>13</v>
+      </c>
+      <c r="G100" t="s">
+        <v>83</v>
+      </c>
+      <c r="H100" t="s">
+        <v>70</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>2</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>3</v>
+      </c>
+      <c r="O100" t="s">
+        <v>159</v>
+      </c>
+      <c r="P100" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q100">
+        <v>2.32</v>
+      </c>
+      <c r="R100">
+        <v>2.23</v>
+      </c>
+      <c r="S100">
+        <v>4.45</v>
+      </c>
+      <c r="T100">
+        <v>1.32</v>
+      </c>
+      <c r="U100">
+        <v>3.1</v>
+      </c>
+      <c r="V100">
+        <v>2.53</v>
+      </c>
+      <c r="W100">
+        <v>1.46</v>
+      </c>
+      <c r="X100">
+        <v>5.95</v>
+      </c>
+      <c r="Y100">
+        <v>1.07</v>
+      </c>
+      <c r="Z100">
+        <v>1.82</v>
+      </c>
+      <c r="AA100">
+        <v>3.72</v>
+      </c>
+      <c r="AB100">
+        <v>4.05</v>
+      </c>
+      <c r="AC100">
+        <v>1.02</v>
+      </c>
+      <c r="AD100">
+        <v>10</v>
+      </c>
+      <c r="AE100">
+        <v>1.19</v>
+      </c>
+      <c r="AF100">
+        <v>3.8</v>
+      </c>
+      <c r="AG100">
+        <v>1.75</v>
+      </c>
+      <c r="AH100">
+        <v>2.04</v>
+      </c>
+      <c r="AI100">
+        <v>1.65</v>
+      </c>
+      <c r="AJ100">
+        <v>2.11</v>
+      </c>
+      <c r="AK100">
+        <v>1.23</v>
+      </c>
+      <c r="AL100">
+        <v>1.26</v>
+      </c>
+      <c r="AM100">
+        <v>1.95</v>
+      </c>
+      <c r="AN100">
+        <v>1.83</v>
+      </c>
+      <c r="AO100">
+        <v>0.33</v>
+      </c>
+      <c r="AP100">
+        <v>1.88</v>
+      </c>
+      <c r="AQ100">
+        <v>0.25</v>
+      </c>
+      <c r="AR100">
+        <v>1.73</v>
+      </c>
+      <c r="AS100">
+        <v>1.31</v>
+      </c>
+      <c r="AT100">
+        <v>3.04</v>
+      </c>
+      <c r="AU100">
+        <v>9</v>
+      </c>
+      <c r="AV100">
+        <v>8</v>
+      </c>
+      <c r="AW100">
+        <v>9</v>
+      </c>
+      <c r="AX100">
+        <v>2</v>
+      </c>
+      <c r="AY100">
+        <v>18</v>
+      </c>
+      <c r="AZ100">
+        <v>10</v>
+      </c>
+      <c r="BA100">
+        <v>7</v>
+      </c>
+      <c r="BB100">
+        <v>5</v>
+      </c>
+      <c r="BC100">
+        <v>12</v>
+      </c>
+      <c r="BD100">
+        <v>1.71</v>
+      </c>
+      <c r="BE100">
+        <v>6.4</v>
+      </c>
+      <c r="BF100">
+        <v>2.4</v>
+      </c>
+      <c r="BG100">
+        <v>1.32</v>
+      </c>
+      <c r="BH100">
+        <v>2.95</v>
+      </c>
+      <c r="BI100">
+        <v>1.54</v>
+      </c>
+      <c r="BJ100">
+        <v>2.23</v>
+      </c>
+      <c r="BK100">
+        <v>1.88</v>
+      </c>
+      <c r="BL100">
+        <v>1.77</v>
+      </c>
+      <c r="BM100">
+        <v>2.38</v>
+      </c>
+      <c r="BN100">
+        <v>1.47</v>
+      </c>
+      <c r="BO100">
+        <v>3.05</v>
+      </c>
+      <c r="BP100">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7818907</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45811.66666666666</v>
+      </c>
+      <c r="F101">
+        <v>13</v>
+      </c>
+      <c r="G101" t="s">
+        <v>79</v>
+      </c>
+      <c r="H101" t="s">
+        <v>75</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>2</v>
+      </c>
+      <c r="N101">
+        <v>4</v>
+      </c>
+      <c r="O101" t="s">
+        <v>160</v>
+      </c>
+      <c r="P101" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q101">
+        <v>2.75</v>
+      </c>
+      <c r="R101">
+        <v>2.38</v>
+      </c>
+      <c r="S101">
+        <v>3.4</v>
+      </c>
+      <c r="T101">
+        <v>1.3</v>
+      </c>
+      <c r="U101">
+        <v>3.4</v>
+      </c>
+      <c r="V101">
+        <v>2.38</v>
+      </c>
+      <c r="W101">
+        <v>1.53</v>
+      </c>
+      <c r="X101">
+        <v>6</v>
+      </c>
+      <c r="Y101">
+        <v>1.13</v>
+      </c>
+      <c r="Z101">
+        <v>2.16</v>
+      </c>
+      <c r="AA101">
+        <v>3.75</v>
+      </c>
+      <c r="AB101">
+        <v>3.03</v>
+      </c>
+      <c r="AC101">
+        <v>1.01</v>
+      </c>
+      <c r="AD101">
+        <v>11</v>
+      </c>
+      <c r="AE101">
+        <v>1.14</v>
+      </c>
+      <c r="AF101">
+        <v>4.45</v>
+      </c>
+      <c r="AG101">
+        <v>1.65</v>
+      </c>
+      <c r="AH101">
+        <v>2.2</v>
+      </c>
+      <c r="AI101">
+        <v>1.53</v>
+      </c>
+      <c r="AJ101">
+        <v>2.38</v>
+      </c>
+      <c r="AK101">
+        <v>1.36</v>
+      </c>
+      <c r="AL101">
+        <v>1.3</v>
+      </c>
+      <c r="AM101">
+        <v>1.62</v>
+      </c>
+      <c r="AN101">
+        <v>0.6</v>
+      </c>
+      <c r="AO101">
+        <v>0.2</v>
+      </c>
+      <c r="AP101">
+        <v>0.5</v>
+      </c>
+      <c r="AQ101">
+        <v>0.43</v>
+      </c>
+      <c r="AR101">
+        <v>1.56</v>
+      </c>
+      <c r="AS101">
+        <v>1.66</v>
+      </c>
+      <c r="AT101">
+        <v>3.22</v>
+      </c>
+      <c r="AU101">
+        <v>7</v>
+      </c>
+      <c r="AV101">
+        <v>3</v>
+      </c>
+      <c r="AW101">
+        <v>5</v>
+      </c>
+      <c r="AX101">
+        <v>5</v>
+      </c>
+      <c r="AY101">
+        <v>12</v>
+      </c>
+      <c r="AZ101">
+        <v>8</v>
+      </c>
+      <c r="BA101">
+        <v>10</v>
+      </c>
+      <c r="BB101">
+        <v>3</v>
+      </c>
+      <c r="BC101">
+        <v>13</v>
+      </c>
+      <c r="BD101">
+        <v>1.78</v>
+      </c>
+      <c r="BE101">
+        <v>6.75</v>
+      </c>
+      <c r="BF101">
+        <v>2.23</v>
+      </c>
+      <c r="BG101">
+        <v>1.16</v>
+      </c>
+      <c r="BH101">
+        <v>4.1</v>
+      </c>
+      <c r="BI101">
+        <v>1.32</v>
+      </c>
+      <c r="BJ101">
+        <v>2.95</v>
+      </c>
+      <c r="BK101">
+        <v>1.52</v>
+      </c>
+      <c r="BL101">
+        <v>2.28</v>
+      </c>
+      <c r="BM101">
+        <v>1.82</v>
+      </c>
+      <c r="BN101">
+        <v>1.82</v>
+      </c>
+      <c r="BO101">
+        <v>2.25</v>
+      </c>
+      <c r="BP101">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7818863</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45820.875</v>
+      </c>
+      <c r="F102">
+        <v>8</v>
+      </c>
+      <c r="G102" t="s">
+        <v>70</v>
+      </c>
+      <c r="H102" t="s">
+        <v>84</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>2</v>
+      </c>
+      <c r="M102">
+        <v>2</v>
+      </c>
+      <c r="N102">
+        <v>4</v>
+      </c>
+      <c r="O102" t="s">
+        <v>161</v>
+      </c>
+      <c r="P102" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q102">
+        <v>5.5</v>
+      </c>
+      <c r="R102">
+        <v>2.3</v>
+      </c>
+      <c r="S102">
+        <v>2.1</v>
+      </c>
+      <c r="T102">
+        <v>1.36</v>
+      </c>
+      <c r="U102">
+        <v>3</v>
+      </c>
+      <c r="V102">
+        <v>2.63</v>
+      </c>
+      <c r="W102">
+        <v>1.44</v>
+      </c>
+      <c r="X102">
+        <v>7</v>
+      </c>
+      <c r="Y102">
+        <v>1.1</v>
+      </c>
+      <c r="Z102">
+        <v>5.31</v>
+      </c>
+      <c r="AA102">
+        <v>4.05</v>
+      </c>
+      <c r="AB102">
+        <v>1.59</v>
+      </c>
+      <c r="AC102">
+        <v>1.01</v>
+      </c>
+      <c r="AD102">
+        <v>11</v>
+      </c>
+      <c r="AE102">
+        <v>1.2</v>
+      </c>
+      <c r="AF102">
+        <v>3.72</v>
+      </c>
+      <c r="AG102">
+        <v>1.85</v>
+      </c>
+      <c r="AH102">
+        <v>1.95</v>
+      </c>
+      <c r="AI102">
+        <v>1.83</v>
+      </c>
+      <c r="AJ102">
+        <v>1.83</v>
+      </c>
+      <c r="AK102">
+        <v>2.25</v>
+      </c>
+      <c r="AL102">
+        <v>1.25</v>
+      </c>
+      <c r="AM102">
+        <v>1.17</v>
+      </c>
+      <c r="AN102">
+        <v>0.6</v>
+      </c>
+      <c r="AO102">
+        <v>1.5</v>
+      </c>
+      <c r="AP102">
+        <v>0.57</v>
+      </c>
+      <c r="AQ102">
+        <v>1.17</v>
+      </c>
+      <c r="AR102">
+        <v>1.69</v>
+      </c>
+      <c r="AS102">
+        <v>1.89</v>
+      </c>
+      <c r="AT102">
+        <v>3.58</v>
+      </c>
+      <c r="AU102">
+        <v>2</v>
+      </c>
+      <c r="AV102">
+        <v>4</v>
+      </c>
+      <c r="AW102">
+        <v>9</v>
+      </c>
+      <c r="AX102">
+        <v>4</v>
+      </c>
+      <c r="AY102">
+        <v>11</v>
+      </c>
+      <c r="AZ102">
+        <v>8</v>
+      </c>
+      <c r="BA102">
+        <v>6</v>
+      </c>
+      <c r="BB102">
+        <v>7</v>
+      </c>
+      <c r="BC102">
+        <v>13</v>
+      </c>
+      <c r="BD102">
+        <v>3.15</v>
+      </c>
+      <c r="BE102">
+        <v>6.75</v>
+      </c>
+      <c r="BF102">
+        <v>1.44</v>
+      </c>
+      <c r="BG102">
+        <v>1.36</v>
+      </c>
+      <c r="BH102">
+        <v>2.75</v>
+      </c>
+      <c r="BI102">
+        <v>1.63</v>
+      </c>
+      <c r="BJ102">
+        <v>2.06</v>
+      </c>
+      <c r="BK102">
+        <v>2.06</v>
+      </c>
+      <c r="BL102">
+        <v>1.63</v>
+      </c>
+      <c r="BM102">
+        <v>2.65</v>
+      </c>
+      <c r="BN102">
+        <v>1.38</v>
+      </c>
+      <c r="BO102">
+        <v>3.45</v>
+      </c>
+      <c r="BP102">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7818914</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45821.875</v>
+      </c>
+      <c r="F103">
+        <v>14</v>
+      </c>
+      <c r="G103" t="s">
+        <v>75</v>
+      </c>
+      <c r="H103" t="s">
+        <v>77</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" t="s">
+        <v>86</v>
+      </c>
+      <c r="P103" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q103">
+        <v>2.88</v>
+      </c>
+      <c r="R103">
+        <v>2.05</v>
+      </c>
+      <c r="S103">
+        <v>4</v>
+      </c>
+      <c r="T103">
+        <v>1.44</v>
+      </c>
+      <c r="U103">
+        <v>2.63</v>
+      </c>
+      <c r="V103">
+        <v>3.25</v>
+      </c>
+      <c r="W103">
+        <v>1.33</v>
+      </c>
+      <c r="X103">
+        <v>10</v>
+      </c>
+      <c r="Y103">
+        <v>1.06</v>
+      </c>
+      <c r="Z103">
+        <v>2.12</v>
+      </c>
+      <c r="AA103">
+        <v>3.43</v>
+      </c>
+      <c r="AB103">
+        <v>3.36</v>
+      </c>
+      <c r="AC103">
+        <v>1.02</v>
+      </c>
+      <c r="AD103">
+        <v>7.8</v>
+      </c>
+      <c r="AE103">
+        <v>1.41</v>
+      </c>
+      <c r="AF103">
+        <v>2.83</v>
+      </c>
+      <c r="AG103">
+        <v>2.25</v>
+      </c>
+      <c r="AH103">
+        <v>1.62</v>
+      </c>
+      <c r="AI103">
+        <v>1.91</v>
+      </c>
+      <c r="AJ103">
+        <v>1.8</v>
+      </c>
+      <c r="AK103">
+        <v>1.3</v>
+      </c>
+      <c r="AL103">
+        <v>1.35</v>
+      </c>
+      <c r="AM103">
+        <v>1.7</v>
+      </c>
+      <c r="AN103">
+        <v>1.43</v>
+      </c>
+      <c r="AO103">
+        <v>0.83</v>
+      </c>
+      <c r="AP103">
+        <v>1.25</v>
+      </c>
+      <c r="AQ103">
+        <v>1.14</v>
+      </c>
+      <c r="AR103">
+        <v>1.48</v>
+      </c>
+      <c r="AS103">
+        <v>1.23</v>
+      </c>
+      <c r="AT103">
+        <v>2.71</v>
+      </c>
+      <c r="AU103">
+        <v>5</v>
+      </c>
+      <c r="AV103">
+        <v>3</v>
+      </c>
+      <c r="AW103">
+        <v>8</v>
+      </c>
+      <c r="AX103">
+        <v>4</v>
+      </c>
+      <c r="AY103">
+        <v>13</v>
+      </c>
+      <c r="AZ103">
+        <v>7</v>
+      </c>
+      <c r="BA103">
+        <v>6</v>
+      </c>
+      <c r="BB103">
+        <v>2</v>
+      </c>
+      <c r="BC103">
+        <v>8</v>
+      </c>
+      <c r="BD103">
+        <v>1.85</v>
+      </c>
+      <c r="BE103">
+        <v>6.75</v>
+      </c>
+      <c r="BF103">
+        <v>2.12</v>
+      </c>
+      <c r="BG103">
+        <v>1.3</v>
+      </c>
+      <c r="BH103">
+        <v>3</v>
+      </c>
+      <c r="BI103">
+        <v>1.54</v>
+      </c>
+      <c r="BJ103">
+        <v>2.23</v>
+      </c>
+      <c r="BK103">
+        <v>1.9</v>
+      </c>
+      <c r="BL103">
+        <v>1.75</v>
+      </c>
+      <c r="BM103">
+        <v>2.4</v>
+      </c>
+      <c r="BN103">
+        <v>1.47</v>
+      </c>
+      <c r="BO103">
+        <v>3.1</v>
+      </c>
+      <c r="BP103">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7818913</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45822.5625</v>
+      </c>
+      <c r="F104">
+        <v>14</v>
+      </c>
+      <c r="G104" t="s">
+        <v>71</v>
+      </c>
+      <c r="H104" t="s">
+        <v>74</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>3</v>
+      </c>
+      <c r="O104" t="s">
+        <v>162</v>
+      </c>
+      <c r="P104" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q104">
+        <v>2.38</v>
+      </c>
+      <c r="R104">
+        <v>2.2</v>
+      </c>
+      <c r="S104">
+        <v>5</v>
+      </c>
+      <c r="T104">
+        <v>1.4</v>
+      </c>
+      <c r="U104">
+        <v>2.75</v>
+      </c>
+      <c r="V104">
+        <v>2.75</v>
+      </c>
+      <c r="W104">
+        <v>1.4</v>
+      </c>
+      <c r="X104">
+        <v>8</v>
+      </c>
+      <c r="Y104">
+        <v>1.08</v>
+      </c>
+      <c r="Z104">
+        <v>1.75</v>
+      </c>
+      <c r="AA104">
+        <v>3.75</v>
+      </c>
+      <c r="AB104">
+        <v>4.33</v>
+      </c>
+      <c r="AC104">
+        <v>1.01</v>
+      </c>
+      <c r="AD104">
+        <v>8.4</v>
+      </c>
+      <c r="AE104">
+        <v>1.28</v>
+      </c>
+      <c r="AF104">
+        <v>3.1</v>
+      </c>
+      <c r="AG104">
+        <v>2</v>
+      </c>
+      <c r="AH104">
+        <v>1.8</v>
+      </c>
+      <c r="AI104">
+        <v>1.91</v>
+      </c>
+      <c r="AJ104">
+        <v>1.8</v>
+      </c>
+      <c r="AK104">
+        <v>1.2</v>
+      </c>
+      <c r="AL104">
+        <v>1.3</v>
+      </c>
+      <c r="AM104">
+        <v>2</v>
+      </c>
+      <c r="AN104">
+        <v>1.67</v>
+      </c>
+      <c r="AO104">
+        <v>0.57</v>
+      </c>
+      <c r="AP104">
+        <v>1.86</v>
+      </c>
+      <c r="AQ104">
+        <v>0.5</v>
+      </c>
+      <c r="AR104">
+        <v>1.8</v>
+      </c>
+      <c r="AS104">
+        <v>1.29</v>
+      </c>
+      <c r="AT104">
+        <v>3.09</v>
+      </c>
+      <c r="AU104">
+        <v>7</v>
+      </c>
+      <c r="AV104">
+        <v>3</v>
+      </c>
+      <c r="AW104">
+        <v>7</v>
+      </c>
+      <c r="AX104">
+        <v>7</v>
+      </c>
+      <c r="AY104">
+        <v>14</v>
+      </c>
+      <c r="AZ104">
+        <v>10</v>
+      </c>
+      <c r="BA104">
+        <v>7</v>
+      </c>
+      <c r="BB104">
+        <v>4</v>
+      </c>
+      <c r="BC104">
+        <v>11</v>
+      </c>
+      <c r="BD104">
+        <v>1.49</v>
+      </c>
+      <c r="BE104">
+        <v>6.5</v>
+      </c>
+      <c r="BF104">
+        <v>2.95</v>
+      </c>
+      <c r="BG104">
+        <v>1.42</v>
+      </c>
+      <c r="BH104">
+        <v>2.55</v>
+      </c>
+      <c r="BI104">
+        <v>1.71</v>
+      </c>
+      <c r="BJ104">
+        <v>1.94</v>
+      </c>
+      <c r="BK104">
+        <v>2.14</v>
+      </c>
+      <c r="BL104">
+        <v>1.58</v>
+      </c>
+      <c r="BM104">
+        <v>2.8</v>
+      </c>
+      <c r="BN104">
+        <v>1.35</v>
+      </c>
+      <c r="BO104">
+        <v>3.7</v>
+      </c>
+      <c r="BP104">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7818918</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45822.66666666666</v>
+      </c>
+      <c r="F105">
+        <v>14</v>
+      </c>
+      <c r="G105" t="s">
+        <v>76</v>
+      </c>
+      <c r="H105" t="s">
+        <v>82</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>163</v>
+      </c>
+      <c r="P105" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q105">
+        <v>2.3</v>
+      </c>
+      <c r="R105">
+        <v>2.25</v>
+      </c>
+      <c r="S105">
+        <v>5</v>
+      </c>
+      <c r="T105">
+        <v>1.36</v>
+      </c>
+      <c r="U105">
+        <v>3</v>
+      </c>
+      <c r="V105">
+        <v>2.75</v>
+      </c>
+      <c r="W105">
+        <v>1.4</v>
+      </c>
+      <c r="X105">
+        <v>7</v>
+      </c>
+      <c r="Y105">
+        <v>1.1</v>
+      </c>
+      <c r="Z105">
+        <v>1.72</v>
+      </c>
+      <c r="AA105">
+        <v>3.77</v>
+      </c>
+      <c r="AB105">
+        <v>4.63</v>
+      </c>
+      <c r="AC105">
+        <v>1</v>
+      </c>
+      <c r="AD105">
+        <v>9.1</v>
+      </c>
+      <c r="AE105">
+        <v>1.24</v>
+      </c>
+      <c r="AF105">
+        <v>3.36</v>
+      </c>
+      <c r="AG105">
+        <v>1.9</v>
+      </c>
+      <c r="AH105">
+        <v>1.9</v>
+      </c>
+      <c r="AI105">
+        <v>1.83</v>
+      </c>
+      <c r="AJ105">
+        <v>1.83</v>
+      </c>
+      <c r="AK105">
+        <v>1.18</v>
+      </c>
+      <c r="AL105">
+        <v>1.29</v>
+      </c>
+      <c r="AM105">
+        <v>2.1</v>
+      </c>
+      <c r="AN105">
+        <v>2.4</v>
+      </c>
+      <c r="AO105">
+        <v>0.71</v>
+      </c>
+      <c r="AP105">
+        <v>2.5</v>
+      </c>
+      <c r="AQ105">
+        <v>0.63</v>
+      </c>
+      <c r="AR105">
+        <v>1.74</v>
+      </c>
+      <c r="AS105">
+        <v>1.29</v>
+      </c>
+      <c r="AT105">
+        <v>3.03</v>
+      </c>
+      <c r="AU105">
+        <v>4</v>
+      </c>
+      <c r="AV105">
+        <v>4</v>
+      </c>
+      <c r="AW105">
+        <v>8</v>
+      </c>
+      <c r="AX105">
+        <v>1</v>
+      </c>
+      <c r="AY105">
+        <v>12</v>
+      </c>
+      <c r="AZ105">
+        <v>5</v>
+      </c>
+      <c r="BA105">
+        <v>4</v>
+      </c>
+      <c r="BB105">
+        <v>0</v>
+      </c>
+      <c r="BC105">
+        <v>4</v>
+      </c>
+      <c r="BD105">
+        <v>1.65</v>
+      </c>
+      <c r="BE105">
+        <v>6.4</v>
+      </c>
+      <c r="BF105">
+        <v>2.5</v>
+      </c>
+      <c r="BG105">
+        <v>1.32</v>
+      </c>
+      <c r="BH105">
+        <v>2.9</v>
+      </c>
+      <c r="BI105">
+        <v>1.55</v>
+      </c>
+      <c r="BJ105">
+        <v>2.2</v>
+      </c>
+      <c r="BK105">
+        <v>1.9</v>
+      </c>
+      <c r="BL105">
+        <v>1.74</v>
+      </c>
+      <c r="BM105">
+        <v>2.43</v>
+      </c>
+      <c r="BN105">
+        <v>1.45</v>
+      </c>
+      <c r="BO105">
+        <v>3.2</v>
+      </c>
+      <c r="BP105">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7818917</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45823.5625</v>
+      </c>
+      <c r="F106">
+        <v>14</v>
+      </c>
+      <c r="G106" t="s">
+        <v>72</v>
+      </c>
+      <c r="H106" t="s">
+        <v>79</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>1</v>
+      </c>
+      <c r="O106" t="s">
+        <v>153</v>
+      </c>
+      <c r="P106" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q106">
+        <v>2.4</v>
+      </c>
+      <c r="R106">
+        <v>2.25</v>
+      </c>
+      <c r="S106">
+        <v>4.33</v>
+      </c>
+      <c r="T106">
+        <v>1.36</v>
+      </c>
+      <c r="U106">
+        <v>3</v>
+      </c>
+      <c r="V106">
+        <v>2.63</v>
+      </c>
+      <c r="W106">
+        <v>1.44</v>
+      </c>
+      <c r="X106">
+        <v>7</v>
+      </c>
+      <c r="Y106">
+        <v>1.1</v>
+      </c>
+      <c r="Z106">
+        <v>1.9</v>
+      </c>
+      <c r="AA106">
+        <v>3.65</v>
+      </c>
+      <c r="AB106">
+        <v>3.85</v>
+      </c>
+      <c r="AC106">
+        <v>1.05</v>
+      </c>
+      <c r="AD106">
+        <v>8.5</v>
+      </c>
+      <c r="AE106">
+        <v>1.25</v>
+      </c>
+      <c r="AF106">
+        <v>3.6</v>
+      </c>
+      <c r="AG106">
+        <v>1.85</v>
+      </c>
+      <c r="AH106">
+        <v>1.95</v>
+      </c>
+      <c r="AI106">
+        <v>1.73</v>
+      </c>
+      <c r="AJ106">
+        <v>2</v>
+      </c>
+      <c r="AK106">
+        <v>1.24</v>
+      </c>
+      <c r="AL106">
+        <v>1.27</v>
+      </c>
+      <c r="AM106">
+        <v>1.88</v>
+      </c>
+      <c r="AN106">
+        <v>2</v>
+      </c>
+      <c r="AO106">
+        <v>0.5</v>
+      </c>
+      <c r="AP106">
+        <v>2.14</v>
+      </c>
+      <c r="AQ106">
+        <v>0.43</v>
+      </c>
+      <c r="AR106">
+        <v>1.87</v>
+      </c>
+      <c r="AS106">
+        <v>1.69</v>
+      </c>
+      <c r="AT106">
+        <v>3.56</v>
+      </c>
+      <c r="AU106">
+        <v>4</v>
+      </c>
+      <c r="AV106">
+        <v>2</v>
+      </c>
+      <c r="AW106">
+        <v>10</v>
+      </c>
+      <c r="AX106">
+        <v>3</v>
+      </c>
+      <c r="AY106">
+        <v>14</v>
+      </c>
+      <c r="AZ106">
+        <v>5</v>
+      </c>
+      <c r="BA106">
+        <v>6</v>
+      </c>
+      <c r="BB106">
+        <v>9</v>
+      </c>
+      <c r="BC106">
+        <v>15</v>
+      </c>
+      <c r="BD106">
+        <v>1.6</v>
+      </c>
+      <c r="BE106">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF106">
+        <v>2.73</v>
+      </c>
+      <c r="BG106">
+        <v>1.27</v>
+      </c>
+      <c r="BH106">
+        <v>3.2</v>
+      </c>
+      <c r="BI106">
+        <v>1.34</v>
+      </c>
+      <c r="BJ106">
+        <v>2.78</v>
+      </c>
+      <c r="BK106">
+        <v>1.62</v>
+      </c>
+      <c r="BL106">
+        <v>2.1</v>
+      </c>
+      <c r="BM106">
+        <v>2.06</v>
+      </c>
+      <c r="BN106">
+        <v>1.68</v>
+      </c>
+      <c r="BO106">
+        <v>2.67</v>
+      </c>
+      <c r="BP106">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7818911</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45823.66666666666</v>
+      </c>
+      <c r="F107">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s">
+        <v>80</v>
+      </c>
+      <c r="H107" t="s">
+        <v>73</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
+      <c r="O107" t="s">
+        <v>164</v>
+      </c>
+      <c r="P107" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q107">
+        <v>3.4</v>
+      </c>
+      <c r="R107">
+        <v>2.1</v>
+      </c>
+      <c r="S107">
+        <v>3.2</v>
+      </c>
+      <c r="T107">
+        <v>1.4</v>
+      </c>
+      <c r="U107">
+        <v>2.75</v>
+      </c>
+      <c r="V107">
+        <v>3</v>
+      </c>
+      <c r="W107">
+        <v>1.36</v>
+      </c>
+      <c r="X107">
+        <v>8</v>
+      </c>
+      <c r="Y107">
+        <v>1.08</v>
+      </c>
+      <c r="Z107">
+        <v>2.72</v>
+      </c>
+      <c r="AA107">
+        <v>3.28</v>
+      </c>
+      <c r="AB107">
+        <v>2.59</v>
+      </c>
+      <c r="AC107">
+        <v>1.06</v>
+      </c>
+      <c r="AD107">
+        <v>8</v>
+      </c>
+      <c r="AE107">
+        <v>1.35</v>
+      </c>
+      <c r="AF107">
+        <v>3</v>
+      </c>
+      <c r="AG107">
+        <v>2.08</v>
+      </c>
+      <c r="AH107">
+        <v>1.73</v>
+      </c>
+      <c r="AI107">
+        <v>1.8</v>
+      </c>
+      <c r="AJ107">
+        <v>1.91</v>
+      </c>
+      <c r="AK107">
+        <v>1.49</v>
+      </c>
+      <c r="AL107">
+        <v>1.31</v>
+      </c>
+      <c r="AM107">
+        <v>1.44</v>
+      </c>
+      <c r="AN107">
+        <v>2</v>
+      </c>
+      <c r="AO107">
+        <v>0.8</v>
+      </c>
+      <c r="AP107">
+        <v>2.14</v>
+      </c>
+      <c r="AQ107">
+        <v>1</v>
+      </c>
+      <c r="AR107">
+        <v>1.82</v>
+      </c>
+      <c r="AS107">
+        <v>1.91</v>
+      </c>
+      <c r="AT107">
+        <v>3.73</v>
+      </c>
+      <c r="AU107">
+        <v>3</v>
+      </c>
+      <c r="AV107">
+        <v>4</v>
+      </c>
+      <c r="AW107">
+        <v>1</v>
+      </c>
+      <c r="AX107">
+        <v>5</v>
+      </c>
+      <c r="AY107">
+        <v>4</v>
+      </c>
+      <c r="AZ107">
+        <v>9</v>
+      </c>
+      <c r="BA107">
+        <v>1</v>
+      </c>
+      <c r="BB107">
+        <v>4</v>
+      </c>
+      <c r="BC107">
+        <v>5</v>
+      </c>
+      <c r="BD107">
+        <v>1.97</v>
+      </c>
+      <c r="BE107">
+        <v>6.35</v>
+      </c>
+      <c r="BF107">
+        <v>2.27</v>
+      </c>
+      <c r="BG107">
+        <v>1.24</v>
+      </c>
+      <c r="BH107">
+        <v>3.34</v>
+      </c>
+      <c r="BI107">
+        <v>1.47</v>
+      </c>
+      <c r="BJ107">
+        <v>2.42</v>
+      </c>
+      <c r="BK107">
+        <v>1.83</v>
+      </c>
+      <c r="BL107">
+        <v>1.87</v>
+      </c>
+      <c r="BM107">
+        <v>2.34</v>
+      </c>
+      <c r="BN107">
+        <v>1.5</v>
+      </c>
+      <c r="BO107">
+        <v>3.14</v>
+      </c>
+      <c r="BP107">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7818916</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45823.875</v>
+      </c>
+      <c r="F108">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s">
+        <v>81</v>
+      </c>
+      <c r="H108" t="s">
+        <v>78</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>2</v>
+      </c>
+      <c r="K108">
+        <v>3</v>
+      </c>
+      <c r="L108">
+        <v>2</v>
+      </c>
+      <c r="M108">
+        <v>3</v>
+      </c>
+      <c r="N108">
+        <v>5</v>
+      </c>
+      <c r="O108" t="s">
+        <v>165</v>
+      </c>
+      <c r="P108" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q108">
+        <v>3.1</v>
+      </c>
+      <c r="R108">
+        <v>2.05</v>
+      </c>
+      <c r="S108">
+        <v>3.75</v>
+      </c>
+      <c r="T108">
+        <v>1.44</v>
+      </c>
+      <c r="U108">
+        <v>2.63</v>
+      </c>
+      <c r="V108">
+        <v>3.25</v>
+      </c>
+      <c r="W108">
+        <v>1.33</v>
+      </c>
+      <c r="X108">
+        <v>10</v>
+      </c>
+      <c r="Y108">
+        <v>1.06</v>
+      </c>
+      <c r="Z108">
+        <v>2.33</v>
+      </c>
+      <c r="AA108">
+        <v>3.26</v>
+      </c>
+      <c r="AB108">
+        <v>3.09</v>
+      </c>
+      <c r="AC108">
+        <v>1.07</v>
+      </c>
+      <c r="AD108">
+        <v>7.5</v>
+      </c>
+      <c r="AE108">
+        <v>1.38</v>
+      </c>
+      <c r="AF108">
+        <v>2.88</v>
+      </c>
+      <c r="AG108">
+        <v>2.15</v>
+      </c>
+      <c r="AH108">
+        <v>1.67</v>
+      </c>
+      <c r="AI108">
+        <v>1.91</v>
+      </c>
+      <c r="AJ108">
+        <v>1.8</v>
+      </c>
+      <c r="AK108">
+        <v>1.39</v>
+      </c>
+      <c r="AL108">
+        <v>1.32</v>
+      </c>
+      <c r="AM108">
+        <v>1.55</v>
+      </c>
+      <c r="AN108">
+        <v>1.14</v>
+      </c>
+      <c r="AO108">
+        <v>1.17</v>
+      </c>
+      <c r="AP108">
+        <v>1</v>
+      </c>
+      <c r="AQ108">
+        <v>1.43</v>
+      </c>
+      <c r="AR108">
+        <v>1.78</v>
+      </c>
+      <c r="AS108">
+        <v>1.21</v>
+      </c>
+      <c r="AT108">
+        <v>2.99</v>
+      </c>
+      <c r="AU108">
+        <v>4</v>
+      </c>
+      <c r="AV108">
+        <v>4</v>
+      </c>
+      <c r="AW108">
+        <v>9</v>
+      </c>
+      <c r="AX108">
+        <v>3</v>
+      </c>
+      <c r="AY108">
+        <v>13</v>
+      </c>
+      <c r="AZ108">
+        <v>7</v>
+      </c>
+      <c r="BA108">
+        <v>7</v>
+      </c>
+      <c r="BB108">
+        <v>1</v>
+      </c>
+      <c r="BC108">
+        <v>8</v>
+      </c>
+      <c r="BD108">
+        <v>1.64</v>
+      </c>
+      <c r="BE108">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF108">
+        <v>2.66</v>
+      </c>
+      <c r="BG108">
+        <v>1.24</v>
+      </c>
+      <c r="BH108">
+        <v>3.34</v>
+      </c>
+      <c r="BI108">
+        <v>1.48</v>
+      </c>
+      <c r="BJ108">
+        <v>2.4</v>
+      </c>
+      <c r="BK108">
+        <v>1.91</v>
+      </c>
+      <c r="BL108">
+        <v>1.8</v>
+      </c>
+      <c r="BM108">
+        <v>2.38</v>
+      </c>
+      <c r="BN108">
+        <v>1.49</v>
+      </c>
+      <c r="BO108">
+        <v>3.14</v>
+      </c>
+      <c r="BP108">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7818915</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45824.875</v>
+      </c>
+      <c r="F109">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>70</v>
+      </c>
+      <c r="H109" t="s">
+        <v>85</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="M109">
+        <v>2</v>
+      </c>
+      <c r="N109">
+        <v>3</v>
+      </c>
+      <c r="O109" t="s">
+        <v>157</v>
+      </c>
+      <c r="P109" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q109">
+        <v>3.2</v>
+      </c>
+      <c r="R109">
+        <v>2</v>
+      </c>
+      <c r="S109">
+        <v>3.75</v>
+      </c>
+      <c r="T109">
+        <v>1.5</v>
+      </c>
+      <c r="U109">
+        <v>2.5</v>
+      </c>
+      <c r="V109">
+        <v>3.4</v>
+      </c>
+      <c r="W109">
+        <v>1.3</v>
+      </c>
+      <c r="X109">
+        <v>10</v>
+      </c>
+      <c r="Y109">
+        <v>1.06</v>
+      </c>
+      <c r="Z109">
+        <v>2.68</v>
+      </c>
+      <c r="AA109">
+        <v>3.32</v>
+      </c>
+      <c r="AB109">
+        <v>2.53</v>
+      </c>
+      <c r="AC109">
+        <v>1.04</v>
+      </c>
+      <c r="AD109">
+        <v>7.1</v>
+      </c>
+      <c r="AE109">
+        <v>1.5</v>
+      </c>
+      <c r="AF109">
+        <v>2.52</v>
+      </c>
+      <c r="AG109">
+        <v>2.35</v>
+      </c>
+      <c r="AH109">
+        <v>1.57</v>
+      </c>
+      <c r="AI109">
+        <v>2</v>
+      </c>
+      <c r="AJ109">
+        <v>1.73</v>
+      </c>
+      <c r="AK109">
+        <v>1.37</v>
+      </c>
+      <c r="AL109">
+        <v>1.36</v>
+      </c>
+      <c r="AM109">
+        <v>1.52</v>
+      </c>
+      <c r="AN109">
+        <v>0.67</v>
+      </c>
+      <c r="AO109">
+        <v>0.67</v>
+      </c>
+      <c r="AP109">
+        <v>0.57</v>
+      </c>
+      <c r="AQ109">
+        <v>1</v>
+      </c>
+      <c r="AR109">
+        <v>1.69</v>
+      </c>
+      <c r="AS109">
+        <v>1.47</v>
+      </c>
+      <c r="AT109">
+        <v>3.16</v>
+      </c>
+      <c r="AU109">
+        <v>5</v>
+      </c>
+      <c r="AV109">
+        <v>6</v>
+      </c>
+      <c r="AW109">
+        <v>5</v>
+      </c>
+      <c r="AX109">
+        <v>4</v>
+      </c>
+      <c r="AY109">
+        <v>10</v>
+      </c>
+      <c r="AZ109">
+        <v>10</v>
+      </c>
+      <c r="BA109">
+        <v>4</v>
+      </c>
+      <c r="BB109">
+        <v>4</v>
+      </c>
+      <c r="BC109">
+        <v>8</v>
+      </c>
+      <c r="BD109">
+        <v>1.8</v>
+      </c>
+      <c r="BE109">
+        <v>6.5</v>
+      </c>
+      <c r="BF109">
+        <v>2.18</v>
+      </c>
+      <c r="BG109">
+        <v>1.33</v>
+      </c>
+      <c r="BH109">
+        <v>2.88</v>
+      </c>
+      <c r="BI109">
+        <v>1.58</v>
+      </c>
+      <c r="BJ109">
+        <v>2.14</v>
+      </c>
+      <c r="BK109">
+        <v>1.96</v>
+      </c>
+      <c r="BL109">
+        <v>1.7</v>
+      </c>
+      <c r="BM109">
+        <v>2.5</v>
+      </c>
+      <c r="BN109">
+        <v>1.43</v>
+      </c>
+      <c r="BO109">
+        <v>3.3</v>
+      </c>
+      <c r="BP109">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7818912</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45825.79166666666</v>
+      </c>
+      <c r="F110">
+        <v>14</v>
+      </c>
+      <c r="G110" t="s">
+        <v>84</v>
+      </c>
+      <c r="H110" t="s">
+        <v>83</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>4</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>4</v>
+      </c>
+      <c r="O110" t="s">
+        <v>166</v>
+      </c>
+      <c r="P110" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q110">
+        <v>1.95</v>
+      </c>
+      <c r="R110">
+        <v>2.4</v>
+      </c>
+      <c r="S110">
+        <v>6.5</v>
+      </c>
+      <c r="T110">
+        <v>1.33</v>
+      </c>
+      <c r="U110">
+        <v>3.25</v>
+      </c>
+      <c r="V110">
+        <v>2.63</v>
+      </c>
+      <c r="W110">
+        <v>1.44</v>
+      </c>
+      <c r="X110">
+        <v>6.5</v>
+      </c>
+      <c r="Y110">
+        <v>1.11</v>
+      </c>
+      <c r="Z110">
+        <v>1.45</v>
+      </c>
+      <c r="AA110">
+        <v>4</v>
+      </c>
+      <c r="AB110">
+        <v>7.5</v>
+      </c>
+      <c r="AC110">
+        <v>1.01</v>
+      </c>
+      <c r="AD110">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE110">
+        <v>1.19</v>
+      </c>
+      <c r="AF110">
+        <v>3.78</v>
+      </c>
+      <c r="AG110">
+        <v>1.75</v>
+      </c>
+      <c r="AH110">
+        <v>2.05</v>
+      </c>
+      <c r="AI110">
+        <v>1.91</v>
+      </c>
+      <c r="AJ110">
+        <v>1.8</v>
+      </c>
+      <c r="AK110">
+        <v>1.08</v>
+      </c>
+      <c r="AL110">
+        <v>1.18</v>
+      </c>
+      <c r="AM110">
+        <v>2.78</v>
+      </c>
+      <c r="AN110">
+        <v>1.83</v>
+      </c>
+      <c r="AO110">
+        <v>1.33</v>
+      </c>
+      <c r="AP110">
+        <v>2</v>
+      </c>
+      <c r="AQ110">
+        <v>1.14</v>
+      </c>
+      <c r="AR110">
+        <v>2.16</v>
+      </c>
+      <c r="AS110">
+        <v>1.49</v>
+      </c>
+      <c r="AT110">
+        <v>3.65</v>
+      </c>
+      <c r="AU110">
+        <v>9</v>
+      </c>
+      <c r="AV110">
+        <v>5</v>
+      </c>
+      <c r="AW110">
+        <v>4</v>
+      </c>
+      <c r="AX110">
+        <v>5</v>
+      </c>
+      <c r="AY110">
+        <v>13</v>
+      </c>
+      <c r="AZ110">
+        <v>10</v>
+      </c>
+      <c r="BA110">
+        <v>8</v>
+      </c>
+      <c r="BB110">
+        <v>2</v>
+      </c>
+      <c r="BC110">
+        <v>10</v>
+      </c>
+      <c r="BD110">
+        <v>1.32</v>
+      </c>
+      <c r="BE110">
+        <v>7.5</v>
+      </c>
+      <c r="BF110">
+        <v>3.65</v>
+      </c>
+      <c r="BG110">
+        <v>1.28</v>
+      </c>
+      <c r="BH110">
+        <v>3.15</v>
+      </c>
+      <c r="BI110">
+        <v>1.49</v>
+      </c>
+      <c r="BJ110">
+        <v>2.35</v>
+      </c>
+      <c r="BK110">
+        <v>1.79</v>
+      </c>
+      <c r="BL110">
+        <v>1.85</v>
+      </c>
+      <c r="BM110">
+        <v>2.23</v>
+      </c>
+      <c r="BN110">
+        <v>1.54</v>
+      </c>
+      <c r="BO110">
+        <v>2.88</v>
+      </c>
+      <c r="BP110">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7818920</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45828.77083333334</v>
+      </c>
+      <c r="F111">
+        <v>15</v>
+      </c>
+      <c r="G111" t="s">
+        <v>77</v>
+      </c>
+      <c r="H111" t="s">
+        <v>76</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>2</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>2</v>
+      </c>
+      <c r="O111" t="s">
+        <v>167</v>
+      </c>
+      <c r="P111" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q111">
+        <v>3.3</v>
+      </c>
+      <c r="R111">
+        <v>2</v>
+      </c>
+      <c r="S111">
+        <v>3.3</v>
+      </c>
+      <c r="T111">
+        <v>1.48</v>
+      </c>
+      <c r="U111">
+        <v>2.48</v>
+      </c>
+      <c r="V111">
+        <v>3.3</v>
+      </c>
+      <c r="W111">
+        <v>1.29</v>
+      </c>
+      <c r="X111">
+        <v>8</v>
+      </c>
+      <c r="Y111">
+        <v>1.04</v>
+      </c>
+      <c r="Z111">
+        <v>2.55</v>
+      </c>
+      <c r="AA111">
+        <v>3.2</v>
+      </c>
+      <c r="AB111">
+        <v>2.65</v>
+      </c>
+      <c r="AC111">
+        <v>1.05</v>
+      </c>
+      <c r="AD111">
+        <v>8</v>
+      </c>
+      <c r="AE111">
+        <v>1.36</v>
+      </c>
+      <c r="AF111">
+        <v>2.88</v>
+      </c>
+      <c r="AG111">
+        <v>2.28</v>
+      </c>
+      <c r="AH111">
+        <v>1.58</v>
+      </c>
+      <c r="AI111">
+        <v>1.91</v>
+      </c>
+      <c r="AJ111">
+        <v>1.77</v>
+      </c>
+      <c r="AK111">
+        <v>1.46</v>
+      </c>
+      <c r="AL111">
+        <v>1.33</v>
+      </c>
+      <c r="AM111">
+        <v>1.49</v>
+      </c>
+      <c r="AN111">
+        <v>1.86</v>
+      </c>
+      <c r="AO111">
+        <v>0.86</v>
+      </c>
+      <c r="AP111">
+        <v>1.75</v>
+      </c>
+      <c r="AQ111">
+        <v>0.88</v>
+      </c>
+      <c r="AR111">
+        <v>1.47</v>
+      </c>
+      <c r="AS111">
+        <v>1.22</v>
+      </c>
+      <c r="AT111">
+        <v>2.69</v>
+      </c>
+      <c r="AU111">
+        <v>4</v>
+      </c>
+      <c r="AV111">
+        <v>6</v>
+      </c>
+      <c r="AW111">
+        <v>3</v>
+      </c>
+      <c r="AX111">
+        <v>5</v>
+      </c>
+      <c r="AY111">
+        <v>7</v>
+      </c>
+      <c r="AZ111">
+        <v>11</v>
+      </c>
+      <c r="BA111">
+        <v>7</v>
+      </c>
+      <c r="BB111">
+        <v>5</v>
+      </c>
+      <c r="BC111">
+        <v>12</v>
+      </c>
+      <c r="BD111">
+        <v>1.82</v>
+      </c>
+      <c r="BE111">
+        <v>6.4</v>
+      </c>
+      <c r="BF111">
+        <v>2.18</v>
+      </c>
+      <c r="BG111">
+        <v>1.38</v>
+      </c>
+      <c r="BH111">
+        <v>2.65</v>
+      </c>
+      <c r="BI111">
+        <v>1.65</v>
+      </c>
+      <c r="BJ111">
+        <v>2.02</v>
+      </c>
+      <c r="BK111">
+        <v>2.06</v>
+      </c>
+      <c r="BL111">
+        <v>1.63</v>
+      </c>
+      <c r="BM111">
+        <v>2.65</v>
+      </c>
+      <c r="BN111">
+        <v>1.38</v>
+      </c>
+      <c r="BO111">
+        <v>3.5</v>
+      </c>
+      <c r="BP111">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7818922</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45829.5625</v>
+      </c>
+      <c r="F112">
+        <v>15</v>
+      </c>
+      <c r="G112" t="s">
+        <v>79</v>
+      </c>
+      <c r="H112" t="s">
+        <v>80</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>1</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>2</v>
+      </c>
+      <c r="N112">
+        <v>2</v>
+      </c>
+      <c r="O112" t="s">
+        <v>86</v>
+      </c>
+      <c r="P112" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q112">
+        <v>3.45</v>
+      </c>
+      <c r="R112">
+        <v>2.18</v>
+      </c>
+      <c r="S112">
+        <v>2.75</v>
+      </c>
+      <c r="T112">
+        <v>1.36</v>
+      </c>
+      <c r="U112">
+        <v>2.95</v>
+      </c>
+      <c r="V112">
+        <v>2.7</v>
+      </c>
+      <c r="W112">
+        <v>1.43</v>
+      </c>
+      <c r="X112">
+        <v>6.4</v>
+      </c>
+      <c r="Y112">
+        <v>1.08</v>
+      </c>
+      <c r="Z112">
+        <v>2.95</v>
+      </c>
+      <c r="AA112">
+        <v>3.45</v>
+      </c>
+      <c r="AB112">
+        <v>2.2</v>
+      </c>
+      <c r="AC112">
+        <v>1.01</v>
+      </c>
+      <c r="AD112">
+        <v>8.4</v>
+      </c>
+      <c r="AE112">
+        <v>1.28</v>
+      </c>
+      <c r="AF112">
+        <v>3.1</v>
+      </c>
+      <c r="AG112">
+        <v>1.86</v>
+      </c>
+      <c r="AH112">
+        <v>1.86</v>
+      </c>
+      <c r="AI112">
+        <v>1.68</v>
+      </c>
+      <c r="AJ112">
+        <v>2.04</v>
+      </c>
+      <c r="AK112">
+        <v>1.63</v>
+      </c>
+      <c r="AL112">
+        <v>1.29</v>
+      </c>
+      <c r="AM112">
+        <v>1.38</v>
+      </c>
+      <c r="AN112">
+        <v>0.67</v>
+      </c>
+      <c r="AO112">
+        <v>2</v>
+      </c>
+      <c r="AP112">
+        <v>0.5</v>
+      </c>
+      <c r="AQ112">
+        <v>2.13</v>
+      </c>
+      <c r="AR112">
+        <v>1.56</v>
+      </c>
+      <c r="AS112">
+        <v>1.39</v>
+      </c>
+      <c r="AT112">
+        <v>2.95</v>
+      </c>
+      <c r="AU112">
+        <v>2</v>
+      </c>
+      <c r="AV112">
+        <v>10</v>
+      </c>
+      <c r="AW112">
+        <v>4</v>
+      </c>
+      <c r="AX112">
+        <v>8</v>
+      </c>
+      <c r="AY112">
+        <v>6</v>
+      </c>
+      <c r="AZ112">
+        <v>18</v>
+      </c>
+      <c r="BA112">
+        <v>2</v>
+      </c>
+      <c r="BB112">
+        <v>9</v>
+      </c>
+      <c r="BC112">
+        <v>11</v>
+      </c>
+      <c r="BD112">
+        <v>1.95</v>
+      </c>
+      <c r="BE112">
+        <v>6.75</v>
+      </c>
+      <c r="BF112">
+        <v>2.02</v>
+      </c>
+      <c r="BG112">
+        <v>1.18</v>
+      </c>
+      <c r="BH112">
+        <v>3.9</v>
+      </c>
+      <c r="BI112">
+        <v>1.34</v>
+      </c>
+      <c r="BJ112">
+        <v>2.8</v>
+      </c>
+      <c r="BK112">
+        <v>1.57</v>
+      </c>
+      <c r="BL112">
+        <v>2.17</v>
+      </c>
+      <c r="BM112">
+        <v>1.91</v>
+      </c>
+      <c r="BN112">
+        <v>1.74</v>
+      </c>
+      <c r="BO112">
+        <v>2.38</v>
+      </c>
+      <c r="BP112">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7818921</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45829.66666666666</v>
+      </c>
+      <c r="F113">
+        <v>15</v>
+      </c>
+      <c r="G113" t="s">
+        <v>73</v>
+      </c>
+      <c r="H113" t="s">
+        <v>70</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>3</v>
+      </c>
+      <c r="M113">
+        <v>1</v>
+      </c>
+      <c r="N113">
+        <v>4</v>
+      </c>
+      <c r="O113" t="s">
+        <v>168</v>
+      </c>
+      <c r="P113" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q113">
+        <v>1.76</v>
+      </c>
+      <c r="R113">
+        <v>2.55</v>
+      </c>
+      <c r="S113">
+        <v>6.75</v>
+      </c>
+      <c r="T113">
+        <v>1.27</v>
+      </c>
+      <c r="U113">
+        <v>3.4</v>
+      </c>
+      <c r="V113">
+        <v>2.3</v>
+      </c>
+      <c r="W113">
+        <v>1.55</v>
+      </c>
+      <c r="X113">
+        <v>5.1</v>
+      </c>
+      <c r="Y113">
+        <v>1.13</v>
+      </c>
+      <c r="Z113">
+        <v>1.29</v>
+      </c>
+      <c r="AA113">
+        <v>4.8</v>
+      </c>
+      <c r="AB113">
+        <v>10</v>
+      </c>
+      <c r="AC113">
+        <v>1.01</v>
+      </c>
+      <c r="AD113">
+        <v>17</v>
+      </c>
+      <c r="AE113">
+        <v>1.1</v>
+      </c>
+      <c r="AF113">
+        <v>5.1</v>
+      </c>
+      <c r="AG113">
+        <v>1.57</v>
+      </c>
+      <c r="AH113">
+        <v>2.28</v>
+      </c>
+      <c r="AI113">
+        <v>1.89</v>
+      </c>
+      <c r="AJ113">
+        <v>1.8</v>
+      </c>
+      <c r="AK113">
+        <v>1.05</v>
+      </c>
+      <c r="AL113">
+        <v>1.18</v>
+      </c>
+      <c r="AM113">
+        <v>3.2</v>
+      </c>
+      <c r="AN113">
+        <v>3</v>
+      </c>
+      <c r="AO113">
+        <v>0.29</v>
+      </c>
+      <c r="AP113">
+        <v>3</v>
+      </c>
+      <c r="AQ113">
+        <v>0.25</v>
+      </c>
+      <c r="AR113">
+        <v>2.13</v>
+      </c>
+      <c r="AS113">
+        <v>1.31</v>
+      </c>
+      <c r="AT113">
+        <v>3.44</v>
+      </c>
+      <c r="AU113">
+        <v>10</v>
+      </c>
+      <c r="AV113">
+        <v>4</v>
+      </c>
+      <c r="AW113">
+        <v>8</v>
+      </c>
+      <c r="AX113">
+        <v>3</v>
+      </c>
+      <c r="AY113">
+        <v>18</v>
+      </c>
+      <c r="AZ113">
+        <v>7</v>
+      </c>
+      <c r="BA113">
+        <v>7</v>
+      </c>
+      <c r="BB113">
+        <v>1</v>
+      </c>
+      <c r="BC113">
+        <v>8</v>
+      </c>
+      <c r="BD113">
+        <v>1.26</v>
+      </c>
+      <c r="BE113">
+        <v>8</v>
+      </c>
+      <c r="BF113">
+        <v>4.1</v>
+      </c>
+      <c r="BG113">
+        <v>1.27</v>
+      </c>
+      <c r="BH113">
+        <v>3.2</v>
+      </c>
+      <c r="BI113">
+        <v>1.47</v>
+      </c>
+      <c r="BJ113">
+        <v>2.38</v>
+      </c>
+      <c r="BK113">
+        <v>1.78</v>
+      </c>
+      <c r="BL113">
+        <v>1.87</v>
+      </c>
+      <c r="BM113">
+        <v>2.2</v>
+      </c>
+      <c r="BN113">
+        <v>1.55</v>
+      </c>
+      <c r="BO113">
+        <v>2.8</v>
+      </c>
+      <c r="BP113">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7818924</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45829.77083333334</v>
+      </c>
+      <c r="F114">
+        <v>15</v>
+      </c>
+      <c r="G114" t="s">
+        <v>82</v>
+      </c>
+      <c r="H114" t="s">
+        <v>71</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>2</v>
+      </c>
+      <c r="K114">
+        <v>2</v>
+      </c>
+      <c r="L114">
+        <v>2</v>
+      </c>
+      <c r="M114">
+        <v>2</v>
+      </c>
+      <c r="N114">
+        <v>4</v>
+      </c>
+      <c r="O114" t="s">
+        <v>169</v>
+      </c>
+      <c r="P114" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q114">
+        <v>3.3</v>
+      </c>
+      <c r="R114">
+        <v>2.17</v>
+      </c>
+      <c r="S114">
+        <v>2.9</v>
+      </c>
+      <c r="T114">
+        <v>1.38</v>
+      </c>
+      <c r="U114">
+        <v>2.88</v>
+      </c>
+      <c r="V114">
+        <v>2.8</v>
+      </c>
+      <c r="W114">
+        <v>1.38</v>
+      </c>
+      <c r="X114">
+        <v>6.75</v>
+      </c>
+      <c r="Y114">
+        <v>1.07</v>
+      </c>
+      <c r="Z114">
+        <v>2.75</v>
+      </c>
+      <c r="AA114">
+        <v>3.25</v>
+      </c>
+      <c r="AB114">
+        <v>2.3</v>
+      </c>
+      <c r="AC114">
+        <v>1.03</v>
+      </c>
+      <c r="AD114">
+        <v>9</v>
+      </c>
+      <c r="AE114">
+        <v>1.29</v>
+      </c>
+      <c r="AF114">
+        <v>3.3</v>
+      </c>
+      <c r="AG114">
+        <v>1.94</v>
+      </c>
+      <c r="AH114">
+        <v>1.79</v>
+      </c>
+      <c r="AI114">
+        <v>1.73</v>
+      </c>
+      <c r="AJ114">
+        <v>1.97</v>
+      </c>
+      <c r="AK114">
+        <v>1.55</v>
+      </c>
+      <c r="AL114">
+        <v>1.29</v>
+      </c>
+      <c r="AM114">
+        <v>1.44</v>
+      </c>
+      <c r="AN114">
+        <v>2</v>
+      </c>
+      <c r="AO114">
+        <v>2</v>
+      </c>
+      <c r="AP114">
+        <v>1.86</v>
+      </c>
+      <c r="AQ114">
+        <v>1.88</v>
+      </c>
+      <c r="AR114">
+        <v>1.4</v>
+      </c>
+      <c r="AS114">
+        <v>1.53</v>
+      </c>
+      <c r="AT114">
+        <v>2.93</v>
+      </c>
+      <c r="AU114">
+        <v>8</v>
+      </c>
+      <c r="AV114">
+        <v>5</v>
+      </c>
+      <c r="AW114">
+        <v>9</v>
+      </c>
+      <c r="AX114">
+        <v>4</v>
+      </c>
+      <c r="AY114">
+        <v>17</v>
+      </c>
+      <c r="AZ114">
+        <v>9</v>
+      </c>
+      <c r="BA114">
+        <v>4</v>
+      </c>
+      <c r="BB114">
+        <v>2</v>
+      </c>
+      <c r="BC114">
+        <v>6</v>
+      </c>
+      <c r="BD114">
+        <v>1.95</v>
+      </c>
+      <c r="BE114">
+        <v>6.4</v>
+      </c>
+      <c r="BF114">
+        <v>2.05</v>
+      </c>
+      <c r="BG114">
+        <v>1.35</v>
+      </c>
+      <c r="BH114">
+        <v>2.8</v>
+      </c>
+      <c r="BI114">
+        <v>1.58</v>
+      </c>
+      <c r="BJ114">
+        <v>2.12</v>
+      </c>
+      <c r="BK114">
+        <v>1.96</v>
+      </c>
+      <c r="BL114">
+        <v>1.7</v>
+      </c>
+      <c r="BM114">
+        <v>2.55</v>
+      </c>
+      <c r="BN114">
+        <v>1.42</v>
+      </c>
+      <c r="BO114">
+        <v>3.3</v>
+      </c>
+      <c r="BP114">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7818923</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45830.5625</v>
+      </c>
+      <c r="F115">
+        <v>15</v>
+      </c>
+      <c r="G115" t="s">
+        <v>74</v>
+      </c>
+      <c r="H115" t="s">
+        <v>75</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>2</v>
+      </c>
+      <c r="O115" t="s">
+        <v>170</v>
+      </c>
+      <c r="P115" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q115">
+        <v>3</v>
+      </c>
+      <c r="R115">
+        <v>2.25</v>
+      </c>
+      <c r="S115">
+        <v>3.4</v>
+      </c>
+      <c r="T115">
+        <v>1.36</v>
+      </c>
+      <c r="U115">
+        <v>3</v>
+      </c>
+      <c r="V115">
+        <v>2.63</v>
+      </c>
+      <c r="W115">
+        <v>1.44</v>
+      </c>
+      <c r="X115">
+        <v>7</v>
+      </c>
+      <c r="Y115">
+        <v>1.1</v>
+      </c>
+      <c r="Z115">
+        <v>2.44</v>
+      </c>
+      <c r="AA115">
+        <v>3.54</v>
+      </c>
+      <c r="AB115">
+        <v>2.75</v>
+      </c>
+      <c r="AC115">
+        <v>1</v>
+      </c>
+      <c r="AD115">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE115">
+        <v>1.27</v>
+      </c>
+      <c r="AF115">
+        <v>3.66</v>
+      </c>
+      <c r="AG115">
+        <v>1.86</v>
+      </c>
+      <c r="AH115">
+        <v>1.96</v>
+      </c>
+      <c r="AI115">
+        <v>1.67</v>
+      </c>
+      <c r="AJ115">
+        <v>2.1</v>
+      </c>
+      <c r="AK115">
+        <v>1.44</v>
+      </c>
+      <c r="AL115">
+        <v>1.29</v>
+      </c>
+      <c r="AM115">
+        <v>1.53</v>
+      </c>
+      <c r="AN115">
+        <v>2</v>
+      </c>
+      <c r="AO115">
+        <v>0.33</v>
+      </c>
+      <c r="AP115">
+        <v>1.86</v>
+      </c>
+      <c r="AQ115">
+        <v>0.43</v>
+      </c>
+      <c r="AR115">
+        <v>1.68</v>
+      </c>
+      <c r="AS115">
+        <v>1.66</v>
+      </c>
+      <c r="AT115">
+        <v>3.34</v>
+      </c>
+      <c r="AU115">
+        <v>6</v>
+      </c>
+      <c r="AV115">
+        <v>6</v>
+      </c>
+      <c r="AW115">
+        <v>9</v>
+      </c>
+      <c r="AX115">
+        <v>6</v>
+      </c>
+      <c r="AY115">
+        <v>15</v>
+      </c>
+      <c r="AZ115">
+        <v>12</v>
+      </c>
+      <c r="BA115">
+        <v>2</v>
+      </c>
+      <c r="BB115">
+        <v>5</v>
+      </c>
+      <c r="BC115">
+        <v>7</v>
+      </c>
+      <c r="BD115">
+        <v>1.97</v>
+      </c>
+      <c r="BE115">
+        <v>6.4</v>
+      </c>
+      <c r="BF115">
+        <v>2.02</v>
+      </c>
+      <c r="BG115">
+        <v>1.26</v>
+      </c>
+      <c r="BH115">
+        <v>3.3</v>
+      </c>
+      <c r="BI115">
+        <v>1.46</v>
+      </c>
+      <c r="BJ115">
+        <v>2.4</v>
+      </c>
+      <c r="BK115">
+        <v>1.77</v>
+      </c>
+      <c r="BL115">
+        <v>1.88</v>
+      </c>
+      <c r="BM115">
+        <v>2.2</v>
+      </c>
+      <c r="BN115">
+        <v>1.55</v>
+      </c>
+      <c r="BO115">
+        <v>2.8</v>
+      </c>
+      <c r="BP115">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7818919</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45830.66666666666</v>
+      </c>
+      <c r="F116">
+        <v>15</v>
+      </c>
+      <c r="G116" t="s">
+        <v>78</v>
+      </c>
+      <c r="H116" t="s">
+        <v>84</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>2</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116">
+        <v>3</v>
+      </c>
+      <c r="O116" t="s">
+        <v>171</v>
+      </c>
+      <c r="P116" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q116">
+        <v>4.33</v>
+      </c>
+      <c r="R116">
+        <v>2.2</v>
+      </c>
+      <c r="S116">
+        <v>2.5</v>
+      </c>
+      <c r="T116">
+        <v>1.36</v>
+      </c>
+      <c r="U116">
+        <v>3</v>
+      </c>
+      <c r="V116">
+        <v>2.75</v>
+      </c>
+      <c r="W116">
+        <v>1.4</v>
+      </c>
+      <c r="X116">
+        <v>7</v>
+      </c>
+      <c r="Y116">
+        <v>1.1</v>
+      </c>
+      <c r="Z116">
+        <v>3.7</v>
+      </c>
+      <c r="AA116">
+        <v>3.5</v>
+      </c>
+      <c r="AB116">
+        <v>1.91</v>
+      </c>
+      <c r="AC116">
+        <v>1.01</v>
+      </c>
+      <c r="AD116">
+        <v>9.9</v>
+      </c>
+      <c r="AE116">
+        <v>1.24</v>
+      </c>
+      <c r="AF116">
+        <v>3.36</v>
+      </c>
+      <c r="AG116">
+        <v>1.9</v>
+      </c>
+      <c r="AH116">
+        <v>1.9</v>
+      </c>
+      <c r="AI116">
+        <v>1.73</v>
+      </c>
+      <c r="AJ116">
+        <v>2</v>
+      </c>
+      <c r="AK116">
+        <v>1.79</v>
+      </c>
+      <c r="AL116">
+        <v>1.28</v>
+      </c>
+      <c r="AM116">
+        <v>1.28</v>
+      </c>
+      <c r="AN116">
+        <v>2.71</v>
+      </c>
+      <c r="AO116">
+        <v>1.4</v>
+      </c>
+      <c r="AP116">
+        <v>2.75</v>
+      </c>
+      <c r="AQ116">
+        <v>1.17</v>
+      </c>
+      <c r="AR116">
+        <v>1.79</v>
+      </c>
+      <c r="AS116">
+        <v>1.89</v>
+      </c>
+      <c r="AT116">
+        <v>3.68</v>
+      </c>
+      <c r="AU116">
+        <v>5</v>
+      </c>
+      <c r="AV116">
+        <v>12</v>
+      </c>
+      <c r="AW116">
+        <v>6</v>
+      </c>
+      <c r="AX116">
+        <v>10</v>
+      </c>
+      <c r="AY116">
+        <v>11</v>
+      </c>
+      <c r="AZ116">
+        <v>22</v>
+      </c>
+      <c r="BA116">
+        <v>2</v>
+      </c>
+      <c r="BB116">
+        <v>7</v>
+      </c>
+      <c r="BC116">
+        <v>9</v>
+      </c>
+      <c r="BD116">
+        <v>2.65</v>
+      </c>
+      <c r="BE116">
+        <v>6.5</v>
+      </c>
+      <c r="BF116">
+        <v>1.56</v>
+      </c>
+      <c r="BG116">
+        <v>1.37</v>
+      </c>
+      <c r="BH116">
+        <v>2.7</v>
+      </c>
+      <c r="BI116">
+        <v>1.62</v>
+      </c>
+      <c r="BJ116">
+        <v>2.08</v>
+      </c>
+      <c r="BK116">
+        <v>2</v>
+      </c>
+      <c r="BL116">
+        <v>1.67</v>
+      </c>
+      <c r="BM116">
+        <v>2.55</v>
+      </c>
+      <c r="BN116">
+        <v>1.42</v>
+      </c>
+      <c r="BO116">
+        <v>3.35</v>
+      </c>
+      <c r="BP116">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7818926</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45830.77083333334</v>
+      </c>
+      <c r="F117">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>83</v>
+      </c>
+      <c r="H117" t="s">
+        <v>81</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117">
+        <v>2</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>2</v>
+      </c>
+      <c r="O117" t="s">
+        <v>172</v>
+      </c>
+      <c r="P117" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q117">
+        <v>2.75</v>
+      </c>
+      <c r="R117">
+        <v>2.2</v>
+      </c>
+      <c r="S117">
+        <v>3.75</v>
+      </c>
+      <c r="T117">
+        <v>1.36</v>
+      </c>
+      <c r="U117">
+        <v>3</v>
+      </c>
+      <c r="V117">
+        <v>2.75</v>
+      </c>
+      <c r="W117">
+        <v>1.4</v>
+      </c>
+      <c r="X117">
+        <v>7</v>
+      </c>
+      <c r="Y117">
+        <v>1.1</v>
+      </c>
+      <c r="Z117">
+        <v>2.15</v>
+      </c>
+      <c r="AA117">
+        <v>3.25</v>
+      </c>
+      <c r="AB117">
+        <v>3.3</v>
+      </c>
+      <c r="AC117">
+        <v>1.01</v>
+      </c>
+      <c r="AD117">
+        <v>9.85</v>
+      </c>
+      <c r="AE117">
+        <v>1.22</v>
+      </c>
+      <c r="AF117">
+        <v>3.5</v>
+      </c>
+      <c r="AG117">
+        <v>1.85</v>
+      </c>
+      <c r="AH117">
+        <v>1.95</v>
+      </c>
+      <c r="AI117">
+        <v>1.67</v>
+      </c>
+      <c r="AJ117">
+        <v>2.1</v>
+      </c>
+      <c r="AK117">
+        <v>1.33</v>
+      </c>
+      <c r="AL117">
+        <v>1.29</v>
+      </c>
+      <c r="AM117">
+        <v>1.67</v>
+      </c>
+      <c r="AN117">
+        <v>2</v>
+      </c>
+      <c r="AO117">
+        <v>1.17</v>
+      </c>
+      <c r="AP117">
+        <v>1.88</v>
+      </c>
+      <c r="AQ117">
+        <v>1.14</v>
+      </c>
+      <c r="AR117">
+        <v>1.73</v>
+      </c>
+      <c r="AS117">
+        <v>1.22</v>
+      </c>
+      <c r="AT117">
+        <v>2.95</v>
+      </c>
+      <c r="AU117">
+        <v>6</v>
+      </c>
+      <c r="AV117">
+        <v>4</v>
+      </c>
+      <c r="AW117">
+        <v>6</v>
+      </c>
+      <c r="AX117">
+        <v>8</v>
+      </c>
+      <c r="AY117">
+        <v>12</v>
+      </c>
+      <c r="AZ117">
+        <v>12</v>
+      </c>
+      <c r="BA117">
+        <v>3</v>
+      </c>
+      <c r="BB117">
+        <v>12</v>
+      </c>
+      <c r="BC117">
+        <v>15</v>
+      </c>
+      <c r="BD117">
+        <v>1.75</v>
+      </c>
+      <c r="BE117">
+        <v>6.5</v>
+      </c>
+      <c r="BF117">
+        <v>2.3</v>
+      </c>
+      <c r="BG117">
+        <v>1.3</v>
+      </c>
+      <c r="BH117">
+        <v>3.05</v>
+      </c>
+      <c r="BI117">
+        <v>1.53</v>
+      </c>
+      <c r="BJ117">
+        <v>2.25</v>
+      </c>
+      <c r="BK117">
+        <v>1.87</v>
+      </c>
+      <c r="BL117">
+        <v>1.78</v>
+      </c>
+      <c r="BM117">
+        <v>2.35</v>
+      </c>
+      <c r="BN117">
+        <v>1.49</v>
+      </c>
+      <c r="BO117">
+        <v>3.05</v>
+      </c>
+      <c r="BP117">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7818925</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45830.875</v>
+      </c>
+      <c r="F118">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s">
+        <v>85</v>
+      </c>
+      <c r="H118" t="s">
+        <v>72</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>1</v>
+      </c>
+      <c r="N118">
+        <v>1</v>
+      </c>
+      <c r="O118" t="s">
+        <v>86</v>
+      </c>
+      <c r="P118" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q118">
+        <v>3</v>
+      </c>
+      <c r="R118">
+        <v>2.1</v>
+      </c>
+      <c r="S118">
+        <v>3.6</v>
+      </c>
+      <c r="T118">
+        <v>1.4</v>
+      </c>
+      <c r="U118">
+        <v>2.75</v>
+      </c>
+      <c r="V118">
+        <v>3</v>
+      </c>
+      <c r="W118">
+        <v>1.36</v>
+      </c>
+      <c r="X118">
+        <v>8</v>
+      </c>
+      <c r="Y118">
+        <v>1.08</v>
+      </c>
+      <c r="Z118">
+        <v>2.3</v>
+      </c>
+      <c r="AA118">
+        <v>3.2</v>
+      </c>
+      <c r="AB118">
+        <v>3.1</v>
+      </c>
+      <c r="AC118">
+        <v>1.02</v>
+      </c>
+      <c r="AD118">
+        <v>7.9</v>
+      </c>
+      <c r="AE118">
+        <v>1.27</v>
+      </c>
+      <c r="AF118">
+        <v>3.15</v>
+      </c>
+      <c r="AG118">
+        <v>2.05</v>
+      </c>
+      <c r="AH118">
+        <v>1.75</v>
+      </c>
+      <c r="AI118">
+        <v>1.8</v>
+      </c>
+      <c r="AJ118">
+        <v>1.91</v>
+      </c>
+      <c r="AK118">
+        <v>1.36</v>
+      </c>
+      <c r="AL118">
+        <v>1.31</v>
+      </c>
+      <c r="AM118">
+        <v>1.61</v>
+      </c>
+      <c r="AN118">
+        <v>1</v>
+      </c>
+      <c r="AO118">
+        <v>1.14</v>
+      </c>
+      <c r="AP118">
+        <v>0.88</v>
+      </c>
+      <c r="AQ118">
+        <v>1.38</v>
+      </c>
+      <c r="AR118">
+        <v>1.81</v>
+      </c>
+      <c r="AS118">
+        <v>1.65</v>
+      </c>
+      <c r="AT118">
+        <v>3.46</v>
+      </c>
+      <c r="AU118">
+        <v>3</v>
+      </c>
+      <c r="AV118">
+        <v>5</v>
+      </c>
+      <c r="AW118">
+        <v>7</v>
+      </c>
+      <c r="AX118">
+        <v>10</v>
+      </c>
+      <c r="AY118">
+        <v>10</v>
+      </c>
+      <c r="AZ118">
+        <v>15</v>
+      </c>
+      <c r="BA118">
+        <v>3</v>
+      </c>
+      <c r="BB118">
+        <v>7</v>
+      </c>
+      <c r="BC118">
+        <v>10</v>
+      </c>
+      <c r="BD118">
+        <v>1.71</v>
+      </c>
+      <c r="BE118">
+        <v>6.75</v>
+      </c>
+      <c r="BF118">
+        <v>2.33</v>
+      </c>
+      <c r="BG118">
+        <v>1.19</v>
+      </c>
+      <c r="BH118">
+        <v>3.8</v>
+      </c>
+      <c r="BI118">
+        <v>1.35</v>
+      </c>
+      <c r="BJ118">
+        <v>2.8</v>
+      </c>
+      <c r="BK118">
+        <v>1.6</v>
+      </c>
+      <c r="BL118">
+        <v>2.12</v>
+      </c>
+      <c r="BM118">
+        <v>1.93</v>
+      </c>
+      <c r="BN118">
+        <v>1.72</v>
+      </c>
+      <c r="BO118">
+        <v>2.43</v>
+      </c>
+      <c r="BP118">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7818831</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
         <v>45843.66666666666</v>
       </c>
-      <c r="F98">
+      <c r="F119">
         <v>4</v>
       </c>
-      <c r="G98" t="s">
+      <c r="G119" t="s">
         <v>79</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H119" t="s">
         <v>73</v>
       </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98">
-        <v>1</v>
-      </c>
-      <c r="K98">
-        <v>1</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98">
-        <v>2</v>
-      </c>
-      <c r="N98">
-        <v>2</v>
-      </c>
-      <c r="O98" t="s">
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>1</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>2</v>
+      </c>
+      <c r="N119">
+        <v>2</v>
+      </c>
+      <c r="O119" t="s">
         <v>86</v>
       </c>
-      <c r="P98" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q98">
+      <c r="P119" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q119">
         <v>4.5</v>
       </c>
-      <c r="R98">
+      <c r="R119">
         <v>2.3</v>
       </c>
-      <c r="S98">
+      <c r="S119">
         <v>2.38</v>
       </c>
-      <c r="T98">
+      <c r="T119">
         <v>1.33</v>
       </c>
-      <c r="U98">
+      <c r="U119">
         <v>3.25</v>
       </c>
-      <c r="V98">
+      <c r="V119">
         <v>2.5</v>
       </c>
-      <c r="W98">
+      <c r="W119">
         <v>1.5</v>
       </c>
-      <c r="X98">
+      <c r="X119">
         <v>6.5</v>
       </c>
-      <c r="Y98">
+      <c r="Y119">
         <v>1.11</v>
       </c>
-      <c r="Z98">
+      <c r="Z119">
         <v>4.2</v>
       </c>
-      <c r="AA98">
+      <c r="AA119">
         <v>3.8</v>
       </c>
-      <c r="AB98">
+      <c r="AB119">
         <v>1.8</v>
       </c>
-      <c r="AC98">
+      <c r="AC119">
         <v>1.04</v>
       </c>
-      <c r="AD98">
+      <c r="AD119">
         <v>13</v>
       </c>
-      <c r="AE98">
+      <c r="AE119">
         <v>1.21</v>
       </c>
-      <c r="AF98">
+      <c r="AF119">
         <v>4.32</v>
       </c>
-      <c r="AG98">
+      <c r="AG119">
         <v>1.67</v>
       </c>
-      <c r="AH98">
+      <c r="AH119">
         <v>2.15</v>
       </c>
-      <c r="AI98">
+      <c r="AI119">
         <v>1.62</v>
       </c>
-      <c r="AJ98">
+      <c r="AJ119">
         <v>2.2</v>
       </c>
-      <c r="AK98">
+      <c r="AK119">
         <v>1.91</v>
       </c>
-      <c r="AL98">
+      <c r="AL119">
         <v>1.29</v>
       </c>
-      <c r="AM98">
+      <c r="AM119">
         <v>1.25</v>
       </c>
-      <c r="AN98">
-        <v>0.6</v>
-      </c>
-      <c r="AO98">
-        <v>0.8</v>
-      </c>
-      <c r="AP98">
+      <c r="AN119">
+        <v>0.57</v>
+      </c>
+      <c r="AO119">
+        <v>0.67</v>
+      </c>
+      <c r="AP119">
         <v>0.5</v>
       </c>
-      <c r="AQ98">
-        <v>1.17</v>
-      </c>
-      <c r="AR98">
+      <c r="AQ119">
+        <v>1</v>
+      </c>
+      <c r="AR119">
         <v>1.56</v>
       </c>
-      <c r="AS98">
+      <c r="AS119">
         <v>1.91</v>
       </c>
-      <c r="AT98">
+      <c r="AT119">
         <v>3.47</v>
       </c>
-      <c r="AU98">
+      <c r="AU119">
         <v>4</v>
       </c>
-      <c r="AV98">
+      <c r="AV119">
         <v>3</v>
       </c>
-      <c r="AW98">
+      <c r="AW119">
         <v>6</v>
       </c>
-      <c r="AX98">
+      <c r="AX119">
         <v>7</v>
       </c>
-      <c r="AY98">
+      <c r="AY119">
         <v>10</v>
       </c>
-      <c r="AZ98">
+      <c r="AZ119">
         <v>10</v>
       </c>
-      <c r="BA98">
+      <c r="BA119">
         <v>4</v>
       </c>
-      <c r="BB98">
+      <c r="BB119">
         <v>3</v>
       </c>
-      <c r="BC98">
+      <c r="BC119">
         <v>7</v>
       </c>
-      <c r="BD98">
+      <c r="BD119">
         <v>2.6</v>
       </c>
-      <c r="BE98">
+      <c r="BE119">
         <v>6.75</v>
       </c>
-      <c r="BF98">
+      <c r="BF119">
         <v>1.58</v>
       </c>
-      <c r="BG98">
+      <c r="BG119">
         <v>1.25</v>
       </c>
-      <c r="BH98">
+      <c r="BH119">
         <v>3.35</v>
       </c>
-      <c r="BI98">
+      <c r="BI119">
         <v>1.44</v>
       </c>
-      <c r="BJ98">
+      <c r="BJ119">
         <v>2.45</v>
       </c>
-      <c r="BK98">
+      <c r="BK119">
         <v>1.73</v>
       </c>
-      <c r="BL98">
+      <c r="BL119">
         <v>1.93</v>
       </c>
-      <c r="BM98">
+      <c r="BM119">
         <v>2.14</v>
       </c>
-      <c r="BN98">
+      <c r="BN119">
         <v>1.58</v>
       </c>
-      <c r="BO98">
+      <c r="BO119">
         <v>2.7</v>
       </c>
-      <c r="BP98">
+      <c r="BP119">
         <v>1.37</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -21790,22 +21790,22 @@
         <v>3.22</v>
       </c>
       <c r="AU101">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV101">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW101">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AX101">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY101">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AZ101">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA101">
         <v>10</v>
@@ -21996,31 +21996,31 @@
         <v>3.58</v>
       </c>
       <c r="AU102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV102">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW102">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX102">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY102">
         <v>11</v>
       </c>
       <c r="AZ102">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BA102">
         <v>6</v>
       </c>
       <c r="BB102">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC102">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD102">
         <v>3.15</v>
@@ -22202,31 +22202,31 @@
         <v>2.71</v>
       </c>
       <c r="AU103">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV103">
         <v>3</v>
       </c>
       <c r="AW103">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX103">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY103">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AZ103">
+        <v>12</v>
+      </c>
+      <c r="BA103">
+        <v>5</v>
+      </c>
+      <c r="BB103">
+        <v>2</v>
+      </c>
+      <c r="BC103">
         <v>7</v>
-      </c>
-      <c r="BA103">
-        <v>6</v>
-      </c>
-      <c r="BB103">
-        <v>2</v>
-      </c>
-      <c r="BC103">
-        <v>8</v>
       </c>
       <c r="BD103">
         <v>1.85</v>
@@ -22411,19 +22411,19 @@
         <v>7</v>
       </c>
       <c r="AV104">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW104">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX104">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY104">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ104">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA104">
         <v>7</v>
@@ -22614,22 +22614,22 @@
         <v>3.03</v>
       </c>
       <c r="AU105">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV105">
         <v>4</v>
       </c>
       <c r="AW105">
+        <v>13</v>
+      </c>
+      <c r="AX105">
+        <v>4</v>
+      </c>
+      <c r="AY105">
+        <v>20</v>
+      </c>
+      <c r="AZ105">
         <v>8</v>
-      </c>
-      <c r="AX105">
-        <v>1</v>
-      </c>
-      <c r="AY105">
-        <v>12</v>
-      </c>
-      <c r="AZ105">
-        <v>5</v>
       </c>
       <c r="BA105">
         <v>4</v>
@@ -22820,22 +22820,22 @@
         <v>3.56</v>
       </c>
       <c r="AU106">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV106">
         <v>2</v>
       </c>
       <c r="AW106">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AX106">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY106">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AZ106">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA106">
         <v>6</v>
@@ -23029,28 +23029,28 @@
         <v>3</v>
       </c>
       <c r="AV107">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW107">
         <v>1</v>
       </c>
       <c r="AX107">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AY107">
         <v>4</v>
       </c>
       <c r="AZ107">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BA107">
         <v>1</v>
       </c>
       <c r="BB107">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC107">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD107">
         <v>1.97</v>
@@ -23235,28 +23235,28 @@
         <v>4</v>
       </c>
       <c r="AV108">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW108">
+        <v>15</v>
+      </c>
+      <c r="AX108">
+        <v>5</v>
+      </c>
+      <c r="AY108">
+        <v>19</v>
+      </c>
+      <c r="AZ108">
+        <v>10</v>
+      </c>
+      <c r="BA108">
+        <v>8</v>
+      </c>
+      <c r="BB108">
+        <v>1</v>
+      </c>
+      <c r="BC108">
         <v>9</v>
-      </c>
-      <c r="AX108">
-        <v>3</v>
-      </c>
-      <c r="AY108">
-        <v>13</v>
-      </c>
-      <c r="AZ108">
-        <v>7</v>
-      </c>
-      <c r="BA108">
-        <v>7</v>
-      </c>
-      <c r="BB108">
-        <v>1</v>
-      </c>
-      <c r="BC108">
-        <v>8</v>
       </c>
       <c r="BD108">
         <v>1.64</v>
@@ -23429,31 +23429,31 @@
         <v>1</v>
       </c>
       <c r="AR109">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AS109">
         <v>1.47</v>
       </c>
       <c r="AT109">
-        <v>3.16</v>
+        <v>3.07</v>
       </c>
       <c r="AU109">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV109">
         <v>6</v>
       </c>
       <c r="AW109">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX109">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY109">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ109">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA109">
         <v>4</v>
@@ -23644,22 +23644,22 @@
         <v>3.65</v>
       </c>
       <c r="AU110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV110">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW110">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AX110">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY110">
+        <v>17</v>
+      </c>
+      <c r="AZ110">
         <v>13</v>
-      </c>
-      <c r="AZ110">
-        <v>10</v>
       </c>
       <c r="BA110">
         <v>8</v>
@@ -23850,22 +23850,22 @@
         <v>2.69</v>
       </c>
       <c r="AU111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV111">
         <v>6</v>
       </c>
       <c r="AW111">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX111">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY111">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ111">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA111">
         <v>7</v>
@@ -24047,13 +24047,13 @@
         <v>2.13</v>
       </c>
       <c r="AR112">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AS112">
         <v>1.39</v>
       </c>
       <c r="AT112">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="AU112">
         <v>2</v>
@@ -24065,13 +24065,13 @@
         <v>4</v>
       </c>
       <c r="AX112">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY112">
         <v>6</v>
       </c>
       <c r="AZ112">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA112">
         <v>2</v>
@@ -24265,19 +24265,19 @@
         <v>10</v>
       </c>
       <c r="AV113">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW113">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX113">
         <v>3</v>
       </c>
       <c r="AY113">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ113">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA113">
         <v>7</v>
@@ -24468,22 +24468,22 @@
         <v>2.93</v>
       </c>
       <c r="AU114">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV114">
         <v>5</v>
       </c>
       <c r="AW114">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX114">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY114">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AZ114">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA114">
         <v>4</v>
@@ -24668,28 +24668,28 @@
         <v>1.68</v>
       </c>
       <c r="AS115">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AT115">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AU115">
         <v>6</v>
       </c>
       <c r="AV115">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW115">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX115">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY115">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ115">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA115">
         <v>2</v>
@@ -24874,28 +24874,28 @@
         <v>1.79</v>
       </c>
       <c r="AS116">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AT116">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
       <c r="AU116">
         <v>5</v>
       </c>
       <c r="AV116">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW116">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX116">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AY116">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ116">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BA116">
         <v>2</v>
@@ -25089,28 +25089,28 @@
         <v>6</v>
       </c>
       <c r="AV117">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW117">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX117">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY117">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ117">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BA117">
         <v>3</v>
       </c>
       <c r="BB117">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC117">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD117">
         <v>1.75</v>
@@ -25295,16 +25295,16 @@
         <v>3</v>
       </c>
       <c r="AV118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW118">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX118">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY118">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ118">
         <v>15</v>
@@ -25489,13 +25489,13 @@
         <v>1</v>
       </c>
       <c r="AR119">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AS119">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AT119">
-        <v>3.47</v>
+        <v>3.37</v>
       </c>
       <c r="AU119">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -535,6 +535,9 @@
     <t>['45+1']</t>
   </si>
   <si>
+    <t>['70', '90+5']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -1047,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1303,7 +1306,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -2127,7 +2130,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2208,7 +2211,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2333,7 +2336,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2539,7 +2542,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2617,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AQ8">
         <v>1.43</v>
@@ -2951,7 +2954,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3157,7 +3160,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3981,7 +3984,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4599,7 +4602,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -5089,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AQ20">
         <v>0.25</v>
@@ -5217,7 +5220,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5423,7 +5426,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5629,7 +5632,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5710,7 +5713,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ23">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -5835,7 +5838,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -6041,7 +6044,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6453,7 +6456,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6659,7 +6662,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6865,7 +6868,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7071,7 +7074,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7895,7 +7898,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8925,7 +8928,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9131,7 +9134,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9543,7 +9546,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9955,7 +9958,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10367,7 +10370,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10985,7 +10988,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11397,7 +11400,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -12633,7 +12636,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12839,7 +12842,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -12917,7 +12920,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AQ58">
         <v>0.43</v>
@@ -13045,7 +13048,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -14153,7 +14156,7 @@
         <v>0.25</v>
       </c>
       <c r="AP64">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14281,7 +14284,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14693,7 +14696,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14899,7 +14902,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15105,7 +15108,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15392,7 +15395,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15723,7 +15726,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16547,7 +16550,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16753,7 +16756,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17165,7 +17168,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17577,7 +17580,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17989,7 +17992,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18195,7 +18198,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18401,7 +18404,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18813,7 +18816,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19637,7 +19640,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19715,7 +19718,7 @@
         <v>0.17</v>
       </c>
       <c r="AP91">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AQ91">
         <v>0.5</v>
@@ -20049,7 +20052,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20255,7 +20258,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20461,7 +20464,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -21079,7 +21082,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21285,7 +21288,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21366,7 +21369,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ99">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR99">
         <v>1.47</v>
@@ -21491,7 +21494,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21697,7 +21700,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q101">
         <v>2.75</v>
@@ -21903,7 +21906,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -21984,7 +21987,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ102">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR102">
         <v>1.69</v>
@@ -22109,7 +22112,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22599,7 +22602,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AQ105">
         <v>0.63</v>
@@ -23139,7 +23142,7 @@
         <v>165</v>
       </c>
       <c r="P108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23345,7 +23348,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23963,7 +23966,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q112">
         <v>3.45</v>
@@ -24169,7 +24172,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q113">
         <v>1.76</v>
@@ -24375,7 +24378,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q114">
         <v>3.3</v>
@@ -24581,7 +24584,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24787,7 +24790,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -24868,7 +24871,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ116">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR116">
         <v>1.79</v>
@@ -24993,7 +24996,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25199,7 +25202,7 @@
         <v>86</v>
       </c>
       <c r="P118" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q118">
         <v>3</v>
@@ -25405,7 +25408,7 @@
         <v>86</v>
       </c>
       <c r="P119" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25562,6 +25565,212 @@
       </c>
       <c r="BP119">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7818839</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45844.66666666666</v>
+      </c>
+      <c r="F120">
+        <v>5</v>
+      </c>
+      <c r="G120" t="s">
+        <v>76</v>
+      </c>
+      <c r="H120" t="s">
+        <v>84</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>2</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>2</v>
+      </c>
+      <c r="O120" t="s">
+        <v>173</v>
+      </c>
+      <c r="P120" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q120">
+        <v>4.75</v>
+      </c>
+      <c r="R120">
+        <v>2.05</v>
+      </c>
+      <c r="S120">
+        <v>2.6</v>
+      </c>
+      <c r="T120">
+        <v>1.44</v>
+      </c>
+      <c r="U120">
+        <v>2.63</v>
+      </c>
+      <c r="V120">
+        <v>3.25</v>
+      </c>
+      <c r="W120">
+        <v>1.33</v>
+      </c>
+      <c r="X120">
+        <v>10</v>
+      </c>
+      <c r="Y120">
+        <v>1.06</v>
+      </c>
+      <c r="Z120">
+        <v>3.8</v>
+      </c>
+      <c r="AA120">
+        <v>3.6</v>
+      </c>
+      <c r="AB120">
+        <v>1.9</v>
+      </c>
+      <c r="AC120">
+        <v>1.03</v>
+      </c>
+      <c r="AD120">
+        <v>7.3</v>
+      </c>
+      <c r="AE120">
+        <v>1.35</v>
+      </c>
+      <c r="AF120">
+        <v>2.75</v>
+      </c>
+      <c r="AG120">
+        <v>2.2</v>
+      </c>
+      <c r="AH120">
+        <v>1.65</v>
+      </c>
+      <c r="AI120">
+        <v>2</v>
+      </c>
+      <c r="AJ120">
+        <v>1.73</v>
+      </c>
+      <c r="AK120">
+        <v>1.85</v>
+      </c>
+      <c r="AL120">
+        <v>1.33</v>
+      </c>
+      <c r="AM120">
+        <v>1.22</v>
+      </c>
+      <c r="AN120">
+        <v>2.5</v>
+      </c>
+      <c r="AO120">
+        <v>1.17</v>
+      </c>
+      <c r="AP120">
+        <v>2.57</v>
+      </c>
+      <c r="AQ120">
+        <v>1</v>
+      </c>
+      <c r="AR120">
+        <v>1.79</v>
+      </c>
+      <c r="AS120">
+        <v>2.08</v>
+      </c>
+      <c r="AT120">
+        <v>3.87</v>
+      </c>
+      <c r="AU120">
+        <v>8</v>
+      </c>
+      <c r="AV120">
+        <v>0</v>
+      </c>
+      <c r="AW120">
+        <v>5</v>
+      </c>
+      <c r="AX120">
+        <v>4</v>
+      </c>
+      <c r="AY120">
+        <v>13</v>
+      </c>
+      <c r="AZ120">
+        <v>4</v>
+      </c>
+      <c r="BA120">
+        <v>3</v>
+      </c>
+      <c r="BB120">
+        <v>1</v>
+      </c>
+      <c r="BC120">
+        <v>4</v>
+      </c>
+      <c r="BD120">
+        <v>2.45</v>
+      </c>
+      <c r="BE120">
+        <v>6.5</v>
+      </c>
+      <c r="BF120">
+        <v>1.67</v>
+      </c>
+      <c r="BG120">
+        <v>1.37</v>
+      </c>
+      <c r="BH120">
+        <v>2.7</v>
+      </c>
+      <c r="BI120">
+        <v>1.64</v>
+      </c>
+      <c r="BJ120">
+        <v>2.05</v>
+      </c>
+      <c r="BK120">
+        <v>2.02</v>
+      </c>
+      <c r="BL120">
+        <v>1.65</v>
+      </c>
+      <c r="BM120">
+        <v>2.55</v>
+      </c>
+      <c r="BN120">
+        <v>1.41</v>
+      </c>
+      <c r="BO120">
+        <v>3.4</v>
+      </c>
+      <c r="BP120">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -538,6 +538,9 @@
     <t>['70', '90+5']</t>
   </si>
   <si>
+    <t>['33', '56']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -1050,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1306,7 +1309,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -2130,7 +2133,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2211,7 +2214,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2336,7 +2339,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2542,7 +2545,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2954,7 +2957,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3160,7 +3163,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3984,7 +3987,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4602,7 +4605,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -5220,7 +5223,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5426,7 +5429,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5632,7 +5635,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5713,7 +5716,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -5838,7 +5841,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -6044,7 +6047,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6456,7 +6459,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6662,7 +6665,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6868,7 +6871,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7074,7 +7077,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7898,7 +7901,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8928,7 +8931,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9134,7 +9137,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9546,7 +9549,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9958,7 +9961,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10370,7 +10373,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10988,7 +10991,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11400,7 +11403,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -12636,7 +12639,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12842,7 +12845,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13048,7 +13051,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -14284,7 +14287,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14696,7 +14699,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14902,7 +14905,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15108,7 +15111,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15395,7 +15398,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15726,7 +15729,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16550,7 +16553,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16756,7 +16759,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17168,7 +17171,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17580,7 +17583,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17992,7 +17995,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18198,7 +18201,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18404,7 +18407,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18816,7 +18819,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19640,7 +19643,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -20052,7 +20055,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20258,7 +20261,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20464,7 +20467,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -21082,7 +21085,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21288,7 +21291,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21369,7 +21372,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR99">
         <v>1.47</v>
@@ -21494,7 +21497,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21700,7 +21703,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q101">
         <v>2.75</v>
@@ -21906,7 +21909,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -21987,7 +21990,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR102">
         <v>1.69</v>
@@ -22112,7 +22115,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23142,7 +23145,7 @@
         <v>165</v>
       </c>
       <c r="P108" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23348,7 +23351,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23966,7 +23969,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q112">
         <v>3.45</v>
@@ -24172,7 +24175,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q113">
         <v>1.76</v>
@@ -24378,7 +24381,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q114">
         <v>3.3</v>
@@ -24584,7 +24587,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24790,7 +24793,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -24871,7 +24874,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ116">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR116">
         <v>1.79</v>
@@ -24996,7 +24999,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25202,7 +25205,7 @@
         <v>86</v>
       </c>
       <c r="P118" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q118">
         <v>3</v>
@@ -25408,7 +25411,7 @@
         <v>86</v>
       </c>
       <c r="P119" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25695,7 +25698,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR120">
         <v>1.79</v>
@@ -25771,6 +25774,212 @@
       </c>
       <c r="BP120">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7818855</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45850.66666666666</v>
+      </c>
+      <c r="F121">
+        <v>7</v>
+      </c>
+      <c r="G121" t="s">
+        <v>73</v>
+      </c>
+      <c r="H121" t="s">
+        <v>84</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>2</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>3</v>
+      </c>
+      <c r="O121" t="s">
+        <v>174</v>
+      </c>
+      <c r="P121" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q121">
+        <v>2.9</v>
+      </c>
+      <c r="R121">
+        <v>2</v>
+      </c>
+      <c r="S121">
+        <v>3.5</v>
+      </c>
+      <c r="T121">
+        <v>1.44</v>
+      </c>
+      <c r="U121">
+        <v>2.6</v>
+      </c>
+      <c r="V121">
+        <v>3</v>
+      </c>
+      <c r="W121">
+        <v>1.33</v>
+      </c>
+      <c r="X121">
+        <v>8.25</v>
+      </c>
+      <c r="Y121">
+        <v>1.06</v>
+      </c>
+      <c r="Z121">
+        <v>2.3</v>
+      </c>
+      <c r="AA121">
+        <v>3.3</v>
+      </c>
+      <c r="AB121">
+        <v>2.95</v>
+      </c>
+      <c r="AC121">
+        <v>1.07</v>
+      </c>
+      <c r="AD121">
+        <v>8</v>
+      </c>
+      <c r="AE121">
+        <v>1.36</v>
+      </c>
+      <c r="AF121">
+        <v>2.87</v>
+      </c>
+      <c r="AG121">
+        <v>2.05</v>
+      </c>
+      <c r="AH121">
+        <v>1.65</v>
+      </c>
+      <c r="AI121">
+        <v>1.87</v>
+      </c>
+      <c r="AJ121">
+        <v>1.8</v>
+      </c>
+      <c r="AK121">
+        <v>1.37</v>
+      </c>
+      <c r="AL121">
+        <v>1.31</v>
+      </c>
+      <c r="AM121">
+        <v>1.58</v>
+      </c>
+      <c r="AN121">
+        <v>3</v>
+      </c>
+      <c r="AO121">
+        <v>1</v>
+      </c>
+      <c r="AP121">
+        <v>3</v>
+      </c>
+      <c r="AQ121">
+        <v>0.88</v>
+      </c>
+      <c r="AR121">
+        <v>2.16</v>
+      </c>
+      <c r="AS121">
+        <v>1.81</v>
+      </c>
+      <c r="AT121">
+        <v>3.97</v>
+      </c>
+      <c r="AU121">
+        <v>5</v>
+      </c>
+      <c r="AV121">
+        <v>5</v>
+      </c>
+      <c r="AW121">
+        <v>6</v>
+      </c>
+      <c r="AX121">
+        <v>6</v>
+      </c>
+      <c r="AY121">
+        <v>11</v>
+      </c>
+      <c r="AZ121">
+        <v>11</v>
+      </c>
+      <c r="BA121">
+        <v>1</v>
+      </c>
+      <c r="BB121">
+        <v>4</v>
+      </c>
+      <c r="BC121">
+        <v>5</v>
+      </c>
+      <c r="BD121">
+        <v>1.74</v>
+      </c>
+      <c r="BE121">
+        <v>6.5</v>
+      </c>
+      <c r="BF121">
+        <v>2.65</v>
+      </c>
+      <c r="BG121">
+        <v>1.24</v>
+      </c>
+      <c r="BH121">
+        <v>3.6</v>
+      </c>
+      <c r="BI121">
+        <v>1.44</v>
+      </c>
+      <c r="BJ121">
+        <v>2.45</v>
+      </c>
+      <c r="BK121">
+        <v>1.78</v>
+      </c>
+      <c r="BL121">
+        <v>1.85</v>
+      </c>
+      <c r="BM121">
+        <v>2.35</v>
+      </c>
+      <c r="BN121">
+        <v>1.49</v>
+      </c>
+      <c r="BO121">
+        <v>3.2</v>
+      </c>
+      <c r="BP121">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1053,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3656,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ22">
         <v>1.14</v>
@@ -6952,7 +6952,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ29">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR29">
         <v>1.73</v>
@@ -8185,7 +8185,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ35">
         <v>2.13</v>
@@ -9421,7 +9421,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -10042,7 +10042,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ44">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR44">
         <v>2.49</v>
@@ -12926,7 +12926,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ58">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13129,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ59">
         <v>1.14</v>
@@ -14368,7 +14368,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ65">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR65">
         <v>1.71</v>
@@ -15807,7 +15807,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ72">
         <v>1.88</v>
@@ -18897,7 +18897,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ87">
         <v>1.14</v>
@@ -20957,7 +20957,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ97">
         <v>1.43</v>
@@ -21784,7 +21784,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ101">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR101">
         <v>1.56</v>
@@ -24668,7 +24668,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ115">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR115">
         <v>1.68</v>
@@ -25283,7 +25283,7 @@
         <v>1.14</v>
       </c>
       <c r="AP118">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ118">
         <v>1.38</v>
@@ -25980,6 +25980,212 @@
       </c>
       <c r="BP121">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7818930</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45856.83333333334</v>
+      </c>
+      <c r="F122">
+        <v>16</v>
+      </c>
+      <c r="G122" t="s">
+        <v>85</v>
+      </c>
+      <c r="H122" t="s">
+        <v>75</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122" t="s">
+        <v>86</v>
+      </c>
+      <c r="P122" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q122">
+        <v>2.7</v>
+      </c>
+      <c r="R122">
+        <v>2.15</v>
+      </c>
+      <c r="S122">
+        <v>3.5</v>
+      </c>
+      <c r="T122">
+        <v>1.35</v>
+      </c>
+      <c r="U122">
+        <v>2.9</v>
+      </c>
+      <c r="V122">
+        <v>2.6</v>
+      </c>
+      <c r="W122">
+        <v>1.43</v>
+      </c>
+      <c r="X122">
+        <v>6.5</v>
+      </c>
+      <c r="Y122">
+        <v>1.1</v>
+      </c>
+      <c r="Z122">
+        <v>2.15</v>
+      </c>
+      <c r="AA122">
+        <v>3.5</v>
+      </c>
+      <c r="AB122">
+        <v>3.1</v>
+      </c>
+      <c r="AC122">
+        <v>1.05</v>
+      </c>
+      <c r="AD122">
+        <v>8.5</v>
+      </c>
+      <c r="AE122">
+        <v>1.25</v>
+      </c>
+      <c r="AF122">
+        <v>3.6</v>
+      </c>
+      <c r="AG122">
+        <v>1.77</v>
+      </c>
+      <c r="AH122">
+        <v>1.9</v>
+      </c>
+      <c r="AI122">
+        <v>1.68</v>
+      </c>
+      <c r="AJ122">
+        <v>2.05</v>
+      </c>
+      <c r="AK122">
+        <v>1.34</v>
+      </c>
+      <c r="AL122">
+        <v>1.29</v>
+      </c>
+      <c r="AM122">
+        <v>1.66</v>
+      </c>
+      <c r="AN122">
+        <v>0.88</v>
+      </c>
+      <c r="AO122">
+        <v>0.43</v>
+      </c>
+      <c r="AP122">
+        <v>0.89</v>
+      </c>
+      <c r="AQ122">
+        <v>0.5</v>
+      </c>
+      <c r="AR122">
+        <v>1.72</v>
+      </c>
+      <c r="AS122">
+        <v>1.61</v>
+      </c>
+      <c r="AT122">
+        <v>3.33</v>
+      </c>
+      <c r="AU122">
+        <v>5</v>
+      </c>
+      <c r="AV122">
+        <v>0</v>
+      </c>
+      <c r="AW122">
+        <v>6</v>
+      </c>
+      <c r="AX122">
+        <v>7</v>
+      </c>
+      <c r="AY122">
+        <v>11</v>
+      </c>
+      <c r="AZ122">
+        <v>7</v>
+      </c>
+      <c r="BA122">
+        <v>6</v>
+      </c>
+      <c r="BB122">
+        <v>5</v>
+      </c>
+      <c r="BC122">
+        <v>11</v>
+      </c>
+      <c r="BD122">
+        <v>1.96</v>
+      </c>
+      <c r="BE122">
+        <v>8.5</v>
+      </c>
+      <c r="BF122">
+        <v>2.2</v>
+      </c>
+      <c r="BG122">
+        <v>1.18</v>
+      </c>
+      <c r="BH122">
+        <v>4</v>
+      </c>
+      <c r="BI122">
+        <v>1.33</v>
+      </c>
+      <c r="BJ122">
+        <v>2.9</v>
+      </c>
+      <c r="BK122">
+        <v>1.55</v>
+      </c>
+      <c r="BL122">
+        <v>2.2</v>
+      </c>
+      <c r="BM122">
+        <v>1.87</v>
+      </c>
+      <c r="BN122">
+        <v>1.77</v>
+      </c>
+      <c r="BO122">
+        <v>2.35</v>
+      </c>
+      <c r="BP122">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -26122,22 +26122,22 @@
         <v>3.33</v>
       </c>
       <c r="AU122">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV122">
         <v>0</v>
       </c>
       <c r="AW122">
+        <v>8</v>
+      </c>
+      <c r="AX122">
         <v>6</v>
-      </c>
-      <c r="AX122">
-        <v>7</v>
       </c>
       <c r="AY122">
         <v>11</v>
       </c>
       <c r="AZ122">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA122">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="230">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -541,6 +541,15 @@
     <t>['33', '56']</t>
   </si>
   <si>
+    <t>['48', '69', '81']</t>
+  </si>
+  <si>
+    <t>['68', '81']</t>
+  </si>
+  <si>
+    <t>['3', '66', '74', '81']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -692,6 +701,9 @@
   </si>
   <si>
     <t>['25', '90+7']</t>
+  </si>
+  <si>
+    <t>['12']</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP122"/>
+  <dimension ref="A1:BP125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1309,7 +1321,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -2133,7 +2145,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2339,7 +2351,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2545,7 +2557,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2957,7 +2969,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3038,7 +3050,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ10">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3163,7 +3175,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3241,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AQ11">
         <v>1.88</v>
@@ -3447,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ12">
         <v>0.88</v>
@@ -3987,7 +3999,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4068,7 +4080,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4274,7 +4286,7 @@
         <v>3</v>
       </c>
       <c r="AQ16">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>3.44</v>
@@ -4477,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ17">
         <v>1.38</v>
@@ -4605,7 +4617,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -5098,7 +5110,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ20">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR20">
         <v>1.33</v>
@@ -5223,7 +5235,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5429,7 +5441,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5635,7 +5647,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5841,7 +5853,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -6047,7 +6059,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6459,7 +6471,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6665,7 +6677,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6871,7 +6883,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7077,7 +7089,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7155,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ30">
         <v>1.14</v>
@@ -7364,7 +7376,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -7567,7 +7579,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7901,7 +7913,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8394,7 +8406,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ36">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>1.55</v>
@@ -8931,7 +8943,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9137,7 +9149,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9215,7 +9227,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ40">
         <v>1.88</v>
@@ -9549,7 +9561,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9627,7 +9639,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AQ42">
         <v>0.88</v>
@@ -9836,7 +9848,7 @@
         <v>1</v>
       </c>
       <c r="AQ43">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR43">
         <v>1.91</v>
@@ -9961,7 +9973,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10248,7 +10260,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ45">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR45">
         <v>1.28</v>
@@ -10373,7 +10385,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10451,7 +10463,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ46">
         <v>1.43</v>
@@ -10863,7 +10875,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ48">
         <v>0.63</v>
@@ -10991,7 +11003,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11403,7 +11415,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -11690,7 +11702,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ52">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR52">
         <v>1.77</v>
@@ -11893,7 +11905,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AQ53">
         <v>1.14</v>
@@ -12102,7 +12114,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ54">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR54">
         <v>1.28</v>
@@ -12308,7 +12320,7 @@
         <v>3</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR55">
         <v>2.44</v>
@@ -12639,7 +12651,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12845,7 +12857,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13051,7 +13063,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13132,7 +13144,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ59">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.93</v>
@@ -13956,7 +13968,7 @@
         <v>1</v>
       </c>
       <c r="AQ63">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR63">
         <v>1.77</v>
@@ -14287,7 +14299,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14571,7 +14583,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ66">
         <v>2.13</v>
@@ -14699,7 +14711,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14780,7 +14792,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ67">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR67">
         <v>2.15</v>
@@ -14905,7 +14917,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15111,7 +15123,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15601,7 +15613,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AQ71">
         <v>1.14</v>
@@ -15729,7 +15741,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16219,7 +16231,7 @@
         <v>1.25</v>
       </c>
       <c r="AP74">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ74">
         <v>1.38</v>
@@ -16553,7 +16565,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16634,7 +16646,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ76">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR76">
         <v>1.65</v>
@@ -16759,7 +16771,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -16840,7 +16852,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.74</v>
@@ -17171,7 +17183,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17583,7 +17595,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17995,7 +18007,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18073,7 +18085,7 @@
         <v>0.2</v>
       </c>
       <c r="AP83">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18201,7 +18213,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18279,7 +18291,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ84">
         <v>1.14</v>
@@ -18407,7 +18419,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18488,7 +18500,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ85">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR85">
         <v>1.47</v>
@@ -18819,7 +18831,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19103,7 +19115,7 @@
         <v>0.6</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ88">
         <v>0.43</v>
@@ -19309,7 +19321,7 @@
         <v>2.17</v>
       </c>
       <c r="AP89">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ89">
         <v>1.88</v>
@@ -19643,7 +19655,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19724,7 +19736,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ91">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR91">
         <v>1.68</v>
@@ -19930,7 +19942,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ92">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.67</v>
@@ -20055,7 +20067,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20261,7 +20273,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20467,7 +20479,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -21085,7 +21097,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21291,7 +21303,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21497,7 +21509,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21578,7 +21590,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ100">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR100">
         <v>1.73</v>
@@ -21703,7 +21715,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q101">
         <v>2.75</v>
@@ -21781,7 +21793,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AQ101">
         <v>0.5</v>
@@ -21909,7 +21921,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -22115,7 +22127,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22196,7 +22208,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ103">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR103">
         <v>1.48</v>
@@ -22402,7 +22414,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ104">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR104">
         <v>1.8</v>
@@ -23017,7 +23029,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23145,7 +23157,7 @@
         <v>165</v>
       </c>
       <c r="P108" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23351,7 +23363,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23635,7 +23647,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ110">
         <v>1.14</v>
@@ -23969,7 +23981,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q112">
         <v>3.45</v>
@@ -24047,7 +24059,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AQ112">
         <v>2.13</v>
@@ -24175,7 +24187,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q113">
         <v>1.76</v>
@@ -24256,7 +24268,7 @@
         <v>3</v>
       </c>
       <c r="AQ113">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR113">
         <v>2.13</v>
@@ -24381,7 +24393,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q114">
         <v>3.3</v>
@@ -24587,7 +24599,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24793,7 +24805,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -24999,7 +25011,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25205,7 +25217,7 @@
         <v>86</v>
       </c>
       <c r="P118" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q118">
         <v>3</v>
@@ -25411,7 +25423,7 @@
         <v>86</v>
       </c>
       <c r="P119" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25489,7 +25501,7 @@
         <v>0.67</v>
       </c>
       <c r="AP119">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -26186,6 +26198,624 @@
       </c>
       <c r="BP122">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7818932</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45857.5625</v>
+      </c>
+      <c r="F123">
+        <v>16</v>
+      </c>
+      <c r="G123" t="s">
+        <v>79</v>
+      </c>
+      <c r="H123" t="s">
+        <v>77</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123">
+        <v>3</v>
+      </c>
+      <c r="M123">
+        <v>1</v>
+      </c>
+      <c r="N123">
+        <v>4</v>
+      </c>
+      <c r="O123" t="s">
+        <v>175</v>
+      </c>
+      <c r="P123" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q123">
+        <v>3.2</v>
+      </c>
+      <c r="R123">
+        <v>2.05</v>
+      </c>
+      <c r="S123">
+        <v>3.5</v>
+      </c>
+      <c r="T123">
+        <v>1.44</v>
+      </c>
+      <c r="U123">
+        <v>2.63</v>
+      </c>
+      <c r="V123">
+        <v>3.25</v>
+      </c>
+      <c r="W123">
+        <v>1.33</v>
+      </c>
+      <c r="X123">
+        <v>9</v>
+      </c>
+      <c r="Y123">
+        <v>1.07</v>
+      </c>
+      <c r="Z123">
+        <v>2.53</v>
+      </c>
+      <c r="AA123">
+        <v>3.21</v>
+      </c>
+      <c r="AB123">
+        <v>2.85</v>
+      </c>
+      <c r="AC123">
+        <v>1.03</v>
+      </c>
+      <c r="AD123">
+        <v>7.4</v>
+      </c>
+      <c r="AE123">
+        <v>1.33</v>
+      </c>
+      <c r="AF123">
+        <v>2.84</v>
+      </c>
+      <c r="AG123">
+        <v>2.15</v>
+      </c>
+      <c r="AH123">
+        <v>1.67</v>
+      </c>
+      <c r="AI123">
+        <v>1.83</v>
+      </c>
+      <c r="AJ123">
+        <v>1.83</v>
+      </c>
+      <c r="AK123">
+        <v>1.41</v>
+      </c>
+      <c r="AL123">
+        <v>1.33</v>
+      </c>
+      <c r="AM123">
+        <v>1.51</v>
+      </c>
+      <c r="AN123">
+        <v>0.5</v>
+      </c>
+      <c r="AO123">
+        <v>1.14</v>
+      </c>
+      <c r="AP123">
+        <v>0.78</v>
+      </c>
+      <c r="AQ123">
+        <v>1</v>
+      </c>
+      <c r="AR123">
+        <v>1.48</v>
+      </c>
+      <c r="AS123">
+        <v>1.22</v>
+      </c>
+      <c r="AT123">
+        <v>2.7</v>
+      </c>
+      <c r="AU123">
+        <v>5</v>
+      </c>
+      <c r="AV123">
+        <v>2</v>
+      </c>
+      <c r="AW123">
+        <v>8</v>
+      </c>
+      <c r="AX123">
+        <v>4</v>
+      </c>
+      <c r="AY123">
+        <v>13</v>
+      </c>
+      <c r="AZ123">
+        <v>6</v>
+      </c>
+      <c r="BA123">
+        <v>10</v>
+      </c>
+      <c r="BB123">
+        <v>2</v>
+      </c>
+      <c r="BC123">
+        <v>12</v>
+      </c>
+      <c r="BD123">
+        <v>1.74</v>
+      </c>
+      <c r="BE123">
+        <v>8.5</v>
+      </c>
+      <c r="BF123">
+        <v>2.55</v>
+      </c>
+      <c r="BG123">
+        <v>1.26</v>
+      </c>
+      <c r="BH123">
+        <v>3.3</v>
+      </c>
+      <c r="BI123">
+        <v>1.46</v>
+      </c>
+      <c r="BJ123">
+        <v>2.43</v>
+      </c>
+      <c r="BK123">
+        <v>1.76</v>
+      </c>
+      <c r="BL123">
+        <v>1.89</v>
+      </c>
+      <c r="BM123">
+        <v>2.2</v>
+      </c>
+      <c r="BN123">
+        <v>1.56</v>
+      </c>
+      <c r="BO123">
+        <v>2.85</v>
+      </c>
+      <c r="BP123">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7818927</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45857.66666666666</v>
+      </c>
+      <c r="F124">
+        <v>16</v>
+      </c>
+      <c r="G124" t="s">
+        <v>84</v>
+      </c>
+      <c r="H124" t="s">
+        <v>74</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>2</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124">
+        <v>3</v>
+      </c>
+      <c r="O124" t="s">
+        <v>176</v>
+      </c>
+      <c r="P124" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q124">
+        <v>1.8</v>
+      </c>
+      <c r="R124">
+        <v>2.5</v>
+      </c>
+      <c r="S124">
+        <v>8</v>
+      </c>
+      <c r="T124">
+        <v>1.3</v>
+      </c>
+      <c r="U124">
+        <v>3.4</v>
+      </c>
+      <c r="V124">
+        <v>2.5</v>
+      </c>
+      <c r="W124">
+        <v>1.5</v>
+      </c>
+      <c r="X124">
+        <v>6</v>
+      </c>
+      <c r="Y124">
+        <v>1.13</v>
+      </c>
+      <c r="Z124">
+        <v>1.34</v>
+      </c>
+      <c r="AA124">
+        <v>4.96</v>
+      </c>
+      <c r="AB124">
+        <v>8.35</v>
+      </c>
+      <c r="AC124">
+        <v>1.01</v>
+      </c>
+      <c r="AD124">
+        <v>11</v>
+      </c>
+      <c r="AE124">
+        <v>1.17</v>
+      </c>
+      <c r="AF124">
+        <v>4</v>
+      </c>
+      <c r="AG124">
+        <v>1.73</v>
+      </c>
+      <c r="AH124">
+        <v>2.08</v>
+      </c>
+      <c r="AI124">
+        <v>2.1</v>
+      </c>
+      <c r="AJ124">
+        <v>1.67</v>
+      </c>
+      <c r="AK124">
+        <v>1.05</v>
+      </c>
+      <c r="AL124">
+        <v>1.16</v>
+      </c>
+      <c r="AM124">
+        <v>3.28</v>
+      </c>
+      <c r="AN124">
+        <v>2</v>
+      </c>
+      <c r="AO124">
+        <v>0.5</v>
+      </c>
+      <c r="AP124">
+        <v>2.13</v>
+      </c>
+      <c r="AQ124">
+        <v>0.44</v>
+      </c>
+      <c r="AR124">
+        <v>2.12</v>
+      </c>
+      <c r="AS124">
+        <v>1.29</v>
+      </c>
+      <c r="AT124">
+        <v>3.41</v>
+      </c>
+      <c r="AU124">
+        <v>7</v>
+      </c>
+      <c r="AV124">
+        <v>8</v>
+      </c>
+      <c r="AW124">
+        <v>12</v>
+      </c>
+      <c r="AX124">
+        <v>6</v>
+      </c>
+      <c r="AY124">
+        <v>19</v>
+      </c>
+      <c r="AZ124">
+        <v>14</v>
+      </c>
+      <c r="BA124">
+        <v>7</v>
+      </c>
+      <c r="BB124">
+        <v>4</v>
+      </c>
+      <c r="BC124">
+        <v>11</v>
+      </c>
+      <c r="BD124">
+        <v>1.25</v>
+      </c>
+      <c r="BE124">
+        <v>11</v>
+      </c>
+      <c r="BF124">
+        <v>5.2</v>
+      </c>
+      <c r="BG124">
+        <v>1.24</v>
+      </c>
+      <c r="BH124">
+        <v>3.4</v>
+      </c>
+      <c r="BI124">
+        <v>1.43</v>
+      </c>
+      <c r="BJ124">
+        <v>2.5</v>
+      </c>
+      <c r="BK124">
+        <v>1.7</v>
+      </c>
+      <c r="BL124">
+        <v>1.96</v>
+      </c>
+      <c r="BM124">
+        <v>2.08</v>
+      </c>
+      <c r="BN124">
+        <v>1.61</v>
+      </c>
+      <c r="BO124">
+        <v>2.63</v>
+      </c>
+      <c r="BP124">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7818929</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45857.77083333334</v>
+      </c>
+      <c r="F125">
+        <v>16</v>
+      </c>
+      <c r="G125" t="s">
+        <v>80</v>
+      </c>
+      <c r="H125" t="s">
+        <v>70</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>1</v>
+      </c>
+      <c r="K125">
+        <v>2</v>
+      </c>
+      <c r="L125">
+        <v>4</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>5</v>
+      </c>
+      <c r="O125" t="s">
+        <v>177</v>
+      </c>
+      <c r="P125" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q125">
+        <v>2.05</v>
+      </c>
+      <c r="R125">
+        <v>2.3</v>
+      </c>
+      <c r="S125">
+        <v>6.5</v>
+      </c>
+      <c r="T125">
+        <v>1.36</v>
+      </c>
+      <c r="U125">
+        <v>3</v>
+      </c>
+      <c r="V125">
+        <v>2.63</v>
+      </c>
+      <c r="W125">
+        <v>1.44</v>
+      </c>
+      <c r="X125">
+        <v>7</v>
+      </c>
+      <c r="Y125">
+        <v>1.1</v>
+      </c>
+      <c r="Z125">
+        <v>1.47</v>
+      </c>
+      <c r="AA125">
+        <v>4.25</v>
+      </c>
+      <c r="AB125">
+        <v>6.55</v>
+      </c>
+      <c r="AC125">
+        <v>1.01</v>
+      </c>
+      <c r="AD125">
+        <v>11</v>
+      </c>
+      <c r="AE125">
+        <v>1.22</v>
+      </c>
+      <c r="AF125">
+        <v>3.52</v>
+      </c>
+      <c r="AG125">
+        <v>1.85</v>
+      </c>
+      <c r="AH125">
+        <v>1.95</v>
+      </c>
+      <c r="AI125">
+        <v>1.91</v>
+      </c>
+      <c r="AJ125">
+        <v>1.8</v>
+      </c>
+      <c r="AK125">
+        <v>1.1</v>
+      </c>
+      <c r="AL125">
+        <v>1.22</v>
+      </c>
+      <c r="AM125">
+        <v>2.58</v>
+      </c>
+      <c r="AN125">
+        <v>2.14</v>
+      </c>
+      <c r="AO125">
+        <v>0.25</v>
+      </c>
+      <c r="AP125">
+        <v>2.25</v>
+      </c>
+      <c r="AQ125">
+        <v>0.22</v>
+      </c>
+      <c r="AR125">
+        <v>1.66</v>
+      </c>
+      <c r="AS125">
+        <v>1.28</v>
+      </c>
+      <c r="AT125">
+        <v>2.94</v>
+      </c>
+      <c r="AU125">
+        <v>9</v>
+      </c>
+      <c r="AV125">
+        <v>2</v>
+      </c>
+      <c r="AW125">
+        <v>5</v>
+      </c>
+      <c r="AX125">
+        <v>7</v>
+      </c>
+      <c r="AY125">
+        <v>14</v>
+      </c>
+      <c r="AZ125">
+        <v>9</v>
+      </c>
+      <c r="BA125">
+        <v>7</v>
+      </c>
+      <c r="BB125">
+        <v>2</v>
+      </c>
+      <c r="BC125">
+        <v>9</v>
+      </c>
+      <c r="BD125">
+        <v>1.38</v>
+      </c>
+      <c r="BE125">
+        <v>9</v>
+      </c>
+      <c r="BF125">
+        <v>4</v>
+      </c>
+      <c r="BG125">
+        <v>1.36</v>
+      </c>
+      <c r="BH125">
+        <v>2.75</v>
+      </c>
+      <c r="BI125">
+        <v>1.62</v>
+      </c>
+      <c r="BJ125">
+        <v>2.07</v>
+      </c>
+      <c r="BK125">
+        <v>2.02</v>
+      </c>
+      <c r="BL125">
+        <v>1.66</v>
+      </c>
+      <c r="BM125">
+        <v>2.55</v>
+      </c>
+      <c r="BN125">
+        <v>1.41</v>
+      </c>
+      <c r="BO125">
+        <v>3.4</v>
+      </c>
+      <c r="BP125">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -26752,31 +26752,31 @@
         <v>2.94</v>
       </c>
       <c r="AU125">
+        <v>10</v>
+      </c>
+      <c r="AV125">
+        <v>2</v>
+      </c>
+      <c r="AW125">
+        <v>6</v>
+      </c>
+      <c r="AX125">
         <v>9</v>
       </c>
-      <c r="AV125">
-        <v>2</v>
-      </c>
-      <c r="AW125">
-        <v>5</v>
-      </c>
-      <c r="AX125">
-        <v>7</v>
-      </c>
       <c r="AY125">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ125">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA125">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB125">
         <v>2</v>
       </c>
       <c r="BC125">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD125">
         <v>1.38</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="231">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -550,6 +550,9 @@
     <t>['3', '66', '74', '81']</t>
   </si>
   <si>
+    <t>['69']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -1065,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP125"/>
+  <dimension ref="A1:BP126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1321,7 +1324,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -2145,7 +2148,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2351,7 +2354,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2557,7 +2560,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2969,7 +2972,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3047,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AQ10">
         <v>0.22</v>
@@ -3175,7 +3178,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3462,7 +3465,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ12">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3999,7 +4002,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4617,7 +4620,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -5235,7 +5238,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5441,7 +5444,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5647,7 +5650,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5853,7 +5856,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -6059,7 +6062,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6471,7 +6474,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6552,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR27">
         <v>2.18</v>
@@ -6677,7 +6680,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6883,7 +6886,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -6961,7 +6964,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AQ29">
         <v>0.5</v>
@@ -7089,7 +7092,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7785,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -7913,7 +7916,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8943,7 +8946,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9149,7 +9152,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9561,7 +9564,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9642,7 +9645,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ42">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR42">
         <v>1.33</v>
@@ -9973,7 +9976,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10385,7 +10388,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -11003,7 +11006,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11084,7 +11087,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ49">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -11287,7 +11290,7 @@
         <v>1.67</v>
       </c>
       <c r="AP50">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AQ50">
         <v>1.38</v>
@@ -11415,7 +11418,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -12523,7 +12526,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AQ56">
         <v>0.43</v>
@@ -12651,7 +12654,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12857,7 +12860,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13063,7 +13066,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -14299,7 +14302,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14711,7 +14714,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14917,7 +14920,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15123,7 +15126,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15741,7 +15744,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16028,7 +16031,7 @@
         <v>3</v>
       </c>
       <c r="AQ73">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR73">
         <v>2.35</v>
@@ -16565,7 +16568,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16643,7 +16646,7 @@
         <v>0.2</v>
       </c>
       <c r="AP76">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AQ76">
         <v>0.44</v>
@@ -16771,7 +16774,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17183,7 +17186,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17470,7 +17473,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ80">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR80">
         <v>2.04</v>
@@ -17595,7 +17598,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -18007,7 +18010,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18213,7 +18216,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18419,7 +18422,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18831,7 +18834,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19655,7 +19658,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -20067,7 +20070,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20145,7 +20148,7 @@
         <v>0.83</v>
       </c>
       <c r="AP93">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AQ93">
         <v>0.63</v>
@@ -20273,7 +20276,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20479,7 +20482,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -21097,7 +21100,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21178,7 +21181,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ98">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR98">
         <v>1.8</v>
@@ -21303,7 +21306,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21509,7 +21512,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21715,7 +21718,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q101">
         <v>2.75</v>
@@ -21921,7 +21924,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -22127,7 +22130,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23157,7 +23160,7 @@
         <v>165</v>
       </c>
       <c r="P108" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23363,7 +23366,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23856,7 +23859,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ111">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR111">
         <v>1.47</v>
@@ -23981,7 +23984,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q112">
         <v>3.45</v>
@@ -24187,7 +24190,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q113">
         <v>1.76</v>
@@ -24393,7 +24396,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q114">
         <v>3.3</v>
@@ -24599,7 +24602,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24805,7 +24808,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -24883,7 +24886,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AQ116">
         <v>0.88</v>
@@ -25011,7 +25014,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25217,7 +25220,7 @@
         <v>86</v>
       </c>
       <c r="P118" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q118">
         <v>3</v>
@@ -25423,7 +25426,7 @@
         <v>86</v>
       </c>
       <c r="P119" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26247,7 +26250,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26659,7 +26662,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q125">
         <v>2.05</v>
@@ -26816,6 +26819,212 @@
       </c>
       <c r="BP125">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7818931</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45858.5625</v>
+      </c>
+      <c r="F126">
+        <v>16</v>
+      </c>
+      <c r="G126" t="s">
+        <v>78</v>
+      </c>
+      <c r="H126" t="s">
+        <v>76</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>1</v>
+      </c>
+      <c r="N126">
+        <v>2</v>
+      </c>
+      <c r="O126" t="s">
+        <v>178</v>
+      </c>
+      <c r="P126" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q126">
+        <v>3.4</v>
+      </c>
+      <c r="R126">
+        <v>2.1</v>
+      </c>
+      <c r="S126">
+        <v>3.4</v>
+      </c>
+      <c r="T126">
+        <v>1.44</v>
+      </c>
+      <c r="U126">
+        <v>2.63</v>
+      </c>
+      <c r="V126">
+        <v>3.25</v>
+      </c>
+      <c r="W126">
+        <v>1.33</v>
+      </c>
+      <c r="X126">
+        <v>9</v>
+      </c>
+      <c r="Y126">
+        <v>1.07</v>
+      </c>
+      <c r="Z126">
+        <v>2.63</v>
+      </c>
+      <c r="AA126">
+        <v>3.25</v>
+      </c>
+      <c r="AB126">
+        <v>2.63</v>
+      </c>
+      <c r="AC126">
+        <v>1.07</v>
+      </c>
+      <c r="AD126">
+        <v>7.5</v>
+      </c>
+      <c r="AE126">
+        <v>1.38</v>
+      </c>
+      <c r="AF126">
+        <v>2.9</v>
+      </c>
+      <c r="AG126">
+        <v>2.15</v>
+      </c>
+      <c r="AH126">
+        <v>1.67</v>
+      </c>
+      <c r="AI126">
+        <v>1.83</v>
+      </c>
+      <c r="AJ126">
+        <v>1.83</v>
+      </c>
+      <c r="AK126">
+        <v>1.46</v>
+      </c>
+      <c r="AL126">
+        <v>1.31</v>
+      </c>
+      <c r="AM126">
+        <v>1.47</v>
+      </c>
+      <c r="AN126">
+        <v>2.75</v>
+      </c>
+      <c r="AO126">
+        <v>0.88</v>
+      </c>
+      <c r="AP126">
+        <v>2.56</v>
+      </c>
+      <c r="AQ126">
+        <v>0.89</v>
+      </c>
+      <c r="AR126">
+        <v>1.75</v>
+      </c>
+      <c r="AS126">
+        <v>1.27</v>
+      </c>
+      <c r="AT126">
+        <v>3.02</v>
+      </c>
+      <c r="AU126">
+        <v>5</v>
+      </c>
+      <c r="AV126">
+        <v>4</v>
+      </c>
+      <c r="AW126">
+        <v>7</v>
+      </c>
+      <c r="AX126">
+        <v>8</v>
+      </c>
+      <c r="AY126">
+        <v>12</v>
+      </c>
+      <c r="AZ126">
+        <v>12</v>
+      </c>
+      <c r="BA126">
+        <v>2</v>
+      </c>
+      <c r="BB126">
+        <v>5</v>
+      </c>
+      <c r="BC126">
+        <v>7</v>
+      </c>
+      <c r="BD126">
+        <v>2.16</v>
+      </c>
+      <c r="BE126">
+        <v>8</v>
+      </c>
+      <c r="BF126">
+        <v>2.02</v>
+      </c>
+      <c r="BG126">
+        <v>1.41</v>
+      </c>
+      <c r="BH126">
+        <v>2.6</v>
+      </c>
+      <c r="BI126">
+        <v>1.7</v>
+      </c>
+      <c r="BJ126">
+        <v>1.97</v>
+      </c>
+      <c r="BK126">
+        <v>2.12</v>
+      </c>
+      <c r="BL126">
+        <v>1.58</v>
+      </c>
+      <c r="BM126">
+        <v>2.8</v>
+      </c>
+      <c r="BN126">
+        <v>1.35</v>
+      </c>
+      <c r="BO126">
+        <v>3.7</v>
+      </c>
+      <c r="BP126">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="233">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -553,6 +553,9 @@
     <t>['69']</t>
   </si>
   <si>
+    <t>['61', '89']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -707,6 +710,9 @@
   </si>
   <si>
     <t>['12']</t>
+  </si>
+  <si>
+    <t>['75', '81']</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1324,7 +1330,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -2148,7 +2154,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2354,7 +2360,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2560,7 +2566,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2972,7 +2978,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3178,7 +3184,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -4002,7 +4008,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4620,7 +4626,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -5238,7 +5244,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5444,7 +5450,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5650,7 +5656,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5856,7 +5862,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -6062,7 +6068,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6474,7 +6480,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6680,7 +6686,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6886,7 +6892,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7092,7 +7098,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7916,7 +7922,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8946,7 +8952,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9152,7 +9158,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9564,7 +9570,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9976,7 +9982,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10388,7 +10394,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -11006,7 +11012,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11418,7 +11424,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -12654,7 +12660,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12860,7 +12866,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13066,7 +13072,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -14302,7 +14308,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14714,7 +14720,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14920,7 +14926,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15126,7 +15132,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15744,7 +15750,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16568,7 +16574,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16774,7 +16780,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17186,7 +17192,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17598,7 +17604,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -18010,7 +18016,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18216,7 +18222,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18422,7 +18428,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18834,7 +18840,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19658,7 +19664,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -20070,7 +20076,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20276,7 +20282,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20482,7 +20488,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -21100,7 +21106,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21306,7 +21312,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21512,7 +21518,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21718,7 +21724,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q101">
         <v>2.75</v>
@@ -21924,7 +21930,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -22130,7 +22136,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23160,7 +23166,7 @@
         <v>165</v>
       </c>
       <c r="P108" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23366,7 +23372,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23984,7 +23990,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q112">
         <v>3.45</v>
@@ -24190,7 +24196,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q113">
         <v>1.76</v>
@@ -24396,7 +24402,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q114">
         <v>3.3</v>
@@ -24602,7 +24608,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24808,7 +24814,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25014,7 +25020,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25220,7 +25226,7 @@
         <v>86</v>
       </c>
       <c r="P118" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q118">
         <v>3</v>
@@ -25426,7 +25432,7 @@
         <v>86</v>
       </c>
       <c r="P119" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26250,7 +26256,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26662,7 +26668,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q125">
         <v>2.05</v>
@@ -26868,7 +26874,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27025,6 +27031,212 @@
       </c>
       <c r="BP126">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7818933</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45858.66666666666</v>
+      </c>
+      <c r="F127">
+        <v>16</v>
+      </c>
+      <c r="G127" t="s">
+        <v>81</v>
+      </c>
+      <c r="H127" t="s">
+        <v>73</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>2</v>
+      </c>
+      <c r="M127">
+        <v>2</v>
+      </c>
+      <c r="N127">
+        <v>4</v>
+      </c>
+      <c r="O127" t="s">
+        <v>179</v>
+      </c>
+      <c r="P127" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q127">
+        <v>4</v>
+      </c>
+      <c r="R127">
+        <v>2.2</v>
+      </c>
+      <c r="S127">
+        <v>2.63</v>
+      </c>
+      <c r="T127">
+        <v>1.36</v>
+      </c>
+      <c r="U127">
+        <v>3</v>
+      </c>
+      <c r="V127">
+        <v>2.75</v>
+      </c>
+      <c r="W127">
+        <v>1.4</v>
+      </c>
+      <c r="X127">
+        <v>7</v>
+      </c>
+      <c r="Y127">
+        <v>1.1</v>
+      </c>
+      <c r="Z127">
+        <v>3.8</v>
+      </c>
+      <c r="AA127">
+        <v>3.3</v>
+      </c>
+      <c r="AB127">
+        <v>2</v>
+      </c>
+      <c r="AC127">
+        <v>1.05</v>
+      </c>
+      <c r="AD127">
+        <v>8.5</v>
+      </c>
+      <c r="AE127">
+        <v>1.28</v>
+      </c>
+      <c r="AF127">
+        <v>3.4</v>
+      </c>
+      <c r="AG127">
+        <v>1.9</v>
+      </c>
+      <c r="AH127">
+        <v>1.9</v>
+      </c>
+      <c r="AI127">
+        <v>1.73</v>
+      </c>
+      <c r="AJ127">
+        <v>2</v>
+      </c>
+      <c r="AK127">
+        <v>1.73</v>
+      </c>
+      <c r="AL127">
+        <v>1.28</v>
+      </c>
+      <c r="AM127">
+        <v>1.31</v>
+      </c>
+      <c r="AN127">
+        <v>1</v>
+      </c>
+      <c r="AO127">
+        <v>1</v>
+      </c>
+      <c r="AP127">
+        <v>1</v>
+      </c>
+      <c r="AQ127">
+        <v>1</v>
+      </c>
+      <c r="AR127">
+        <v>1.81</v>
+      </c>
+      <c r="AS127">
+        <v>1.72</v>
+      </c>
+      <c r="AT127">
+        <v>3.53</v>
+      </c>
+      <c r="AU127">
+        <v>4</v>
+      </c>
+      <c r="AV127">
+        <v>6</v>
+      </c>
+      <c r="AW127">
+        <v>5</v>
+      </c>
+      <c r="AX127">
+        <v>5</v>
+      </c>
+      <c r="AY127">
+        <v>9</v>
+      </c>
+      <c r="AZ127">
+        <v>11</v>
+      </c>
+      <c r="BA127">
+        <v>1</v>
+      </c>
+      <c r="BB127">
+        <v>3</v>
+      </c>
+      <c r="BC127">
+        <v>4</v>
+      </c>
+      <c r="BD127">
+        <v>2.75</v>
+      </c>
+      <c r="BE127">
+        <v>9</v>
+      </c>
+      <c r="BF127">
+        <v>1.66</v>
+      </c>
+      <c r="BG127">
+        <v>1.25</v>
+      </c>
+      <c r="BH127">
+        <v>3.3</v>
+      </c>
+      <c r="BI127">
+        <v>1.46</v>
+      </c>
+      <c r="BJ127">
+        <v>2.43</v>
+      </c>
+      <c r="BK127">
+        <v>1.76</v>
+      </c>
+      <c r="BL127">
+        <v>1.89</v>
+      </c>
+      <c r="BM127">
+        <v>2.17</v>
+      </c>
+      <c r="BN127">
+        <v>1.57</v>
+      </c>
+      <c r="BO127">
+        <v>2.75</v>
+      </c>
+      <c r="BP127">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -556,6 +556,9 @@
     <t>['61', '89']</t>
   </si>
   <si>
+    <t>['51', '90+8']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -713,6 +716,9 @@
   </si>
   <si>
     <t>['75', '81']</t>
+  </si>
+  <si>
+    <t>['22']</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1330,7 +1336,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -2154,7 +2160,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2360,7 +2366,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2566,7 +2572,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2978,7 +2984,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3184,7 +3190,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3880,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4008,7 +4014,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4501,7 +4507,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ17">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4626,7 +4632,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -5244,7 +5250,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5450,7 +5456,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5656,7 +5662,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5734,7 +5740,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
         <v>0.88</v>
@@ -5862,7 +5868,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -6068,7 +6074,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6149,7 +6155,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR25">
         <v>1.33</v>
@@ -6480,7 +6486,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6686,7 +6692,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6892,7 +6898,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7098,7 +7104,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7922,7 +7928,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8827,7 +8833,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ38">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR38">
         <v>2</v>
@@ -8952,7 +8958,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9158,7 +9164,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9570,7 +9576,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9982,7 +9988,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10266,7 +10272,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>0.44</v>
@@ -10394,7 +10400,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -11012,7 +11018,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11299,7 +11305,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ50">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR50">
         <v>1.54</v>
@@ -11424,7 +11430,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -12660,7 +12666,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12738,7 +12744,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
         <v>1.14</v>
@@ -12866,7 +12872,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13072,7 +13078,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -14308,7 +14314,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14720,7 +14726,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14926,7 +14932,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15132,7 +15138,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15210,7 +15216,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>0.43</v>
@@ -15750,7 +15756,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16243,7 +16249,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ74">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR74">
         <v>1.93</v>
@@ -16574,7 +16580,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16780,7 +16786,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17192,7 +17198,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17604,7 +17610,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -18016,7 +18022,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18222,7 +18228,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18428,7 +18434,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18840,7 +18846,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19539,7 +19545,7 @@
         <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR90">
         <v>1.8</v>
@@ -19664,7 +19670,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -20076,7 +20082,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20282,7 +20288,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20360,7 +20366,7 @@
         <v>0.8</v>
       </c>
       <c r="AP94">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>1.14</v>
@@ -20488,7 +20494,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -20775,7 +20781,7 @@
         <v>3</v>
       </c>
       <c r="AQ96">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR96">
         <v>2.13</v>
@@ -21106,7 +21112,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21312,7 +21318,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21518,7 +21524,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21724,7 +21730,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q101">
         <v>2.75</v>
@@ -21930,7 +21936,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -22136,7 +22142,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23166,7 +23172,7 @@
         <v>165</v>
       </c>
       <c r="P108" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23372,7 +23378,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23990,7 +23996,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q112">
         <v>3.45</v>
@@ -24196,7 +24202,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q113">
         <v>1.76</v>
@@ -24402,7 +24408,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q114">
         <v>3.3</v>
@@ -24480,7 +24486,7 @@
         <v>2</v>
       </c>
       <c r="AP114">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
         <v>1.88</v>
@@ -24608,7 +24614,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24814,7 +24820,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25020,7 +25026,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25226,7 +25232,7 @@
         <v>86</v>
       </c>
       <c r="P118" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q118">
         <v>3</v>
@@ -25307,7 +25313,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ118">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR118">
         <v>1.81</v>
@@ -25432,7 +25438,7 @@
         <v>86</v>
       </c>
       <c r="P119" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26256,7 +26262,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26668,7 +26674,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q125">
         <v>2.05</v>
@@ -26874,7 +26880,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27080,7 +27086,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27237,6 +27243,212 @@
       </c>
       <c r="BP127">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7818934</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45859.83333333334</v>
+      </c>
+      <c r="F128">
+        <v>16</v>
+      </c>
+      <c r="G128" t="s">
+        <v>82</v>
+      </c>
+      <c r="H128" t="s">
+        <v>72</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>1</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>1</v>
+      </c>
+      <c r="N128">
+        <v>3</v>
+      </c>
+      <c r="O128" t="s">
+        <v>180</v>
+      </c>
+      <c r="P128" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q128">
+        <v>3.25</v>
+      </c>
+      <c r="R128">
+        <v>2.1</v>
+      </c>
+      <c r="S128">
+        <v>3.25</v>
+      </c>
+      <c r="T128">
+        <v>1.4</v>
+      </c>
+      <c r="U128">
+        <v>2.75</v>
+      </c>
+      <c r="V128">
+        <v>3</v>
+      </c>
+      <c r="W128">
+        <v>1.36</v>
+      </c>
+      <c r="X128">
+        <v>8</v>
+      </c>
+      <c r="Y128">
+        <v>1.08</v>
+      </c>
+      <c r="Z128">
+        <v>2.55</v>
+      </c>
+      <c r="AA128">
+        <v>3.3</v>
+      </c>
+      <c r="AB128">
+        <v>2.55</v>
+      </c>
+      <c r="AC128">
+        <v>1.06</v>
+      </c>
+      <c r="AD128">
+        <v>8</v>
+      </c>
+      <c r="AE128">
+        <v>1.33</v>
+      </c>
+      <c r="AF128">
+        <v>3.1</v>
+      </c>
+      <c r="AG128">
+        <v>2.05</v>
+      </c>
+      <c r="AH128">
+        <v>1.75</v>
+      </c>
+      <c r="AI128">
+        <v>1.8</v>
+      </c>
+      <c r="AJ128">
+        <v>1.91</v>
+      </c>
+      <c r="AK128">
+        <v>1.47</v>
+      </c>
+      <c r="AL128">
+        <v>1.31</v>
+      </c>
+      <c r="AM128">
+        <v>1.46</v>
+      </c>
+      <c r="AN128">
+        <v>1.86</v>
+      </c>
+      <c r="AO128">
+        <v>1.38</v>
+      </c>
+      <c r="AP128">
+        <v>2</v>
+      </c>
+      <c r="AQ128">
+        <v>1.22</v>
+      </c>
+      <c r="AR128">
+        <v>1.54</v>
+      </c>
+      <c r="AS128">
+        <v>1.64</v>
+      </c>
+      <c r="AT128">
+        <v>3.18</v>
+      </c>
+      <c r="AU128">
+        <v>7</v>
+      </c>
+      <c r="AV128">
+        <v>6</v>
+      </c>
+      <c r="AW128">
+        <v>7</v>
+      </c>
+      <c r="AX128">
+        <v>11</v>
+      </c>
+      <c r="AY128">
+        <v>14</v>
+      </c>
+      <c r="AZ128">
+        <v>17</v>
+      </c>
+      <c r="BA128">
+        <v>6</v>
+      </c>
+      <c r="BB128">
+        <v>4</v>
+      </c>
+      <c r="BC128">
+        <v>10</v>
+      </c>
+      <c r="BD128">
+        <v>1.91</v>
+      </c>
+      <c r="BE128">
+        <v>6.4</v>
+      </c>
+      <c r="BF128">
+        <v>2.35</v>
+      </c>
+      <c r="BG128">
+        <v>1.24</v>
+      </c>
+      <c r="BH128">
+        <v>3.34</v>
+      </c>
+      <c r="BI128">
+        <v>1.47</v>
+      </c>
+      <c r="BJ128">
+        <v>2.42</v>
+      </c>
+      <c r="BK128">
+        <v>1.83</v>
+      </c>
+      <c r="BL128">
+        <v>1.87</v>
+      </c>
+      <c r="BM128">
+        <v>2.34</v>
+      </c>
+      <c r="BN128">
+        <v>1.5</v>
+      </c>
+      <c r="BO128">
+        <v>3.08</v>
+      </c>
+      <c r="BP128">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
